--- a/2023-24 RLS Codebook.xlsx
+++ b/2023-24 RLS Codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d324e58270d0c0b/Desktop/Math_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAB5FB7-467A-4FFE-BD62-267D7CBFA7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FFAB5FB7-467A-4FFE-BD62-267D7CBFA7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE3AF3E-00F4-4857-93CA-3E59A131CE16}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7109,7 +7109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7127,16 +7127,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7564,7 +7570,7 @@
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="3">
@@ -7578,7 +7584,7 @@
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="10"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="2">
         <v>2</v>
       </c>
@@ -7590,7 +7596,7 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="10"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="2">
         <v>3</v>
       </c>
@@ -7602,7 +7608,7 @@
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="10"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="2">
         <v>99</v>
       </c>
@@ -7614,7 +7620,7 @@
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3">
@@ -7628,7 +7634,7 @@
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="10"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="2">
         <v>2</v>
       </c>
@@ -7640,7 +7646,7 @@
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="10"/>
+      <c r="B16" s="12"/>
       <c r="C16" s="2">
         <v>3</v>
       </c>
@@ -7652,7 +7658,7 @@
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="2">
         <v>4</v>
       </c>
@@ -7664,7 +7670,7 @@
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="2">
         <v>5</v>
       </c>
@@ -7676,7 +7682,7 @@
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="10"/>
+      <c r="B19" s="12"/>
       <c r="C19" s="2">
         <v>99</v>
       </c>
@@ -7688,7 +7694,7 @@
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C20" s="3">
@@ -7702,7 +7708,7 @@
       <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="10"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="2">
         <v>2</v>
       </c>
@@ -7714,7 +7720,7 @@
       <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="10"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="2">
         <v>3</v>
       </c>
@@ -7726,7 +7732,7 @@
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="10"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="2">
         <v>4</v>
       </c>
@@ -7738,7 +7744,7 @@
       <c r="A24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="10"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="2">
         <v>5</v>
       </c>
@@ -7750,7 +7756,7 @@
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="2">
         <v>99</v>
       </c>
@@ -7762,7 +7768,7 @@
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="3">
@@ -7776,7 +7782,7 @@
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="10"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="2">
         <v>2</v>
       </c>
@@ -7788,7 +7794,7 @@
       <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="10"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="2">
         <v>3</v>
       </c>
@@ -7800,7 +7806,7 @@
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="10"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="2">
         <v>99</v>
       </c>
@@ -7812,7 +7818,7 @@
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="3">
@@ -7826,7 +7832,7 @@
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="2">
         <v>2</v>
       </c>
@@ -7838,7 +7844,7 @@
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="2">
         <v>3</v>
       </c>
@@ -7850,7 +7856,7 @@
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="10"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="2">
         <v>99</v>
       </c>
@@ -7862,7 +7868,7 @@
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="3">
@@ -7876,7 +7882,7 @@
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="10"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="2">
         <v>2</v>
       </c>
@@ -7888,7 +7894,7 @@
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="2">
         <v>3</v>
       </c>
@@ -7900,7 +7906,7 @@
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="10"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="2">
         <v>99</v>
       </c>
@@ -7912,7 +7918,7 @@
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="3">
@@ -7926,7 +7932,7 @@
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="10"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="2">
         <v>2</v>
       </c>
@@ -7938,7 +7944,7 @@
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="10"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="2">
         <v>3</v>
       </c>
@@ -7950,7 +7956,7 @@
       <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="10"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="2">
         <v>99</v>
       </c>
@@ -7962,7 +7968,7 @@
       <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C42" s="3">
@@ -7976,7 +7982,7 @@
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="10"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="2">
         <v>2</v>
       </c>
@@ -7988,7 +7994,7 @@
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="10"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="2">
         <v>3</v>
       </c>
@@ -8000,7 +8006,7 @@
       <c r="A45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="10"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="2">
         <v>99</v>
       </c>
@@ -8012,7 +8018,7 @@
       <c r="A46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C46" s="3">
@@ -8026,7 +8032,7 @@
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="10"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="2">
         <v>2</v>
       </c>
@@ -8038,7 +8044,7 @@
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="10"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="2">
         <v>99</v>
       </c>
@@ -8050,7 +8056,7 @@
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="3">
@@ -8064,7 +8070,7 @@
       <c r="A50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="10"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="2">
         <v>2</v>
       </c>
@@ -8076,7 +8082,7 @@
       <c r="A51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="10"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="2">
         <v>99</v>
       </c>
@@ -8088,7 +8094,7 @@
       <c r="A52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="3">
@@ -8102,7 +8108,7 @@
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="10"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="2">
         <v>2</v>
       </c>
@@ -8114,7 +8120,7 @@
       <c r="A54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="10"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="2">
         <v>99</v>
       </c>
@@ -8126,7 +8132,7 @@
       <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="3">
@@ -8140,7 +8146,7 @@
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="10"/>
+      <c r="B56" s="8"/>
       <c r="C56" s="2">
         <v>2</v>
       </c>
@@ -8152,7 +8158,7 @@
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="10"/>
+      <c r="B57" s="8"/>
       <c r="C57" s="2">
         <v>99</v>
       </c>
@@ -8164,7 +8170,7 @@
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="3">
@@ -8178,7 +8184,7 @@
       <c r="A59" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="10"/>
+      <c r="B59" s="8"/>
       <c r="C59" s="2">
         <v>2</v>
       </c>
@@ -8190,7 +8196,7 @@
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="10"/>
+      <c r="B60" s="8"/>
       <c r="C60" s="2">
         <v>3</v>
       </c>
@@ -8202,7 +8208,7 @@
       <c r="A61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="10"/>
+      <c r="B61" s="8"/>
       <c r="C61" s="2">
         <v>99</v>
       </c>
@@ -8214,7 +8220,7 @@
       <c r="A62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="3">
@@ -8228,7 +8234,7 @@
       <c r="A63" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="10"/>
+      <c r="B63" s="8"/>
       <c r="C63" s="2">
         <v>2</v>
       </c>
@@ -8240,7 +8246,7 @@
       <c r="A64" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="10"/>
+      <c r="B64" s="8"/>
       <c r="C64" s="2">
         <v>99</v>
       </c>
@@ -8252,7 +8258,7 @@
       <c r="A65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C65" s="3">
@@ -8266,7 +8272,7 @@
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="10"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="2">
         <v>2</v>
       </c>
@@ -8278,7 +8284,7 @@
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="10"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="2">
         <v>3</v>
       </c>
@@ -8290,7 +8296,7 @@
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="10"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="2">
         <v>4</v>
       </c>
@@ -8302,7 +8308,7 @@
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="10"/>
+      <c r="B69" s="8"/>
       <c r="C69" s="2">
         <v>99</v>
       </c>
@@ -8314,7 +8320,7 @@
       <c r="A70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C70" s="3">
@@ -8328,7 +8334,7 @@
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="10"/>
+      <c r="B71" s="8"/>
       <c r="C71" s="2">
         <v>2</v>
       </c>
@@ -8340,7 +8346,7 @@
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="10"/>
+      <c r="B72" s="8"/>
       <c r="C72" s="2">
         <v>3</v>
       </c>
@@ -8352,7 +8358,7 @@
       <c r="A73" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="10"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="2">
         <v>4</v>
       </c>
@@ -8364,7 +8370,7 @@
       <c r="A74" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="10"/>
+      <c r="B74" s="8"/>
       <c r="C74" s="2">
         <v>99</v>
       </c>
@@ -8376,7 +8382,7 @@
       <c r="A75" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C75" s="3">
@@ -8390,7 +8396,7 @@
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="10"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="2">
         <v>2</v>
       </c>
@@ -8402,7 +8408,7 @@
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="2">
         <v>99</v>
       </c>
@@ -8576,7 +8582,7 @@
       <c r="A91" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C91" s="3">
@@ -8590,7 +8596,7 @@
       <c r="A92" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B92" s="10"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="2">
         <v>2</v>
       </c>
@@ -8602,7 +8608,7 @@
       <c r="A93" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B93" s="10"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="2">
         <v>3</v>
       </c>
@@ -8614,7 +8620,7 @@
       <c r="A94" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="10"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="2">
         <v>4</v>
       </c>
@@ -8626,7 +8632,7 @@
       <c r="A95" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B95" s="10"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="2">
         <v>5</v>
       </c>
@@ -8638,7 +8644,7 @@
       <c r="A96" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="10"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="2">
         <v>99</v>
       </c>
@@ -8650,7 +8656,7 @@
       <c r="A97" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>113</v>
       </c>
       <c r="C97" s="3">
@@ -8664,7 +8670,7 @@
       <c r="A98" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B98" s="10"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="2">
         <v>2</v>
       </c>
@@ -8676,7 +8682,7 @@
       <c r="A99" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B99" s="10"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="2">
         <v>3</v>
       </c>
@@ -8688,7 +8694,7 @@
       <c r="A100" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B100" s="10"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="2">
         <v>4</v>
       </c>
@@ -8700,7 +8706,7 @@
       <c r="A101" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="10"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="2">
         <v>5</v>
       </c>
@@ -8712,7 +8718,7 @@
       <c r="A102" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B102" s="10"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="2">
         <v>99</v>
       </c>
@@ -8724,7 +8730,7 @@
       <c r="A103" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C103" s="3">
@@ -8738,7 +8744,7 @@
       <c r="A104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="10"/>
+      <c r="B104" s="8"/>
       <c r="C104" s="2">
         <v>2</v>
       </c>
@@ -8750,7 +8756,7 @@
       <c r="A105" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B105" s="10"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="2">
         <v>3</v>
       </c>
@@ -8762,7 +8768,7 @@
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="10"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="2">
         <v>4</v>
       </c>
@@ -8774,7 +8780,7 @@
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="10"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="2">
         <v>5</v>
       </c>
@@ -8786,7 +8792,7 @@
       <c r="A108" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="10"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="2">
         <v>99</v>
       </c>
@@ -8798,7 +8804,7 @@
       <c r="A109" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="7" t="s">
         <v>117</v>
       </c>
       <c r="C109" s="3">
@@ -8812,7 +8818,7 @@
       <c r="A110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="10"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="2">
         <v>2</v>
       </c>
@@ -8824,7 +8830,7 @@
       <c r="A111" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="10"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="2">
         <v>3</v>
       </c>
@@ -8836,7 +8842,7 @@
       <c r="A112" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="10"/>
+      <c r="B112" s="8"/>
       <c r="C112" s="2">
         <v>4</v>
       </c>
@@ -8848,7 +8854,7 @@
       <c r="A113" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B113" s="10"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="2">
         <v>5</v>
       </c>
@@ -8860,7 +8866,7 @@
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="10"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="2">
         <v>99</v>
       </c>
@@ -10544,7 +10550,7 @@
       <c r="A254" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="7" t="s">
         <v>258</v>
       </c>
       <c r="C254" s="3">
@@ -10558,7 +10564,7 @@
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B255" s="10"/>
+      <c r="B255" s="8"/>
       <c r="C255" s="2">
         <v>1200</v>
       </c>
@@ -10570,7 +10576,7 @@
       <c r="A256" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B256" s="10"/>
+      <c r="B256" s="8"/>
       <c r="C256" s="2">
         <v>1300</v>
       </c>
@@ -10582,7 +10588,7 @@
       <c r="A257" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="10"/>
+      <c r="B257" s="8"/>
       <c r="C257" s="2">
         <v>10000</v>
       </c>
@@ -10594,7 +10600,7 @@
       <c r="A258" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="10"/>
+      <c r="B258" s="8"/>
       <c r="C258" s="2">
         <v>20000</v>
       </c>
@@ -10606,7 +10612,7 @@
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259" s="10"/>
+      <c r="B259" s="8"/>
       <c r="C259" s="2">
         <v>30000</v>
       </c>
@@ -10618,7 +10624,7 @@
       <c r="A260" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B260" s="10"/>
+      <c r="B260" s="8"/>
       <c r="C260" s="2">
         <v>40001</v>
       </c>
@@ -10630,7 +10636,7 @@
       <c r="A261" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B261" s="10"/>
+      <c r="B261" s="8"/>
       <c r="C261" s="2">
         <v>40002</v>
       </c>
@@ -10642,7 +10648,7 @@
       <c r="A262" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B262" s="10"/>
+      <c r="B262" s="8"/>
       <c r="C262" s="2">
         <v>50000</v>
       </c>
@@ -10654,7 +10660,7 @@
       <c r="A263" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B263" s="10"/>
+      <c r="B263" s="8"/>
       <c r="C263" s="2">
         <v>60000</v>
       </c>
@@ -10666,7 +10672,7 @@
       <c r="A264" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B264" s="10"/>
+      <c r="B264" s="8"/>
       <c r="C264" s="2">
         <v>70000</v>
       </c>
@@ -10678,7 +10684,7 @@
       <c r="A265" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B265" s="10"/>
+      <c r="B265" s="8"/>
       <c r="C265" s="2">
         <v>80000</v>
       </c>
@@ -10690,7 +10696,7 @@
       <c r="A266" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B266" s="10"/>
+      <c r="B266" s="8"/>
       <c r="C266" s="2">
         <v>90001</v>
       </c>
@@ -10702,7 +10708,7 @@
       <c r="A267" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B267" s="10"/>
+      <c r="B267" s="8"/>
       <c r="C267" s="2">
         <v>90002</v>
       </c>
@@ -10714,7 +10720,7 @@
       <c r="A268" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B268" s="10"/>
+      <c r="B268" s="8"/>
       <c r="C268" s="2">
         <v>100000</v>
       </c>
@@ -10726,7 +10732,7 @@
       <c r="A269" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B269" s="10"/>
+      <c r="B269" s="8"/>
       <c r="C269" s="2">
         <v>900000</v>
       </c>
@@ -10956,7 +10962,7 @@
       <c r="A288" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="7" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="3">
@@ -10970,7 +10976,7 @@
       <c r="A289" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B289" s="10"/>
+      <c r="B289" s="8"/>
       <c r="C289" s="2">
         <v>10000</v>
       </c>
@@ -10982,7 +10988,7 @@
       <c r="A290" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B290" s="10"/>
+      <c r="B290" s="8"/>
       <c r="C290" s="2">
         <v>20000</v>
       </c>
@@ -10994,7 +11000,7 @@
       <c r="A291" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B291" s="10"/>
+      <c r="B291" s="8"/>
       <c r="C291" s="2">
         <v>30000</v>
       </c>
@@ -11006,7 +11012,7 @@
       <c r="A292" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B292" s="10"/>
+      <c r="B292" s="8"/>
       <c r="C292" s="2">
         <v>40001</v>
       </c>
@@ -11018,7 +11024,7 @@
       <c r="A293" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B293" s="10"/>
+      <c r="B293" s="8"/>
       <c r="C293" s="2">
         <v>40002</v>
       </c>
@@ -11030,7 +11036,7 @@
       <c r="A294" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B294" s="10"/>
+      <c r="B294" s="8"/>
       <c r="C294" s="2">
         <v>50000</v>
       </c>
@@ -11042,7 +11048,7 @@
       <c r="A295" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B295" s="10"/>
+      <c r="B295" s="8"/>
       <c r="C295" s="2">
         <v>60000</v>
       </c>
@@ -11054,7 +11060,7 @@
       <c r="A296" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B296" s="10"/>
+      <c r="B296" s="8"/>
       <c r="C296" s="2">
         <v>70000</v>
       </c>
@@ -11066,7 +11072,7 @@
       <c r="A297" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B297" s="10"/>
+      <c r="B297" s="8"/>
       <c r="C297" s="2">
         <v>80000</v>
       </c>
@@ -11078,7 +11084,7 @@
       <c r="A298" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B298" s="10"/>
+      <c r="B298" s="8"/>
       <c r="C298" s="2">
         <v>90001</v>
       </c>
@@ -11090,7 +11096,7 @@
       <c r="A299" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B299" s="10"/>
+      <c r="B299" s="8"/>
       <c r="C299" s="2">
         <v>90002</v>
       </c>
@@ -11102,7 +11108,7 @@
       <c r="A300" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B300" s="10"/>
+      <c r="B300" s="8"/>
       <c r="C300" s="2">
         <v>100000</v>
       </c>
@@ -11114,7 +11120,7 @@
       <c r="A301" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B301" s="10"/>
+      <c r="B301" s="8"/>
       <c r="C301" s="2">
         <v>900000</v>
       </c>
@@ -11612,7 +11618,7 @@
       <c r="A342" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B342" s="9" t="s">
+      <c r="B342" s="7" t="s">
         <v>304</v>
       </c>
       <c r="C342" s="3">
@@ -11626,7 +11632,7 @@
       <c r="A343" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B343" s="10"/>
+      <c r="B343" s="8"/>
       <c r="C343" s="2">
         <v>2</v>
       </c>
@@ -11638,7 +11644,7 @@
       <c r="A344" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B344" s="10"/>
+      <c r="B344" s="8"/>
       <c r="C344" s="2">
         <v>3</v>
       </c>
@@ -11650,7 +11656,7 @@
       <c r="A345" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B345" s="10"/>
+      <c r="B345" s="8"/>
       <c r="C345" s="2">
         <v>4</v>
       </c>
@@ -11662,7 +11668,7 @@
       <c r="A346" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B346" s="10"/>
+      <c r="B346" s="8"/>
       <c r="C346" s="2">
         <v>99</v>
       </c>
@@ -11674,7 +11680,7 @@
       <c r="A347" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B347" s="9" t="s">
+      <c r="B347" s="7" t="s">
         <v>310</v>
       </c>
       <c r="C347" s="3">
@@ -11688,7 +11694,7 @@
       <c r="A348" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B348" s="10"/>
+      <c r="B348" s="8"/>
       <c r="C348" s="2">
         <v>2</v>
       </c>
@@ -11700,7 +11706,7 @@
       <c r="A349" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B349" s="10"/>
+      <c r="B349" s="8"/>
       <c r="C349" s="2">
         <v>3</v>
       </c>
@@ -11712,7 +11718,7 @@
       <c r="A350" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B350" s="10"/>
+      <c r="B350" s="8"/>
       <c r="C350" s="2">
         <v>4</v>
       </c>
@@ -11724,7 +11730,7 @@
       <c r="A351" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B351" s="10"/>
+      <c r="B351" s="8"/>
       <c r="C351" s="2">
         <v>99</v>
       </c>
@@ -11986,7 +11992,7 @@
       <c r="A372" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B372" s="9" t="s">
+      <c r="B372" s="7" t="s">
         <v>333</v>
       </c>
       <c r="C372" s="3">
@@ -12000,7 +12006,7 @@
       <c r="A373" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B373" s="10"/>
+      <c r="B373" s="8"/>
       <c r="C373" s="2">
         <v>2</v>
       </c>
@@ -12012,7 +12018,7 @@
       <c r="A374" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B374" s="10"/>
+      <c r="B374" s="8"/>
       <c r="C374" s="2">
         <v>3</v>
       </c>
@@ -12024,7 +12030,7 @@
       <c r="A375" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B375" s="10"/>
+      <c r="B375" s="8"/>
       <c r="C375" s="2">
         <v>4</v>
       </c>
@@ -12036,7 +12042,7 @@
       <c r="A376" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B376" s="10"/>
+      <c r="B376" s="8"/>
       <c r="C376" s="2">
         <v>5</v>
       </c>
@@ -12048,7 +12054,7 @@
       <c r="A377" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B377" s="10"/>
+      <c r="B377" s="8"/>
       <c r="C377" s="2">
         <v>6</v>
       </c>
@@ -12060,7 +12066,7 @@
       <c r="A378" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B378" s="10"/>
+      <c r="B378" s="8"/>
       <c r="C378" s="2">
         <v>99</v>
       </c>
@@ -12072,7 +12078,7 @@
       <c r="A379" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="7" t="s">
         <v>341</v>
       </c>
       <c r="C379" s="3">
@@ -12086,7 +12092,7 @@
       <c r="A380" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B380" s="10"/>
+      <c r="B380" s="8"/>
       <c r="C380" s="2">
         <v>2</v>
       </c>
@@ -12098,7 +12104,7 @@
       <c r="A381" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B381" s="10"/>
+      <c r="B381" s="8"/>
       <c r="C381" s="2">
         <v>3</v>
       </c>
@@ -12110,7 +12116,7 @@
       <c r="A382" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B382" s="10"/>
+      <c r="B382" s="8"/>
       <c r="C382" s="2">
         <v>4</v>
       </c>
@@ -12122,7 +12128,7 @@
       <c r="A383" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B383" s="10"/>
+      <c r="B383" s="8"/>
       <c r="C383" s="2">
         <v>5</v>
       </c>
@@ -12134,7 +12140,7 @@
       <c r="A384" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B384" s="10"/>
+      <c r="B384" s="8"/>
       <c r="C384" s="2">
         <v>6</v>
       </c>
@@ -12146,7 +12152,7 @@
       <c r="A385" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B385" s="10"/>
+      <c r="B385" s="8"/>
       <c r="C385" s="2">
         <v>99</v>
       </c>
@@ -12330,7 +12336,7 @@
       <c r="A400" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="7" t="s">
         <v>353</v>
       </c>
       <c r="C400" s="3">
@@ -12344,7 +12350,7 @@
       <c r="A401" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B401" s="10"/>
+      <c r="B401" s="8"/>
       <c r="C401" s="2">
         <v>2</v>
       </c>
@@ -12356,7 +12362,7 @@
       <c r="A402" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B402" s="10"/>
+      <c r="B402" s="8"/>
       <c r="C402" s="2">
         <v>3</v>
       </c>
@@ -12368,7 +12374,7 @@
       <c r="A403" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B403" s="10"/>
+      <c r="B403" s="8"/>
       <c r="C403" s="2">
         <v>4</v>
       </c>
@@ -12380,7 +12386,7 @@
       <c r="A404" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B404" s="10"/>
+      <c r="B404" s="8"/>
       <c r="C404" s="2">
         <v>99</v>
       </c>
@@ -12392,7 +12398,7 @@
       <c r="A405" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B405" s="9" t="s">
+      <c r="B405" s="7" t="s">
         <v>355</v>
       </c>
       <c r="C405" s="3">
@@ -12406,7 +12412,7 @@
       <c r="A406" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B406" s="10"/>
+      <c r="B406" s="8"/>
       <c r="C406" s="2">
         <v>2</v>
       </c>
@@ -12418,7 +12424,7 @@
       <c r="A407" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B407" s="10"/>
+      <c r="B407" s="8"/>
       <c r="C407" s="2">
         <v>99</v>
       </c>
@@ -12430,7 +12436,7 @@
       <c r="A408" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B408" s="9" t="s">
+      <c r="B408" s="7" t="s">
         <v>357</v>
       </c>
       <c r="C408" s="3">
@@ -12444,7 +12450,7 @@
       <c r="A409" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B409" s="10"/>
+      <c r="B409" s="8"/>
       <c r="C409" s="2">
         <v>2</v>
       </c>
@@ -12456,7 +12462,7 @@
       <c r="A410" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B410" s="10"/>
+      <c r="B410" s="8"/>
       <c r="C410" s="2">
         <v>99</v>
       </c>
@@ -12530,7 +12536,7 @@
       <c r="A416" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B416" s="9" t="s">
+      <c r="B416" s="7" t="s">
         <v>365</v>
       </c>
       <c r="C416" s="3">
@@ -12544,7 +12550,7 @@
       <c r="A417" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B417" s="10"/>
+      <c r="B417" s="8"/>
       <c r="C417" s="2">
         <v>2</v>
       </c>
@@ -12556,7 +12562,7 @@
       <c r="A418" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B418" s="10"/>
+      <c r="B418" s="8"/>
       <c r="C418" s="2">
         <v>99</v>
       </c>
@@ -12568,7 +12574,7 @@
       <c r="A419" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B419" s="9" t="s">
+      <c r="B419" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C419" s="3">
@@ -12582,7 +12588,7 @@
       <c r="A420" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B420" s="10"/>
+      <c r="B420" s="8"/>
       <c r="C420" s="2">
         <v>2</v>
       </c>
@@ -12594,7 +12600,7 @@
       <c r="A421" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B421" s="10"/>
+      <c r="B421" s="8"/>
       <c r="C421" s="2">
         <v>99</v>
       </c>
@@ -12606,7 +12612,7 @@
       <c r="A422" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B422" s="9" t="s">
+      <c r="B422" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C422" s="3">
@@ -12620,7 +12626,7 @@
       <c r="A423" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B423" s="10"/>
+      <c r="B423" s="8"/>
       <c r="C423" s="2">
         <v>2</v>
       </c>
@@ -12632,7 +12638,7 @@
       <c r="A424" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B424" s="10"/>
+      <c r="B424" s="8"/>
       <c r="C424" s="2">
         <v>99</v>
       </c>
@@ -12644,7 +12650,7 @@
       <c r="A425" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B425" s="9" t="s">
+      <c r="B425" s="7" t="s">
         <v>371</v>
       </c>
       <c r="C425" s="3">
@@ -12658,7 +12664,7 @@
       <c r="A426" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B426" s="10"/>
+      <c r="B426" s="8"/>
       <c r="C426" s="2">
         <v>2</v>
       </c>
@@ -12670,7 +12676,7 @@
       <c r="A427" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B427" s="10"/>
+      <c r="B427" s="8"/>
       <c r="C427" s="2">
         <v>3</v>
       </c>
@@ -12682,7 +12688,7 @@
       <c r="A428" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B428" s="10"/>
+      <c r="B428" s="8"/>
       <c r="C428" s="2">
         <v>4</v>
       </c>
@@ -12694,7 +12700,7 @@
       <c r="A429" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B429" s="10"/>
+      <c r="B429" s="8"/>
       <c r="C429" s="2">
         <v>5</v>
       </c>
@@ -12706,7 +12712,7 @@
       <c r="A430" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B430" s="10"/>
+      <c r="B430" s="8"/>
       <c r="C430" s="2">
         <v>99</v>
       </c>
@@ -12718,7 +12724,7 @@
       <c r="A431" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B431" s="9" t="s">
+      <c r="B431" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C431" s="3">
@@ -12732,7 +12738,7 @@
       <c r="A432" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B432" s="10"/>
+      <c r="B432" s="8"/>
       <c r="C432" s="2">
         <v>2</v>
       </c>
@@ -12744,7 +12750,7 @@
       <c r="A433" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B433" s="10"/>
+      <c r="B433" s="8"/>
       <c r="C433" s="2">
         <v>3</v>
       </c>
@@ -12756,7 +12762,7 @@
       <c r="A434" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B434" s="10"/>
+      <c r="B434" s="8"/>
       <c r="C434" s="2">
         <v>4</v>
       </c>
@@ -12768,7 +12774,7 @@
       <c r="A435" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B435" s="10"/>
+      <c r="B435" s="8"/>
       <c r="C435" s="2">
         <v>5</v>
       </c>
@@ -12780,7 +12786,7 @@
       <c r="A436" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B436" s="10"/>
+      <c r="B436" s="8"/>
       <c r="C436" s="2">
         <v>99</v>
       </c>
@@ -12792,7 +12798,7 @@
       <c r="A437" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B437" s="9" t="s">
+      <c r="B437" s="7" t="s">
         <v>380</v>
       </c>
       <c r="C437" s="3">
@@ -12806,7 +12812,7 @@
       <c r="A438" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B438" s="10"/>
+      <c r="B438" s="8"/>
       <c r="C438" s="2">
         <v>2</v>
       </c>
@@ -12818,7 +12824,7 @@
       <c r="A439" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B439" s="10"/>
+      <c r="B439" s="8"/>
       <c r="C439" s="2">
         <v>3</v>
       </c>
@@ -12830,7 +12836,7 @@
       <c r="A440" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B440" s="10"/>
+      <c r="B440" s="8"/>
       <c r="C440" s="2">
         <v>4</v>
       </c>
@@ -12842,7 +12848,7 @@
       <c r="A441" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B441" s="10"/>
+      <c r="B441" s="8"/>
       <c r="C441" s="2">
         <v>5</v>
       </c>
@@ -12854,7 +12860,7 @@
       <c r="A442" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B442" s="10"/>
+      <c r="B442" s="8"/>
       <c r="C442" s="2">
         <v>99</v>
       </c>
@@ -12866,7 +12872,7 @@
       <c r="A443" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B443" s="9" t="s">
+      <c r="B443" s="7" t="s">
         <v>382</v>
       </c>
       <c r="C443" s="3">
@@ -12880,7 +12886,7 @@
       <c r="A444" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B444" s="10"/>
+      <c r="B444" s="8"/>
       <c r="C444" s="2">
         <v>2</v>
       </c>
@@ -12892,7 +12898,7 @@
       <c r="A445" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B445" s="10"/>
+      <c r="B445" s="8"/>
       <c r="C445" s="2">
         <v>3</v>
       </c>
@@ -12904,7 +12910,7 @@
       <c r="A446" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B446" s="10"/>
+      <c r="B446" s="8"/>
       <c r="C446" s="2">
         <v>4</v>
       </c>
@@ -12916,7 +12922,7 @@
       <c r="A447" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B447" s="10"/>
+      <c r="B447" s="8"/>
       <c r="C447" s="2">
         <v>5</v>
       </c>
@@ -12928,7 +12934,7 @@
       <c r="A448" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B448" s="10"/>
+      <c r="B448" s="8"/>
       <c r="C448" s="2">
         <v>6</v>
       </c>
@@ -12940,7 +12946,7 @@
       <c r="A449" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B449" s="10"/>
+      <c r="B449" s="8"/>
       <c r="C449" s="2">
         <v>7</v>
       </c>
@@ -12952,7 +12958,7 @@
       <c r="A450" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B450" s="10"/>
+      <c r="B450" s="8"/>
       <c r="C450" s="2">
         <v>99</v>
       </c>
@@ -12964,7 +12970,7 @@
       <c r="A451" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B451" s="9" t="s">
+      <c r="B451" s="7" t="s">
         <v>388</v>
       </c>
       <c r="C451" s="3">
@@ -12978,7 +12984,7 @@
       <c r="A452" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B452" s="10"/>
+      <c r="B452" s="8"/>
       <c r="C452" s="2">
         <v>2</v>
       </c>
@@ -12990,7 +12996,7 @@
       <c r="A453" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B453" s="10"/>
+      <c r="B453" s="8"/>
       <c r="C453" s="2">
         <v>3</v>
       </c>
@@ -13002,7 +13008,7 @@
       <c r="A454" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B454" s="10"/>
+      <c r="B454" s="8"/>
       <c r="C454" s="2">
         <v>4</v>
       </c>
@@ -13014,7 +13020,7 @@
       <c r="A455" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B455" s="10"/>
+      <c r="B455" s="8"/>
       <c r="C455" s="2">
         <v>5</v>
       </c>
@@ -13026,7 +13032,7 @@
       <c r="A456" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B456" s="10"/>
+      <c r="B456" s="8"/>
       <c r="C456" s="2">
         <v>99</v>
       </c>
@@ -13038,7 +13044,7 @@
       <c r="A457" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B457" s="9" t="s">
+      <c r="B457" s="7" t="s">
         <v>393</v>
       </c>
       <c r="C457" s="3">
@@ -13052,7 +13058,7 @@
       <c r="A458" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B458" s="10"/>
+      <c r="B458" s="8"/>
       <c r="C458" s="2">
         <v>2</v>
       </c>
@@ -13064,7 +13070,7 @@
       <c r="A459" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B459" s="10"/>
+      <c r="B459" s="8"/>
       <c r="C459" s="2">
         <v>3</v>
       </c>
@@ -13076,7 +13082,7 @@
       <c r="A460" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B460" s="10"/>
+      <c r="B460" s="8"/>
       <c r="C460" s="2">
         <v>4</v>
       </c>
@@ -13088,7 +13094,7 @@
       <c r="A461" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B461" s="10"/>
+      <c r="B461" s="8"/>
       <c r="C461" s="2">
         <v>5</v>
       </c>
@@ -13100,7 +13106,7 @@
       <c r="A462" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B462" s="10"/>
+      <c r="B462" s="8"/>
       <c r="C462" s="2">
         <v>99</v>
       </c>
@@ -13112,7 +13118,7 @@
       <c r="A463" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B463" s="9" t="s">
+      <c r="B463" s="7" t="s">
         <v>397</v>
       </c>
       <c r="C463" s="3">
@@ -13126,7 +13132,7 @@
       <c r="A464" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B464" s="10"/>
+      <c r="B464" s="8"/>
       <c r="C464" s="2">
         <v>2</v>
       </c>
@@ -13138,7 +13144,7 @@
       <c r="A465" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B465" s="10"/>
+      <c r="B465" s="8"/>
       <c r="C465" s="2">
         <v>3</v>
       </c>
@@ -13150,7 +13156,7 @@
       <c r="A466" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B466" s="10"/>
+      <c r="B466" s="8"/>
       <c r="C466" s="2">
         <v>4</v>
       </c>
@@ -13162,7 +13168,7 @@
       <c r="A467" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B467" s="10"/>
+      <c r="B467" s="8"/>
       <c r="C467" s="2">
         <v>5</v>
       </c>
@@ -13174,7 +13180,7 @@
       <c r="A468" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B468" s="10"/>
+      <c r="B468" s="8"/>
       <c r="C468" s="2">
         <v>99</v>
       </c>
@@ -13186,7 +13192,7 @@
       <c r="A469" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B469" s="9" t="s">
+      <c r="B469" s="7" t="s">
         <v>399</v>
       </c>
       <c r="C469" s="3">
@@ -13200,7 +13206,7 @@
       <c r="A470" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B470" s="10"/>
+      <c r="B470" s="8"/>
       <c r="C470" s="2">
         <v>2</v>
       </c>
@@ -13212,7 +13218,7 @@
       <c r="A471" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B471" s="10"/>
+      <c r="B471" s="8"/>
       <c r="C471" s="2">
         <v>3</v>
       </c>
@@ -13224,7 +13230,7 @@
       <c r="A472" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B472" s="10"/>
+      <c r="B472" s="8"/>
       <c r="C472" s="2">
         <v>4</v>
       </c>
@@ -13236,7 +13242,7 @@
       <c r="A473" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B473" s="10"/>
+      <c r="B473" s="8"/>
       <c r="C473" s="2">
         <v>5</v>
       </c>
@@ -13248,7 +13254,7 @@
       <c r="A474" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B474" s="10"/>
+      <c r="B474" s="8"/>
       <c r="C474" s="2">
         <v>99</v>
       </c>
@@ -13260,7 +13266,7 @@
       <c r="A475" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B475" s="9" t="s">
+      <c r="B475" s="7" t="s">
         <v>401</v>
       </c>
       <c r="C475" s="3">
@@ -13274,7 +13280,7 @@
       <c r="A476" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B476" s="10"/>
+      <c r="B476" s="8"/>
       <c r="C476" s="2">
         <v>2</v>
       </c>
@@ -13286,7 +13292,7 @@
       <c r="A477" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B477" s="10"/>
+      <c r="B477" s="8"/>
       <c r="C477" s="2">
         <v>3</v>
       </c>
@@ -13298,7 +13304,7 @@
       <c r="A478" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B478" s="10"/>
+      <c r="B478" s="8"/>
       <c r="C478" s="2">
         <v>4</v>
       </c>
@@ -13310,7 +13316,7 @@
       <c r="A479" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B479" s="10"/>
+      <c r="B479" s="8"/>
       <c r="C479" s="2">
         <v>5</v>
       </c>
@@ -13322,7 +13328,7 @@
       <c r="A480" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B480" s="10"/>
+      <c r="B480" s="8"/>
       <c r="C480" s="2">
         <v>99</v>
       </c>
@@ -13334,7 +13340,7 @@
       <c r="A481" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B481" s="9" t="s">
+      <c r="B481" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C481" s="3">
@@ -13348,7 +13354,7 @@
       <c r="A482" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B482" s="10"/>
+      <c r="B482" s="8"/>
       <c r="C482" s="2">
         <v>2</v>
       </c>
@@ -13360,7 +13366,7 @@
       <c r="A483" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B483" s="10"/>
+      <c r="B483" s="8"/>
       <c r="C483" s="2">
         <v>3</v>
       </c>
@@ -13372,7 +13378,7 @@
       <c r="A484" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B484" s="10"/>
+      <c r="B484" s="8"/>
       <c r="C484" s="2">
         <v>4</v>
       </c>
@@ -13384,7 +13390,7 @@
       <c r="A485" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B485" s="10"/>
+      <c r="B485" s="8"/>
       <c r="C485" s="2">
         <v>5</v>
       </c>
@@ -13396,7 +13402,7 @@
       <c r="A486" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B486" s="10"/>
+      <c r="B486" s="8"/>
       <c r="C486" s="2">
         <v>99</v>
       </c>
@@ -13408,7 +13414,7 @@
       <c r="A487" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B487" s="9" t="s">
+      <c r="B487" s="7" t="s">
         <v>405</v>
       </c>
       <c r="C487" s="3">
@@ -13422,7 +13428,7 @@
       <c r="A488" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B488" s="10"/>
+      <c r="B488" s="8"/>
       <c r="C488" s="2">
         <v>2</v>
       </c>
@@ -13434,7 +13440,7 @@
       <c r="A489" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B489" s="10"/>
+      <c r="B489" s="8"/>
       <c r="C489" s="2">
         <v>3</v>
       </c>
@@ -13446,7 +13452,7 @@
       <c r="A490" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B490" s="10"/>
+      <c r="B490" s="8"/>
       <c r="C490" s="2">
         <v>4</v>
       </c>
@@ -13458,7 +13464,7 @@
       <c r="A491" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B491" s="10"/>
+      <c r="B491" s="8"/>
       <c r="C491" s="2">
         <v>5</v>
       </c>
@@ -13470,7 +13476,7 @@
       <c r="A492" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B492" s="10"/>
+      <c r="B492" s="8"/>
       <c r="C492" s="2">
         <v>99</v>
       </c>
@@ -13482,7 +13488,7 @@
       <c r="A493" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B493" s="9" t="s">
+      <c r="B493" s="7" t="s">
         <v>407</v>
       </c>
       <c r="C493" s="3">
@@ -13496,7 +13502,7 @@
       <c r="A494" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B494" s="10"/>
+      <c r="B494" s="8"/>
       <c r="C494" s="2">
         <v>2</v>
       </c>
@@ -13508,7 +13514,7 @@
       <c r="A495" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B495" s="10"/>
+      <c r="B495" s="8"/>
       <c r="C495" s="2">
         <v>3</v>
       </c>
@@ -13520,7 +13526,7 @@
       <c r="A496" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B496" s="10"/>
+      <c r="B496" s="8"/>
       <c r="C496" s="2">
         <v>4</v>
       </c>
@@ -13532,7 +13538,7 @@
       <c r="A497" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B497" s="10"/>
+      <c r="B497" s="8"/>
       <c r="C497" s="2">
         <v>5</v>
       </c>
@@ -13544,7 +13550,7 @@
       <c r="A498" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B498" s="10"/>
+      <c r="B498" s="8"/>
       <c r="C498" s="2">
         <v>99</v>
       </c>
@@ -13556,7 +13562,7 @@
       <c r="A499" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B499" s="9" t="s">
+      <c r="B499" s="7" t="s">
         <v>409</v>
       </c>
       <c r="C499" s="3">
@@ -13570,7 +13576,7 @@
       <c r="A500" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B500" s="10"/>
+      <c r="B500" s="8"/>
       <c r="C500" s="2">
         <v>2</v>
       </c>
@@ -13582,7 +13588,7 @@
       <c r="A501" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B501" s="10"/>
+      <c r="B501" s="8"/>
       <c r="C501" s="2">
         <v>3</v>
       </c>
@@ -13594,7 +13600,7 @@
       <c r="A502" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B502" s="10"/>
+      <c r="B502" s="8"/>
       <c r="C502" s="2">
         <v>4</v>
       </c>
@@ -13606,7 +13612,7 @@
       <c r="A503" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B503" s="10"/>
+      <c r="B503" s="8"/>
       <c r="C503" s="2">
         <v>5</v>
       </c>
@@ -13618,7 +13624,7 @@
       <c r="A504" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B504" s="10"/>
+      <c r="B504" s="8"/>
       <c r="C504" s="2">
         <v>99</v>
       </c>
@@ -13630,7 +13636,7 @@
       <c r="A505" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B505" s="9" t="s">
+      <c r="B505" s="7" t="s">
         <v>411</v>
       </c>
       <c r="C505" s="3">
@@ -13644,7 +13650,7 @@
       <c r="A506" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B506" s="10"/>
+      <c r="B506" s="8"/>
       <c r="C506" s="2">
         <v>2</v>
       </c>
@@ -13656,7 +13662,7 @@
       <c r="A507" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B507" s="10"/>
+      <c r="B507" s="8"/>
       <c r="C507" s="2">
         <v>3</v>
       </c>
@@ -13668,7 +13674,7 @@
       <c r="A508" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B508" s="10"/>
+      <c r="B508" s="8"/>
       <c r="C508" s="2">
         <v>4</v>
       </c>
@@ -13680,7 +13686,7 @@
       <c r="A509" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B509" s="10"/>
+      <c r="B509" s="8"/>
       <c r="C509" s="2">
         <v>5</v>
       </c>
@@ -13692,7 +13698,7 @@
       <c r="A510" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B510" s="10"/>
+      <c r="B510" s="8"/>
       <c r="C510" s="2">
         <v>99</v>
       </c>
@@ -13704,7 +13710,7 @@
       <c r="A511" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B511" s="9" t="s">
+      <c r="B511" s="7" t="s">
         <v>413</v>
       </c>
       <c r="C511" s="3">
@@ -13718,7 +13724,7 @@
       <c r="A512" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B512" s="10"/>
+      <c r="B512" s="8"/>
       <c r="C512" s="2">
         <v>2</v>
       </c>
@@ -13730,7 +13736,7 @@
       <c r="A513" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B513" s="10"/>
+      <c r="B513" s="8"/>
       <c r="C513" s="2">
         <v>3</v>
       </c>
@@ -13742,7 +13748,7 @@
       <c r="A514" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B514" s="10"/>
+      <c r="B514" s="8"/>
       <c r="C514" s="2">
         <v>4</v>
       </c>
@@ -13754,7 +13760,7 @@
       <c r="A515" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B515" s="10"/>
+      <c r="B515" s="8"/>
       <c r="C515" s="2">
         <v>5</v>
       </c>
@@ -13766,7 +13772,7 @@
       <c r="A516" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B516" s="10"/>
+      <c r="B516" s="8"/>
       <c r="C516" s="2">
         <v>99</v>
       </c>
@@ -13778,7 +13784,7 @@
       <c r="A517" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B517" s="9" t="s">
+      <c r="B517" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C517" s="3">
@@ -13792,7 +13798,7 @@
       <c r="A518" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B518" s="10"/>
+      <c r="B518" s="8"/>
       <c r="C518" s="2">
         <v>2</v>
       </c>
@@ -13804,7 +13810,7 @@
       <c r="A519" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B519" s="10"/>
+      <c r="B519" s="8"/>
       <c r="C519" s="2">
         <v>3</v>
       </c>
@@ -13816,7 +13822,7 @@
       <c r="A520" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B520" s="10"/>
+      <c r="B520" s="8"/>
       <c r="C520" s="2">
         <v>4</v>
       </c>
@@ -13828,7 +13834,7 @@
       <c r="A521" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B521" s="10"/>
+      <c r="B521" s="8"/>
       <c r="C521" s="2">
         <v>5</v>
       </c>
@@ -13840,7 +13846,7 @@
       <c r="A522" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B522" s="10"/>
+      <c r="B522" s="8"/>
       <c r="C522" s="2">
         <v>99</v>
       </c>
@@ -13852,7 +13858,7 @@
       <c r="A523" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B523" s="9" t="s">
+      <c r="B523" s="7" t="s">
         <v>417</v>
       </c>
       <c r="C523" s="3">
@@ -13866,7 +13872,7 @@
       <c r="A524" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B524" s="10"/>
+      <c r="B524" s="8"/>
       <c r="C524" s="2">
         <v>2</v>
       </c>
@@ -13878,7 +13884,7 @@
       <c r="A525" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B525" s="10"/>
+      <c r="B525" s="8"/>
       <c r="C525" s="2">
         <v>3</v>
       </c>
@@ -13890,7 +13896,7 @@
       <c r="A526" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B526" s="10"/>
+      <c r="B526" s="8"/>
       <c r="C526" s="2">
         <v>4</v>
       </c>
@@ -13902,7 +13908,7 @@
       <c r="A527" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B527" s="10"/>
+      <c r="B527" s="8"/>
       <c r="C527" s="2">
         <v>5</v>
       </c>
@@ -13914,7 +13920,7 @@
       <c r="A528" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B528" s="10"/>
+      <c r="B528" s="8"/>
       <c r="C528" s="2">
         <v>99</v>
       </c>
@@ -13926,7 +13932,7 @@
       <c r="A529" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B529" s="9" t="s">
+      <c r="B529" s="7" t="s">
         <v>424</v>
       </c>
       <c r="C529" s="3">
@@ -13940,7 +13946,7 @@
       <c r="A530" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B530" s="10"/>
+      <c r="B530" s="8"/>
       <c r="C530" s="2">
         <v>2</v>
       </c>
@@ -13952,7 +13958,7 @@
       <c r="A531" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B531" s="10"/>
+      <c r="B531" s="8"/>
       <c r="C531" s="2">
         <v>3</v>
       </c>
@@ -13964,7 +13970,7 @@
       <c r="A532" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B532" s="10"/>
+      <c r="B532" s="8"/>
       <c r="C532" s="2">
         <v>4</v>
       </c>
@@ -13976,7 +13982,7 @@
       <c r="A533" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B533" s="10"/>
+      <c r="B533" s="8"/>
       <c r="C533" s="2">
         <v>5</v>
       </c>
@@ -13988,7 +13994,7 @@
       <c r="A534" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B534" s="10"/>
+      <c r="B534" s="8"/>
       <c r="C534" s="2">
         <v>99</v>
       </c>
@@ -14000,7 +14006,7 @@
       <c r="A535" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B535" s="9" t="s">
+      <c r="B535" s="7" t="s">
         <v>426</v>
       </c>
       <c r="C535" s="3">
@@ -14014,7 +14020,7 @@
       <c r="A536" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B536" s="10"/>
+      <c r="B536" s="8"/>
       <c r="C536" s="2">
         <v>2</v>
       </c>
@@ -14026,7 +14032,7 @@
       <c r="A537" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B537" s="10"/>
+      <c r="B537" s="8"/>
       <c r="C537" s="2">
         <v>3</v>
       </c>
@@ -14038,7 +14044,7 @@
       <c r="A538" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B538" s="10"/>
+      <c r="B538" s="8"/>
       <c r="C538" s="2">
         <v>4</v>
       </c>
@@ -14050,7 +14056,7 @@
       <c r="A539" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B539" s="10"/>
+      <c r="B539" s="8"/>
       <c r="C539" s="2">
         <v>5</v>
       </c>
@@ -14062,7 +14068,7 @@
       <c r="A540" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B540" s="10"/>
+      <c r="B540" s="8"/>
       <c r="C540" s="2">
         <v>99</v>
       </c>
@@ -14074,7 +14080,7 @@
       <c r="A541" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B541" s="9" t="s">
+      <c r="B541" s="7" t="s">
         <v>428</v>
       </c>
       <c r="C541" s="3">
@@ -14088,7 +14094,7 @@
       <c r="A542" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B542" s="10"/>
+      <c r="B542" s="8"/>
       <c r="C542" s="2">
         <v>2</v>
       </c>
@@ -14100,7 +14106,7 @@
       <c r="A543" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B543" s="10"/>
+      <c r="B543" s="8"/>
       <c r="C543" s="2">
         <v>3</v>
       </c>
@@ -14112,7 +14118,7 @@
       <c r="A544" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B544" s="10"/>
+      <c r="B544" s="8"/>
       <c r="C544" s="2">
         <v>4</v>
       </c>
@@ -14124,7 +14130,7 @@
       <c r="A545" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B545" s="10"/>
+      <c r="B545" s="8"/>
       <c r="C545" s="2">
         <v>5</v>
       </c>
@@ -14136,7 +14142,7 @@
       <c r="A546" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B546" s="10"/>
+      <c r="B546" s="8"/>
       <c r="C546" s="2">
         <v>99</v>
       </c>
@@ -14148,7 +14154,7 @@
       <c r="A547" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B547" s="9" t="s">
+      <c r="B547" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C547" s="3">
@@ -14162,7 +14168,7 @@
       <c r="A548" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B548" s="10"/>
+      <c r="B548" s="8"/>
       <c r="C548" s="2">
         <v>2</v>
       </c>
@@ -14174,7 +14180,7 @@
       <c r="A549" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B549" s="10"/>
+      <c r="B549" s="8"/>
       <c r="C549" s="2">
         <v>3</v>
       </c>
@@ -14186,7 +14192,7 @@
       <c r="A550" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B550" s="10"/>
+      <c r="B550" s="8"/>
       <c r="C550" s="2">
         <v>4</v>
       </c>
@@ -14198,7 +14204,7 @@
       <c r="A551" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B551" s="10"/>
+      <c r="B551" s="8"/>
       <c r="C551" s="2">
         <v>5</v>
       </c>
@@ -14210,7 +14216,7 @@
       <c r="A552" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B552" s="10"/>
+      <c r="B552" s="8"/>
       <c r="C552" s="2">
         <v>99</v>
       </c>
@@ -14222,7 +14228,7 @@
       <c r="A553" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B553" s="9" t="s">
+      <c r="B553" s="7" t="s">
         <v>432</v>
       </c>
       <c r="C553" s="3">
@@ -14236,7 +14242,7 @@
       <c r="A554" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B554" s="10"/>
+      <c r="B554" s="8"/>
       <c r="C554" s="2">
         <v>2</v>
       </c>
@@ -14248,7 +14254,7 @@
       <c r="A555" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B555" s="10"/>
+      <c r="B555" s="8"/>
       <c r="C555" s="2">
         <v>3</v>
       </c>
@@ -14260,7 +14266,7 @@
       <c r="A556" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B556" s="10"/>
+      <c r="B556" s="8"/>
       <c r="C556" s="2">
         <v>4</v>
       </c>
@@ -14272,7 +14278,7 @@
       <c r="A557" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B557" s="10"/>
+      <c r="B557" s="8"/>
       <c r="C557" s="2">
         <v>5</v>
       </c>
@@ -14284,7 +14290,7 @@
       <c r="A558" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B558" s="10"/>
+      <c r="B558" s="8"/>
       <c r="C558" s="2">
         <v>99</v>
       </c>
@@ -14558,7 +14564,7 @@
       <c r="A580" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B580" s="9" t="s">
+      <c r="B580" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C580" s="3">
@@ -14572,7 +14578,7 @@
       <c r="A581" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B581" s="10"/>
+      <c r="B581" s="8"/>
       <c r="C581" s="2">
         <v>2</v>
       </c>
@@ -14584,7 +14590,7 @@
       <c r="A582" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B582" s="10"/>
+      <c r="B582" s="8"/>
       <c r="C582" s="2">
         <v>99</v>
       </c>
@@ -14596,7 +14602,7 @@
       <c r="A583" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B583" s="9" t="s">
+      <c r="B583" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C583" s="3">
@@ -14610,7 +14616,7 @@
       <c r="A584" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B584" s="10"/>
+      <c r="B584" s="8"/>
       <c r="C584" s="2">
         <v>2</v>
       </c>
@@ -14622,7 +14628,7 @@
       <c r="A585" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B585" s="10"/>
+      <c r="B585" s="8"/>
       <c r="C585" s="2">
         <v>99</v>
       </c>
@@ -14634,7 +14640,7 @@
       <c r="A586" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B586" s="9" t="s">
+      <c r="B586" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C586" s="3">
@@ -14648,7 +14654,7 @@
       <c r="A587" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B587" s="10"/>
+      <c r="B587" s="8"/>
       <c r="C587" s="2">
         <v>2</v>
       </c>
@@ -14660,7 +14666,7 @@
       <c r="A588" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B588" s="10"/>
+      <c r="B588" s="8"/>
       <c r="C588" s="2">
         <v>99</v>
       </c>
@@ -14672,7 +14678,7 @@
       <c r="A589" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B589" s="9" t="s">
+      <c r="B589" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C589" s="3">
@@ -14686,7 +14692,7 @@
       <c r="A590" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B590" s="10"/>
+      <c r="B590" s="8"/>
       <c r="C590" s="2">
         <v>2</v>
       </c>
@@ -14698,7 +14704,7 @@
       <c r="A591" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B591" s="10"/>
+      <c r="B591" s="8"/>
       <c r="C591" s="2">
         <v>99</v>
       </c>
@@ -14710,7 +14716,7 @@
       <c r="A592" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B592" s="9" t="s">
+      <c r="B592" s="7" t="s">
         <v>466</v>
       </c>
       <c r="C592" s="3">
@@ -14724,7 +14730,7 @@
       <c r="A593" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B593" s="10"/>
+      <c r="B593" s="8"/>
       <c r="C593" s="2">
         <v>10000</v>
       </c>
@@ -14736,7 +14742,7 @@
       <c r="A594" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B594" s="10"/>
+      <c r="B594" s="8"/>
       <c r="C594" s="2">
         <v>20000</v>
       </c>
@@ -14748,7 +14754,7 @@
       <c r="A595" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B595" s="10"/>
+      <c r="B595" s="8"/>
       <c r="C595" s="2">
         <v>30000</v>
       </c>
@@ -14760,7 +14766,7 @@
       <c r="A596" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B596" s="10"/>
+      <c r="B596" s="8"/>
       <c r="C596" s="2">
         <v>40001</v>
       </c>
@@ -14772,7 +14778,7 @@
       <c r="A597" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B597" s="10"/>
+      <c r="B597" s="8"/>
       <c r="C597" s="2">
         <v>40002</v>
       </c>
@@ -14784,7 +14790,7 @@
       <c r="A598" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B598" s="10"/>
+      <c r="B598" s="8"/>
       <c r="C598" s="2">
         <v>50000</v>
       </c>
@@ -14796,7 +14802,7 @@
       <c r="A599" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B599" s="10"/>
+      <c r="B599" s="8"/>
       <c r="C599" s="2">
         <v>60000</v>
       </c>
@@ -14808,7 +14814,7 @@
       <c r="A600" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B600" s="10"/>
+      <c r="B600" s="8"/>
       <c r="C600" s="2">
         <v>70000</v>
       </c>
@@ -14820,7 +14826,7 @@
       <c r="A601" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B601" s="10"/>
+      <c r="B601" s="8"/>
       <c r="C601" s="2">
         <v>80000</v>
       </c>
@@ -14832,7 +14838,7 @@
       <c r="A602" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B602" s="10"/>
+      <c r="B602" s="8"/>
       <c r="C602" s="2">
         <v>90001</v>
       </c>
@@ -14844,7 +14850,7 @@
       <c r="A603" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B603" s="10"/>
+      <c r="B603" s="8"/>
       <c r="C603" s="2">
         <v>90002</v>
       </c>
@@ -14856,7 +14862,7 @@
       <c r="A604" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B604" s="10"/>
+      <c r="B604" s="8"/>
       <c r="C604" s="2">
         <v>100000</v>
       </c>
@@ -14868,7 +14874,7 @@
       <c r="A605" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B605" s="10"/>
+      <c r="B605" s="8"/>
       <c r="C605" s="2">
         <v>900000</v>
       </c>
@@ -15316,7 +15322,7 @@
       <c r="A642" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B642" s="9" t="s">
+      <c r="B642" s="7" t="s">
         <v>474</v>
       </c>
       <c r="C642" s="3">
@@ -15330,7 +15336,7 @@
       <c r="A643" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B643" s="10"/>
+      <c r="B643" s="8"/>
       <c r="C643" s="2">
         <v>2</v>
       </c>
@@ -15342,7 +15348,7 @@
       <c r="A644" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B644" s="10"/>
+      <c r="B644" s="8"/>
       <c r="C644" s="2">
         <v>3</v>
       </c>
@@ -15354,7 +15360,7 @@
       <c r="A645" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B645" s="10"/>
+      <c r="B645" s="8"/>
       <c r="C645" s="2">
         <v>4</v>
       </c>
@@ -15366,7 +15372,7 @@
       <c r="A646" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B646" s="10"/>
+      <c r="B646" s="8"/>
       <c r="C646" s="2">
         <v>99</v>
       </c>
@@ -15378,7 +15384,7 @@
       <c r="A647" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B647" s="9" t="s">
+      <c r="B647" s="7" t="s">
         <v>476</v>
       </c>
       <c r="C647" s="3">
@@ -15392,7 +15398,7 @@
       <c r="A648" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B648" s="10"/>
+      <c r="B648" s="8"/>
       <c r="C648" s="2">
         <v>2</v>
       </c>
@@ -15404,7 +15410,7 @@
       <c r="A649" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B649" s="10"/>
+      <c r="B649" s="8"/>
       <c r="C649" s="2">
         <v>3</v>
       </c>
@@ -15416,7 +15422,7 @@
       <c r="A650" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B650" s="10"/>
+      <c r="B650" s="8"/>
       <c r="C650" s="2">
         <v>4</v>
       </c>
@@ -15428,7 +15434,7 @@
       <c r="A651" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B651" s="10"/>
+      <c r="B651" s="8"/>
       <c r="C651" s="2">
         <v>99</v>
       </c>
@@ -15440,7 +15446,7 @@
       <c r="A652" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B652" s="9" t="s">
+      <c r="B652" s="7" t="s">
         <v>478</v>
       </c>
       <c r="C652" s="3">
@@ -15454,7 +15460,7 @@
       <c r="A653" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B653" s="10"/>
+      <c r="B653" s="8"/>
       <c r="C653" s="2">
         <v>2</v>
       </c>
@@ -15466,7 +15472,7 @@
       <c r="A654" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B654" s="10"/>
+      <c r="B654" s="8"/>
       <c r="C654" s="2">
         <v>3</v>
       </c>
@@ -15478,7 +15484,7 @@
       <c r="A655" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B655" s="10"/>
+      <c r="B655" s="8"/>
       <c r="C655" s="2">
         <v>4</v>
       </c>
@@ -15490,7 +15496,7 @@
       <c r="A656" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B656" s="10"/>
+      <c r="B656" s="8"/>
       <c r="C656" s="2">
         <v>5</v>
       </c>
@@ -15502,7 +15508,7 @@
       <c r="A657" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B657" s="10"/>
+      <c r="B657" s="8"/>
       <c r="C657" s="2">
         <v>6</v>
       </c>
@@ -15514,7 +15520,7 @@
       <c r="A658" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B658" s="10"/>
+      <c r="B658" s="8"/>
       <c r="C658" s="2">
         <v>99</v>
       </c>
@@ -15736,7 +15742,7 @@
       <c r="A676" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B676" s="9" t="s">
+      <c r="B676" s="7" t="s">
         <v>497</v>
       </c>
       <c r="C676" s="3">
@@ -15750,7 +15756,7 @@
       <c r="A677" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B677" s="10"/>
+      <c r="B677" s="8"/>
       <c r="C677" s="2">
         <v>2</v>
       </c>
@@ -15762,7 +15768,7 @@
       <c r="A678" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B678" s="10"/>
+      <c r="B678" s="8"/>
       <c r="C678" s="2">
         <v>3</v>
       </c>
@@ -15774,7 +15780,7 @@
       <c r="A679" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B679" s="10"/>
+      <c r="B679" s="8"/>
       <c r="C679" s="2">
         <v>4</v>
       </c>
@@ -15786,7 +15792,7 @@
       <c r="A680" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B680" s="10"/>
+      <c r="B680" s="8"/>
       <c r="C680" s="2">
         <v>99</v>
       </c>
@@ -15798,7 +15804,7 @@
       <c r="A681" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B681" s="9" t="s">
+      <c r="B681" s="7" t="s">
         <v>503</v>
       </c>
       <c r="C681" s="3">
@@ -15812,7 +15818,7 @@
       <c r="A682" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B682" s="10"/>
+      <c r="B682" s="8"/>
       <c r="C682" s="2">
         <v>2</v>
       </c>
@@ -15824,7 +15830,7 @@
       <c r="A683" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B683" s="10"/>
+      <c r="B683" s="8"/>
       <c r="C683" s="2">
         <v>3</v>
       </c>
@@ -15836,7 +15842,7 @@
       <c r="A684" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B684" s="10"/>
+      <c r="B684" s="8"/>
       <c r="C684" s="2">
         <v>4</v>
       </c>
@@ -15848,7 +15854,7 @@
       <c r="A685" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B685" s="10"/>
+      <c r="B685" s="8"/>
       <c r="C685" s="2">
         <v>99</v>
       </c>
@@ -15860,7 +15866,7 @@
       <c r="A686" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B686" s="9" t="s">
+      <c r="B686" s="7" t="s">
         <v>509</v>
       </c>
       <c r="C686" s="3">
@@ -15874,7 +15880,7 @@
       <c r="A687" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B687" s="10"/>
+      <c r="B687" s="8"/>
       <c r="C687" s="2">
         <v>2</v>
       </c>
@@ -15886,7 +15892,7 @@
       <c r="A688" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B688" s="10"/>
+      <c r="B688" s="8"/>
       <c r="C688" s="2">
         <v>3</v>
       </c>
@@ -15898,7 +15904,7 @@
       <c r="A689" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B689" s="10"/>
+      <c r="B689" s="8"/>
       <c r="C689" s="2">
         <v>4</v>
       </c>
@@ -15910,7 +15916,7 @@
       <c r="A690" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B690" s="10"/>
+      <c r="B690" s="8"/>
       <c r="C690" s="2">
         <v>5</v>
       </c>
@@ -15922,7 +15928,7 @@
       <c r="A691" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B691" s="10"/>
+      <c r="B691" s="8"/>
       <c r="C691" s="2">
         <v>99</v>
       </c>
@@ -15934,7 +15940,7 @@
       <c r="A692" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B692" s="9" t="s">
+      <c r="B692" s="7" t="s">
         <v>515</v>
       </c>
       <c r="C692" s="3">
@@ -15948,7 +15954,7 @@
       <c r="A693" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B693" s="10"/>
+      <c r="B693" s="8"/>
       <c r="C693" s="2">
         <v>2</v>
       </c>
@@ -15960,7 +15966,7 @@
       <c r="A694" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B694" s="10"/>
+      <c r="B694" s="8"/>
       <c r="C694" s="2">
         <v>3</v>
       </c>
@@ -15972,7 +15978,7 @@
       <c r="A695" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B695" s="10"/>
+      <c r="B695" s="8"/>
       <c r="C695" s="2">
         <v>4</v>
       </c>
@@ -15984,7 +15990,7 @@
       <c r="A696" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B696" s="10"/>
+      <c r="B696" s="8"/>
       <c r="C696" s="2">
         <v>5</v>
       </c>
@@ -15996,7 +16002,7 @@
       <c r="A697" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B697" s="10"/>
+      <c r="B697" s="8"/>
       <c r="C697" s="2">
         <v>6</v>
       </c>
@@ -16008,7 +16014,7 @@
       <c r="A698" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B698" s="10"/>
+      <c r="B698" s="8"/>
       <c r="C698" s="2">
         <v>99</v>
       </c>
@@ -17238,7 +17244,7 @@
       <c r="A798" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B798" s="9" t="s">
+      <c r="B798" s="7" t="s">
         <v>572</v>
       </c>
       <c r="C798" s="3">
@@ -17252,7 +17258,7 @@
       <c r="A799" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B799" s="10"/>
+      <c r="B799" s="8"/>
       <c r="C799" s="2">
         <v>2</v>
       </c>
@@ -17264,7 +17270,7 @@
       <c r="A800" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B800" s="10"/>
+      <c r="B800" s="8"/>
       <c r="C800" s="2">
         <v>99</v>
       </c>
@@ -17276,7 +17282,7 @@
       <c r="A801" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B801" s="9" t="s">
+      <c r="B801" s="7" t="s">
         <v>576</v>
       </c>
       <c r="C801" s="3">
@@ -17290,7 +17296,7 @@
       <c r="A802" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B802" s="10"/>
+      <c r="B802" s="8"/>
       <c r="C802" s="2">
         <v>2</v>
       </c>
@@ -17302,7 +17308,7 @@
       <c r="A803" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B803" s="10"/>
+      <c r="B803" s="8"/>
       <c r="C803" s="2">
         <v>99</v>
       </c>
@@ -17314,7 +17320,7 @@
       <c r="A804" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B804" s="9" t="s">
+      <c r="B804" s="7" t="s">
         <v>578</v>
       </c>
       <c r="C804" s="3">
@@ -17328,7 +17334,7 @@
       <c r="A805" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B805" s="10"/>
+      <c r="B805" s="8"/>
       <c r="C805" s="2">
         <v>2</v>
       </c>
@@ -17340,7 +17346,7 @@
       <c r="A806" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B806" s="10"/>
+      <c r="B806" s="8"/>
       <c r="C806" s="2">
         <v>99</v>
       </c>
@@ -17352,7 +17358,7 @@
       <c r="A807" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B807" s="9" t="s">
+      <c r="B807" s="7" t="s">
         <v>580</v>
       </c>
       <c r="C807" s="3">
@@ -17366,7 +17372,7 @@
       <c r="A808" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B808" s="10"/>
+      <c r="B808" s="8"/>
       <c r="C808" s="2">
         <v>2</v>
       </c>
@@ -17378,7 +17384,7 @@
       <c r="A809" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B809" s="10"/>
+      <c r="B809" s="8"/>
       <c r="C809" s="2">
         <v>99</v>
       </c>
@@ -17390,7 +17396,7 @@
       <c r="A810" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B810" s="9" t="s">
+      <c r="B810" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C810" s="3">
@@ -17404,7 +17410,7 @@
       <c r="A811" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B811" s="10"/>
+      <c r="B811" s="8"/>
       <c r="C811" s="2">
         <v>2</v>
       </c>
@@ -17416,7 +17422,7 @@
       <c r="A812" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B812" s="10"/>
+      <c r="B812" s="8"/>
       <c r="C812" s="2">
         <v>99</v>
       </c>
@@ -17428,7 +17434,7 @@
       <c r="A813" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B813" s="9" t="s">
+      <c r="B813" s="7" t="s">
         <v>584</v>
       </c>
       <c r="C813" s="3">
@@ -17442,7 +17448,7 @@
       <c r="A814" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B814" s="10"/>
+      <c r="B814" s="8"/>
       <c r="C814" s="2">
         <v>2</v>
       </c>
@@ -17454,7 +17460,7 @@
       <c r="A815" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B815" s="10"/>
+      <c r="B815" s="8"/>
       <c r="C815" s="2">
         <v>99</v>
       </c>
@@ -17466,7 +17472,7 @@
       <c r="A816" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B816" s="9" t="s">
+      <c r="B816" s="7" t="s">
         <v>586</v>
       </c>
       <c r="C816" s="3">
@@ -17480,7 +17486,7 @@
       <c r="A817" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B817" s="10"/>
+      <c r="B817" s="8"/>
       <c r="C817" s="2">
         <v>2</v>
       </c>
@@ -17492,7 +17498,7 @@
       <c r="A818" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B818" s="10"/>
+      <c r="B818" s="8"/>
       <c r="C818" s="2">
         <v>3</v>
       </c>
@@ -17504,7 +17510,7 @@
       <c r="A819" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B819" s="10"/>
+      <c r="B819" s="8"/>
       <c r="C819" s="2">
         <v>4</v>
       </c>
@@ -17516,7 +17522,7 @@
       <c r="A820" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B820" s="10"/>
+      <c r="B820" s="8"/>
       <c r="C820" s="2">
         <v>99</v>
       </c>
@@ -17528,7 +17534,7 @@
       <c r="A821" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B821" s="9" t="s">
+      <c r="B821" s="7" t="s">
         <v>588</v>
       </c>
       <c r="C821" s="3">
@@ -17542,7 +17548,7 @@
       <c r="A822" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B822" s="10"/>
+      <c r="B822" s="8"/>
       <c r="C822" s="2">
         <v>2</v>
       </c>
@@ -17554,7 +17560,7 @@
       <c r="A823" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B823" s="10"/>
+      <c r="B823" s="8"/>
       <c r="C823" s="2">
         <v>3</v>
       </c>
@@ -17566,7 +17572,7 @@
       <c r="A824" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B824" s="10"/>
+      <c r="B824" s="8"/>
       <c r="C824" s="2">
         <v>4</v>
       </c>
@@ -17578,7 +17584,7 @@
       <c r="A825" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B825" s="10"/>
+      <c r="B825" s="8"/>
       <c r="C825" s="2">
         <v>99</v>
       </c>
@@ -17590,7 +17596,7 @@
       <c r="A826" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B826" s="9" t="s">
+      <c r="B826" s="7" t="s">
         <v>590</v>
       </c>
       <c r="C826" s="3">
@@ -17604,7 +17610,7 @@
       <c r="A827" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B827" s="10"/>
+      <c r="B827" s="8"/>
       <c r="C827" s="2">
         <v>2</v>
       </c>
@@ -17616,7 +17622,7 @@
       <c r="A828" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B828" s="10"/>
+      <c r="B828" s="8"/>
       <c r="C828" s="2">
         <v>3</v>
       </c>
@@ -17628,7 +17634,7 @@
       <c r="A829" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B829" s="10"/>
+      <c r="B829" s="8"/>
       <c r="C829" s="2">
         <v>4</v>
       </c>
@@ -17640,7 +17646,7 @@
       <c r="A830" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B830" s="10"/>
+      <c r="B830" s="8"/>
       <c r="C830" s="2">
         <v>99</v>
       </c>
@@ -17652,7 +17658,7 @@
       <c r="A831" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B831" s="9" t="s">
+      <c r="B831" s="7" t="s">
         <v>592</v>
       </c>
       <c r="C831" s="3">
@@ -17666,7 +17672,7 @@
       <c r="A832" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B832" s="10"/>
+      <c r="B832" s="8"/>
       <c r="C832" s="2">
         <v>2</v>
       </c>
@@ -17678,7 +17684,7 @@
       <c r="A833" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B833" s="10"/>
+      <c r="B833" s="8"/>
       <c r="C833" s="2">
         <v>3</v>
       </c>
@@ -17690,7 +17696,7 @@
       <c r="A834" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B834" s="10"/>
+      <c r="B834" s="8"/>
       <c r="C834" s="2">
         <v>4</v>
       </c>
@@ -17702,7 +17708,7 @@
       <c r="A835" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B835" s="10"/>
+      <c r="B835" s="8"/>
       <c r="C835" s="2">
         <v>99</v>
       </c>
@@ -17714,7 +17720,7 @@
       <c r="A836" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B836" s="9" t="s">
+      <c r="B836" s="7" t="s">
         <v>594</v>
       </c>
       <c r="C836" s="3">
@@ -17728,7 +17734,7 @@
       <c r="A837" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B837" s="10"/>
+      <c r="B837" s="8"/>
       <c r="C837" s="2">
         <v>2</v>
       </c>
@@ -17740,7 +17746,7 @@
       <c r="A838" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B838" s="10"/>
+      <c r="B838" s="8"/>
       <c r="C838" s="2">
         <v>3</v>
       </c>
@@ -17752,7 +17758,7 @@
       <c r="A839" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B839" s="10"/>
+      <c r="B839" s="8"/>
       <c r="C839" s="2">
         <v>4</v>
       </c>
@@ -17764,7 +17770,7 @@
       <c r="A840" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B840" s="10"/>
+      <c r="B840" s="8"/>
       <c r="C840" s="2">
         <v>5</v>
       </c>
@@ -17776,7 +17782,7 @@
       <c r="A841" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B841" s="10"/>
+      <c r="B841" s="8"/>
       <c r="C841" s="2">
         <v>6</v>
       </c>
@@ -17788,7 +17794,7 @@
       <c r="A842" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B842" s="10"/>
+      <c r="B842" s="8"/>
       <c r="C842" s="2">
         <v>7</v>
       </c>
@@ -17800,7 +17806,7 @@
       <c r="A843" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B843" s="10"/>
+      <c r="B843" s="8"/>
       <c r="C843" s="2">
         <v>99</v>
       </c>
@@ -17812,7 +17818,7 @@
       <c r="A844" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B844" s="9" t="s">
+      <c r="B844" s="7" t="s">
         <v>598</v>
       </c>
       <c r="C844" s="3">
@@ -17826,7 +17832,7 @@
       <c r="A845" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B845" s="10"/>
+      <c r="B845" s="8"/>
       <c r="C845" s="2">
         <v>2</v>
       </c>
@@ -17838,7 +17844,7 @@
       <c r="A846" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B846" s="10"/>
+      <c r="B846" s="8"/>
       <c r="C846" s="2">
         <v>99</v>
       </c>
@@ -17850,7 +17856,7 @@
       <c r="A847" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B847" s="9" t="s">
+      <c r="B847" s="7" t="s">
         <v>600</v>
       </c>
       <c r="C847" s="3">
@@ -17864,7 +17870,7 @@
       <c r="A848" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B848" s="10"/>
+      <c r="B848" s="8"/>
       <c r="C848" s="2">
         <v>2</v>
       </c>
@@ -17876,7 +17882,7 @@
       <c r="A849" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B849" s="10"/>
+      <c r="B849" s="8"/>
       <c r="C849" s="2">
         <v>3</v>
       </c>
@@ -17888,7 +17894,7 @@
       <c r="A850" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B850" s="10"/>
+      <c r="B850" s="8"/>
       <c r="C850" s="2">
         <v>4</v>
       </c>
@@ -17900,7 +17906,7 @@
       <c r="A851" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B851" s="10"/>
+      <c r="B851" s="8"/>
       <c r="C851" s="2">
         <v>5</v>
       </c>
@@ -17912,7 +17918,7 @@
       <c r="A852" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B852" s="10"/>
+      <c r="B852" s="8"/>
       <c r="C852" s="2">
         <v>9</v>
       </c>
@@ -17924,7 +17930,7 @@
       <c r="A853" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B853" s="9" t="s">
+      <c r="B853" s="7" t="s">
         <v>607</v>
       </c>
       <c r="C853" s="3">
@@ -17938,7 +17944,7 @@
       <c r="A854" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B854" s="10"/>
+      <c r="B854" s="8"/>
       <c r="C854" s="2">
         <v>2</v>
       </c>
@@ -17950,7 +17956,7 @@
       <c r="A855" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B855" s="10"/>
+      <c r="B855" s="8"/>
       <c r="C855" s="2">
         <v>99</v>
       </c>
@@ -17962,7 +17968,7 @@
       <c r="A856" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B856" s="9" t="s">
+      <c r="B856" s="7" t="s">
         <v>609</v>
       </c>
       <c r="C856" s="3">
@@ -17976,7 +17982,7 @@
       <c r="A857" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B857" s="10"/>
+      <c r="B857" s="8"/>
       <c r="C857" s="2">
         <v>2</v>
       </c>
@@ -17988,7 +17994,7 @@
       <c r="A858" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B858" s="10"/>
+      <c r="B858" s="8"/>
       <c r="C858" s="2">
         <v>3</v>
       </c>
@@ -18000,7 +18006,7 @@
       <c r="A859" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B859" s="10"/>
+      <c r="B859" s="8"/>
       <c r="C859" s="2">
         <v>4</v>
       </c>
@@ -18012,7 +18018,7 @@
       <c r="A860" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B860" s="10"/>
+      <c r="B860" s="8"/>
       <c r="C860" s="2">
         <v>99</v>
       </c>
@@ -18024,7 +18030,7 @@
       <c r="A861" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B861" s="9" t="s">
+      <c r="B861" s="7" t="s">
         <v>615</v>
       </c>
       <c r="C861" s="3">
@@ -18038,7 +18044,7 @@
       <c r="A862" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B862" s="10"/>
+      <c r="B862" s="8"/>
       <c r="C862" s="2">
         <v>2</v>
       </c>
@@ -18050,7 +18056,7 @@
       <c r="A863" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B863" s="10"/>
+      <c r="B863" s="8"/>
       <c r="C863" s="2">
         <v>3</v>
       </c>
@@ -18062,7 +18068,7 @@
       <c r="A864" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B864" s="10"/>
+      <c r="B864" s="8"/>
       <c r="C864" s="2">
         <v>99</v>
       </c>
@@ -18074,7 +18080,7 @@
       <c r="A865" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B865" s="9" t="s">
+      <c r="B865" s="7" t="s">
         <v>619</v>
       </c>
       <c r="C865" s="3">
@@ -18088,7 +18094,7 @@
       <c r="A866" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B866" s="10"/>
+      <c r="B866" s="8"/>
       <c r="C866" s="2">
         <v>2</v>
       </c>
@@ -18100,7 +18106,7 @@
       <c r="A867" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B867" s="10"/>
+      <c r="B867" s="8"/>
       <c r="C867" s="2">
         <v>3</v>
       </c>
@@ -18112,7 +18118,7 @@
       <c r="A868" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B868" s="10"/>
+      <c r="B868" s="8"/>
       <c r="C868" s="2">
         <v>4</v>
       </c>
@@ -18124,7 +18130,7 @@
       <c r="A869" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B869" s="10"/>
+      <c r="B869" s="8"/>
       <c r="C869" s="2">
         <v>5</v>
       </c>
@@ -18136,7 +18142,7 @@
       <c r="A870" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B870" s="10"/>
+      <c r="B870" s="8"/>
       <c r="C870" s="2">
         <v>99</v>
       </c>
@@ -18148,7 +18154,7 @@
       <c r="A871" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B871" s="9" t="s">
+      <c r="B871" s="7" t="s">
         <v>626</v>
       </c>
       <c r="C871" s="3">
@@ -18162,7 +18168,7 @@
       <c r="A872" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B872" s="10"/>
+      <c r="B872" s="8"/>
       <c r="C872" s="2">
         <v>2</v>
       </c>
@@ -18174,7 +18180,7 @@
       <c r="A873" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B873" s="10"/>
+      <c r="B873" s="8"/>
       <c r="C873" s="2">
         <v>3</v>
       </c>
@@ -18186,7 +18192,7 @@
       <c r="A874" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B874" s="10"/>
+      <c r="B874" s="8"/>
       <c r="C874" s="2">
         <v>99</v>
       </c>
@@ -18198,7 +18204,7 @@
       <c r="A875" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B875" s="9" t="s">
+      <c r="B875" s="7" t="s">
         <v>632</v>
       </c>
       <c r="C875" s="3">
@@ -18212,7 +18218,7 @@
       <c r="A876" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B876" s="10"/>
+      <c r="B876" s="8"/>
       <c r="C876" s="2">
         <v>2</v>
       </c>
@@ -18224,7 +18230,7 @@
       <c r="A877" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B877" s="10"/>
+      <c r="B877" s="8"/>
       <c r="C877" s="2">
         <v>3</v>
       </c>
@@ -18236,7 +18242,7 @@
       <c r="A878" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B878" s="10"/>
+      <c r="B878" s="8"/>
       <c r="C878" s="2">
         <v>4</v>
       </c>
@@ -18248,7 +18254,7 @@
       <c r="A879" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B879" s="10"/>
+      <c r="B879" s="8"/>
       <c r="C879" s="2">
         <v>99</v>
       </c>
@@ -18260,7 +18266,7 @@
       <c r="A880" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B880" s="9" t="s">
+      <c r="B880" s="7" t="s">
         <v>638</v>
       </c>
       <c r="C880" s="3">
@@ -18274,7 +18280,7 @@
       <c r="A881" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B881" s="10"/>
+      <c r="B881" s="8"/>
       <c r="C881" s="2">
         <v>2</v>
       </c>
@@ -18286,7 +18292,7 @@
       <c r="A882" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B882" s="10"/>
+      <c r="B882" s="8"/>
       <c r="C882" s="2">
         <v>99</v>
       </c>
@@ -18336,7 +18342,7 @@
       <c r="A886" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B886" s="9" t="s">
+      <c r="B886" s="7" t="s">
         <v>644</v>
       </c>
       <c r="C886" s="3">
@@ -18350,7 +18356,7 @@
       <c r="A887" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B887" s="10"/>
+      <c r="B887" s="8"/>
       <c r="C887" s="2">
         <v>2</v>
       </c>
@@ -18362,7 +18368,7 @@
       <c r="A888" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B888" s="9" t="s">
+      <c r="B888" s="7" t="s">
         <v>647</v>
       </c>
       <c r="C888" s="3">
@@ -18376,7 +18382,7 @@
       <c r="A889" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B889" s="10"/>
+      <c r="B889" s="8"/>
       <c r="C889" s="2">
         <v>2</v>
       </c>
@@ -18388,7 +18394,7 @@
       <c r="A890" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B890" s="10"/>
+      <c r="B890" s="8"/>
       <c r="C890" s="2">
         <v>3</v>
       </c>
@@ -18400,7 +18406,7 @@
       <c r="A891" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B891" s="10"/>
+      <c r="B891" s="8"/>
       <c r="C891" s="2">
         <v>4</v>
       </c>
@@ -18412,7 +18418,7 @@
       <c r="A892" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B892" s="10"/>
+      <c r="B892" s="8"/>
       <c r="C892" s="2">
         <v>99</v>
       </c>
@@ -18462,7 +18468,7 @@
       <c r="A896" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B896" s="9" t="s">
+      <c r="B896" s="7" t="s">
         <v>657</v>
       </c>
       <c r="C896" s="3">
@@ -18476,7 +18482,7 @@
       <c r="A897" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B897" s="10"/>
+      <c r="B897" s="8"/>
       <c r="C897" s="2">
         <v>2</v>
       </c>
@@ -18488,7 +18494,7 @@
       <c r="A898" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B898" s="10"/>
+      <c r="B898" s="8"/>
       <c r="C898" s="2">
         <v>3</v>
       </c>
@@ -18500,7 +18506,7 @@
       <c r="A899" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B899" s="10"/>
+      <c r="B899" s="8"/>
       <c r="C899" s="2">
         <v>4</v>
       </c>
@@ -18512,7 +18518,7 @@
       <c r="A900" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B900" s="10"/>
+      <c r="B900" s="8"/>
       <c r="C900" s="2">
         <v>5</v>
       </c>
@@ -18524,7 +18530,7 @@
       <c r="A901" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B901" s="10"/>
+      <c r="B901" s="8"/>
       <c r="C901" s="2">
         <v>99</v>
       </c>
@@ -18722,7 +18728,7 @@
       <c r="A917" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B917" s="9" t="s">
+      <c r="B917" s="7" t="s">
         <v>676</v>
       </c>
       <c r="C917" s="3">
@@ -18736,7 +18742,7 @@
       <c r="A918" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B918" s="10"/>
+      <c r="B918" s="8"/>
       <c r="C918" s="2">
         <v>2</v>
       </c>
@@ -18748,7 +18754,7 @@
       <c r="A919" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B919" s="10"/>
+      <c r="B919" s="8"/>
       <c r="C919" s="2">
         <v>3</v>
       </c>
@@ -18760,7 +18766,7 @@
       <c r="A920" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B920" s="10"/>
+      <c r="B920" s="8"/>
       <c r="C920" s="2">
         <v>4</v>
       </c>
@@ -18772,7 +18778,7 @@
       <c r="A921" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B921" s="10"/>
+      <c r="B921" s="8"/>
       <c r="C921" s="2">
         <v>5</v>
       </c>
@@ -18784,7 +18790,7 @@
       <c r="A922" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B922" s="10"/>
+      <c r="B922" s="8"/>
       <c r="C922" s="2">
         <v>6</v>
       </c>
@@ -18796,7 +18802,7 @@
       <c r="A923" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B923" s="10"/>
+      <c r="B923" s="8"/>
       <c r="C923" s="2">
         <v>7</v>
       </c>
@@ -18808,7 +18814,7 @@
       <c r="A924" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B924" s="10"/>
+      <c r="B924" s="8"/>
       <c r="C924" s="2">
         <v>8</v>
       </c>
@@ -18820,7 +18826,7 @@
       <c r="A925" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B925" s="10"/>
+      <c r="B925" s="8"/>
       <c r="C925" s="2">
         <v>99</v>
       </c>
@@ -18832,7 +18838,7 @@
       <c r="A926" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B926" s="9" t="s">
+      <c r="B926" s="7" t="s">
         <v>686</v>
       </c>
       <c r="C926" s="3">
@@ -18846,7 +18852,7 @@
       <c r="A927" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B927" s="10"/>
+      <c r="B927" s="8"/>
       <c r="C927" s="2">
         <v>2</v>
       </c>
@@ -18858,7 +18864,7 @@
       <c r="A928" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B928" s="10"/>
+      <c r="B928" s="8"/>
       <c r="C928" s="2">
         <v>3</v>
       </c>
@@ -18870,7 +18876,7 @@
       <c r="A929" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B929" s="10"/>
+      <c r="B929" s="8"/>
       <c r="C929" s="2">
         <v>99</v>
       </c>
@@ -18882,7 +18888,7 @@
       <c r="A930" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B930" s="9" t="s">
+      <c r="B930" s="7" t="s">
         <v>691</v>
       </c>
       <c r="C930" s="3">
@@ -18896,7 +18902,7 @@
       <c r="A931" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B931" s="10"/>
+      <c r="B931" s="8"/>
       <c r="C931" s="2">
         <v>1</v>
       </c>
@@ -18908,7 +18914,7 @@
       <c r="A932" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B932" s="10"/>
+      <c r="B932" s="8"/>
       <c r="C932" s="2">
         <v>2</v>
       </c>
@@ -18920,7 +18926,7 @@
       <c r="A933" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B933" s="10"/>
+      <c r="B933" s="8"/>
       <c r="C933" s="2">
         <v>3</v>
       </c>
@@ -18932,7 +18938,7 @@
       <c r="A934" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B934" s="10"/>
+      <c r="B934" s="8"/>
       <c r="C934" s="2">
         <v>4</v>
       </c>
@@ -18944,7 +18950,7 @@
       <c r="A935" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B935" s="10"/>
+      <c r="B935" s="8"/>
       <c r="C935" s="2">
         <v>99</v>
       </c>
@@ -19042,7 +19048,7 @@
       <c r="A943" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B943" s="7" t="s">
+      <c r="B943" s="9" t="s">
         <v>702</v>
       </c>
       <c r="C943" s="3">
@@ -19056,7 +19062,7 @@
       <c r="A944" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B944" s="8"/>
+      <c r="B944" s="10"/>
       <c r="C944" s="2">
         <v>2</v>
       </c>
@@ -19068,7 +19074,7 @@
       <c r="A945" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B945" s="8"/>
+      <c r="B945" s="10"/>
       <c r="C945" s="2">
         <v>3</v>
       </c>
@@ -19080,7 +19086,7 @@
       <c r="A946" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B946" s="8"/>
+      <c r="B946" s="10"/>
       <c r="C946" s="2">
         <v>4</v>
       </c>
@@ -19092,7 +19098,7 @@
       <c r="A947" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B947" s="8"/>
+      <c r="B947" s="10"/>
       <c r="C947" s="2">
         <v>5</v>
       </c>
@@ -19104,7 +19110,7 @@
       <c r="A948" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B948" s="8"/>
+      <c r="B948" s="10"/>
       <c r="C948" s="2">
         <v>6</v>
       </c>
@@ -19116,7 +19122,7 @@
       <c r="A949" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B949" s="8"/>
+      <c r="B949" s="10"/>
       <c r="C949" s="2">
         <v>7</v>
       </c>
@@ -19128,7 +19134,7 @@
       <c r="A950" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B950" s="8"/>
+      <c r="B950" s="10"/>
       <c r="C950" s="2">
         <v>8</v>
       </c>
@@ -19140,7 +19146,7 @@
       <c r="A951" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B951" s="8"/>
+      <c r="B951" s="10"/>
       <c r="C951" s="2">
         <v>9</v>
       </c>
@@ -19152,7 +19158,7 @@
       <c r="A952" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B952" s="8"/>
+      <c r="B952" s="10"/>
       <c r="C952" s="2">
         <v>10</v>
       </c>
@@ -19164,7 +19170,7 @@
       <c r="A953" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B953" s="8"/>
+      <c r="B953" s="10"/>
       <c r="C953" s="2">
         <v>11</v>
       </c>
@@ -19176,7 +19182,7 @@
       <c r="A954" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B954" s="8"/>
+      <c r="B954" s="10"/>
       <c r="C954" s="2">
         <v>12</v>
       </c>
@@ -19188,7 +19194,7 @@
       <c r="A955" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B955" s="8"/>
+      <c r="B955" s="10"/>
       <c r="C955" s="2">
         <v>99</v>
       </c>
@@ -19630,7 +19636,7 @@
       <c r="A991" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B991" s="7" t="s">
+      <c r="B991" s="9" t="s">
         <v>740</v>
       </c>
       <c r="C991" s="3">
@@ -19644,7 +19650,7 @@
       <c r="A992" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B992" s="8"/>
+      <c r="B992" s="10"/>
       <c r="C992" s="2">
         <v>2</v>
       </c>
@@ -19656,7 +19662,7 @@
       <c r="A993" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B993" s="8"/>
+      <c r="B993" s="10"/>
       <c r="C993" s="2">
         <v>4</v>
       </c>
@@ -19668,7 +19674,7 @@
       <c r="A994" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B994" s="8"/>
+      <c r="B994" s="10"/>
       <c r="C994" s="2">
         <v>5</v>
       </c>
@@ -19680,7 +19686,7 @@
       <c r="A995" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B995" s="8"/>
+      <c r="B995" s="10"/>
       <c r="C995" s="2">
         <v>6</v>
       </c>
@@ -19692,7 +19698,7 @@
       <c r="A996" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B996" s="8"/>
+      <c r="B996" s="10"/>
       <c r="C996" s="2">
         <v>8</v>
       </c>
@@ -19704,7 +19710,7 @@
       <c r="A997" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B997" s="8"/>
+      <c r="B997" s="10"/>
       <c r="C997" s="2">
         <v>9</v>
       </c>
@@ -19716,7 +19722,7 @@
       <c r="A998" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B998" s="8"/>
+      <c r="B998" s="10"/>
       <c r="C998" s="2">
         <v>10</v>
       </c>
@@ -19728,7 +19734,7 @@
       <c r="A999" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B999" s="8"/>
+      <c r="B999" s="10"/>
       <c r="C999" s="2">
         <v>11</v>
       </c>
@@ -19740,7 +19746,7 @@
       <c r="A1000" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1000" s="8"/>
+      <c r="B1000" s="10"/>
       <c r="C1000" s="2">
         <v>12</v>
       </c>
@@ -19752,7 +19758,7 @@
       <c r="A1001" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1001" s="8"/>
+      <c r="B1001" s="10"/>
       <c r="C1001" s="2">
         <v>13</v>
       </c>
@@ -19764,7 +19770,7 @@
       <c r="A1002" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1002" s="8"/>
+      <c r="B1002" s="10"/>
       <c r="C1002" s="2">
         <v>15</v>
       </c>
@@ -19776,7 +19782,7 @@
       <c r="A1003" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1003" s="8"/>
+      <c r="B1003" s="10"/>
       <c r="C1003" s="2">
         <v>16</v>
       </c>
@@ -19788,7 +19794,7 @@
       <c r="A1004" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1004" s="8"/>
+      <c r="B1004" s="10"/>
       <c r="C1004" s="2">
         <v>17</v>
       </c>
@@ -19800,7 +19806,7 @@
       <c r="A1005" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1005" s="8"/>
+      <c r="B1005" s="10"/>
       <c r="C1005" s="2">
         <v>18</v>
       </c>
@@ -19812,7 +19818,7 @@
       <c r="A1006" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1006" s="8"/>
+      <c r="B1006" s="10"/>
       <c r="C1006" s="2">
         <v>19</v>
       </c>
@@ -19824,7 +19830,7 @@
       <c r="A1007" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1007" s="8"/>
+      <c r="B1007" s="10"/>
       <c r="C1007" s="2">
         <v>20</v>
       </c>
@@ -19836,7 +19842,7 @@
       <c r="A1008" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1008" s="8"/>
+      <c r="B1008" s="10"/>
       <c r="C1008" s="2">
         <v>21</v>
       </c>
@@ -19848,7 +19854,7 @@
       <c r="A1009" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1009" s="8"/>
+      <c r="B1009" s="10"/>
       <c r="C1009" s="2">
         <v>22</v>
       </c>
@@ -19860,7 +19866,7 @@
       <c r="A1010" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1010" s="8"/>
+      <c r="B1010" s="10"/>
       <c r="C1010" s="2">
         <v>23</v>
       </c>
@@ -19872,7 +19878,7 @@
       <c r="A1011" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1011" s="8"/>
+      <c r="B1011" s="10"/>
       <c r="C1011" s="2">
         <v>24</v>
       </c>
@@ -19884,7 +19890,7 @@
       <c r="A1012" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1012" s="8"/>
+      <c r="B1012" s="10"/>
       <c r="C1012" s="2">
         <v>25</v>
       </c>
@@ -19896,7 +19902,7 @@
       <c r="A1013" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1013" s="8"/>
+      <c r="B1013" s="10"/>
       <c r="C1013" s="2">
         <v>26</v>
       </c>
@@ -19908,7 +19914,7 @@
       <c r="A1014" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1014" s="8"/>
+      <c r="B1014" s="10"/>
       <c r="C1014" s="2">
         <v>27</v>
       </c>
@@ -19920,7 +19926,7 @@
       <c r="A1015" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1015" s="8"/>
+      <c r="B1015" s="10"/>
       <c r="C1015" s="2">
         <v>28</v>
       </c>
@@ -19932,7 +19938,7 @@
       <c r="A1016" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1016" s="8"/>
+      <c r="B1016" s="10"/>
       <c r="C1016" s="2">
         <v>29</v>
       </c>
@@ -19944,7 +19950,7 @@
       <c r="A1017" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1017" s="8"/>
+      <c r="B1017" s="10"/>
       <c r="C1017" s="2">
         <v>30</v>
       </c>
@@ -19956,7 +19962,7 @@
       <c r="A1018" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1018" s="8"/>
+      <c r="B1018" s="10"/>
       <c r="C1018" s="2">
         <v>31</v>
       </c>
@@ -19968,7 +19974,7 @@
       <c r="A1019" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1019" s="8"/>
+      <c r="B1019" s="10"/>
       <c r="C1019" s="2">
         <v>32</v>
       </c>
@@ -19980,7 +19986,7 @@
       <c r="A1020" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1020" s="8"/>
+      <c r="B1020" s="10"/>
       <c r="C1020" s="2">
         <v>33</v>
       </c>
@@ -19992,7 +19998,7 @@
       <c r="A1021" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1021" s="8"/>
+      <c r="B1021" s="10"/>
       <c r="C1021" s="2">
         <v>34</v>
       </c>
@@ -20004,7 +20010,7 @@
       <c r="A1022" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1022" s="8"/>
+      <c r="B1022" s="10"/>
       <c r="C1022" s="2">
         <v>35</v>
       </c>
@@ -20016,7 +20022,7 @@
       <c r="A1023" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1023" s="8"/>
+      <c r="B1023" s="10"/>
       <c r="C1023" s="2">
         <v>36</v>
       </c>
@@ -20028,7 +20034,7 @@
       <c r="A1024" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1024" s="8"/>
+      <c r="B1024" s="10"/>
       <c r="C1024" s="2">
         <v>37</v>
       </c>
@@ -20040,7 +20046,7 @@
       <c r="A1025" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1025" s="8"/>
+      <c r="B1025" s="10"/>
       <c r="C1025" s="2">
         <v>38</v>
       </c>
@@ -20052,7 +20058,7 @@
       <c r="A1026" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1026" s="8"/>
+      <c r="B1026" s="10"/>
       <c r="C1026" s="2">
         <v>39</v>
       </c>
@@ -20064,7 +20070,7 @@
       <c r="A1027" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1027" s="8"/>
+      <c r="B1027" s="10"/>
       <c r="C1027" s="2">
         <v>40</v>
       </c>
@@ -20076,7 +20082,7 @@
       <c r="A1028" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1028" s="8"/>
+      <c r="B1028" s="10"/>
       <c r="C1028" s="2">
         <v>41</v>
       </c>
@@ -20088,7 +20094,7 @@
       <c r="A1029" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1029" s="8"/>
+      <c r="B1029" s="10"/>
       <c r="C1029" s="2">
         <v>42</v>
       </c>
@@ -20100,7 +20106,7 @@
       <c r="A1030" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1030" s="8"/>
+      <c r="B1030" s="10"/>
       <c r="C1030" s="2">
         <v>44</v>
       </c>
@@ -20112,7 +20118,7 @@
       <c r="A1031" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1031" s="8"/>
+      <c r="B1031" s="10"/>
       <c r="C1031" s="2">
         <v>45</v>
       </c>
@@ -20124,7 +20130,7 @@
       <c r="A1032" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1032" s="8"/>
+      <c r="B1032" s="10"/>
       <c r="C1032" s="2">
         <v>46</v>
       </c>
@@ -20136,7 +20142,7 @@
       <c r="A1033" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1033" s="8"/>
+      <c r="B1033" s="10"/>
       <c r="C1033" s="2">
         <v>47</v>
       </c>
@@ -20148,7 +20154,7 @@
       <c r="A1034" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1034" s="8"/>
+      <c r="B1034" s="10"/>
       <c r="C1034" s="2">
         <v>48</v>
       </c>
@@ -20160,7 +20166,7 @@
       <c r="A1035" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1035" s="8"/>
+      <c r="B1035" s="10"/>
       <c r="C1035" s="2">
         <v>49</v>
       </c>
@@ -20172,7 +20178,7 @@
       <c r="A1036" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1036" s="8"/>
+      <c r="B1036" s="10"/>
       <c r="C1036" s="2">
         <v>50</v>
       </c>
@@ -20184,7 +20190,7 @@
       <c r="A1037" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1037" s="8"/>
+      <c r="B1037" s="10"/>
       <c r="C1037" s="2">
         <v>51</v>
       </c>
@@ -20196,7 +20202,7 @@
       <c r="A1038" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1038" s="8"/>
+      <c r="B1038" s="10"/>
       <c r="C1038" s="2">
         <v>53</v>
       </c>
@@ -20208,7 +20214,7 @@
       <c r="A1039" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1039" s="8"/>
+      <c r="B1039" s="10"/>
       <c r="C1039" s="2">
         <v>54</v>
       </c>
@@ -20220,7 +20226,7 @@
       <c r="A1040" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1040" s="8"/>
+      <c r="B1040" s="10"/>
       <c r="C1040" s="2">
         <v>55</v>
       </c>
@@ -20232,7 +20238,7 @@
       <c r="A1041" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1041" s="8"/>
+      <c r="B1041" s="10"/>
       <c r="C1041" s="2">
         <v>56</v>
       </c>
@@ -33716,645 +33722,6 @@
     </row>
   </sheetData>
   <mergeCells count="654">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B109:B114"/>
-    <mergeCell ref="B115:B200"/>
-    <mergeCell ref="B201:B253"/>
-    <mergeCell ref="B254:B269"/>
-    <mergeCell ref="B270:B287"/>
-    <mergeCell ref="B288:B301"/>
-    <mergeCell ref="B302:B333"/>
-    <mergeCell ref="B334:B337"/>
-    <mergeCell ref="B338:B341"/>
-    <mergeCell ref="B342:B346"/>
-    <mergeCell ref="B347:B351"/>
-    <mergeCell ref="B352:B355"/>
-    <mergeCell ref="B356:B359"/>
-    <mergeCell ref="B360:B363"/>
-    <mergeCell ref="B364:B367"/>
-    <mergeCell ref="B368:B371"/>
-    <mergeCell ref="B372:B378"/>
-    <mergeCell ref="B379:B385"/>
-    <mergeCell ref="B386:B392"/>
-    <mergeCell ref="B393:B399"/>
-    <mergeCell ref="B400:B404"/>
-    <mergeCell ref="B405:B407"/>
-    <mergeCell ref="B408:B410"/>
-    <mergeCell ref="B411:B415"/>
-    <mergeCell ref="B416:B418"/>
-    <mergeCell ref="B419:B421"/>
-    <mergeCell ref="B422:B424"/>
-    <mergeCell ref="B425:B430"/>
-    <mergeCell ref="B431:B436"/>
-    <mergeCell ref="B437:B442"/>
-    <mergeCell ref="B443:B450"/>
-    <mergeCell ref="B451:B456"/>
-    <mergeCell ref="B457:B462"/>
-    <mergeCell ref="B463:B468"/>
-    <mergeCell ref="B469:B474"/>
-    <mergeCell ref="B475:B480"/>
-    <mergeCell ref="B481:B486"/>
-    <mergeCell ref="B487:B492"/>
-    <mergeCell ref="B493:B498"/>
-    <mergeCell ref="B499:B504"/>
-    <mergeCell ref="B505:B510"/>
-    <mergeCell ref="B511:B516"/>
-    <mergeCell ref="B517:B522"/>
-    <mergeCell ref="B523:B528"/>
-    <mergeCell ref="B529:B534"/>
-    <mergeCell ref="B535:B540"/>
-    <mergeCell ref="B541:B546"/>
-    <mergeCell ref="B547:B552"/>
-    <mergeCell ref="B553:B558"/>
-    <mergeCell ref="B559:B564"/>
-    <mergeCell ref="B565:B568"/>
-    <mergeCell ref="B569:B571"/>
-    <mergeCell ref="B572:B575"/>
-    <mergeCell ref="B576:B579"/>
-    <mergeCell ref="B580:B582"/>
-    <mergeCell ref="B583:B585"/>
-    <mergeCell ref="B586:B588"/>
-    <mergeCell ref="B589:B591"/>
-    <mergeCell ref="B592:B605"/>
-    <mergeCell ref="B606:B637"/>
-    <mergeCell ref="B638:B641"/>
-    <mergeCell ref="B642:B646"/>
-    <mergeCell ref="B647:B651"/>
-    <mergeCell ref="B652:B658"/>
-    <mergeCell ref="B659:B665"/>
-    <mergeCell ref="B666:B670"/>
-    <mergeCell ref="B671:B675"/>
-    <mergeCell ref="B676:B680"/>
-    <mergeCell ref="B681:B685"/>
-    <mergeCell ref="B686:B691"/>
-    <mergeCell ref="B692:B698"/>
-    <mergeCell ref="B699:B712"/>
-    <mergeCell ref="B713:B744"/>
-    <mergeCell ref="B745:B746"/>
-    <mergeCell ref="B747:B750"/>
-    <mergeCell ref="B751:B755"/>
-    <mergeCell ref="B756:B761"/>
-    <mergeCell ref="B762:B767"/>
-    <mergeCell ref="B768:B776"/>
-    <mergeCell ref="B777:B779"/>
-    <mergeCell ref="B780:B782"/>
-    <mergeCell ref="B783:B785"/>
-    <mergeCell ref="B786:B788"/>
-    <mergeCell ref="B789:B791"/>
-    <mergeCell ref="B792:B794"/>
-    <mergeCell ref="B795:B797"/>
-    <mergeCell ref="B798:B800"/>
-    <mergeCell ref="B801:B803"/>
-    <mergeCell ref="B804:B806"/>
-    <mergeCell ref="B807:B809"/>
-    <mergeCell ref="B810:B812"/>
-    <mergeCell ref="B813:B815"/>
-    <mergeCell ref="B816:B820"/>
-    <mergeCell ref="B821:B825"/>
-    <mergeCell ref="B826:B830"/>
-    <mergeCell ref="B831:B835"/>
-    <mergeCell ref="B836:B843"/>
-    <mergeCell ref="B844:B846"/>
-    <mergeCell ref="B847:B852"/>
-    <mergeCell ref="B853:B855"/>
-    <mergeCell ref="B856:B860"/>
-    <mergeCell ref="B861:B864"/>
-    <mergeCell ref="B865:B870"/>
-    <mergeCell ref="B871:B874"/>
-    <mergeCell ref="B875:B879"/>
-    <mergeCell ref="B880:B882"/>
-    <mergeCell ref="B883:B885"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="B888:B892"/>
-    <mergeCell ref="B893:B895"/>
-    <mergeCell ref="B896:B901"/>
-    <mergeCell ref="B902:B905"/>
-    <mergeCell ref="B906:B909"/>
-    <mergeCell ref="B910:B916"/>
-    <mergeCell ref="B917:B925"/>
-    <mergeCell ref="B926:B929"/>
-    <mergeCell ref="B930:B935"/>
-    <mergeCell ref="B936:B942"/>
-    <mergeCell ref="B943:B955"/>
-    <mergeCell ref="B956:B963"/>
-    <mergeCell ref="B964:B971"/>
-    <mergeCell ref="B972:B979"/>
-    <mergeCell ref="B980:B984"/>
-    <mergeCell ref="B985:B990"/>
-    <mergeCell ref="B991:B1041"/>
-    <mergeCell ref="B1042:B1076"/>
-    <mergeCell ref="B1077:B1078"/>
-    <mergeCell ref="B1079:B1080"/>
-    <mergeCell ref="B1081:B1082"/>
-    <mergeCell ref="B1083:B1084"/>
-    <mergeCell ref="B1085:B1086"/>
-    <mergeCell ref="B1087:B1088"/>
-    <mergeCell ref="B1089:B1090"/>
-    <mergeCell ref="B1091:B1092"/>
-    <mergeCell ref="B1093:B1094"/>
-    <mergeCell ref="B1095:B1096"/>
-    <mergeCell ref="B1097:B1098"/>
-    <mergeCell ref="B1099:B1100"/>
-    <mergeCell ref="B1101:B1102"/>
-    <mergeCell ref="B1103:B1104"/>
-    <mergeCell ref="B1105:B1106"/>
-    <mergeCell ref="B1107:B1108"/>
-    <mergeCell ref="B1109:B1110"/>
-    <mergeCell ref="B1111:B1112"/>
-    <mergeCell ref="B1113:B1114"/>
-    <mergeCell ref="B1115:B1116"/>
-    <mergeCell ref="B1117:B1118"/>
-    <mergeCell ref="B1119:B1120"/>
-    <mergeCell ref="B1121:B1122"/>
-    <mergeCell ref="B1123:B1124"/>
-    <mergeCell ref="B1125:B1126"/>
-    <mergeCell ref="B1127:B1128"/>
-    <mergeCell ref="B1129:B1130"/>
-    <mergeCell ref="B1131:B1132"/>
-    <mergeCell ref="B1133:B1134"/>
-    <mergeCell ref="B1135:B1136"/>
-    <mergeCell ref="B1137:B1138"/>
-    <mergeCell ref="B1139:B1140"/>
-    <mergeCell ref="B1141:B1142"/>
-    <mergeCell ref="B1143:B1144"/>
-    <mergeCell ref="B1145:B1146"/>
-    <mergeCell ref="B1147:B1148"/>
-    <mergeCell ref="B1149:B1150"/>
-    <mergeCell ref="B1151:B1152"/>
-    <mergeCell ref="B1153:B1154"/>
-    <mergeCell ref="B1155:B1156"/>
-    <mergeCell ref="B1157:B1158"/>
-    <mergeCell ref="B1159:B1160"/>
-    <mergeCell ref="B1161:B1162"/>
-    <mergeCell ref="B1163:B1164"/>
-    <mergeCell ref="B1165:B1166"/>
-    <mergeCell ref="B1167:B1168"/>
-    <mergeCell ref="B1169:B1170"/>
-    <mergeCell ref="B1171:B1172"/>
-    <mergeCell ref="B1173:B1174"/>
-    <mergeCell ref="B1175:B1176"/>
-    <mergeCell ref="B1177:B1178"/>
-    <mergeCell ref="B1179:B1180"/>
-    <mergeCell ref="B1181:B1182"/>
-    <mergeCell ref="B1183:B1184"/>
-    <mergeCell ref="B1185:B1186"/>
-    <mergeCell ref="B1187:B1188"/>
-    <mergeCell ref="B1189:B1190"/>
-    <mergeCell ref="B1191:B1192"/>
-    <mergeCell ref="B1193:B1194"/>
-    <mergeCell ref="B1195:B1196"/>
-    <mergeCell ref="B1197:B1198"/>
-    <mergeCell ref="B1199:B1200"/>
-    <mergeCell ref="B1201:B1202"/>
-    <mergeCell ref="B1203:B1204"/>
-    <mergeCell ref="B1205:B1206"/>
-    <mergeCell ref="B1207:B1208"/>
-    <mergeCell ref="B1209:B1210"/>
-    <mergeCell ref="B1211:B1212"/>
-    <mergeCell ref="B1213:B1214"/>
-    <mergeCell ref="B1215:B1216"/>
-    <mergeCell ref="B1217:B1218"/>
-    <mergeCell ref="B1219:B1220"/>
-    <mergeCell ref="B1221:B1222"/>
-    <mergeCell ref="B1223:B1224"/>
-    <mergeCell ref="B1225:B1226"/>
-    <mergeCell ref="B1227:B1228"/>
-    <mergeCell ref="B1229:B1230"/>
-    <mergeCell ref="B1231:B1232"/>
-    <mergeCell ref="B1233:B1234"/>
-    <mergeCell ref="B1235:B1236"/>
-    <mergeCell ref="B1237:B1238"/>
-    <mergeCell ref="B1239:B1240"/>
-    <mergeCell ref="B1241:B1242"/>
-    <mergeCell ref="B1243:B1244"/>
-    <mergeCell ref="B1245:B1246"/>
-    <mergeCell ref="B1247:B1248"/>
-    <mergeCell ref="B1249:B1250"/>
-    <mergeCell ref="B1251:B1252"/>
-    <mergeCell ref="B1253:B1254"/>
-    <mergeCell ref="B1255:B1256"/>
-    <mergeCell ref="B1257:B1258"/>
-    <mergeCell ref="B1259:B1260"/>
-    <mergeCell ref="B1261:B1262"/>
-    <mergeCell ref="B1263:B1264"/>
-    <mergeCell ref="B1265:B1266"/>
-    <mergeCell ref="B1267:B1268"/>
-    <mergeCell ref="B1269:B1270"/>
-    <mergeCell ref="B1271:B1272"/>
-    <mergeCell ref="B1273:B1274"/>
-    <mergeCell ref="B1275:B1276"/>
-    <mergeCell ref="B1277:B1278"/>
-    <mergeCell ref="B1279:B1280"/>
-    <mergeCell ref="B1281:B1282"/>
-    <mergeCell ref="B1283:B1284"/>
-    <mergeCell ref="B1285:B1286"/>
-    <mergeCell ref="B1287:B1288"/>
-    <mergeCell ref="B1289:B1290"/>
-    <mergeCell ref="B1291:B1292"/>
-    <mergeCell ref="B1293:B1294"/>
-    <mergeCell ref="B1295:B1296"/>
-    <mergeCell ref="B1297:B1298"/>
-    <mergeCell ref="B1299:B1300"/>
-    <mergeCell ref="B1301:B1302"/>
-    <mergeCell ref="B1303:B1304"/>
-    <mergeCell ref="B1305:B1306"/>
-    <mergeCell ref="B1307:B1308"/>
-    <mergeCell ref="B1309:B1310"/>
-    <mergeCell ref="B1311:B1312"/>
-    <mergeCell ref="B1313:B1314"/>
-    <mergeCell ref="B1315:B1316"/>
-    <mergeCell ref="B1317:B1318"/>
-    <mergeCell ref="B1319:B1320"/>
-    <mergeCell ref="B1321:B1322"/>
-    <mergeCell ref="B1323:B1324"/>
-    <mergeCell ref="B1325:B1326"/>
-    <mergeCell ref="B1327:B1328"/>
-    <mergeCell ref="B1329:B1330"/>
-    <mergeCell ref="B1331:B1332"/>
-    <mergeCell ref="B1333:B1334"/>
-    <mergeCell ref="B1335:B1336"/>
-    <mergeCell ref="B1337:B1338"/>
-    <mergeCell ref="B1339:B1340"/>
-    <mergeCell ref="B1341:B1342"/>
-    <mergeCell ref="B1343:B1344"/>
-    <mergeCell ref="B1345:B1346"/>
-    <mergeCell ref="B1347:B1348"/>
-    <mergeCell ref="B1349:B1350"/>
-    <mergeCell ref="B1351:B1352"/>
-    <mergeCell ref="B1353:B1354"/>
-    <mergeCell ref="B1355:B1356"/>
-    <mergeCell ref="B1357:B1358"/>
-    <mergeCell ref="B1359:B1360"/>
-    <mergeCell ref="B1361:B1362"/>
-    <mergeCell ref="B1363:B1364"/>
-    <mergeCell ref="B1365:B1366"/>
-    <mergeCell ref="B1367:B1368"/>
-    <mergeCell ref="B1369:B1370"/>
-    <mergeCell ref="B1371:B1372"/>
-    <mergeCell ref="B1373:B1374"/>
-    <mergeCell ref="B1375:B1376"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B1379:B1380"/>
-    <mergeCell ref="B1381:B1382"/>
-    <mergeCell ref="B1383:B1384"/>
-    <mergeCell ref="B1385:B1386"/>
-    <mergeCell ref="B1387:B1388"/>
-    <mergeCell ref="B1389:B1390"/>
-    <mergeCell ref="B1391:B1392"/>
-    <mergeCell ref="B1393:B1394"/>
-    <mergeCell ref="B1395:B1396"/>
-    <mergeCell ref="B1397:B1398"/>
-    <mergeCell ref="B1399:B1400"/>
-    <mergeCell ref="B1401:B1402"/>
-    <mergeCell ref="B1403:B1404"/>
-    <mergeCell ref="B1405:B1406"/>
-    <mergeCell ref="B1407:B1408"/>
-    <mergeCell ref="B1409:B1410"/>
-    <mergeCell ref="B1411:B1412"/>
-    <mergeCell ref="B1413:B1414"/>
-    <mergeCell ref="B1415:B1416"/>
-    <mergeCell ref="B1417:B1418"/>
-    <mergeCell ref="B1419:B1420"/>
-    <mergeCell ref="B1421:B1422"/>
-    <mergeCell ref="B1423:B1424"/>
-    <mergeCell ref="B1425:B1426"/>
-    <mergeCell ref="B1427:B1428"/>
-    <mergeCell ref="B1429:B1430"/>
-    <mergeCell ref="B1431:B1432"/>
-    <mergeCell ref="B1433:B1434"/>
-    <mergeCell ref="B1435:B1436"/>
-    <mergeCell ref="B1437:B1438"/>
-    <mergeCell ref="B1439:B1440"/>
-    <mergeCell ref="B1441:B1442"/>
-    <mergeCell ref="B1443:B1444"/>
-    <mergeCell ref="B1445:B1446"/>
-    <mergeCell ref="B1447:B1448"/>
-    <mergeCell ref="B1449:B1450"/>
-    <mergeCell ref="B1451:B1452"/>
-    <mergeCell ref="B1453:B1454"/>
-    <mergeCell ref="B1455:B1456"/>
-    <mergeCell ref="B1457:B1458"/>
-    <mergeCell ref="B1459:B1460"/>
-    <mergeCell ref="B1461:B1462"/>
-    <mergeCell ref="B1463:B1464"/>
-    <mergeCell ref="B1465:B1466"/>
-    <mergeCell ref="B1467:B1468"/>
-    <mergeCell ref="B1469:B1470"/>
-    <mergeCell ref="B1471:B1472"/>
-    <mergeCell ref="B1473:B1474"/>
-    <mergeCell ref="B1475:B1476"/>
-    <mergeCell ref="B1477:B1478"/>
-    <mergeCell ref="B1479:B1480"/>
-    <mergeCell ref="B1481:B1482"/>
-    <mergeCell ref="B1483:B1484"/>
-    <mergeCell ref="B1485:B1486"/>
-    <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="B1489:B1490"/>
-    <mergeCell ref="B1491:B1492"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1495:B1496"/>
-    <mergeCell ref="B1497:B1498"/>
-    <mergeCell ref="B1499:B1500"/>
-    <mergeCell ref="B1501:B1502"/>
-    <mergeCell ref="B1503:B1504"/>
-    <mergeCell ref="B1505:B1506"/>
-    <mergeCell ref="B1507:B1508"/>
-    <mergeCell ref="B1509:B1510"/>
-    <mergeCell ref="B1511:B1512"/>
-    <mergeCell ref="B1513:B1514"/>
-    <mergeCell ref="B1515:B1516"/>
-    <mergeCell ref="B1517:B1518"/>
-    <mergeCell ref="B1519:B1520"/>
-    <mergeCell ref="B1521:B1522"/>
-    <mergeCell ref="B1523:B1524"/>
-    <mergeCell ref="B1525:B1526"/>
-    <mergeCell ref="B1527:B1528"/>
-    <mergeCell ref="B1529:B1530"/>
-    <mergeCell ref="B1531:B1532"/>
-    <mergeCell ref="B1533:B1534"/>
-    <mergeCell ref="B1535:B1536"/>
-    <mergeCell ref="B1537:B1538"/>
-    <mergeCell ref="B1539:B1540"/>
-    <mergeCell ref="B1541:B1542"/>
-    <mergeCell ref="B1543:B1544"/>
-    <mergeCell ref="B1545:B1546"/>
-    <mergeCell ref="B1547:B1548"/>
-    <mergeCell ref="B1549:B1550"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B1553:B1554"/>
-    <mergeCell ref="B1555:B1556"/>
-    <mergeCell ref="B1557:B1558"/>
-    <mergeCell ref="B1559:B1560"/>
-    <mergeCell ref="B1561:B1562"/>
-    <mergeCell ref="B1563:B1564"/>
-    <mergeCell ref="B1565:B1566"/>
-    <mergeCell ref="B1567:B1568"/>
-    <mergeCell ref="B1569:B1570"/>
-    <mergeCell ref="B1571:B1572"/>
-    <mergeCell ref="B1573:B1574"/>
-    <mergeCell ref="B1575:B1576"/>
-    <mergeCell ref="B1577:B1578"/>
-    <mergeCell ref="B1579:B1580"/>
-    <mergeCell ref="B1581:B1582"/>
-    <mergeCell ref="B1583:B1584"/>
-    <mergeCell ref="B1585:B1586"/>
-    <mergeCell ref="B1587:B1588"/>
-    <mergeCell ref="B1589:B1590"/>
-    <mergeCell ref="B1591:B1592"/>
-    <mergeCell ref="B1593:B1594"/>
-    <mergeCell ref="B1595:B1596"/>
-    <mergeCell ref="B1597:B1598"/>
-    <mergeCell ref="B1599:B1600"/>
-    <mergeCell ref="B1601:B1602"/>
-    <mergeCell ref="B1603:B1604"/>
-    <mergeCell ref="B1605:B1606"/>
-    <mergeCell ref="B1607:B1608"/>
-    <mergeCell ref="B1609:B1610"/>
-    <mergeCell ref="B1611:B1612"/>
-    <mergeCell ref="B1613:B1614"/>
-    <mergeCell ref="B1615:B1616"/>
-    <mergeCell ref="B1617:B1618"/>
-    <mergeCell ref="B1619:B1620"/>
-    <mergeCell ref="B1621:B1622"/>
-    <mergeCell ref="B1623:B1624"/>
-    <mergeCell ref="B1625:B1626"/>
-    <mergeCell ref="B1627:B1628"/>
-    <mergeCell ref="B1629:B1630"/>
-    <mergeCell ref="B1631:B1632"/>
-    <mergeCell ref="B1633:B1634"/>
-    <mergeCell ref="B1635:B1636"/>
-    <mergeCell ref="B1637:B1638"/>
-    <mergeCell ref="B1639:B1640"/>
-    <mergeCell ref="B1641:B1642"/>
-    <mergeCell ref="B1643:B1644"/>
-    <mergeCell ref="B1645:B1646"/>
-    <mergeCell ref="B1647:B1648"/>
-    <mergeCell ref="B1649:B1650"/>
-    <mergeCell ref="B1651:B1652"/>
-    <mergeCell ref="B1653:B1654"/>
-    <mergeCell ref="B1655:B1656"/>
-    <mergeCell ref="B1657:B1658"/>
-    <mergeCell ref="B1659:B1660"/>
-    <mergeCell ref="B1661:B1662"/>
-    <mergeCell ref="B1663:B1664"/>
-    <mergeCell ref="B1665:B1666"/>
-    <mergeCell ref="B1667:B1668"/>
-    <mergeCell ref="B1669:B1670"/>
-    <mergeCell ref="B1671:B1672"/>
-    <mergeCell ref="B1673:B1674"/>
-    <mergeCell ref="B1675:B1676"/>
-    <mergeCell ref="B1677:B1678"/>
-    <mergeCell ref="B1679:B1680"/>
-    <mergeCell ref="B1681:B1682"/>
-    <mergeCell ref="B1683:B1684"/>
-    <mergeCell ref="B1685:B1686"/>
-    <mergeCell ref="B1687:B1688"/>
-    <mergeCell ref="B1689:B1690"/>
-    <mergeCell ref="B1691:B1692"/>
-    <mergeCell ref="B1693:B1694"/>
-    <mergeCell ref="B1695:B1696"/>
-    <mergeCell ref="B1697:B1698"/>
-    <mergeCell ref="B1699:B1700"/>
-    <mergeCell ref="B1701:B1702"/>
-    <mergeCell ref="B1703:B1704"/>
-    <mergeCell ref="B1705:B1706"/>
-    <mergeCell ref="B1707:B1708"/>
-    <mergeCell ref="B1709:B1710"/>
-    <mergeCell ref="B1711:B1712"/>
-    <mergeCell ref="B1713:B1714"/>
-    <mergeCell ref="B1715:B1716"/>
-    <mergeCell ref="B1717:B1718"/>
-    <mergeCell ref="B1719:B1720"/>
-    <mergeCell ref="B1721:B1722"/>
-    <mergeCell ref="B1723:B1724"/>
-    <mergeCell ref="B1725:B1726"/>
-    <mergeCell ref="B1727:B1728"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="B1731:B1732"/>
-    <mergeCell ref="B1733:B1734"/>
-    <mergeCell ref="B1735:B1736"/>
-    <mergeCell ref="B1737:B1738"/>
-    <mergeCell ref="B1739:B1740"/>
-    <mergeCell ref="B1741:B1742"/>
-    <mergeCell ref="B1743:B1744"/>
-    <mergeCell ref="B1745:B1746"/>
-    <mergeCell ref="B1747:B1748"/>
-    <mergeCell ref="B1749:B1750"/>
-    <mergeCell ref="B1751:B1752"/>
-    <mergeCell ref="B1753:B1754"/>
-    <mergeCell ref="B1755:B1756"/>
-    <mergeCell ref="B1757:B1758"/>
-    <mergeCell ref="B1759:B1760"/>
-    <mergeCell ref="B1761:B1762"/>
-    <mergeCell ref="B1763:B1764"/>
-    <mergeCell ref="B1765:B1766"/>
-    <mergeCell ref="B1767:B1768"/>
-    <mergeCell ref="B1769:B1770"/>
-    <mergeCell ref="B1771:B1772"/>
-    <mergeCell ref="B1773:B1774"/>
-    <mergeCell ref="B1775:B1776"/>
-    <mergeCell ref="B1777:B1778"/>
-    <mergeCell ref="B1779:B1780"/>
-    <mergeCell ref="B1781:B1782"/>
-    <mergeCell ref="B1783:B1784"/>
-    <mergeCell ref="B1785:B1786"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B1789:B1790"/>
-    <mergeCell ref="B1791:B1792"/>
-    <mergeCell ref="B1793:B1794"/>
-    <mergeCell ref="B1795:B1796"/>
-    <mergeCell ref="B1797:B1798"/>
-    <mergeCell ref="B1799:B1800"/>
-    <mergeCell ref="B1801:B1802"/>
-    <mergeCell ref="B1803:B1804"/>
-    <mergeCell ref="B1805:B1806"/>
-    <mergeCell ref="B1807:B1808"/>
-    <mergeCell ref="B1809:B1810"/>
-    <mergeCell ref="B1811:B1812"/>
-    <mergeCell ref="B1813:B1814"/>
-    <mergeCell ref="B1815:B1816"/>
-    <mergeCell ref="B1817:B1818"/>
-    <mergeCell ref="B1819:B1820"/>
-    <mergeCell ref="B1821:B1822"/>
-    <mergeCell ref="B1823:B1824"/>
-    <mergeCell ref="B1825:B1826"/>
-    <mergeCell ref="B1827:B1828"/>
-    <mergeCell ref="B1829:B1830"/>
-    <mergeCell ref="B1831:B1832"/>
-    <mergeCell ref="B1833:B1834"/>
-    <mergeCell ref="B1835:B1836"/>
-    <mergeCell ref="B1837:B1838"/>
-    <mergeCell ref="B1839:B1840"/>
-    <mergeCell ref="B1841:B1842"/>
-    <mergeCell ref="B1843:B1844"/>
-    <mergeCell ref="B1845:B1846"/>
-    <mergeCell ref="B1847:B1848"/>
-    <mergeCell ref="B1849:B1850"/>
-    <mergeCell ref="B1851:B1852"/>
-    <mergeCell ref="B1853:B1854"/>
-    <mergeCell ref="B1855:B1856"/>
-    <mergeCell ref="B1857:B1858"/>
-    <mergeCell ref="B1859:B1860"/>
-    <mergeCell ref="B1861:B1862"/>
-    <mergeCell ref="B1863:B1864"/>
-    <mergeCell ref="B1865:B1866"/>
-    <mergeCell ref="B1867:B1868"/>
-    <mergeCell ref="B1869:B1870"/>
-    <mergeCell ref="B1871:B1872"/>
-    <mergeCell ref="B1873:B1874"/>
-    <mergeCell ref="B1875:B1876"/>
-    <mergeCell ref="B1877:B1878"/>
-    <mergeCell ref="B1879:B1880"/>
-    <mergeCell ref="B1881:B1882"/>
-    <mergeCell ref="B1883:B1884"/>
-    <mergeCell ref="B1885:B1886"/>
-    <mergeCell ref="B1887:B1888"/>
-    <mergeCell ref="B1889:B1890"/>
-    <mergeCell ref="B1891:B1892"/>
-    <mergeCell ref="B1893:B1894"/>
-    <mergeCell ref="B1895:B1896"/>
-    <mergeCell ref="B1897:B1898"/>
-    <mergeCell ref="B1899:B1900"/>
-    <mergeCell ref="B1901:B1902"/>
-    <mergeCell ref="B1903:B1904"/>
-    <mergeCell ref="B1905:B1906"/>
-    <mergeCell ref="B1907:B1908"/>
-    <mergeCell ref="B1909:B1910"/>
-    <mergeCell ref="B1911:B1912"/>
-    <mergeCell ref="B1913:B1914"/>
-    <mergeCell ref="B1915:B1916"/>
-    <mergeCell ref="B1917:B1918"/>
-    <mergeCell ref="B1919:B1920"/>
-    <mergeCell ref="B1921:B1922"/>
-    <mergeCell ref="B1923:B1924"/>
-    <mergeCell ref="B1925:B1926"/>
-    <mergeCell ref="B1927:B1928"/>
-    <mergeCell ref="B1929:B1930"/>
-    <mergeCell ref="B1931:B1932"/>
-    <mergeCell ref="B1933:B1934"/>
-    <mergeCell ref="B1935:B1936"/>
-    <mergeCell ref="B1937:B1938"/>
-    <mergeCell ref="B1939:B1940"/>
-    <mergeCell ref="B1941:B1942"/>
-    <mergeCell ref="B1943:B1944"/>
-    <mergeCell ref="B1945:B1946"/>
-    <mergeCell ref="B1947:B1948"/>
-    <mergeCell ref="B1949:B1950"/>
-    <mergeCell ref="B1951:B1952"/>
-    <mergeCell ref="B1953:B1954"/>
-    <mergeCell ref="B1955:B1956"/>
-    <mergeCell ref="B1957:B1958"/>
-    <mergeCell ref="B1959:B1960"/>
-    <mergeCell ref="B1961:B1962"/>
-    <mergeCell ref="B1963:B1964"/>
-    <mergeCell ref="B1965:B1966"/>
-    <mergeCell ref="B1967:B1968"/>
-    <mergeCell ref="B1969:B1970"/>
-    <mergeCell ref="B1971:B1972"/>
-    <mergeCell ref="B1973:B1974"/>
-    <mergeCell ref="B1975:B1976"/>
-    <mergeCell ref="B1977:B1978"/>
-    <mergeCell ref="B1979:B1980"/>
-    <mergeCell ref="B1981:B1982"/>
-    <mergeCell ref="B1983:B1984"/>
-    <mergeCell ref="B1985:B1986"/>
-    <mergeCell ref="B1987:B1988"/>
-    <mergeCell ref="B1989:B1990"/>
-    <mergeCell ref="B1991:B1992"/>
-    <mergeCell ref="B1993:B1994"/>
-    <mergeCell ref="B1995:B1996"/>
-    <mergeCell ref="B1997:B1998"/>
-    <mergeCell ref="B1999:B2000"/>
-    <mergeCell ref="B2001:B2002"/>
-    <mergeCell ref="B2003:B2004"/>
-    <mergeCell ref="B2005:B2006"/>
-    <mergeCell ref="B2007:B2008"/>
-    <mergeCell ref="B2009:B2010"/>
-    <mergeCell ref="B2011:B2012"/>
-    <mergeCell ref="B2013:B2014"/>
-    <mergeCell ref="B2015:B2016"/>
-    <mergeCell ref="B2017:B2018"/>
-    <mergeCell ref="B2019:B2020"/>
-    <mergeCell ref="B2021:B2022"/>
-    <mergeCell ref="B2023:B2024"/>
-    <mergeCell ref="B2025:B2026"/>
-    <mergeCell ref="B2027:B2028"/>
-    <mergeCell ref="B2029:B2030"/>
-    <mergeCell ref="B2031:B2032"/>
-    <mergeCell ref="B2033:B2034"/>
-    <mergeCell ref="B2035:B2036"/>
-    <mergeCell ref="B2037:B2038"/>
-    <mergeCell ref="B2039:B2040"/>
-    <mergeCell ref="B2041:B2042"/>
-    <mergeCell ref="B2043:B2044"/>
-    <mergeCell ref="B2045:B2046"/>
-    <mergeCell ref="B2047:B2048"/>
-    <mergeCell ref="B2049:B2050"/>
     <mergeCell ref="B2069:B2070"/>
     <mergeCell ref="B2071:B2072"/>
     <mergeCell ref="B2073:B2074"/>
@@ -34370,6 +33737,645 @@
     <mergeCell ref="B2063:B2064"/>
     <mergeCell ref="B2065:B2066"/>
     <mergeCell ref="B2067:B2068"/>
+    <mergeCell ref="B2033:B2034"/>
+    <mergeCell ref="B2035:B2036"/>
+    <mergeCell ref="B2037:B2038"/>
+    <mergeCell ref="B2039:B2040"/>
+    <mergeCell ref="B2041:B2042"/>
+    <mergeCell ref="B2043:B2044"/>
+    <mergeCell ref="B2045:B2046"/>
+    <mergeCell ref="B2047:B2048"/>
+    <mergeCell ref="B2049:B2050"/>
+    <mergeCell ref="B2015:B2016"/>
+    <mergeCell ref="B2017:B2018"/>
+    <mergeCell ref="B2019:B2020"/>
+    <mergeCell ref="B2021:B2022"/>
+    <mergeCell ref="B2023:B2024"/>
+    <mergeCell ref="B2025:B2026"/>
+    <mergeCell ref="B2027:B2028"/>
+    <mergeCell ref="B2029:B2030"/>
+    <mergeCell ref="B2031:B2032"/>
+    <mergeCell ref="B1997:B1998"/>
+    <mergeCell ref="B1999:B2000"/>
+    <mergeCell ref="B2001:B2002"/>
+    <mergeCell ref="B2003:B2004"/>
+    <mergeCell ref="B2005:B2006"/>
+    <mergeCell ref="B2007:B2008"/>
+    <mergeCell ref="B2009:B2010"/>
+    <mergeCell ref="B2011:B2012"/>
+    <mergeCell ref="B2013:B2014"/>
+    <mergeCell ref="B1979:B1980"/>
+    <mergeCell ref="B1981:B1982"/>
+    <mergeCell ref="B1983:B1984"/>
+    <mergeCell ref="B1985:B1986"/>
+    <mergeCell ref="B1987:B1988"/>
+    <mergeCell ref="B1989:B1990"/>
+    <mergeCell ref="B1991:B1992"/>
+    <mergeCell ref="B1993:B1994"/>
+    <mergeCell ref="B1995:B1996"/>
+    <mergeCell ref="B1961:B1962"/>
+    <mergeCell ref="B1963:B1964"/>
+    <mergeCell ref="B1965:B1966"/>
+    <mergeCell ref="B1967:B1968"/>
+    <mergeCell ref="B1969:B1970"/>
+    <mergeCell ref="B1971:B1972"/>
+    <mergeCell ref="B1973:B1974"/>
+    <mergeCell ref="B1975:B1976"/>
+    <mergeCell ref="B1977:B1978"/>
+    <mergeCell ref="B1943:B1944"/>
+    <mergeCell ref="B1945:B1946"/>
+    <mergeCell ref="B1947:B1948"/>
+    <mergeCell ref="B1949:B1950"/>
+    <mergeCell ref="B1951:B1952"/>
+    <mergeCell ref="B1953:B1954"/>
+    <mergeCell ref="B1955:B1956"/>
+    <mergeCell ref="B1957:B1958"/>
+    <mergeCell ref="B1959:B1960"/>
+    <mergeCell ref="B1925:B1926"/>
+    <mergeCell ref="B1927:B1928"/>
+    <mergeCell ref="B1929:B1930"/>
+    <mergeCell ref="B1931:B1932"/>
+    <mergeCell ref="B1933:B1934"/>
+    <mergeCell ref="B1935:B1936"/>
+    <mergeCell ref="B1937:B1938"/>
+    <mergeCell ref="B1939:B1940"/>
+    <mergeCell ref="B1941:B1942"/>
+    <mergeCell ref="B1907:B1908"/>
+    <mergeCell ref="B1909:B1910"/>
+    <mergeCell ref="B1911:B1912"/>
+    <mergeCell ref="B1913:B1914"/>
+    <mergeCell ref="B1915:B1916"/>
+    <mergeCell ref="B1917:B1918"/>
+    <mergeCell ref="B1919:B1920"/>
+    <mergeCell ref="B1921:B1922"/>
+    <mergeCell ref="B1923:B1924"/>
+    <mergeCell ref="B1889:B1890"/>
+    <mergeCell ref="B1891:B1892"/>
+    <mergeCell ref="B1893:B1894"/>
+    <mergeCell ref="B1895:B1896"/>
+    <mergeCell ref="B1897:B1898"/>
+    <mergeCell ref="B1899:B1900"/>
+    <mergeCell ref="B1901:B1902"/>
+    <mergeCell ref="B1903:B1904"/>
+    <mergeCell ref="B1905:B1906"/>
+    <mergeCell ref="B1871:B1872"/>
+    <mergeCell ref="B1873:B1874"/>
+    <mergeCell ref="B1875:B1876"/>
+    <mergeCell ref="B1877:B1878"/>
+    <mergeCell ref="B1879:B1880"/>
+    <mergeCell ref="B1881:B1882"/>
+    <mergeCell ref="B1883:B1884"/>
+    <mergeCell ref="B1885:B1886"/>
+    <mergeCell ref="B1887:B1888"/>
+    <mergeCell ref="B1853:B1854"/>
+    <mergeCell ref="B1855:B1856"/>
+    <mergeCell ref="B1857:B1858"/>
+    <mergeCell ref="B1859:B1860"/>
+    <mergeCell ref="B1861:B1862"/>
+    <mergeCell ref="B1863:B1864"/>
+    <mergeCell ref="B1865:B1866"/>
+    <mergeCell ref="B1867:B1868"/>
+    <mergeCell ref="B1869:B1870"/>
+    <mergeCell ref="B1835:B1836"/>
+    <mergeCell ref="B1837:B1838"/>
+    <mergeCell ref="B1839:B1840"/>
+    <mergeCell ref="B1841:B1842"/>
+    <mergeCell ref="B1843:B1844"/>
+    <mergeCell ref="B1845:B1846"/>
+    <mergeCell ref="B1847:B1848"/>
+    <mergeCell ref="B1849:B1850"/>
+    <mergeCell ref="B1851:B1852"/>
+    <mergeCell ref="B1817:B1818"/>
+    <mergeCell ref="B1819:B1820"/>
+    <mergeCell ref="B1821:B1822"/>
+    <mergeCell ref="B1823:B1824"/>
+    <mergeCell ref="B1825:B1826"/>
+    <mergeCell ref="B1827:B1828"/>
+    <mergeCell ref="B1829:B1830"/>
+    <mergeCell ref="B1831:B1832"/>
+    <mergeCell ref="B1833:B1834"/>
+    <mergeCell ref="B1799:B1800"/>
+    <mergeCell ref="B1801:B1802"/>
+    <mergeCell ref="B1803:B1804"/>
+    <mergeCell ref="B1805:B1806"/>
+    <mergeCell ref="B1807:B1808"/>
+    <mergeCell ref="B1809:B1810"/>
+    <mergeCell ref="B1811:B1812"/>
+    <mergeCell ref="B1813:B1814"/>
+    <mergeCell ref="B1815:B1816"/>
+    <mergeCell ref="B1781:B1782"/>
+    <mergeCell ref="B1783:B1784"/>
+    <mergeCell ref="B1785:B1786"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B1789:B1790"/>
+    <mergeCell ref="B1791:B1792"/>
+    <mergeCell ref="B1793:B1794"/>
+    <mergeCell ref="B1795:B1796"/>
+    <mergeCell ref="B1797:B1798"/>
+    <mergeCell ref="B1763:B1764"/>
+    <mergeCell ref="B1765:B1766"/>
+    <mergeCell ref="B1767:B1768"/>
+    <mergeCell ref="B1769:B1770"/>
+    <mergeCell ref="B1771:B1772"/>
+    <mergeCell ref="B1773:B1774"/>
+    <mergeCell ref="B1775:B1776"/>
+    <mergeCell ref="B1777:B1778"/>
+    <mergeCell ref="B1779:B1780"/>
+    <mergeCell ref="B1745:B1746"/>
+    <mergeCell ref="B1747:B1748"/>
+    <mergeCell ref="B1749:B1750"/>
+    <mergeCell ref="B1751:B1752"/>
+    <mergeCell ref="B1753:B1754"/>
+    <mergeCell ref="B1755:B1756"/>
+    <mergeCell ref="B1757:B1758"/>
+    <mergeCell ref="B1759:B1760"/>
+    <mergeCell ref="B1761:B1762"/>
+    <mergeCell ref="B1727:B1728"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="B1731:B1732"/>
+    <mergeCell ref="B1733:B1734"/>
+    <mergeCell ref="B1735:B1736"/>
+    <mergeCell ref="B1737:B1738"/>
+    <mergeCell ref="B1739:B1740"/>
+    <mergeCell ref="B1741:B1742"/>
+    <mergeCell ref="B1743:B1744"/>
+    <mergeCell ref="B1709:B1710"/>
+    <mergeCell ref="B1711:B1712"/>
+    <mergeCell ref="B1713:B1714"/>
+    <mergeCell ref="B1715:B1716"/>
+    <mergeCell ref="B1717:B1718"/>
+    <mergeCell ref="B1719:B1720"/>
+    <mergeCell ref="B1721:B1722"/>
+    <mergeCell ref="B1723:B1724"/>
+    <mergeCell ref="B1725:B1726"/>
+    <mergeCell ref="B1691:B1692"/>
+    <mergeCell ref="B1693:B1694"/>
+    <mergeCell ref="B1695:B1696"/>
+    <mergeCell ref="B1697:B1698"/>
+    <mergeCell ref="B1699:B1700"/>
+    <mergeCell ref="B1701:B1702"/>
+    <mergeCell ref="B1703:B1704"/>
+    <mergeCell ref="B1705:B1706"/>
+    <mergeCell ref="B1707:B1708"/>
+    <mergeCell ref="B1673:B1674"/>
+    <mergeCell ref="B1675:B1676"/>
+    <mergeCell ref="B1677:B1678"/>
+    <mergeCell ref="B1679:B1680"/>
+    <mergeCell ref="B1681:B1682"/>
+    <mergeCell ref="B1683:B1684"/>
+    <mergeCell ref="B1685:B1686"/>
+    <mergeCell ref="B1687:B1688"/>
+    <mergeCell ref="B1689:B1690"/>
+    <mergeCell ref="B1655:B1656"/>
+    <mergeCell ref="B1657:B1658"/>
+    <mergeCell ref="B1659:B1660"/>
+    <mergeCell ref="B1661:B1662"/>
+    <mergeCell ref="B1663:B1664"/>
+    <mergeCell ref="B1665:B1666"/>
+    <mergeCell ref="B1667:B1668"/>
+    <mergeCell ref="B1669:B1670"/>
+    <mergeCell ref="B1671:B1672"/>
+    <mergeCell ref="B1637:B1638"/>
+    <mergeCell ref="B1639:B1640"/>
+    <mergeCell ref="B1641:B1642"/>
+    <mergeCell ref="B1643:B1644"/>
+    <mergeCell ref="B1645:B1646"/>
+    <mergeCell ref="B1647:B1648"/>
+    <mergeCell ref="B1649:B1650"/>
+    <mergeCell ref="B1651:B1652"/>
+    <mergeCell ref="B1653:B1654"/>
+    <mergeCell ref="B1619:B1620"/>
+    <mergeCell ref="B1621:B1622"/>
+    <mergeCell ref="B1623:B1624"/>
+    <mergeCell ref="B1625:B1626"/>
+    <mergeCell ref="B1627:B1628"/>
+    <mergeCell ref="B1629:B1630"/>
+    <mergeCell ref="B1631:B1632"/>
+    <mergeCell ref="B1633:B1634"/>
+    <mergeCell ref="B1635:B1636"/>
+    <mergeCell ref="B1601:B1602"/>
+    <mergeCell ref="B1603:B1604"/>
+    <mergeCell ref="B1605:B1606"/>
+    <mergeCell ref="B1607:B1608"/>
+    <mergeCell ref="B1609:B1610"/>
+    <mergeCell ref="B1611:B1612"/>
+    <mergeCell ref="B1613:B1614"/>
+    <mergeCell ref="B1615:B1616"/>
+    <mergeCell ref="B1617:B1618"/>
+    <mergeCell ref="B1583:B1584"/>
+    <mergeCell ref="B1585:B1586"/>
+    <mergeCell ref="B1587:B1588"/>
+    <mergeCell ref="B1589:B1590"/>
+    <mergeCell ref="B1591:B1592"/>
+    <mergeCell ref="B1593:B1594"/>
+    <mergeCell ref="B1595:B1596"/>
+    <mergeCell ref="B1597:B1598"/>
+    <mergeCell ref="B1599:B1600"/>
+    <mergeCell ref="B1565:B1566"/>
+    <mergeCell ref="B1567:B1568"/>
+    <mergeCell ref="B1569:B1570"/>
+    <mergeCell ref="B1571:B1572"/>
+    <mergeCell ref="B1573:B1574"/>
+    <mergeCell ref="B1575:B1576"/>
+    <mergeCell ref="B1577:B1578"/>
+    <mergeCell ref="B1579:B1580"/>
+    <mergeCell ref="B1581:B1582"/>
+    <mergeCell ref="B1547:B1548"/>
+    <mergeCell ref="B1549:B1550"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B1553:B1554"/>
+    <mergeCell ref="B1555:B1556"/>
+    <mergeCell ref="B1557:B1558"/>
+    <mergeCell ref="B1559:B1560"/>
+    <mergeCell ref="B1561:B1562"/>
+    <mergeCell ref="B1563:B1564"/>
+    <mergeCell ref="B1529:B1530"/>
+    <mergeCell ref="B1531:B1532"/>
+    <mergeCell ref="B1533:B1534"/>
+    <mergeCell ref="B1535:B1536"/>
+    <mergeCell ref="B1537:B1538"/>
+    <mergeCell ref="B1539:B1540"/>
+    <mergeCell ref="B1541:B1542"/>
+    <mergeCell ref="B1543:B1544"/>
+    <mergeCell ref="B1545:B1546"/>
+    <mergeCell ref="B1511:B1512"/>
+    <mergeCell ref="B1513:B1514"/>
+    <mergeCell ref="B1515:B1516"/>
+    <mergeCell ref="B1517:B1518"/>
+    <mergeCell ref="B1519:B1520"/>
+    <mergeCell ref="B1521:B1522"/>
+    <mergeCell ref="B1523:B1524"/>
+    <mergeCell ref="B1525:B1526"/>
+    <mergeCell ref="B1527:B1528"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1495:B1496"/>
+    <mergeCell ref="B1497:B1498"/>
+    <mergeCell ref="B1499:B1500"/>
+    <mergeCell ref="B1501:B1502"/>
+    <mergeCell ref="B1503:B1504"/>
+    <mergeCell ref="B1505:B1506"/>
+    <mergeCell ref="B1507:B1508"/>
+    <mergeCell ref="B1509:B1510"/>
+    <mergeCell ref="B1475:B1476"/>
+    <mergeCell ref="B1477:B1478"/>
+    <mergeCell ref="B1479:B1480"/>
+    <mergeCell ref="B1481:B1482"/>
+    <mergeCell ref="B1483:B1484"/>
+    <mergeCell ref="B1485:B1486"/>
+    <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="B1489:B1490"/>
+    <mergeCell ref="B1491:B1492"/>
+    <mergeCell ref="B1457:B1458"/>
+    <mergeCell ref="B1459:B1460"/>
+    <mergeCell ref="B1461:B1462"/>
+    <mergeCell ref="B1463:B1464"/>
+    <mergeCell ref="B1465:B1466"/>
+    <mergeCell ref="B1467:B1468"/>
+    <mergeCell ref="B1469:B1470"/>
+    <mergeCell ref="B1471:B1472"/>
+    <mergeCell ref="B1473:B1474"/>
+    <mergeCell ref="B1439:B1440"/>
+    <mergeCell ref="B1441:B1442"/>
+    <mergeCell ref="B1443:B1444"/>
+    <mergeCell ref="B1445:B1446"/>
+    <mergeCell ref="B1447:B1448"/>
+    <mergeCell ref="B1449:B1450"/>
+    <mergeCell ref="B1451:B1452"/>
+    <mergeCell ref="B1453:B1454"/>
+    <mergeCell ref="B1455:B1456"/>
+    <mergeCell ref="B1421:B1422"/>
+    <mergeCell ref="B1423:B1424"/>
+    <mergeCell ref="B1425:B1426"/>
+    <mergeCell ref="B1427:B1428"/>
+    <mergeCell ref="B1429:B1430"/>
+    <mergeCell ref="B1431:B1432"/>
+    <mergeCell ref="B1433:B1434"/>
+    <mergeCell ref="B1435:B1436"/>
+    <mergeCell ref="B1437:B1438"/>
+    <mergeCell ref="B1403:B1404"/>
+    <mergeCell ref="B1405:B1406"/>
+    <mergeCell ref="B1407:B1408"/>
+    <mergeCell ref="B1409:B1410"/>
+    <mergeCell ref="B1411:B1412"/>
+    <mergeCell ref="B1413:B1414"/>
+    <mergeCell ref="B1415:B1416"/>
+    <mergeCell ref="B1417:B1418"/>
+    <mergeCell ref="B1419:B1420"/>
+    <mergeCell ref="B1385:B1386"/>
+    <mergeCell ref="B1387:B1388"/>
+    <mergeCell ref="B1389:B1390"/>
+    <mergeCell ref="B1391:B1392"/>
+    <mergeCell ref="B1393:B1394"/>
+    <mergeCell ref="B1395:B1396"/>
+    <mergeCell ref="B1397:B1398"/>
+    <mergeCell ref="B1399:B1400"/>
+    <mergeCell ref="B1401:B1402"/>
+    <mergeCell ref="B1367:B1368"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1371:B1372"/>
+    <mergeCell ref="B1373:B1374"/>
+    <mergeCell ref="B1375:B1376"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B1379:B1380"/>
+    <mergeCell ref="B1381:B1382"/>
+    <mergeCell ref="B1383:B1384"/>
+    <mergeCell ref="B1349:B1350"/>
+    <mergeCell ref="B1351:B1352"/>
+    <mergeCell ref="B1353:B1354"/>
+    <mergeCell ref="B1355:B1356"/>
+    <mergeCell ref="B1357:B1358"/>
+    <mergeCell ref="B1359:B1360"/>
+    <mergeCell ref="B1361:B1362"/>
+    <mergeCell ref="B1363:B1364"/>
+    <mergeCell ref="B1365:B1366"/>
+    <mergeCell ref="B1331:B1332"/>
+    <mergeCell ref="B1333:B1334"/>
+    <mergeCell ref="B1335:B1336"/>
+    <mergeCell ref="B1337:B1338"/>
+    <mergeCell ref="B1339:B1340"/>
+    <mergeCell ref="B1341:B1342"/>
+    <mergeCell ref="B1343:B1344"/>
+    <mergeCell ref="B1345:B1346"/>
+    <mergeCell ref="B1347:B1348"/>
+    <mergeCell ref="B1313:B1314"/>
+    <mergeCell ref="B1315:B1316"/>
+    <mergeCell ref="B1317:B1318"/>
+    <mergeCell ref="B1319:B1320"/>
+    <mergeCell ref="B1321:B1322"/>
+    <mergeCell ref="B1323:B1324"/>
+    <mergeCell ref="B1325:B1326"/>
+    <mergeCell ref="B1327:B1328"/>
+    <mergeCell ref="B1329:B1330"/>
+    <mergeCell ref="B1295:B1296"/>
+    <mergeCell ref="B1297:B1298"/>
+    <mergeCell ref="B1299:B1300"/>
+    <mergeCell ref="B1301:B1302"/>
+    <mergeCell ref="B1303:B1304"/>
+    <mergeCell ref="B1305:B1306"/>
+    <mergeCell ref="B1307:B1308"/>
+    <mergeCell ref="B1309:B1310"/>
+    <mergeCell ref="B1311:B1312"/>
+    <mergeCell ref="B1277:B1278"/>
+    <mergeCell ref="B1279:B1280"/>
+    <mergeCell ref="B1281:B1282"/>
+    <mergeCell ref="B1283:B1284"/>
+    <mergeCell ref="B1285:B1286"/>
+    <mergeCell ref="B1287:B1288"/>
+    <mergeCell ref="B1289:B1290"/>
+    <mergeCell ref="B1291:B1292"/>
+    <mergeCell ref="B1293:B1294"/>
+    <mergeCell ref="B1259:B1260"/>
+    <mergeCell ref="B1261:B1262"/>
+    <mergeCell ref="B1263:B1264"/>
+    <mergeCell ref="B1265:B1266"/>
+    <mergeCell ref="B1267:B1268"/>
+    <mergeCell ref="B1269:B1270"/>
+    <mergeCell ref="B1271:B1272"/>
+    <mergeCell ref="B1273:B1274"/>
+    <mergeCell ref="B1275:B1276"/>
+    <mergeCell ref="B1241:B1242"/>
+    <mergeCell ref="B1243:B1244"/>
+    <mergeCell ref="B1245:B1246"/>
+    <mergeCell ref="B1247:B1248"/>
+    <mergeCell ref="B1249:B1250"/>
+    <mergeCell ref="B1251:B1252"/>
+    <mergeCell ref="B1253:B1254"/>
+    <mergeCell ref="B1255:B1256"/>
+    <mergeCell ref="B1257:B1258"/>
+    <mergeCell ref="B1223:B1224"/>
+    <mergeCell ref="B1225:B1226"/>
+    <mergeCell ref="B1227:B1228"/>
+    <mergeCell ref="B1229:B1230"/>
+    <mergeCell ref="B1231:B1232"/>
+    <mergeCell ref="B1233:B1234"/>
+    <mergeCell ref="B1235:B1236"/>
+    <mergeCell ref="B1237:B1238"/>
+    <mergeCell ref="B1239:B1240"/>
+    <mergeCell ref="B1205:B1206"/>
+    <mergeCell ref="B1207:B1208"/>
+    <mergeCell ref="B1209:B1210"/>
+    <mergeCell ref="B1211:B1212"/>
+    <mergeCell ref="B1213:B1214"/>
+    <mergeCell ref="B1215:B1216"/>
+    <mergeCell ref="B1217:B1218"/>
+    <mergeCell ref="B1219:B1220"/>
+    <mergeCell ref="B1221:B1222"/>
+    <mergeCell ref="B1187:B1188"/>
+    <mergeCell ref="B1189:B1190"/>
+    <mergeCell ref="B1191:B1192"/>
+    <mergeCell ref="B1193:B1194"/>
+    <mergeCell ref="B1195:B1196"/>
+    <mergeCell ref="B1197:B1198"/>
+    <mergeCell ref="B1199:B1200"/>
+    <mergeCell ref="B1201:B1202"/>
+    <mergeCell ref="B1203:B1204"/>
+    <mergeCell ref="B1169:B1170"/>
+    <mergeCell ref="B1171:B1172"/>
+    <mergeCell ref="B1173:B1174"/>
+    <mergeCell ref="B1175:B1176"/>
+    <mergeCell ref="B1177:B1178"/>
+    <mergeCell ref="B1179:B1180"/>
+    <mergeCell ref="B1181:B1182"/>
+    <mergeCell ref="B1183:B1184"/>
+    <mergeCell ref="B1185:B1186"/>
+    <mergeCell ref="B1151:B1152"/>
+    <mergeCell ref="B1153:B1154"/>
+    <mergeCell ref="B1155:B1156"/>
+    <mergeCell ref="B1157:B1158"/>
+    <mergeCell ref="B1159:B1160"/>
+    <mergeCell ref="B1161:B1162"/>
+    <mergeCell ref="B1163:B1164"/>
+    <mergeCell ref="B1165:B1166"/>
+    <mergeCell ref="B1167:B1168"/>
+    <mergeCell ref="B1133:B1134"/>
+    <mergeCell ref="B1135:B1136"/>
+    <mergeCell ref="B1137:B1138"/>
+    <mergeCell ref="B1139:B1140"/>
+    <mergeCell ref="B1141:B1142"/>
+    <mergeCell ref="B1143:B1144"/>
+    <mergeCell ref="B1145:B1146"/>
+    <mergeCell ref="B1147:B1148"/>
+    <mergeCell ref="B1149:B1150"/>
+    <mergeCell ref="B1115:B1116"/>
+    <mergeCell ref="B1117:B1118"/>
+    <mergeCell ref="B1119:B1120"/>
+    <mergeCell ref="B1121:B1122"/>
+    <mergeCell ref="B1123:B1124"/>
+    <mergeCell ref="B1125:B1126"/>
+    <mergeCell ref="B1127:B1128"/>
+    <mergeCell ref="B1129:B1130"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="B1097:B1098"/>
+    <mergeCell ref="B1099:B1100"/>
+    <mergeCell ref="B1101:B1102"/>
+    <mergeCell ref="B1103:B1104"/>
+    <mergeCell ref="B1105:B1106"/>
+    <mergeCell ref="B1107:B1108"/>
+    <mergeCell ref="B1109:B1110"/>
+    <mergeCell ref="B1111:B1112"/>
+    <mergeCell ref="B1113:B1114"/>
+    <mergeCell ref="B1079:B1080"/>
+    <mergeCell ref="B1081:B1082"/>
+    <mergeCell ref="B1083:B1084"/>
+    <mergeCell ref="B1085:B1086"/>
+    <mergeCell ref="B1087:B1088"/>
+    <mergeCell ref="B1089:B1090"/>
+    <mergeCell ref="B1091:B1092"/>
+    <mergeCell ref="B1093:B1094"/>
+    <mergeCell ref="B1095:B1096"/>
+    <mergeCell ref="B943:B955"/>
+    <mergeCell ref="B956:B963"/>
+    <mergeCell ref="B964:B971"/>
+    <mergeCell ref="B972:B979"/>
+    <mergeCell ref="B980:B984"/>
+    <mergeCell ref="B985:B990"/>
+    <mergeCell ref="B991:B1041"/>
+    <mergeCell ref="B1042:B1076"/>
+    <mergeCell ref="B1077:B1078"/>
+    <mergeCell ref="B893:B895"/>
+    <mergeCell ref="B896:B901"/>
+    <mergeCell ref="B902:B905"/>
+    <mergeCell ref="B906:B909"/>
+    <mergeCell ref="B910:B916"/>
+    <mergeCell ref="B917:B925"/>
+    <mergeCell ref="B926:B929"/>
+    <mergeCell ref="B930:B935"/>
+    <mergeCell ref="B936:B942"/>
+    <mergeCell ref="B856:B860"/>
+    <mergeCell ref="B861:B864"/>
+    <mergeCell ref="B865:B870"/>
+    <mergeCell ref="B871:B874"/>
+    <mergeCell ref="B875:B879"/>
+    <mergeCell ref="B880:B882"/>
+    <mergeCell ref="B883:B885"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="B888:B892"/>
+    <mergeCell ref="B813:B815"/>
+    <mergeCell ref="B816:B820"/>
+    <mergeCell ref="B821:B825"/>
+    <mergeCell ref="B826:B830"/>
+    <mergeCell ref="B831:B835"/>
+    <mergeCell ref="B836:B843"/>
+    <mergeCell ref="B844:B846"/>
+    <mergeCell ref="B847:B852"/>
+    <mergeCell ref="B853:B855"/>
+    <mergeCell ref="B786:B788"/>
+    <mergeCell ref="B789:B791"/>
+    <mergeCell ref="B792:B794"/>
+    <mergeCell ref="B795:B797"/>
+    <mergeCell ref="B798:B800"/>
+    <mergeCell ref="B801:B803"/>
+    <mergeCell ref="B804:B806"/>
+    <mergeCell ref="B807:B809"/>
+    <mergeCell ref="B810:B812"/>
+    <mergeCell ref="B745:B746"/>
+    <mergeCell ref="B747:B750"/>
+    <mergeCell ref="B751:B755"/>
+    <mergeCell ref="B756:B761"/>
+    <mergeCell ref="B762:B767"/>
+    <mergeCell ref="B768:B776"/>
+    <mergeCell ref="B777:B779"/>
+    <mergeCell ref="B780:B782"/>
+    <mergeCell ref="B783:B785"/>
+    <mergeCell ref="B659:B665"/>
+    <mergeCell ref="B666:B670"/>
+    <mergeCell ref="B671:B675"/>
+    <mergeCell ref="B676:B680"/>
+    <mergeCell ref="B681:B685"/>
+    <mergeCell ref="B686:B691"/>
+    <mergeCell ref="B692:B698"/>
+    <mergeCell ref="B699:B712"/>
+    <mergeCell ref="B713:B744"/>
+    <mergeCell ref="B583:B585"/>
+    <mergeCell ref="B586:B588"/>
+    <mergeCell ref="B589:B591"/>
+    <mergeCell ref="B592:B605"/>
+    <mergeCell ref="B606:B637"/>
+    <mergeCell ref="B638:B641"/>
+    <mergeCell ref="B642:B646"/>
+    <mergeCell ref="B647:B651"/>
+    <mergeCell ref="B652:B658"/>
+    <mergeCell ref="B541:B546"/>
+    <mergeCell ref="B547:B552"/>
+    <mergeCell ref="B553:B558"/>
+    <mergeCell ref="B559:B564"/>
+    <mergeCell ref="B565:B568"/>
+    <mergeCell ref="B569:B571"/>
+    <mergeCell ref="B572:B575"/>
+    <mergeCell ref="B576:B579"/>
+    <mergeCell ref="B580:B582"/>
+    <mergeCell ref="B487:B492"/>
+    <mergeCell ref="B493:B498"/>
+    <mergeCell ref="B499:B504"/>
+    <mergeCell ref="B505:B510"/>
+    <mergeCell ref="B511:B516"/>
+    <mergeCell ref="B517:B522"/>
+    <mergeCell ref="B523:B528"/>
+    <mergeCell ref="B529:B534"/>
+    <mergeCell ref="B535:B540"/>
+    <mergeCell ref="B431:B436"/>
+    <mergeCell ref="B437:B442"/>
+    <mergeCell ref="B443:B450"/>
+    <mergeCell ref="B451:B456"/>
+    <mergeCell ref="B457:B462"/>
+    <mergeCell ref="B463:B468"/>
+    <mergeCell ref="B469:B474"/>
+    <mergeCell ref="B475:B480"/>
+    <mergeCell ref="B481:B486"/>
+    <mergeCell ref="B393:B399"/>
+    <mergeCell ref="B400:B404"/>
+    <mergeCell ref="B405:B407"/>
+    <mergeCell ref="B408:B410"/>
+    <mergeCell ref="B411:B415"/>
+    <mergeCell ref="B416:B418"/>
+    <mergeCell ref="B419:B421"/>
+    <mergeCell ref="B422:B424"/>
+    <mergeCell ref="B425:B430"/>
+    <mergeCell ref="B347:B351"/>
+    <mergeCell ref="B352:B355"/>
+    <mergeCell ref="B356:B359"/>
+    <mergeCell ref="B360:B363"/>
+    <mergeCell ref="B364:B367"/>
+    <mergeCell ref="B368:B371"/>
+    <mergeCell ref="B372:B378"/>
+    <mergeCell ref="B379:B385"/>
+    <mergeCell ref="B386:B392"/>
+    <mergeCell ref="B115:B200"/>
+    <mergeCell ref="B201:B253"/>
+    <mergeCell ref="B254:B269"/>
+    <mergeCell ref="B270:B287"/>
+    <mergeCell ref="B288:B301"/>
+    <mergeCell ref="B302:B333"/>
+    <mergeCell ref="B334:B337"/>
+    <mergeCell ref="B338:B341"/>
+    <mergeCell ref="B342:B346"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B109:B114"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/2023-24 RLS Codebook.xlsx
+++ b/2023-24 RLS Codebook.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FFAB5FB7-467A-4FFE-BD62-267D7CBFA7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE3AF3E-00F4-4857-93CA-3E59A131CE16}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="11400" yWindow="2318" windowWidth="7500" windowHeight="9434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Codebook" sheetId="1" r:id="rId1"/>
@@ -7109,7 +7109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7127,22 +7127,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7160,6 +7154,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7570,7 +7568,7 @@
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="3">
@@ -7584,7 +7582,7 @@
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="2">
         <v>2</v>
       </c>
@@ -7596,7 +7594,7 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="2">
         <v>3</v>
       </c>
@@ -7608,7 +7606,7 @@
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="2">
         <v>99</v>
       </c>
@@ -7620,7 +7618,7 @@
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3">
@@ -7634,7 +7632,7 @@
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="12"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="2">
         <v>2</v>
       </c>
@@ -7646,7 +7644,7 @@
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="12"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="2">
         <v>3</v>
       </c>
@@ -7658,7 +7656,7 @@
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="12"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="2">
         <v>4</v>
       </c>
@@ -7670,7 +7668,7 @@
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="12"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="2">
         <v>5</v>
       </c>
@@ -7682,7 +7680,7 @@
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="12"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="2">
         <v>99</v>
       </c>
@@ -7694,7 +7692,7 @@
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C20" s="3">
@@ -7708,7 +7706,7 @@
       <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="2">
         <v>2</v>
       </c>
@@ -7720,7 +7718,7 @@
       <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="12"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="2">
         <v>3</v>
       </c>
@@ -7732,7 +7730,7 @@
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="12"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="2">
         <v>4</v>
       </c>
@@ -7744,7 +7742,7 @@
       <c r="A24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="12"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="2">
         <v>5</v>
       </c>
@@ -7756,7 +7754,7 @@
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="12"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="2">
         <v>99</v>
       </c>
@@ -7768,7 +7766,7 @@
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="3">
@@ -7782,7 +7780,7 @@
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="8"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="2">
         <v>2</v>
       </c>
@@ -7794,7 +7792,7 @@
       <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="2">
         <v>3</v>
       </c>
@@ -7806,7 +7804,7 @@
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="8"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="2">
         <v>99</v>
       </c>
@@ -7818,7 +7816,7 @@
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="3">
@@ -7832,7 +7830,7 @@
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="8"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="2">
         <v>2</v>
       </c>
@@ -7844,7 +7842,7 @@
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="8"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="2">
         <v>3</v>
       </c>
@@ -7856,7 +7854,7 @@
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="8"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="2">
         <v>99</v>
       </c>
@@ -7868,7 +7866,7 @@
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="3">
@@ -7882,7 +7880,7 @@
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="8"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="2">
         <v>2</v>
       </c>
@@ -7894,7 +7892,7 @@
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="2">
         <v>3</v>
       </c>
@@ -7906,7 +7904,7 @@
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="8"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="2">
         <v>99</v>
       </c>
@@ -7918,7 +7916,7 @@
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="3">
@@ -7932,7 +7930,7 @@
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="8"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="2">
         <v>2</v>
       </c>
@@ -7944,7 +7942,7 @@
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="8"/>
+      <c r="B40" s="10"/>
       <c r="C40" s="2">
         <v>3</v>
       </c>
@@ -7956,7 +7954,7 @@
       <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="8"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="2">
         <v>99</v>
       </c>
@@ -7968,7 +7966,7 @@
       <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C42" s="3">
@@ -7982,7 +7980,7 @@
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="8"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="2">
         <v>2</v>
       </c>
@@ -7994,7 +7992,7 @@
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="8"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="2">
         <v>3</v>
       </c>
@@ -8006,7 +8004,7 @@
       <c r="A45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="8"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="2">
         <v>99</v>
       </c>
@@ -8018,7 +8016,7 @@
       <c r="A46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C46" s="3">
@@ -8032,7 +8030,7 @@
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="8"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="2">
         <v>2</v>
       </c>
@@ -8044,7 +8042,7 @@
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="8"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="2">
         <v>99</v>
       </c>
@@ -8056,7 +8054,7 @@
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="3">
@@ -8070,7 +8068,7 @@
       <c r="A50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="8"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="2">
         <v>2</v>
       </c>
@@ -8082,7 +8080,7 @@
       <c r="A51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="8"/>
+      <c r="B51" s="10"/>
       <c r="C51" s="2">
         <v>99</v>
       </c>
@@ -8094,7 +8092,7 @@
       <c r="A52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="3">
@@ -8108,7 +8106,7 @@
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="8"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="2">
         <v>2</v>
       </c>
@@ -8120,7 +8118,7 @@
       <c r="A54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="8"/>
+      <c r="B54" s="10"/>
       <c r="C54" s="2">
         <v>99</v>
       </c>
@@ -8132,7 +8130,7 @@
       <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="3">
@@ -8146,7 +8144,7 @@
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="8"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="2">
         <v>2</v>
       </c>
@@ -8158,7 +8156,7 @@
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="8"/>
+      <c r="B57" s="10"/>
       <c r="C57" s="2">
         <v>99</v>
       </c>
@@ -8170,7 +8168,7 @@
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="3">
@@ -8184,7 +8182,7 @@
       <c r="A59" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="8"/>
+      <c r="B59" s="10"/>
       <c r="C59" s="2">
         <v>2</v>
       </c>
@@ -8196,7 +8194,7 @@
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="8"/>
+      <c r="B60" s="10"/>
       <c r="C60" s="2">
         <v>3</v>
       </c>
@@ -8208,7 +8206,7 @@
       <c r="A61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="8"/>
+      <c r="B61" s="10"/>
       <c r="C61" s="2">
         <v>99</v>
       </c>
@@ -8220,7 +8218,7 @@
       <c r="A62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="3">
@@ -8234,7 +8232,7 @@
       <c r="A63" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="8"/>
+      <c r="B63" s="10"/>
       <c r="C63" s="2">
         <v>2</v>
       </c>
@@ -8246,7 +8244,7 @@
       <c r="A64" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="8"/>
+      <c r="B64" s="10"/>
       <c r="C64" s="2">
         <v>99</v>
       </c>
@@ -8258,7 +8256,7 @@
       <c r="A65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C65" s="3">
@@ -8272,7 +8270,7 @@
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="8"/>
+      <c r="B66" s="10"/>
       <c r="C66" s="2">
         <v>2</v>
       </c>
@@ -8284,7 +8282,7 @@
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="8"/>
+      <c r="B67" s="10"/>
       <c r="C67" s="2">
         <v>3</v>
       </c>
@@ -8296,7 +8294,7 @@
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="8"/>
+      <c r="B68" s="10"/>
       <c r="C68" s="2">
         <v>4</v>
       </c>
@@ -8308,7 +8306,7 @@
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="8"/>
+      <c r="B69" s="10"/>
       <c r="C69" s="2">
         <v>99</v>
       </c>
@@ -8320,7 +8318,7 @@
       <c r="A70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C70" s="3">
@@ -8334,7 +8332,7 @@
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="8"/>
+      <c r="B71" s="10"/>
       <c r="C71" s="2">
         <v>2</v>
       </c>
@@ -8346,7 +8344,7 @@
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="8"/>
+      <c r="B72" s="10"/>
       <c r="C72" s="2">
         <v>3</v>
       </c>
@@ -8358,7 +8356,7 @@
       <c r="A73" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="8"/>
+      <c r="B73" s="10"/>
       <c r="C73" s="2">
         <v>4</v>
       </c>
@@ -8370,7 +8368,7 @@
       <c r="A74" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="8"/>
+      <c r="B74" s="10"/>
       <c r="C74" s="2">
         <v>99</v>
       </c>
@@ -8382,7 +8380,7 @@
       <c r="A75" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C75" s="3">
@@ -8396,7 +8394,7 @@
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="8"/>
+      <c r="B76" s="10"/>
       <c r="C76" s="2">
         <v>2</v>
       </c>
@@ -8408,7 +8406,7 @@
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="8"/>
+      <c r="B77" s="10"/>
       <c r="C77" s="2">
         <v>99</v>
       </c>
@@ -8582,7 +8580,7 @@
       <c r="A91" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C91" s="3">
@@ -8596,7 +8594,7 @@
       <c r="A92" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B92" s="8"/>
+      <c r="B92" s="10"/>
       <c r="C92" s="2">
         <v>2</v>
       </c>
@@ -8608,7 +8606,7 @@
       <c r="A93" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B93" s="8"/>
+      <c r="B93" s="10"/>
       <c r="C93" s="2">
         <v>3</v>
       </c>
@@ -8620,7 +8618,7 @@
       <c r="A94" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="8"/>
+      <c r="B94" s="10"/>
       <c r="C94" s="2">
         <v>4</v>
       </c>
@@ -8632,7 +8630,7 @@
       <c r="A95" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B95" s="8"/>
+      <c r="B95" s="10"/>
       <c r="C95" s="2">
         <v>5</v>
       </c>
@@ -8644,7 +8642,7 @@
       <c r="A96" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="8"/>
+      <c r="B96" s="10"/>
       <c r="C96" s="2">
         <v>99</v>
       </c>
@@ -8656,7 +8654,7 @@
       <c r="A97" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C97" s="3">
@@ -8670,7 +8668,7 @@
       <c r="A98" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B98" s="8"/>
+      <c r="B98" s="10"/>
       <c r="C98" s="2">
         <v>2</v>
       </c>
@@ -8682,7 +8680,7 @@
       <c r="A99" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B99" s="8"/>
+      <c r="B99" s="10"/>
       <c r="C99" s="2">
         <v>3</v>
       </c>
@@ -8694,7 +8692,7 @@
       <c r="A100" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B100" s="8"/>
+      <c r="B100" s="10"/>
       <c r="C100" s="2">
         <v>4</v>
       </c>
@@ -8706,7 +8704,7 @@
       <c r="A101" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="8"/>
+      <c r="B101" s="10"/>
       <c r="C101" s="2">
         <v>5</v>
       </c>
@@ -8718,7 +8716,7 @@
       <c r="A102" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B102" s="8"/>
+      <c r="B102" s="10"/>
       <c r="C102" s="2">
         <v>99</v>
       </c>
@@ -8730,7 +8728,7 @@
       <c r="A103" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C103" s="3">
@@ -8744,7 +8742,7 @@
       <c r="A104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="8"/>
+      <c r="B104" s="10"/>
       <c r="C104" s="2">
         <v>2</v>
       </c>
@@ -8756,7 +8754,7 @@
       <c r="A105" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B105" s="8"/>
+      <c r="B105" s="10"/>
       <c r="C105" s="2">
         <v>3</v>
       </c>
@@ -8768,7 +8766,7 @@
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="8"/>
+      <c r="B106" s="10"/>
       <c r="C106" s="2">
         <v>4</v>
       </c>
@@ -8780,7 +8778,7 @@
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="8"/>
+      <c r="B107" s="10"/>
       <c r="C107" s="2">
         <v>5</v>
       </c>
@@ -8792,7 +8790,7 @@
       <c r="A108" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="8"/>
+      <c r="B108" s="10"/>
       <c r="C108" s="2">
         <v>99</v>
       </c>
@@ -8804,7 +8802,7 @@
       <c r="A109" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C109" s="3">
@@ -8818,7 +8816,7 @@
       <c r="A110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="8"/>
+      <c r="B110" s="10"/>
       <c r="C110" s="2">
         <v>2</v>
       </c>
@@ -8830,7 +8828,7 @@
       <c r="A111" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="8"/>
+      <c r="B111" s="10"/>
       <c r="C111" s="2">
         <v>3</v>
       </c>
@@ -8842,7 +8840,7 @@
       <c r="A112" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="8"/>
+      <c r="B112" s="10"/>
       <c r="C112" s="2">
         <v>4</v>
       </c>
@@ -8854,7 +8852,7 @@
       <c r="A113" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B113" s="8"/>
+      <c r="B113" s="10"/>
       <c r="C113" s="2">
         <v>5</v>
       </c>
@@ -8866,7 +8864,7 @@
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="8"/>
+      <c r="B114" s="10"/>
       <c r="C114" s="2">
         <v>99</v>
       </c>
@@ -10550,7 +10548,7 @@
       <c r="A254" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B254" s="7" t="s">
+      <c r="B254" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C254" s="3">
@@ -10564,7 +10562,7 @@
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B255" s="8"/>
+      <c r="B255" s="10"/>
       <c r="C255" s="2">
         <v>1200</v>
       </c>
@@ -10576,7 +10574,7 @@
       <c r="A256" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B256" s="8"/>
+      <c r="B256" s="10"/>
       <c r="C256" s="2">
         <v>1300</v>
       </c>
@@ -10588,7 +10586,7 @@
       <c r="A257" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="8"/>
+      <c r="B257" s="10"/>
       <c r="C257" s="2">
         <v>10000</v>
       </c>
@@ -10600,7 +10598,7 @@
       <c r="A258" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="8"/>
+      <c r="B258" s="10"/>
       <c r="C258" s="2">
         <v>20000</v>
       </c>
@@ -10612,7 +10610,7 @@
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259" s="8"/>
+      <c r="B259" s="10"/>
       <c r="C259" s="2">
         <v>30000</v>
       </c>
@@ -10624,7 +10622,7 @@
       <c r="A260" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B260" s="8"/>
+      <c r="B260" s="10"/>
       <c r="C260" s="2">
         <v>40001</v>
       </c>
@@ -10636,7 +10634,7 @@
       <c r="A261" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B261" s="8"/>
+      <c r="B261" s="10"/>
       <c r="C261" s="2">
         <v>40002</v>
       </c>
@@ -10648,7 +10646,7 @@
       <c r="A262" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B262" s="8"/>
+      <c r="B262" s="10"/>
       <c r="C262" s="2">
         <v>50000</v>
       </c>
@@ -10660,7 +10658,7 @@
       <c r="A263" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B263" s="8"/>
+      <c r="B263" s="10"/>
       <c r="C263" s="2">
         <v>60000</v>
       </c>
@@ -10672,7 +10670,7 @@
       <c r="A264" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B264" s="8"/>
+      <c r="B264" s="10"/>
       <c r="C264" s="2">
         <v>70000</v>
       </c>
@@ -10684,7 +10682,7 @@
       <c r="A265" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B265" s="8"/>
+      <c r="B265" s="10"/>
       <c r="C265" s="2">
         <v>80000</v>
       </c>
@@ -10696,7 +10694,7 @@
       <c r="A266" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B266" s="8"/>
+      <c r="B266" s="10"/>
       <c r="C266" s="2">
         <v>90001</v>
       </c>
@@ -10708,7 +10706,7 @@
       <c r="A267" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B267" s="8"/>
+      <c r="B267" s="10"/>
       <c r="C267" s="2">
         <v>90002</v>
       </c>
@@ -10720,7 +10718,7 @@
       <c r="A268" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B268" s="8"/>
+      <c r="B268" s="10"/>
       <c r="C268" s="2">
         <v>100000</v>
       </c>
@@ -10732,7 +10730,7 @@
       <c r="A269" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B269" s="8"/>
+      <c r="B269" s="10"/>
       <c r="C269" s="2">
         <v>900000</v>
       </c>
@@ -10962,7 +10960,7 @@
       <c r="A288" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B288" s="7" t="s">
+      <c r="B288" s="9" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="3">
@@ -10976,7 +10974,7 @@
       <c r="A289" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B289" s="8"/>
+      <c r="B289" s="10"/>
       <c r="C289" s="2">
         <v>10000</v>
       </c>
@@ -10988,7 +10986,7 @@
       <c r="A290" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B290" s="8"/>
+      <c r="B290" s="10"/>
       <c r="C290" s="2">
         <v>20000</v>
       </c>
@@ -11000,7 +10998,7 @@
       <c r="A291" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B291" s="8"/>
+      <c r="B291" s="10"/>
       <c r="C291" s="2">
         <v>30000</v>
       </c>
@@ -11012,7 +11010,7 @@
       <c r="A292" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B292" s="8"/>
+      <c r="B292" s="10"/>
       <c r="C292" s="2">
         <v>40001</v>
       </c>
@@ -11024,7 +11022,7 @@
       <c r="A293" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B293" s="8"/>
+      <c r="B293" s="10"/>
       <c r="C293" s="2">
         <v>40002</v>
       </c>
@@ -11036,7 +11034,7 @@
       <c r="A294" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B294" s="8"/>
+      <c r="B294" s="10"/>
       <c r="C294" s="2">
         <v>50000</v>
       </c>
@@ -11048,7 +11046,7 @@
       <c r="A295" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B295" s="8"/>
+      <c r="B295" s="10"/>
       <c r="C295" s="2">
         <v>60000</v>
       </c>
@@ -11060,7 +11058,7 @@
       <c r="A296" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B296" s="8"/>
+      <c r="B296" s="10"/>
       <c r="C296" s="2">
         <v>70000</v>
       </c>
@@ -11072,7 +11070,7 @@
       <c r="A297" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B297" s="8"/>
+      <c r="B297" s="10"/>
       <c r="C297" s="2">
         <v>80000</v>
       </c>
@@ -11084,7 +11082,7 @@
       <c r="A298" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B298" s="8"/>
+      <c r="B298" s="10"/>
       <c r="C298" s="2">
         <v>90001</v>
       </c>
@@ -11096,7 +11094,7 @@
       <c r="A299" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B299" s="8"/>
+      <c r="B299" s="10"/>
       <c r="C299" s="2">
         <v>90002</v>
       </c>
@@ -11108,7 +11106,7 @@
       <c r="A300" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B300" s="8"/>
+      <c r="B300" s="10"/>
       <c r="C300" s="2">
         <v>100000</v>
       </c>
@@ -11120,7 +11118,7 @@
       <c r="A301" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B301" s="8"/>
+      <c r="B301" s="10"/>
       <c r="C301" s="2">
         <v>900000</v>
       </c>
@@ -11618,7 +11616,7 @@
       <c r="A342" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B342" s="7" t="s">
+      <c r="B342" s="9" t="s">
         <v>304</v>
       </c>
       <c r="C342" s="3">
@@ -11632,7 +11630,7 @@
       <c r="A343" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B343" s="8"/>
+      <c r="B343" s="10"/>
       <c r="C343" s="2">
         <v>2</v>
       </c>
@@ -11644,7 +11642,7 @@
       <c r="A344" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B344" s="8"/>
+      <c r="B344" s="10"/>
       <c r="C344" s="2">
         <v>3</v>
       </c>
@@ -11656,7 +11654,7 @@
       <c r="A345" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B345" s="8"/>
+      <c r="B345" s="10"/>
       <c r="C345" s="2">
         <v>4</v>
       </c>
@@ -11668,7 +11666,7 @@
       <c r="A346" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B346" s="8"/>
+      <c r="B346" s="10"/>
       <c r="C346" s="2">
         <v>99</v>
       </c>
@@ -11680,7 +11678,7 @@
       <c r="A347" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B347" s="7" t="s">
+      <c r="B347" s="9" t="s">
         <v>310</v>
       </c>
       <c r="C347" s="3">
@@ -11694,7 +11692,7 @@
       <c r="A348" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B348" s="8"/>
+      <c r="B348" s="10"/>
       <c r="C348" s="2">
         <v>2</v>
       </c>
@@ -11706,7 +11704,7 @@
       <c r="A349" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B349" s="8"/>
+      <c r="B349" s="10"/>
       <c r="C349" s="2">
         <v>3</v>
       </c>
@@ -11718,7 +11716,7 @@
       <c r="A350" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B350" s="8"/>
+      <c r="B350" s="10"/>
       <c r="C350" s="2">
         <v>4</v>
       </c>
@@ -11730,7 +11728,7 @@
       <c r="A351" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B351" s="8"/>
+      <c r="B351" s="10"/>
       <c r="C351" s="2">
         <v>99</v>
       </c>
@@ -11992,7 +11990,7 @@
       <c r="A372" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B372" s="7" t="s">
+      <c r="B372" s="9" t="s">
         <v>333</v>
       </c>
       <c r="C372" s="3">
@@ -12006,7 +12004,7 @@
       <c r="A373" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B373" s="8"/>
+      <c r="B373" s="10"/>
       <c r="C373" s="2">
         <v>2</v>
       </c>
@@ -12018,7 +12016,7 @@
       <c r="A374" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B374" s="8"/>
+      <c r="B374" s="10"/>
       <c r="C374" s="2">
         <v>3</v>
       </c>
@@ -12030,7 +12028,7 @@
       <c r="A375" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B375" s="8"/>
+      <c r="B375" s="10"/>
       <c r="C375" s="2">
         <v>4</v>
       </c>
@@ -12042,7 +12040,7 @@
       <c r="A376" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B376" s="8"/>
+      <c r="B376" s="10"/>
       <c r="C376" s="2">
         <v>5</v>
       </c>
@@ -12054,7 +12052,7 @@
       <c r="A377" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B377" s="8"/>
+      <c r="B377" s="10"/>
       <c r="C377" s="2">
         <v>6</v>
       </c>
@@ -12066,7 +12064,7 @@
       <c r="A378" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B378" s="8"/>
+      <c r="B378" s="10"/>
       <c r="C378" s="2">
         <v>99</v>
       </c>
@@ -12078,7 +12076,7 @@
       <c r="A379" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B379" s="7" t="s">
+      <c r="B379" s="9" t="s">
         <v>341</v>
       </c>
       <c r="C379" s="3">
@@ -12092,7 +12090,7 @@
       <c r="A380" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B380" s="8"/>
+      <c r="B380" s="10"/>
       <c r="C380" s="2">
         <v>2</v>
       </c>
@@ -12104,7 +12102,7 @@
       <c r="A381" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B381" s="8"/>
+      <c r="B381" s="10"/>
       <c r="C381" s="2">
         <v>3</v>
       </c>
@@ -12116,7 +12114,7 @@
       <c r="A382" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B382" s="8"/>
+      <c r="B382" s="10"/>
       <c r="C382" s="2">
         <v>4</v>
       </c>
@@ -12128,7 +12126,7 @@
       <c r="A383" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B383" s="8"/>
+      <c r="B383" s="10"/>
       <c r="C383" s="2">
         <v>5</v>
       </c>
@@ -12140,7 +12138,7 @@
       <c r="A384" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B384" s="8"/>
+      <c r="B384" s="10"/>
       <c r="C384" s="2">
         <v>6</v>
       </c>
@@ -12152,7 +12150,7 @@
       <c r="A385" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B385" s="8"/>
+      <c r="B385" s="10"/>
       <c r="C385" s="2">
         <v>99</v>
       </c>
@@ -12336,7 +12334,7 @@
       <c r="A400" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B400" s="7" t="s">
+      <c r="B400" s="9" t="s">
         <v>353</v>
       </c>
       <c r="C400" s="3">
@@ -12350,7 +12348,7 @@
       <c r="A401" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B401" s="8"/>
+      <c r="B401" s="10"/>
       <c r="C401" s="2">
         <v>2</v>
       </c>
@@ -12362,7 +12360,7 @@
       <c r="A402" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B402" s="8"/>
+      <c r="B402" s="10"/>
       <c r="C402" s="2">
         <v>3</v>
       </c>
@@ -12374,7 +12372,7 @@
       <c r="A403" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B403" s="8"/>
+      <c r="B403" s="10"/>
       <c r="C403" s="2">
         <v>4</v>
       </c>
@@ -12386,7 +12384,7 @@
       <c r="A404" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B404" s="8"/>
+      <c r="B404" s="10"/>
       <c r="C404" s="2">
         <v>99</v>
       </c>
@@ -12398,7 +12396,7 @@
       <c r="A405" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B405" s="7" t="s">
+      <c r="B405" s="9" t="s">
         <v>355</v>
       </c>
       <c r="C405" s="3">
@@ -12412,7 +12410,7 @@
       <c r="A406" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B406" s="8"/>
+      <c r="B406" s="10"/>
       <c r="C406" s="2">
         <v>2</v>
       </c>
@@ -12424,7 +12422,7 @@
       <c r="A407" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B407" s="8"/>
+      <c r="B407" s="10"/>
       <c r="C407" s="2">
         <v>99</v>
       </c>
@@ -12436,7 +12434,7 @@
       <c r="A408" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B408" s="7" t="s">
+      <c r="B408" s="9" t="s">
         <v>357</v>
       </c>
       <c r="C408" s="3">
@@ -12450,7 +12448,7 @@
       <c r="A409" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B409" s="8"/>
+      <c r="B409" s="10"/>
       <c r="C409" s="2">
         <v>2</v>
       </c>
@@ -12462,7 +12460,7 @@
       <c r="A410" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B410" s="8"/>
+      <c r="B410" s="10"/>
       <c r="C410" s="2">
         <v>99</v>
       </c>
@@ -12536,7 +12534,7 @@
       <c r="A416" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B416" s="7" t="s">
+      <c r="B416" s="9" t="s">
         <v>365</v>
       </c>
       <c r="C416" s="3">
@@ -12550,7 +12548,7 @@
       <c r="A417" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B417" s="8"/>
+      <c r="B417" s="10"/>
       <c r="C417" s="2">
         <v>2</v>
       </c>
@@ -12562,7 +12560,7 @@
       <c r="A418" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B418" s="8"/>
+      <c r="B418" s="10"/>
       <c r="C418" s="2">
         <v>99</v>
       </c>
@@ -12574,7 +12572,7 @@
       <c r="A419" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B419" s="7" t="s">
+      <c r="B419" s="9" t="s">
         <v>367</v>
       </c>
       <c r="C419" s="3">
@@ -12588,7 +12586,7 @@
       <c r="A420" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B420" s="8"/>
+      <c r="B420" s="10"/>
       <c r="C420" s="2">
         <v>2</v>
       </c>
@@ -12600,7 +12598,7 @@
       <c r="A421" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B421" s="8"/>
+      <c r="B421" s="10"/>
       <c r="C421" s="2">
         <v>99</v>
       </c>
@@ -12612,7 +12610,7 @@
       <c r="A422" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B422" s="7" t="s">
+      <c r="B422" s="9" t="s">
         <v>369</v>
       </c>
       <c r="C422" s="3">
@@ -12626,7 +12624,7 @@
       <c r="A423" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B423" s="8"/>
+      <c r="B423" s="10"/>
       <c r="C423" s="2">
         <v>2</v>
       </c>
@@ -12638,7 +12636,7 @@
       <c r="A424" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B424" s="8"/>
+      <c r="B424" s="10"/>
       <c r="C424" s="2">
         <v>99</v>
       </c>
@@ -12650,7 +12648,7 @@
       <c r="A425" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B425" s="7" t="s">
+      <c r="B425" s="9" t="s">
         <v>371</v>
       </c>
       <c r="C425" s="3">
@@ -12664,7 +12662,7 @@
       <c r="A426" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B426" s="8"/>
+      <c r="B426" s="10"/>
       <c r="C426" s="2">
         <v>2</v>
       </c>
@@ -12676,7 +12674,7 @@
       <c r="A427" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B427" s="8"/>
+      <c r="B427" s="10"/>
       <c r="C427" s="2">
         <v>3</v>
       </c>
@@ -12688,7 +12686,7 @@
       <c r="A428" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B428" s="8"/>
+      <c r="B428" s="10"/>
       <c r="C428" s="2">
         <v>4</v>
       </c>
@@ -12700,7 +12698,7 @@
       <c r="A429" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B429" s="8"/>
+      <c r="B429" s="10"/>
       <c r="C429" s="2">
         <v>5</v>
       </c>
@@ -12712,7 +12710,7 @@
       <c r="A430" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B430" s="8"/>
+      <c r="B430" s="10"/>
       <c r="C430" s="2">
         <v>99</v>
       </c>
@@ -12724,7 +12722,7 @@
       <c r="A431" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B431" s="7" t="s">
+      <c r="B431" s="9" t="s">
         <v>373</v>
       </c>
       <c r="C431" s="3">
@@ -12738,7 +12736,7 @@
       <c r="A432" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B432" s="8"/>
+      <c r="B432" s="10"/>
       <c r="C432" s="2">
         <v>2</v>
       </c>
@@ -12750,7 +12748,7 @@
       <c r="A433" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B433" s="8"/>
+      <c r="B433" s="10"/>
       <c r="C433" s="2">
         <v>3</v>
       </c>
@@ -12762,7 +12760,7 @@
       <c r="A434" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B434" s="8"/>
+      <c r="B434" s="10"/>
       <c r="C434" s="2">
         <v>4</v>
       </c>
@@ -12774,7 +12772,7 @@
       <c r="A435" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B435" s="8"/>
+      <c r="B435" s="10"/>
       <c r="C435" s="2">
         <v>5</v>
       </c>
@@ -12786,7 +12784,7 @@
       <c r="A436" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B436" s="8"/>
+      <c r="B436" s="10"/>
       <c r="C436" s="2">
         <v>99</v>
       </c>
@@ -12798,7 +12796,7 @@
       <c r="A437" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B437" s="7" t="s">
+      <c r="B437" s="9" t="s">
         <v>380</v>
       </c>
       <c r="C437" s="3">
@@ -12812,7 +12810,7 @@
       <c r="A438" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B438" s="8"/>
+      <c r="B438" s="10"/>
       <c r="C438" s="2">
         <v>2</v>
       </c>
@@ -12824,7 +12822,7 @@
       <c r="A439" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B439" s="8"/>
+      <c r="B439" s="10"/>
       <c r="C439" s="2">
         <v>3</v>
       </c>
@@ -12836,7 +12834,7 @@
       <c r="A440" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B440" s="8"/>
+      <c r="B440" s="10"/>
       <c r="C440" s="2">
         <v>4</v>
       </c>
@@ -12848,7 +12846,7 @@
       <c r="A441" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B441" s="8"/>
+      <c r="B441" s="10"/>
       <c r="C441" s="2">
         <v>5</v>
       </c>
@@ -12860,7 +12858,7 @@
       <c r="A442" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B442" s="8"/>
+      <c r="B442" s="10"/>
       <c r="C442" s="2">
         <v>99</v>
       </c>
@@ -12872,7 +12870,7 @@
       <c r="A443" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B443" s="7" t="s">
+      <c r="B443" s="9" t="s">
         <v>382</v>
       </c>
       <c r="C443" s="3">
@@ -12886,7 +12884,7 @@
       <c r="A444" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B444" s="8"/>
+      <c r="B444" s="10"/>
       <c r="C444" s="2">
         <v>2</v>
       </c>
@@ -12898,7 +12896,7 @@
       <c r="A445" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B445" s="8"/>
+      <c r="B445" s="10"/>
       <c r="C445" s="2">
         <v>3</v>
       </c>
@@ -12910,7 +12908,7 @@
       <c r="A446" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B446" s="8"/>
+      <c r="B446" s="10"/>
       <c r="C446" s="2">
         <v>4</v>
       </c>
@@ -12922,7 +12920,7 @@
       <c r="A447" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B447" s="8"/>
+      <c r="B447" s="10"/>
       <c r="C447" s="2">
         <v>5</v>
       </c>
@@ -12934,7 +12932,7 @@
       <c r="A448" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B448" s="8"/>
+      <c r="B448" s="10"/>
       <c r="C448" s="2">
         <v>6</v>
       </c>
@@ -12946,7 +12944,7 @@
       <c r="A449" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B449" s="8"/>
+      <c r="B449" s="10"/>
       <c r="C449" s="2">
         <v>7</v>
       </c>
@@ -12958,7 +12956,7 @@
       <c r="A450" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B450" s="8"/>
+      <c r="B450" s="10"/>
       <c r="C450" s="2">
         <v>99</v>
       </c>
@@ -12970,7 +12968,7 @@
       <c r="A451" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B451" s="7" t="s">
+      <c r="B451" s="9" t="s">
         <v>388</v>
       </c>
       <c r="C451" s="3">
@@ -12984,7 +12982,7 @@
       <c r="A452" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B452" s="8"/>
+      <c r="B452" s="10"/>
       <c r="C452" s="2">
         <v>2</v>
       </c>
@@ -12996,7 +12994,7 @@
       <c r="A453" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B453" s="8"/>
+      <c r="B453" s="10"/>
       <c r="C453" s="2">
         <v>3</v>
       </c>
@@ -13008,7 +13006,7 @@
       <c r="A454" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B454" s="8"/>
+      <c r="B454" s="10"/>
       <c r="C454" s="2">
         <v>4</v>
       </c>
@@ -13020,7 +13018,7 @@
       <c r="A455" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B455" s="8"/>
+      <c r="B455" s="10"/>
       <c r="C455" s="2">
         <v>5</v>
       </c>
@@ -13032,7 +13030,7 @@
       <c r="A456" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B456" s="8"/>
+      <c r="B456" s="10"/>
       <c r="C456" s="2">
         <v>99</v>
       </c>
@@ -13044,7 +13042,7 @@
       <c r="A457" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B457" s="7" t="s">
+      <c r="B457" s="9" t="s">
         <v>393</v>
       </c>
       <c r="C457" s="3">
@@ -13058,7 +13056,7 @@
       <c r="A458" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B458" s="8"/>
+      <c r="B458" s="10"/>
       <c r="C458" s="2">
         <v>2</v>
       </c>
@@ -13070,7 +13068,7 @@
       <c r="A459" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B459" s="8"/>
+      <c r="B459" s="10"/>
       <c r="C459" s="2">
         <v>3</v>
       </c>
@@ -13082,7 +13080,7 @@
       <c r="A460" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B460" s="8"/>
+      <c r="B460" s="10"/>
       <c r="C460" s="2">
         <v>4</v>
       </c>
@@ -13094,7 +13092,7 @@
       <c r="A461" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B461" s="8"/>
+      <c r="B461" s="10"/>
       <c r="C461" s="2">
         <v>5</v>
       </c>
@@ -13106,7 +13104,7 @@
       <c r="A462" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B462" s="8"/>
+      <c r="B462" s="10"/>
       <c r="C462" s="2">
         <v>99</v>
       </c>
@@ -13118,7 +13116,7 @@
       <c r="A463" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B463" s="7" t="s">
+      <c r="B463" s="9" t="s">
         <v>397</v>
       </c>
       <c r="C463" s="3">
@@ -13132,7 +13130,7 @@
       <c r="A464" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B464" s="8"/>
+      <c r="B464" s="10"/>
       <c r="C464" s="2">
         <v>2</v>
       </c>
@@ -13144,7 +13142,7 @@
       <c r="A465" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B465" s="8"/>
+      <c r="B465" s="10"/>
       <c r="C465" s="2">
         <v>3</v>
       </c>
@@ -13156,7 +13154,7 @@
       <c r="A466" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B466" s="8"/>
+      <c r="B466" s="10"/>
       <c r="C466" s="2">
         <v>4</v>
       </c>
@@ -13168,7 +13166,7 @@
       <c r="A467" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B467" s="8"/>
+      <c r="B467" s="10"/>
       <c r="C467" s="2">
         <v>5</v>
       </c>
@@ -13180,7 +13178,7 @@
       <c r="A468" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B468" s="8"/>
+      <c r="B468" s="10"/>
       <c r="C468" s="2">
         <v>99</v>
       </c>
@@ -13192,7 +13190,7 @@
       <c r="A469" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B469" s="7" t="s">
+      <c r="B469" s="9" t="s">
         <v>399</v>
       </c>
       <c r="C469" s="3">
@@ -13206,7 +13204,7 @@
       <c r="A470" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B470" s="8"/>
+      <c r="B470" s="10"/>
       <c r="C470" s="2">
         <v>2</v>
       </c>
@@ -13218,7 +13216,7 @@
       <c r="A471" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B471" s="8"/>
+      <c r="B471" s="10"/>
       <c r="C471" s="2">
         <v>3</v>
       </c>
@@ -13230,7 +13228,7 @@
       <c r="A472" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B472" s="8"/>
+      <c r="B472" s="10"/>
       <c r="C472" s="2">
         <v>4</v>
       </c>
@@ -13242,7 +13240,7 @@
       <c r="A473" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B473" s="8"/>
+      <c r="B473" s="10"/>
       <c r="C473" s="2">
         <v>5</v>
       </c>
@@ -13254,7 +13252,7 @@
       <c r="A474" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B474" s="8"/>
+      <c r="B474" s="10"/>
       <c r="C474" s="2">
         <v>99</v>
       </c>
@@ -13266,7 +13264,7 @@
       <c r="A475" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B475" s="7" t="s">
+      <c r="B475" s="9" t="s">
         <v>401</v>
       </c>
       <c r="C475" s="3">
@@ -13280,7 +13278,7 @@
       <c r="A476" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B476" s="8"/>
+      <c r="B476" s="10"/>
       <c r="C476" s="2">
         <v>2</v>
       </c>
@@ -13292,7 +13290,7 @@
       <c r="A477" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B477" s="8"/>
+      <c r="B477" s="10"/>
       <c r="C477" s="2">
         <v>3</v>
       </c>
@@ -13304,7 +13302,7 @@
       <c r="A478" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B478" s="8"/>
+      <c r="B478" s="10"/>
       <c r="C478" s="2">
         <v>4</v>
       </c>
@@ -13316,7 +13314,7 @@
       <c r="A479" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B479" s="8"/>
+      <c r="B479" s="10"/>
       <c r="C479" s="2">
         <v>5</v>
       </c>
@@ -13328,7 +13326,7 @@
       <c r="A480" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B480" s="8"/>
+      <c r="B480" s="10"/>
       <c r="C480" s="2">
         <v>99</v>
       </c>
@@ -13340,7 +13338,7 @@
       <c r="A481" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B481" s="7" t="s">
+      <c r="B481" s="9" t="s">
         <v>403</v>
       </c>
       <c r="C481" s="3">
@@ -13354,7 +13352,7 @@
       <c r="A482" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B482" s="8"/>
+      <c r="B482" s="10"/>
       <c r="C482" s="2">
         <v>2</v>
       </c>
@@ -13366,7 +13364,7 @@
       <c r="A483" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B483" s="8"/>
+      <c r="B483" s="10"/>
       <c r="C483" s="2">
         <v>3</v>
       </c>
@@ -13378,7 +13376,7 @@
       <c r="A484" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B484" s="8"/>
+      <c r="B484" s="10"/>
       <c r="C484" s="2">
         <v>4</v>
       </c>
@@ -13390,7 +13388,7 @@
       <c r="A485" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B485" s="8"/>
+      <c r="B485" s="10"/>
       <c r="C485" s="2">
         <v>5</v>
       </c>
@@ -13402,7 +13400,7 @@
       <c r="A486" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B486" s="8"/>
+      <c r="B486" s="10"/>
       <c r="C486" s="2">
         <v>99</v>
       </c>
@@ -13414,7 +13412,7 @@
       <c r="A487" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B487" s="7" t="s">
+      <c r="B487" s="9" t="s">
         <v>405</v>
       </c>
       <c r="C487" s="3">
@@ -13428,7 +13426,7 @@
       <c r="A488" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B488" s="8"/>
+      <c r="B488" s="10"/>
       <c r="C488" s="2">
         <v>2</v>
       </c>
@@ -13440,7 +13438,7 @@
       <c r="A489" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B489" s="8"/>
+      <c r="B489" s="10"/>
       <c r="C489" s="2">
         <v>3</v>
       </c>
@@ -13452,7 +13450,7 @@
       <c r="A490" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B490" s="8"/>
+      <c r="B490" s="10"/>
       <c r="C490" s="2">
         <v>4</v>
       </c>
@@ -13464,7 +13462,7 @@
       <c r="A491" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B491" s="8"/>
+      <c r="B491" s="10"/>
       <c r="C491" s="2">
         <v>5</v>
       </c>
@@ -13476,7 +13474,7 @@
       <c r="A492" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B492" s="8"/>
+      <c r="B492" s="10"/>
       <c r="C492" s="2">
         <v>99</v>
       </c>
@@ -13488,7 +13486,7 @@
       <c r="A493" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B493" s="7" t="s">
+      <c r="B493" s="9" t="s">
         <v>407</v>
       </c>
       <c r="C493" s="3">
@@ -13502,7 +13500,7 @@
       <c r="A494" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B494" s="8"/>
+      <c r="B494" s="10"/>
       <c r="C494" s="2">
         <v>2</v>
       </c>
@@ -13514,7 +13512,7 @@
       <c r="A495" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B495" s="8"/>
+      <c r="B495" s="10"/>
       <c r="C495" s="2">
         <v>3</v>
       </c>
@@ -13526,7 +13524,7 @@
       <c r="A496" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B496" s="8"/>
+      <c r="B496" s="10"/>
       <c r="C496" s="2">
         <v>4</v>
       </c>
@@ -13538,7 +13536,7 @@
       <c r="A497" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B497" s="8"/>
+      <c r="B497" s="10"/>
       <c r="C497" s="2">
         <v>5</v>
       </c>
@@ -13550,7 +13548,7 @@
       <c r="A498" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B498" s="8"/>
+      <c r="B498" s="10"/>
       <c r="C498" s="2">
         <v>99</v>
       </c>
@@ -13562,7 +13560,7 @@
       <c r="A499" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B499" s="7" t="s">
+      <c r="B499" s="9" t="s">
         <v>409</v>
       </c>
       <c r="C499" s="3">
@@ -13576,7 +13574,7 @@
       <c r="A500" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B500" s="8"/>
+      <c r="B500" s="10"/>
       <c r="C500" s="2">
         <v>2</v>
       </c>
@@ -13588,7 +13586,7 @@
       <c r="A501" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B501" s="8"/>
+      <c r="B501" s="10"/>
       <c r="C501" s="2">
         <v>3</v>
       </c>
@@ -13600,7 +13598,7 @@
       <c r="A502" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B502" s="8"/>
+      <c r="B502" s="10"/>
       <c r="C502" s="2">
         <v>4</v>
       </c>
@@ -13612,7 +13610,7 @@
       <c r="A503" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B503" s="8"/>
+      <c r="B503" s="10"/>
       <c r="C503" s="2">
         <v>5</v>
       </c>
@@ -13624,7 +13622,7 @@
       <c r="A504" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B504" s="8"/>
+      <c r="B504" s="10"/>
       <c r="C504" s="2">
         <v>99</v>
       </c>
@@ -13636,7 +13634,7 @@
       <c r="A505" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B505" s="7" t="s">
+      <c r="B505" s="9" t="s">
         <v>411</v>
       </c>
       <c r="C505" s="3">
@@ -13650,7 +13648,7 @@
       <c r="A506" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B506" s="8"/>
+      <c r="B506" s="10"/>
       <c r="C506" s="2">
         <v>2</v>
       </c>
@@ -13662,7 +13660,7 @@
       <c r="A507" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B507" s="8"/>
+      <c r="B507" s="10"/>
       <c r="C507" s="2">
         <v>3</v>
       </c>
@@ -13674,7 +13672,7 @@
       <c r="A508" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B508" s="8"/>
+      <c r="B508" s="10"/>
       <c r="C508" s="2">
         <v>4</v>
       </c>
@@ -13686,7 +13684,7 @@
       <c r="A509" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B509" s="8"/>
+      <c r="B509" s="10"/>
       <c r="C509" s="2">
         <v>5</v>
       </c>
@@ -13698,7 +13696,7 @@
       <c r="A510" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B510" s="8"/>
+      <c r="B510" s="10"/>
       <c r="C510" s="2">
         <v>99</v>
       </c>
@@ -13710,7 +13708,7 @@
       <c r="A511" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B511" s="7" t="s">
+      <c r="B511" s="9" t="s">
         <v>413</v>
       </c>
       <c r="C511" s="3">
@@ -13724,7 +13722,7 @@
       <c r="A512" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B512" s="8"/>
+      <c r="B512" s="10"/>
       <c r="C512" s="2">
         <v>2</v>
       </c>
@@ -13736,7 +13734,7 @@
       <c r="A513" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B513" s="8"/>
+      <c r="B513" s="10"/>
       <c r="C513" s="2">
         <v>3</v>
       </c>
@@ -13748,7 +13746,7 @@
       <c r="A514" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B514" s="8"/>
+      <c r="B514" s="10"/>
       <c r="C514" s="2">
         <v>4</v>
       </c>
@@ -13760,7 +13758,7 @@
       <c r="A515" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B515" s="8"/>
+      <c r="B515" s="10"/>
       <c r="C515" s="2">
         <v>5</v>
       </c>
@@ -13772,7 +13770,7 @@
       <c r="A516" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B516" s="8"/>
+      <c r="B516" s="10"/>
       <c r="C516" s="2">
         <v>99</v>
       </c>
@@ -13784,7 +13782,7 @@
       <c r="A517" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B517" s="7" t="s">
+      <c r="B517" s="9" t="s">
         <v>415</v>
       </c>
       <c r="C517" s="3">
@@ -13798,7 +13796,7 @@
       <c r="A518" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B518" s="8"/>
+      <c r="B518" s="10"/>
       <c r="C518" s="2">
         <v>2</v>
       </c>
@@ -13810,7 +13808,7 @@
       <c r="A519" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B519" s="8"/>
+      <c r="B519" s="10"/>
       <c r="C519" s="2">
         <v>3</v>
       </c>
@@ -13822,7 +13820,7 @@
       <c r="A520" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B520" s="8"/>
+      <c r="B520" s="10"/>
       <c r="C520" s="2">
         <v>4</v>
       </c>
@@ -13834,7 +13832,7 @@
       <c r="A521" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B521" s="8"/>
+      <c r="B521" s="10"/>
       <c r="C521" s="2">
         <v>5</v>
       </c>
@@ -13846,7 +13844,7 @@
       <c r="A522" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B522" s="8"/>
+      <c r="B522" s="10"/>
       <c r="C522" s="2">
         <v>99</v>
       </c>
@@ -13858,7 +13856,7 @@
       <c r="A523" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B523" s="7" t="s">
+      <c r="B523" s="9" t="s">
         <v>417</v>
       </c>
       <c r="C523" s="3">
@@ -13872,7 +13870,7 @@
       <c r="A524" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B524" s="8"/>
+      <c r="B524" s="10"/>
       <c r="C524" s="2">
         <v>2</v>
       </c>
@@ -13884,7 +13882,7 @@
       <c r="A525" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B525" s="8"/>
+      <c r="B525" s="10"/>
       <c r="C525" s="2">
         <v>3</v>
       </c>
@@ -13896,7 +13894,7 @@
       <c r="A526" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B526" s="8"/>
+      <c r="B526" s="10"/>
       <c r="C526" s="2">
         <v>4</v>
       </c>
@@ -13908,7 +13906,7 @@
       <c r="A527" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B527" s="8"/>
+      <c r="B527" s="10"/>
       <c r="C527" s="2">
         <v>5</v>
       </c>
@@ -13920,7 +13918,7 @@
       <c r="A528" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B528" s="8"/>
+      <c r="B528" s="10"/>
       <c r="C528" s="2">
         <v>99</v>
       </c>
@@ -13932,7 +13930,7 @@
       <c r="A529" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B529" s="7" t="s">
+      <c r="B529" s="9" t="s">
         <v>424</v>
       </c>
       <c r="C529" s="3">
@@ -13946,7 +13944,7 @@
       <c r="A530" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B530" s="8"/>
+      <c r="B530" s="10"/>
       <c r="C530" s="2">
         <v>2</v>
       </c>
@@ -13958,7 +13956,7 @@
       <c r="A531" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B531" s="8"/>
+      <c r="B531" s="10"/>
       <c r="C531" s="2">
         <v>3</v>
       </c>
@@ -13970,7 +13968,7 @@
       <c r="A532" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B532" s="8"/>
+      <c r="B532" s="10"/>
       <c r="C532" s="2">
         <v>4</v>
       </c>
@@ -13982,7 +13980,7 @@
       <c r="A533" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B533" s="8"/>
+      <c r="B533" s="10"/>
       <c r="C533" s="2">
         <v>5</v>
       </c>
@@ -13994,7 +13992,7 @@
       <c r="A534" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B534" s="8"/>
+      <c r="B534" s="10"/>
       <c r="C534" s="2">
         <v>99</v>
       </c>
@@ -14006,7 +14004,7 @@
       <c r="A535" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B535" s="7" t="s">
+      <c r="B535" s="9" t="s">
         <v>426</v>
       </c>
       <c r="C535" s="3">
@@ -14020,7 +14018,7 @@
       <c r="A536" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B536" s="8"/>
+      <c r="B536" s="10"/>
       <c r="C536" s="2">
         <v>2</v>
       </c>
@@ -14032,7 +14030,7 @@
       <c r="A537" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B537" s="8"/>
+      <c r="B537" s="10"/>
       <c r="C537" s="2">
         <v>3</v>
       </c>
@@ -14044,7 +14042,7 @@
       <c r="A538" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B538" s="8"/>
+      <c r="B538" s="10"/>
       <c r="C538" s="2">
         <v>4</v>
       </c>
@@ -14056,7 +14054,7 @@
       <c r="A539" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B539" s="8"/>
+      <c r="B539" s="10"/>
       <c r="C539" s="2">
         <v>5</v>
       </c>
@@ -14068,7 +14066,7 @@
       <c r="A540" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B540" s="8"/>
+      <c r="B540" s="10"/>
       <c r="C540" s="2">
         <v>99</v>
       </c>
@@ -14080,7 +14078,7 @@
       <c r="A541" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B541" s="7" t="s">
+      <c r="B541" s="9" t="s">
         <v>428</v>
       </c>
       <c r="C541" s="3">
@@ -14094,7 +14092,7 @@
       <c r="A542" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B542" s="8"/>
+      <c r="B542" s="10"/>
       <c r="C542" s="2">
         <v>2</v>
       </c>
@@ -14106,7 +14104,7 @@
       <c r="A543" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B543" s="8"/>
+      <c r="B543" s="10"/>
       <c r="C543" s="2">
         <v>3</v>
       </c>
@@ -14118,7 +14116,7 @@
       <c r="A544" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B544" s="8"/>
+      <c r="B544" s="10"/>
       <c r="C544" s="2">
         <v>4</v>
       </c>
@@ -14130,7 +14128,7 @@
       <c r="A545" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B545" s="8"/>
+      <c r="B545" s="10"/>
       <c r="C545" s="2">
         <v>5</v>
       </c>
@@ -14142,7 +14140,7 @@
       <c r="A546" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B546" s="8"/>
+      <c r="B546" s="10"/>
       <c r="C546" s="2">
         <v>99</v>
       </c>
@@ -14154,7 +14152,7 @@
       <c r="A547" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B547" s="7" t="s">
+      <c r="B547" s="9" t="s">
         <v>430</v>
       </c>
       <c r="C547" s="3">
@@ -14168,7 +14166,7 @@
       <c r="A548" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B548" s="8"/>
+      <c r="B548" s="10"/>
       <c r="C548" s="2">
         <v>2</v>
       </c>
@@ -14180,7 +14178,7 @@
       <c r="A549" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B549" s="8"/>
+      <c r="B549" s="10"/>
       <c r="C549" s="2">
         <v>3</v>
       </c>
@@ -14192,7 +14190,7 @@
       <c r="A550" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B550" s="8"/>
+      <c r="B550" s="10"/>
       <c r="C550" s="2">
         <v>4</v>
       </c>
@@ -14204,7 +14202,7 @@
       <c r="A551" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B551" s="8"/>
+      <c r="B551" s="10"/>
       <c r="C551" s="2">
         <v>5</v>
       </c>
@@ -14216,7 +14214,7 @@
       <c r="A552" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B552" s="8"/>
+      <c r="B552" s="10"/>
       <c r="C552" s="2">
         <v>99</v>
       </c>
@@ -14228,7 +14226,7 @@
       <c r="A553" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B553" s="7" t="s">
+      <c r="B553" s="9" t="s">
         <v>432</v>
       </c>
       <c r="C553" s="3">
@@ -14242,7 +14240,7 @@
       <c r="A554" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B554" s="8"/>
+      <c r="B554" s="10"/>
       <c r="C554" s="2">
         <v>2</v>
       </c>
@@ -14254,7 +14252,7 @@
       <c r="A555" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B555" s="8"/>
+      <c r="B555" s="10"/>
       <c r="C555" s="2">
         <v>3</v>
       </c>
@@ -14266,7 +14264,7 @@
       <c r="A556" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B556" s="8"/>
+      <c r="B556" s="10"/>
       <c r="C556" s="2">
         <v>4</v>
       </c>
@@ -14278,7 +14276,7 @@
       <c r="A557" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B557" s="8"/>
+      <c r="B557" s="10"/>
       <c r="C557" s="2">
         <v>5</v>
       </c>
@@ -14290,7 +14288,7 @@
       <c r="A558" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B558" s="8"/>
+      <c r="B558" s="10"/>
       <c r="C558" s="2">
         <v>99</v>
       </c>
@@ -14564,7 +14562,7 @@
       <c r="A580" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B580" s="7" t="s">
+      <c r="B580" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C580" s="3">
@@ -14578,7 +14576,7 @@
       <c r="A581" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B581" s="8"/>
+      <c r="B581" s="10"/>
       <c r="C581" s="2">
         <v>2</v>
       </c>
@@ -14590,7 +14588,7 @@
       <c r="A582" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B582" s="8"/>
+      <c r="B582" s="10"/>
       <c r="C582" s="2">
         <v>99</v>
       </c>
@@ -14602,7 +14600,7 @@
       <c r="A583" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B583" s="7" t="s">
+      <c r="B583" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C583" s="3">
@@ -14616,7 +14614,7 @@
       <c r="A584" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B584" s="8"/>
+      <c r="B584" s="10"/>
       <c r="C584" s="2">
         <v>2</v>
       </c>
@@ -14628,7 +14626,7 @@
       <c r="A585" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B585" s="8"/>
+      <c r="B585" s="10"/>
       <c r="C585" s="2">
         <v>99</v>
       </c>
@@ -14640,7 +14638,7 @@
       <c r="A586" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B586" s="7" t="s">
+      <c r="B586" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C586" s="3">
@@ -14654,7 +14652,7 @@
       <c r="A587" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B587" s="8"/>
+      <c r="B587" s="10"/>
       <c r="C587" s="2">
         <v>2</v>
       </c>
@@ -14666,7 +14664,7 @@
       <c r="A588" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B588" s="8"/>
+      <c r="B588" s="10"/>
       <c r="C588" s="2">
         <v>99</v>
       </c>
@@ -14678,7 +14676,7 @@
       <c r="A589" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B589" s="7" t="s">
+      <c r="B589" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C589" s="3">
@@ -14692,7 +14690,7 @@
       <c r="A590" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B590" s="8"/>
+      <c r="B590" s="10"/>
       <c r="C590" s="2">
         <v>2</v>
       </c>
@@ -14704,7 +14702,7 @@
       <c r="A591" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B591" s="8"/>
+      <c r="B591" s="10"/>
       <c r="C591" s="2">
         <v>99</v>
       </c>
@@ -14716,7 +14714,7 @@
       <c r="A592" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B592" s="7" t="s">
+      <c r="B592" s="9" t="s">
         <v>466</v>
       </c>
       <c r="C592" s="3">
@@ -14730,7 +14728,7 @@
       <c r="A593" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B593" s="8"/>
+      <c r="B593" s="10"/>
       <c r="C593" s="2">
         <v>10000</v>
       </c>
@@ -14742,7 +14740,7 @@
       <c r="A594" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B594" s="8"/>
+      <c r="B594" s="10"/>
       <c r="C594" s="2">
         <v>20000</v>
       </c>
@@ -14754,7 +14752,7 @@
       <c r="A595" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B595" s="8"/>
+      <c r="B595" s="10"/>
       <c r="C595" s="2">
         <v>30000</v>
       </c>
@@ -14766,7 +14764,7 @@
       <c r="A596" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B596" s="8"/>
+      <c r="B596" s="10"/>
       <c r="C596" s="2">
         <v>40001</v>
       </c>
@@ -14778,7 +14776,7 @@
       <c r="A597" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B597" s="8"/>
+      <c r="B597" s="10"/>
       <c r="C597" s="2">
         <v>40002</v>
       </c>
@@ -14790,7 +14788,7 @@
       <c r="A598" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B598" s="8"/>
+      <c r="B598" s="10"/>
       <c r="C598" s="2">
         <v>50000</v>
       </c>
@@ -14802,7 +14800,7 @@
       <c r="A599" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B599" s="8"/>
+      <c r="B599" s="10"/>
       <c r="C599" s="2">
         <v>60000</v>
       </c>
@@ -14814,7 +14812,7 @@
       <c r="A600" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B600" s="8"/>
+      <c r="B600" s="10"/>
       <c r="C600" s="2">
         <v>70000</v>
       </c>
@@ -14826,7 +14824,7 @@
       <c r="A601" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B601" s="8"/>
+      <c r="B601" s="10"/>
       <c r="C601" s="2">
         <v>80000</v>
       </c>
@@ -14838,7 +14836,7 @@
       <c r="A602" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B602" s="8"/>
+      <c r="B602" s="10"/>
       <c r="C602" s="2">
         <v>90001</v>
       </c>
@@ -14850,7 +14848,7 @@
       <c r="A603" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B603" s="8"/>
+      <c r="B603" s="10"/>
       <c r="C603" s="2">
         <v>90002</v>
       </c>
@@ -14862,7 +14860,7 @@
       <c r="A604" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B604" s="8"/>
+      <c r="B604" s="10"/>
       <c r="C604" s="2">
         <v>100000</v>
       </c>
@@ -14874,7 +14872,7 @@
       <c r="A605" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B605" s="8"/>
+      <c r="B605" s="10"/>
       <c r="C605" s="2">
         <v>900000</v>
       </c>
@@ -15322,7 +15320,7 @@
       <c r="A642" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B642" s="7" t="s">
+      <c r="B642" s="9" t="s">
         <v>474</v>
       </c>
       <c r="C642" s="3">
@@ -15336,7 +15334,7 @@
       <c r="A643" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B643" s="8"/>
+      <c r="B643" s="10"/>
       <c r="C643" s="2">
         <v>2</v>
       </c>
@@ -15348,7 +15346,7 @@
       <c r="A644" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B644" s="8"/>
+      <c r="B644" s="10"/>
       <c r="C644" s="2">
         <v>3</v>
       </c>
@@ -15360,7 +15358,7 @@
       <c r="A645" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B645" s="8"/>
+      <c r="B645" s="10"/>
       <c r="C645" s="2">
         <v>4</v>
       </c>
@@ -15372,7 +15370,7 @@
       <c r="A646" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B646" s="8"/>
+      <c r="B646" s="10"/>
       <c r="C646" s="2">
         <v>99</v>
       </c>
@@ -15384,7 +15382,7 @@
       <c r="A647" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B647" s="7" t="s">
+      <c r="B647" s="9" t="s">
         <v>476</v>
       </c>
       <c r="C647" s="3">
@@ -15398,7 +15396,7 @@
       <c r="A648" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B648" s="8"/>
+      <c r="B648" s="10"/>
       <c r="C648" s="2">
         <v>2</v>
       </c>
@@ -15410,7 +15408,7 @@
       <c r="A649" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B649" s="8"/>
+      <c r="B649" s="10"/>
       <c r="C649" s="2">
         <v>3</v>
       </c>
@@ -15422,7 +15420,7 @@
       <c r="A650" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B650" s="8"/>
+      <c r="B650" s="10"/>
       <c r="C650" s="2">
         <v>4</v>
       </c>
@@ -15434,7 +15432,7 @@
       <c r="A651" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B651" s="8"/>
+      <c r="B651" s="10"/>
       <c r="C651" s="2">
         <v>99</v>
       </c>
@@ -15446,7 +15444,7 @@
       <c r="A652" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B652" s="7" t="s">
+      <c r="B652" s="9" t="s">
         <v>478</v>
       </c>
       <c r="C652" s="3">
@@ -15460,7 +15458,7 @@
       <c r="A653" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B653" s="8"/>
+      <c r="B653" s="10"/>
       <c r="C653" s="2">
         <v>2</v>
       </c>
@@ -15472,7 +15470,7 @@
       <c r="A654" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B654" s="8"/>
+      <c r="B654" s="10"/>
       <c r="C654" s="2">
         <v>3</v>
       </c>
@@ -15484,7 +15482,7 @@
       <c r="A655" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B655" s="8"/>
+      <c r="B655" s="10"/>
       <c r="C655" s="2">
         <v>4</v>
       </c>
@@ -15496,7 +15494,7 @@
       <c r="A656" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B656" s="8"/>
+      <c r="B656" s="10"/>
       <c r="C656" s="2">
         <v>5</v>
       </c>
@@ -15508,7 +15506,7 @@
       <c r="A657" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B657" s="8"/>
+      <c r="B657" s="10"/>
       <c r="C657" s="2">
         <v>6</v>
       </c>
@@ -15520,7 +15518,7 @@
       <c r="A658" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B658" s="8"/>
+      <c r="B658" s="10"/>
       <c r="C658" s="2">
         <v>99</v>
       </c>
@@ -15742,7 +15740,7 @@
       <c r="A676" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B676" s="7" t="s">
+      <c r="B676" s="9" t="s">
         <v>497</v>
       </c>
       <c r="C676" s="3">
@@ -15756,7 +15754,7 @@
       <c r="A677" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B677" s="8"/>
+      <c r="B677" s="10"/>
       <c r="C677" s="2">
         <v>2</v>
       </c>
@@ -15768,7 +15766,7 @@
       <c r="A678" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B678" s="8"/>
+      <c r="B678" s="10"/>
       <c r="C678" s="2">
         <v>3</v>
       </c>
@@ -15780,7 +15778,7 @@
       <c r="A679" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B679" s="8"/>
+      <c r="B679" s="10"/>
       <c r="C679" s="2">
         <v>4</v>
       </c>
@@ -15792,7 +15790,7 @@
       <c r="A680" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B680" s="8"/>
+      <c r="B680" s="10"/>
       <c r="C680" s="2">
         <v>99</v>
       </c>
@@ -15804,7 +15802,7 @@
       <c r="A681" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B681" s="7" t="s">
+      <c r="B681" s="9" t="s">
         <v>503</v>
       </c>
       <c r="C681" s="3">
@@ -15818,7 +15816,7 @@
       <c r="A682" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B682" s="8"/>
+      <c r="B682" s="10"/>
       <c r="C682" s="2">
         <v>2</v>
       </c>
@@ -15830,7 +15828,7 @@
       <c r="A683" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B683" s="8"/>
+      <c r="B683" s="10"/>
       <c r="C683" s="2">
         <v>3</v>
       </c>
@@ -15842,7 +15840,7 @@
       <c r="A684" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B684" s="8"/>
+      <c r="B684" s="10"/>
       <c r="C684" s="2">
         <v>4</v>
       </c>
@@ -15854,7 +15852,7 @@
       <c r="A685" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B685" s="8"/>
+      <c r="B685" s="10"/>
       <c r="C685" s="2">
         <v>99</v>
       </c>
@@ -15866,7 +15864,7 @@
       <c r="A686" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B686" s="7" t="s">
+      <c r="B686" s="9" t="s">
         <v>509</v>
       </c>
       <c r="C686" s="3">
@@ -15880,7 +15878,7 @@
       <c r="A687" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B687" s="8"/>
+      <c r="B687" s="10"/>
       <c r="C687" s="2">
         <v>2</v>
       </c>
@@ -15892,7 +15890,7 @@
       <c r="A688" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B688" s="8"/>
+      <c r="B688" s="10"/>
       <c r="C688" s="2">
         <v>3</v>
       </c>
@@ -15904,7 +15902,7 @@
       <c r="A689" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B689" s="8"/>
+      <c r="B689" s="10"/>
       <c r="C689" s="2">
         <v>4</v>
       </c>
@@ -15916,7 +15914,7 @@
       <c r="A690" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B690" s="8"/>
+      <c r="B690" s="10"/>
       <c r="C690" s="2">
         <v>5</v>
       </c>
@@ -15928,7 +15926,7 @@
       <c r="A691" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B691" s="8"/>
+      <c r="B691" s="10"/>
       <c r="C691" s="2">
         <v>99</v>
       </c>
@@ -15940,7 +15938,7 @@
       <c r="A692" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B692" s="7" t="s">
+      <c r="B692" s="9" t="s">
         <v>515</v>
       </c>
       <c r="C692" s="3">
@@ -15954,7 +15952,7 @@
       <c r="A693" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B693" s="8"/>
+      <c r="B693" s="10"/>
       <c r="C693" s="2">
         <v>2</v>
       </c>
@@ -15966,7 +15964,7 @@
       <c r="A694" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B694" s="8"/>
+      <c r="B694" s="10"/>
       <c r="C694" s="2">
         <v>3</v>
       </c>
@@ -15978,7 +15976,7 @@
       <c r="A695" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B695" s="8"/>
+      <c r="B695" s="10"/>
       <c r="C695" s="2">
         <v>4</v>
       </c>
@@ -15990,7 +15988,7 @@
       <c r="A696" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B696" s="8"/>
+      <c r="B696" s="10"/>
       <c r="C696" s="2">
         <v>5</v>
       </c>
@@ -16002,7 +16000,7 @@
       <c r="A697" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B697" s="8"/>
+      <c r="B697" s="10"/>
       <c r="C697" s="2">
         <v>6</v>
       </c>
@@ -16014,7 +16012,7 @@
       <c r="A698" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B698" s="8"/>
+      <c r="B698" s="10"/>
       <c r="C698" s="2">
         <v>99</v>
       </c>
@@ -17244,7 +17242,7 @@
       <c r="A798" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B798" s="7" t="s">
+      <c r="B798" s="9" t="s">
         <v>572</v>
       </c>
       <c r="C798" s="3">
@@ -17258,7 +17256,7 @@
       <c r="A799" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B799" s="8"/>
+      <c r="B799" s="10"/>
       <c r="C799" s="2">
         <v>2</v>
       </c>
@@ -17270,7 +17268,7 @@
       <c r="A800" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B800" s="8"/>
+      <c r="B800" s="10"/>
       <c r="C800" s="2">
         <v>99</v>
       </c>
@@ -17282,7 +17280,7 @@
       <c r="A801" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B801" s="7" t="s">
+      <c r="B801" s="9" t="s">
         <v>576</v>
       </c>
       <c r="C801" s="3">
@@ -17296,7 +17294,7 @@
       <c r="A802" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B802" s="8"/>
+      <c r="B802" s="10"/>
       <c r="C802" s="2">
         <v>2</v>
       </c>
@@ -17308,7 +17306,7 @@
       <c r="A803" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B803" s="8"/>
+      <c r="B803" s="10"/>
       <c r="C803" s="2">
         <v>99</v>
       </c>
@@ -17320,7 +17318,7 @@
       <c r="A804" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B804" s="7" t="s">
+      <c r="B804" s="9" t="s">
         <v>578</v>
       </c>
       <c r="C804" s="3">
@@ -17334,7 +17332,7 @@
       <c r="A805" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B805" s="8"/>
+      <c r="B805" s="10"/>
       <c r="C805" s="2">
         <v>2</v>
       </c>
@@ -17346,7 +17344,7 @@
       <c r="A806" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B806" s="8"/>
+      <c r="B806" s="10"/>
       <c r="C806" s="2">
         <v>99</v>
       </c>
@@ -17358,7 +17356,7 @@
       <c r="A807" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B807" s="7" t="s">
+      <c r="B807" s="9" t="s">
         <v>580</v>
       </c>
       <c r="C807" s="3">
@@ -17372,7 +17370,7 @@
       <c r="A808" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B808" s="8"/>
+      <c r="B808" s="10"/>
       <c r="C808" s="2">
         <v>2</v>
       </c>
@@ -17384,7 +17382,7 @@
       <c r="A809" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B809" s="8"/>
+      <c r="B809" s="10"/>
       <c r="C809" s="2">
         <v>99</v>
       </c>
@@ -17396,7 +17394,7 @@
       <c r="A810" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B810" s="7" t="s">
+      <c r="B810" s="9" t="s">
         <v>582</v>
       </c>
       <c r="C810" s="3">
@@ -17410,7 +17408,7 @@
       <c r="A811" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B811" s="8"/>
+      <c r="B811" s="10"/>
       <c r="C811" s="2">
         <v>2</v>
       </c>
@@ -17422,7 +17420,7 @@
       <c r="A812" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B812" s="8"/>
+      <c r="B812" s="10"/>
       <c r="C812" s="2">
         <v>99</v>
       </c>
@@ -17434,7 +17432,7 @@
       <c r="A813" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B813" s="7" t="s">
+      <c r="B813" s="9" t="s">
         <v>584</v>
       </c>
       <c r="C813" s="3">
@@ -17448,7 +17446,7 @@
       <c r="A814" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B814" s="8"/>
+      <c r="B814" s="10"/>
       <c r="C814" s="2">
         <v>2</v>
       </c>
@@ -17460,7 +17458,7 @@
       <c r="A815" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B815" s="8"/>
+      <c r="B815" s="10"/>
       <c r="C815" s="2">
         <v>99</v>
       </c>
@@ -17472,7 +17470,7 @@
       <c r="A816" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B816" s="7" t="s">
+      <c r="B816" s="9" t="s">
         <v>586</v>
       </c>
       <c r="C816" s="3">
@@ -17486,7 +17484,7 @@
       <c r="A817" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B817" s="8"/>
+      <c r="B817" s="10"/>
       <c r="C817" s="2">
         <v>2</v>
       </c>
@@ -17498,7 +17496,7 @@
       <c r="A818" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B818" s="8"/>
+      <c r="B818" s="10"/>
       <c r="C818" s="2">
         <v>3</v>
       </c>
@@ -17510,7 +17508,7 @@
       <c r="A819" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B819" s="8"/>
+      <c r="B819" s="10"/>
       <c r="C819" s="2">
         <v>4</v>
       </c>
@@ -17522,7 +17520,7 @@
       <c r="A820" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B820" s="8"/>
+      <c r="B820" s="10"/>
       <c r="C820" s="2">
         <v>99</v>
       </c>
@@ -17534,7 +17532,7 @@
       <c r="A821" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B821" s="7" t="s">
+      <c r="B821" s="9" t="s">
         <v>588</v>
       </c>
       <c r="C821" s="3">
@@ -17548,7 +17546,7 @@
       <c r="A822" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B822" s="8"/>
+      <c r="B822" s="10"/>
       <c r="C822" s="2">
         <v>2</v>
       </c>
@@ -17560,7 +17558,7 @@
       <c r="A823" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B823" s="8"/>
+      <c r="B823" s="10"/>
       <c r="C823" s="2">
         <v>3</v>
       </c>
@@ -17572,7 +17570,7 @@
       <c r="A824" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B824" s="8"/>
+      <c r="B824" s="10"/>
       <c r="C824" s="2">
         <v>4</v>
       </c>
@@ -17584,7 +17582,7 @@
       <c r="A825" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B825" s="8"/>
+      <c r="B825" s="10"/>
       <c r="C825" s="2">
         <v>99</v>
       </c>
@@ -17596,7 +17594,7 @@
       <c r="A826" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B826" s="7" t="s">
+      <c r="B826" s="9" t="s">
         <v>590</v>
       </c>
       <c r="C826" s="3">
@@ -17610,7 +17608,7 @@
       <c r="A827" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B827" s="8"/>
+      <c r="B827" s="10"/>
       <c r="C827" s="2">
         <v>2</v>
       </c>
@@ -17622,7 +17620,7 @@
       <c r="A828" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B828" s="8"/>
+      <c r="B828" s="10"/>
       <c r="C828" s="2">
         <v>3</v>
       </c>
@@ -17634,7 +17632,7 @@
       <c r="A829" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B829" s="8"/>
+      <c r="B829" s="10"/>
       <c r="C829" s="2">
         <v>4</v>
       </c>
@@ -17646,7 +17644,7 @@
       <c r="A830" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B830" s="8"/>
+      <c r="B830" s="10"/>
       <c r="C830" s="2">
         <v>99</v>
       </c>
@@ -17658,7 +17656,7 @@
       <c r="A831" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B831" s="7" t="s">
+      <c r="B831" s="9" t="s">
         <v>592</v>
       </c>
       <c r="C831" s="3">
@@ -17672,7 +17670,7 @@
       <c r="A832" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B832" s="8"/>
+      <c r="B832" s="10"/>
       <c r="C832" s="2">
         <v>2</v>
       </c>
@@ -17684,7 +17682,7 @@
       <c r="A833" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B833" s="8"/>
+      <c r="B833" s="10"/>
       <c r="C833" s="2">
         <v>3</v>
       </c>
@@ -17696,7 +17694,7 @@
       <c r="A834" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B834" s="8"/>
+      <c r="B834" s="10"/>
       <c r="C834" s="2">
         <v>4</v>
       </c>
@@ -17708,7 +17706,7 @@
       <c r="A835" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B835" s="8"/>
+      <c r="B835" s="10"/>
       <c r="C835" s="2">
         <v>99</v>
       </c>
@@ -17720,7 +17718,7 @@
       <c r="A836" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B836" s="7" t="s">
+      <c r="B836" s="9" t="s">
         <v>594</v>
       </c>
       <c r="C836" s="3">
@@ -17734,7 +17732,7 @@
       <c r="A837" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B837" s="8"/>
+      <c r="B837" s="10"/>
       <c r="C837" s="2">
         <v>2</v>
       </c>
@@ -17746,7 +17744,7 @@
       <c r="A838" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B838" s="8"/>
+      <c r="B838" s="10"/>
       <c r="C838" s="2">
         <v>3</v>
       </c>
@@ -17758,7 +17756,7 @@
       <c r="A839" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B839" s="8"/>
+      <c r="B839" s="10"/>
       <c r="C839" s="2">
         <v>4</v>
       </c>
@@ -17770,7 +17768,7 @@
       <c r="A840" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B840" s="8"/>
+      <c r="B840" s="10"/>
       <c r="C840" s="2">
         <v>5</v>
       </c>
@@ -17782,7 +17780,7 @@
       <c r="A841" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B841" s="8"/>
+      <c r="B841" s="10"/>
       <c r="C841" s="2">
         <v>6</v>
       </c>
@@ -17794,7 +17792,7 @@
       <c r="A842" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B842" s="8"/>
+      <c r="B842" s="10"/>
       <c r="C842" s="2">
         <v>7</v>
       </c>
@@ -17806,7 +17804,7 @@
       <c r="A843" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B843" s="8"/>
+      <c r="B843" s="10"/>
       <c r="C843" s="2">
         <v>99</v>
       </c>
@@ -17818,7 +17816,7 @@
       <c r="A844" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B844" s="7" t="s">
+      <c r="B844" s="9" t="s">
         <v>598</v>
       </c>
       <c r="C844" s="3">
@@ -17832,7 +17830,7 @@
       <c r="A845" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B845" s="8"/>
+      <c r="B845" s="10"/>
       <c r="C845" s="2">
         <v>2</v>
       </c>
@@ -17844,7 +17842,7 @@
       <c r="A846" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B846" s="8"/>
+      <c r="B846" s="10"/>
       <c r="C846" s="2">
         <v>99</v>
       </c>
@@ -17856,7 +17854,7 @@
       <c r="A847" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B847" s="7" t="s">
+      <c r="B847" s="9" t="s">
         <v>600</v>
       </c>
       <c r="C847" s="3">
@@ -17870,7 +17868,7 @@
       <c r="A848" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B848" s="8"/>
+      <c r="B848" s="10"/>
       <c r="C848" s="2">
         <v>2</v>
       </c>
@@ -17882,7 +17880,7 @@
       <c r="A849" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B849" s="8"/>
+      <c r="B849" s="10"/>
       <c r="C849" s="2">
         <v>3</v>
       </c>
@@ -17894,7 +17892,7 @@
       <c r="A850" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B850" s="8"/>
+      <c r="B850" s="10"/>
       <c r="C850" s="2">
         <v>4</v>
       </c>
@@ -17906,7 +17904,7 @@
       <c r="A851" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B851" s="8"/>
+      <c r="B851" s="10"/>
       <c r="C851" s="2">
         <v>5</v>
       </c>
@@ -17918,7 +17916,7 @@
       <c r="A852" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B852" s="8"/>
+      <c r="B852" s="10"/>
       <c r="C852" s="2">
         <v>9</v>
       </c>
@@ -17930,7 +17928,7 @@
       <c r="A853" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B853" s="7" t="s">
+      <c r="B853" s="9" t="s">
         <v>607</v>
       </c>
       <c r="C853" s="3">
@@ -17944,7 +17942,7 @@
       <c r="A854" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B854" s="8"/>
+      <c r="B854" s="10"/>
       <c r="C854" s="2">
         <v>2</v>
       </c>
@@ -17956,7 +17954,7 @@
       <c r="A855" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B855" s="8"/>
+      <c r="B855" s="10"/>
       <c r="C855" s="2">
         <v>99</v>
       </c>
@@ -17968,7 +17966,7 @@
       <c r="A856" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B856" s="7" t="s">
+      <c r="B856" s="9" t="s">
         <v>609</v>
       </c>
       <c r="C856" s="3">
@@ -17982,7 +17980,7 @@
       <c r="A857" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B857" s="8"/>
+      <c r="B857" s="10"/>
       <c r="C857" s="2">
         <v>2</v>
       </c>
@@ -17994,7 +17992,7 @@
       <c r="A858" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B858" s="8"/>
+      <c r="B858" s="10"/>
       <c r="C858" s="2">
         <v>3</v>
       </c>
@@ -18006,7 +18004,7 @@
       <c r="A859" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B859" s="8"/>
+      <c r="B859" s="10"/>
       <c r="C859" s="2">
         <v>4</v>
       </c>
@@ -18018,7 +18016,7 @@
       <c r="A860" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B860" s="8"/>
+      <c r="B860" s="10"/>
       <c r="C860" s="2">
         <v>99</v>
       </c>
@@ -18030,7 +18028,7 @@
       <c r="A861" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B861" s="7" t="s">
+      <c r="B861" s="9" t="s">
         <v>615</v>
       </c>
       <c r="C861" s="3">
@@ -18044,7 +18042,7 @@
       <c r="A862" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B862" s="8"/>
+      <c r="B862" s="10"/>
       <c r="C862" s="2">
         <v>2</v>
       </c>
@@ -18056,7 +18054,7 @@
       <c r="A863" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B863" s="8"/>
+      <c r="B863" s="10"/>
       <c r="C863" s="2">
         <v>3</v>
       </c>
@@ -18068,7 +18066,7 @@
       <c r="A864" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B864" s="8"/>
+      <c r="B864" s="10"/>
       <c r="C864" s="2">
         <v>99</v>
       </c>
@@ -18080,7 +18078,7 @@
       <c r="A865" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B865" s="7" t="s">
+      <c r="B865" s="9" t="s">
         <v>619</v>
       </c>
       <c r="C865" s="3">
@@ -18094,7 +18092,7 @@
       <c r="A866" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B866" s="8"/>
+      <c r="B866" s="10"/>
       <c r="C866" s="2">
         <v>2</v>
       </c>
@@ -18106,7 +18104,7 @@
       <c r="A867" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B867" s="8"/>
+      <c r="B867" s="10"/>
       <c r="C867" s="2">
         <v>3</v>
       </c>
@@ -18118,7 +18116,7 @@
       <c r="A868" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B868" s="8"/>
+      <c r="B868" s="10"/>
       <c r="C868" s="2">
         <v>4</v>
       </c>
@@ -18130,7 +18128,7 @@
       <c r="A869" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B869" s="8"/>
+      <c r="B869" s="10"/>
       <c r="C869" s="2">
         <v>5</v>
       </c>
@@ -18142,7 +18140,7 @@
       <c r="A870" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B870" s="8"/>
+      <c r="B870" s="10"/>
       <c r="C870" s="2">
         <v>99</v>
       </c>
@@ -18154,7 +18152,7 @@
       <c r="A871" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B871" s="7" t="s">
+      <c r="B871" s="9" t="s">
         <v>626</v>
       </c>
       <c r="C871" s="3">
@@ -18168,7 +18166,7 @@
       <c r="A872" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B872" s="8"/>
+      <c r="B872" s="10"/>
       <c r="C872" s="2">
         <v>2</v>
       </c>
@@ -18180,7 +18178,7 @@
       <c r="A873" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B873" s="8"/>
+      <c r="B873" s="10"/>
       <c r="C873" s="2">
         <v>3</v>
       </c>
@@ -18192,7 +18190,7 @@
       <c r="A874" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B874" s="8"/>
+      <c r="B874" s="10"/>
       <c r="C874" s="2">
         <v>99</v>
       </c>
@@ -18204,7 +18202,7 @@
       <c r="A875" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B875" s="7" t="s">
+      <c r="B875" s="9" t="s">
         <v>632</v>
       </c>
       <c r="C875" s="3">
@@ -18218,7 +18216,7 @@
       <c r="A876" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B876" s="8"/>
+      <c r="B876" s="10"/>
       <c r="C876" s="2">
         <v>2</v>
       </c>
@@ -18230,7 +18228,7 @@
       <c r="A877" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B877" s="8"/>
+      <c r="B877" s="10"/>
       <c r="C877" s="2">
         <v>3</v>
       </c>
@@ -18242,7 +18240,7 @@
       <c r="A878" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B878" s="8"/>
+      <c r="B878" s="10"/>
       <c r="C878" s="2">
         <v>4</v>
       </c>
@@ -18254,7 +18252,7 @@
       <c r="A879" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B879" s="8"/>
+      <c r="B879" s="10"/>
       <c r="C879" s="2">
         <v>99</v>
       </c>
@@ -18266,7 +18264,7 @@
       <c r="A880" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B880" s="7" t="s">
+      <c r="B880" s="9" t="s">
         <v>638</v>
       </c>
       <c r="C880" s="3">
@@ -18280,7 +18278,7 @@
       <c r="A881" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B881" s="8"/>
+      <c r="B881" s="10"/>
       <c r="C881" s="2">
         <v>2</v>
       </c>
@@ -18292,7 +18290,7 @@
       <c r="A882" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B882" s="8"/>
+      <c r="B882" s="10"/>
       <c r="C882" s="2">
         <v>99</v>
       </c>
@@ -18342,7 +18340,7 @@
       <c r="A886" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B886" s="7" t="s">
+      <c r="B886" s="9" t="s">
         <v>644</v>
       </c>
       <c r="C886" s="3">
@@ -18356,7 +18354,7 @@
       <c r="A887" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B887" s="8"/>
+      <c r="B887" s="10"/>
       <c r="C887" s="2">
         <v>2</v>
       </c>
@@ -18368,7 +18366,7 @@
       <c r="A888" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B888" s="7" t="s">
+      <c r="B888" s="9" t="s">
         <v>647</v>
       </c>
       <c r="C888" s="3">
@@ -18382,7 +18380,7 @@
       <c r="A889" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B889" s="8"/>
+      <c r="B889" s="10"/>
       <c r="C889" s="2">
         <v>2</v>
       </c>
@@ -18394,7 +18392,7 @@
       <c r="A890" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B890" s="8"/>
+      <c r="B890" s="10"/>
       <c r="C890" s="2">
         <v>3</v>
       </c>
@@ -18406,7 +18404,7 @@
       <c r="A891" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B891" s="8"/>
+      <c r="B891" s="10"/>
       <c r="C891" s="2">
         <v>4</v>
       </c>
@@ -18418,7 +18416,7 @@
       <c r="A892" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B892" s="8"/>
+      <c r="B892" s="10"/>
       <c r="C892" s="2">
         <v>99</v>
       </c>
@@ -18468,7 +18466,7 @@
       <c r="A896" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B896" s="7" t="s">
+      <c r="B896" s="9" t="s">
         <v>657</v>
       </c>
       <c r="C896" s="3">
@@ -18482,7 +18480,7 @@
       <c r="A897" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B897" s="8"/>
+      <c r="B897" s="10"/>
       <c r="C897" s="2">
         <v>2</v>
       </c>
@@ -18494,7 +18492,7 @@
       <c r="A898" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B898" s="8"/>
+      <c r="B898" s="10"/>
       <c r="C898" s="2">
         <v>3</v>
       </c>
@@ -18506,7 +18504,7 @@
       <c r="A899" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B899" s="8"/>
+      <c r="B899" s="10"/>
       <c r="C899" s="2">
         <v>4</v>
       </c>
@@ -18518,7 +18516,7 @@
       <c r="A900" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B900" s="8"/>
+      <c r="B900" s="10"/>
       <c r="C900" s="2">
         <v>5</v>
       </c>
@@ -18530,7 +18528,7 @@
       <c r="A901" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B901" s="8"/>
+      <c r="B901" s="10"/>
       <c r="C901" s="2">
         <v>99</v>
       </c>
@@ -18728,7 +18726,7 @@
       <c r="A917" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B917" s="7" t="s">
+      <c r="B917" s="9" t="s">
         <v>676</v>
       </c>
       <c r="C917" s="3">
@@ -18742,7 +18740,7 @@
       <c r="A918" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B918" s="8"/>
+      <c r="B918" s="10"/>
       <c r="C918" s="2">
         <v>2</v>
       </c>
@@ -18754,7 +18752,7 @@
       <c r="A919" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B919" s="8"/>
+      <c r="B919" s="10"/>
       <c r="C919" s="2">
         <v>3</v>
       </c>
@@ -18766,7 +18764,7 @@
       <c r="A920" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B920" s="8"/>
+      <c r="B920" s="10"/>
       <c r="C920" s="2">
         <v>4</v>
       </c>
@@ -18778,7 +18776,7 @@
       <c r="A921" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B921" s="8"/>
+      <c r="B921" s="10"/>
       <c r="C921" s="2">
         <v>5</v>
       </c>
@@ -18790,7 +18788,7 @@
       <c r="A922" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B922" s="8"/>
+      <c r="B922" s="10"/>
       <c r="C922" s="2">
         <v>6</v>
       </c>
@@ -18802,7 +18800,7 @@
       <c r="A923" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B923" s="8"/>
+      <c r="B923" s="10"/>
       <c r="C923" s="2">
         <v>7</v>
       </c>
@@ -18814,7 +18812,7 @@
       <c r="A924" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B924" s="8"/>
+      <c r="B924" s="10"/>
       <c r="C924" s="2">
         <v>8</v>
       </c>
@@ -18826,7 +18824,7 @@
       <c r="A925" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B925" s="8"/>
+      <c r="B925" s="10"/>
       <c r="C925" s="2">
         <v>99</v>
       </c>
@@ -18838,7 +18836,7 @@
       <c r="A926" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B926" s="7" t="s">
+      <c r="B926" s="9" t="s">
         <v>686</v>
       </c>
       <c r="C926" s="3">
@@ -18852,7 +18850,7 @@
       <c r="A927" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B927" s="8"/>
+      <c r="B927" s="10"/>
       <c r="C927" s="2">
         <v>2</v>
       </c>
@@ -18864,7 +18862,7 @@
       <c r="A928" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B928" s="8"/>
+      <c r="B928" s="10"/>
       <c r="C928" s="2">
         <v>3</v>
       </c>
@@ -18876,7 +18874,7 @@
       <c r="A929" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B929" s="8"/>
+      <c r="B929" s="10"/>
       <c r="C929" s="2">
         <v>99</v>
       </c>
@@ -18888,7 +18886,7 @@
       <c r="A930" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B930" s="7" t="s">
+      <c r="B930" s="9" t="s">
         <v>691</v>
       </c>
       <c r="C930" s="3">
@@ -18902,7 +18900,7 @@
       <c r="A931" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B931" s="8"/>
+      <c r="B931" s="10"/>
       <c r="C931" s="2">
         <v>1</v>
       </c>
@@ -18914,7 +18912,7 @@
       <c r="A932" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B932" s="8"/>
+      <c r="B932" s="10"/>
       <c r="C932" s="2">
         <v>2</v>
       </c>
@@ -18926,7 +18924,7 @@
       <c r="A933" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B933" s="8"/>
+      <c r="B933" s="10"/>
       <c r="C933" s="2">
         <v>3</v>
       </c>
@@ -18938,7 +18936,7 @@
       <c r="A934" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B934" s="8"/>
+      <c r="B934" s="10"/>
       <c r="C934" s="2">
         <v>4</v>
       </c>
@@ -18950,7 +18948,7 @@
       <c r="A935" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B935" s="8"/>
+      <c r="B935" s="10"/>
       <c r="C935" s="2">
         <v>99</v>
       </c>
@@ -19048,7 +19046,7 @@
       <c r="A943" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B943" s="9" t="s">
+      <c r="B943" s="7" t="s">
         <v>702</v>
       </c>
       <c r="C943" s="3">
@@ -19062,7 +19060,7 @@
       <c r="A944" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B944" s="10"/>
+      <c r="B944" s="8"/>
       <c r="C944" s="2">
         <v>2</v>
       </c>
@@ -19074,7 +19072,7 @@
       <c r="A945" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B945" s="10"/>
+      <c r="B945" s="8"/>
       <c r="C945" s="2">
         <v>3</v>
       </c>
@@ -19086,7 +19084,7 @@
       <c r="A946" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B946" s="10"/>
+      <c r="B946" s="8"/>
       <c r="C946" s="2">
         <v>4</v>
       </c>
@@ -19098,7 +19096,7 @@
       <c r="A947" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B947" s="10"/>
+      <c r="B947" s="8"/>
       <c r="C947" s="2">
         <v>5</v>
       </c>
@@ -19110,7 +19108,7 @@
       <c r="A948" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B948" s="10"/>
+      <c r="B948" s="8"/>
       <c r="C948" s="2">
         <v>6</v>
       </c>
@@ -19122,7 +19120,7 @@
       <c r="A949" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B949" s="10"/>
+      <c r="B949" s="8"/>
       <c r="C949" s="2">
         <v>7</v>
       </c>
@@ -19134,7 +19132,7 @@
       <c r="A950" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B950" s="10"/>
+      <c r="B950" s="8"/>
       <c r="C950" s="2">
         <v>8</v>
       </c>
@@ -19146,7 +19144,7 @@
       <c r="A951" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B951" s="10"/>
+      <c r="B951" s="8"/>
       <c r="C951" s="2">
         <v>9</v>
       </c>
@@ -19158,7 +19156,7 @@
       <c r="A952" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B952" s="10"/>
+      <c r="B952" s="8"/>
       <c r="C952" s="2">
         <v>10</v>
       </c>
@@ -19170,7 +19168,7 @@
       <c r="A953" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B953" s="10"/>
+      <c r="B953" s="8"/>
       <c r="C953" s="2">
         <v>11</v>
       </c>
@@ -19182,7 +19180,7 @@
       <c r="A954" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B954" s="10"/>
+      <c r="B954" s="8"/>
       <c r="C954" s="2">
         <v>12</v>
       </c>
@@ -19194,7 +19192,7 @@
       <c r="A955" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B955" s="10"/>
+      <c r="B955" s="8"/>
       <c r="C955" s="2">
         <v>99</v>
       </c>
@@ -19636,7 +19634,7 @@
       <c r="A991" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B991" s="9" t="s">
+      <c r="B991" s="7" t="s">
         <v>740</v>
       </c>
       <c r="C991" s="3">
@@ -19650,7 +19648,7 @@
       <c r="A992" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B992" s="10"/>
+      <c r="B992" s="8"/>
       <c r="C992" s="2">
         <v>2</v>
       </c>
@@ -19662,7 +19660,7 @@
       <c r="A993" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B993" s="10"/>
+      <c r="B993" s="8"/>
       <c r="C993" s="2">
         <v>4</v>
       </c>
@@ -19674,7 +19672,7 @@
       <c r="A994" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B994" s="10"/>
+      <c r="B994" s="8"/>
       <c r="C994" s="2">
         <v>5</v>
       </c>
@@ -19686,7 +19684,7 @@
       <c r="A995" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B995" s="10"/>
+      <c r="B995" s="8"/>
       <c r="C995" s="2">
         <v>6</v>
       </c>
@@ -19698,7 +19696,7 @@
       <c r="A996" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B996" s="10"/>
+      <c r="B996" s="8"/>
       <c r="C996" s="2">
         <v>8</v>
       </c>
@@ -19710,7 +19708,7 @@
       <c r="A997" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B997" s="10"/>
+      <c r="B997" s="8"/>
       <c r="C997" s="2">
         <v>9</v>
       </c>
@@ -19722,7 +19720,7 @@
       <c r="A998" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B998" s="10"/>
+      <c r="B998" s="8"/>
       <c r="C998" s="2">
         <v>10</v>
       </c>
@@ -19734,7 +19732,7 @@
       <c r="A999" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B999" s="10"/>
+      <c r="B999" s="8"/>
       <c r="C999" s="2">
         <v>11</v>
       </c>
@@ -19746,7 +19744,7 @@
       <c r="A1000" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1000" s="10"/>
+      <c r="B1000" s="8"/>
       <c r="C1000" s="2">
         <v>12</v>
       </c>
@@ -19758,7 +19756,7 @@
       <c r="A1001" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1001" s="10"/>
+      <c r="B1001" s="8"/>
       <c r="C1001" s="2">
         <v>13</v>
       </c>
@@ -19770,7 +19768,7 @@
       <c r="A1002" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1002" s="10"/>
+      <c r="B1002" s="8"/>
       <c r="C1002" s="2">
         <v>15</v>
       </c>
@@ -19782,7 +19780,7 @@
       <c r="A1003" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1003" s="10"/>
+      <c r="B1003" s="8"/>
       <c r="C1003" s="2">
         <v>16</v>
       </c>
@@ -19794,7 +19792,7 @@
       <c r="A1004" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1004" s="10"/>
+      <c r="B1004" s="8"/>
       <c r="C1004" s="2">
         <v>17</v>
       </c>
@@ -19806,7 +19804,7 @@
       <c r="A1005" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1005" s="10"/>
+      <c r="B1005" s="8"/>
       <c r="C1005" s="2">
         <v>18</v>
       </c>
@@ -19818,7 +19816,7 @@
       <c r="A1006" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1006" s="10"/>
+      <c r="B1006" s="8"/>
       <c r="C1006" s="2">
         <v>19</v>
       </c>
@@ -19830,7 +19828,7 @@
       <c r="A1007" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1007" s="10"/>
+      <c r="B1007" s="8"/>
       <c r="C1007" s="2">
         <v>20</v>
       </c>
@@ -19842,7 +19840,7 @@
       <c r="A1008" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1008" s="10"/>
+      <c r="B1008" s="8"/>
       <c r="C1008" s="2">
         <v>21</v>
       </c>
@@ -19854,7 +19852,7 @@
       <c r="A1009" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1009" s="10"/>
+      <c r="B1009" s="8"/>
       <c r="C1009" s="2">
         <v>22</v>
       </c>
@@ -19866,7 +19864,7 @@
       <c r="A1010" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1010" s="10"/>
+      <c r="B1010" s="8"/>
       <c r="C1010" s="2">
         <v>23</v>
       </c>
@@ -19878,7 +19876,7 @@
       <c r="A1011" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1011" s="10"/>
+      <c r="B1011" s="8"/>
       <c r="C1011" s="2">
         <v>24</v>
       </c>
@@ -19890,7 +19888,7 @@
       <c r="A1012" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1012" s="10"/>
+      <c r="B1012" s="8"/>
       <c r="C1012" s="2">
         <v>25</v>
       </c>
@@ -19902,7 +19900,7 @@
       <c r="A1013" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1013" s="10"/>
+      <c r="B1013" s="8"/>
       <c r="C1013" s="2">
         <v>26</v>
       </c>
@@ -19914,7 +19912,7 @@
       <c r="A1014" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1014" s="10"/>
+      <c r="B1014" s="8"/>
       <c r="C1014" s="2">
         <v>27</v>
       </c>
@@ -19926,7 +19924,7 @@
       <c r="A1015" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1015" s="10"/>
+      <c r="B1015" s="8"/>
       <c r="C1015" s="2">
         <v>28</v>
       </c>
@@ -19938,7 +19936,7 @@
       <c r="A1016" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1016" s="10"/>
+      <c r="B1016" s="8"/>
       <c r="C1016" s="2">
         <v>29</v>
       </c>
@@ -19950,7 +19948,7 @@
       <c r="A1017" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1017" s="10"/>
+      <c r="B1017" s="8"/>
       <c r="C1017" s="2">
         <v>30</v>
       </c>
@@ -19962,7 +19960,7 @@
       <c r="A1018" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1018" s="10"/>
+      <c r="B1018" s="8"/>
       <c r="C1018" s="2">
         <v>31</v>
       </c>
@@ -19974,7 +19972,7 @@
       <c r="A1019" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1019" s="10"/>
+      <c r="B1019" s="8"/>
       <c r="C1019" s="2">
         <v>32</v>
       </c>
@@ -19986,7 +19984,7 @@
       <c r="A1020" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1020" s="10"/>
+      <c r="B1020" s="8"/>
       <c r="C1020" s="2">
         <v>33</v>
       </c>
@@ -19998,7 +19996,7 @@
       <c r="A1021" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1021" s="10"/>
+      <c r="B1021" s="8"/>
       <c r="C1021" s="2">
         <v>34</v>
       </c>
@@ -20010,7 +20008,7 @@
       <c r="A1022" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1022" s="10"/>
+      <c r="B1022" s="8"/>
       <c r="C1022" s="2">
         <v>35</v>
       </c>
@@ -20022,7 +20020,7 @@
       <c r="A1023" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1023" s="10"/>
+      <c r="B1023" s="8"/>
       <c r="C1023" s="2">
         <v>36</v>
       </c>
@@ -20034,7 +20032,7 @@
       <c r="A1024" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1024" s="10"/>
+      <c r="B1024" s="8"/>
       <c r="C1024" s="2">
         <v>37</v>
       </c>
@@ -20046,7 +20044,7 @@
       <c r="A1025" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1025" s="10"/>
+      <c r="B1025" s="8"/>
       <c r="C1025" s="2">
         <v>38</v>
       </c>
@@ -20058,7 +20056,7 @@
       <c r="A1026" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1026" s="10"/>
+      <c r="B1026" s="8"/>
       <c r="C1026" s="2">
         <v>39</v>
       </c>
@@ -20070,7 +20068,7 @@
       <c r="A1027" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1027" s="10"/>
+      <c r="B1027" s="8"/>
       <c r="C1027" s="2">
         <v>40</v>
       </c>
@@ -20082,7 +20080,7 @@
       <c r="A1028" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1028" s="10"/>
+      <c r="B1028" s="8"/>
       <c r="C1028" s="2">
         <v>41</v>
       </c>
@@ -20094,7 +20092,7 @@
       <c r="A1029" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1029" s="10"/>
+      <c r="B1029" s="8"/>
       <c r="C1029" s="2">
         <v>42</v>
       </c>
@@ -20106,7 +20104,7 @@
       <c r="A1030" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1030" s="10"/>
+      <c r="B1030" s="8"/>
       <c r="C1030" s="2">
         <v>44</v>
       </c>
@@ -20118,7 +20116,7 @@
       <c r="A1031" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1031" s="10"/>
+      <c r="B1031" s="8"/>
       <c r="C1031" s="2">
         <v>45</v>
       </c>
@@ -20130,7 +20128,7 @@
       <c r="A1032" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1032" s="10"/>
+      <c r="B1032" s="8"/>
       <c r="C1032" s="2">
         <v>46</v>
       </c>
@@ -20142,7 +20140,7 @@
       <c r="A1033" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1033" s="10"/>
+      <c r="B1033" s="8"/>
       <c r="C1033" s="2">
         <v>47</v>
       </c>
@@ -20154,7 +20152,7 @@
       <c r="A1034" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1034" s="10"/>
+      <c r="B1034" s="8"/>
       <c r="C1034" s="2">
         <v>48</v>
       </c>
@@ -20166,7 +20164,7 @@
       <c r="A1035" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1035" s="10"/>
+      <c r="B1035" s="8"/>
       <c r="C1035" s="2">
         <v>49</v>
       </c>
@@ -20178,7 +20176,7 @@
       <c r="A1036" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1036" s="10"/>
+      <c r="B1036" s="8"/>
       <c r="C1036" s="2">
         <v>50</v>
       </c>
@@ -20190,7 +20188,7 @@
       <c r="A1037" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1037" s="10"/>
+      <c r="B1037" s="8"/>
       <c r="C1037" s="2">
         <v>51</v>
       </c>
@@ -20202,7 +20200,7 @@
       <c r="A1038" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1038" s="10"/>
+      <c r="B1038" s="8"/>
       <c r="C1038" s="2">
         <v>53</v>
       </c>
@@ -20214,7 +20212,7 @@
       <c r="A1039" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1039" s="10"/>
+      <c r="B1039" s="8"/>
       <c r="C1039" s="2">
         <v>54</v>
       </c>
@@ -20226,7 +20224,7 @@
       <c r="A1040" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1040" s="10"/>
+      <c r="B1040" s="8"/>
       <c r="C1040" s="2">
         <v>55</v>
       </c>
@@ -20238,7 +20236,7 @@
       <c r="A1041" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1041" s="10"/>
+      <c r="B1041" s="8"/>
       <c r="C1041" s="2">
         <v>56</v>
       </c>
@@ -33722,6 +33720,645 @@
     </row>
   </sheetData>
   <mergeCells count="654">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B109:B114"/>
+    <mergeCell ref="B115:B200"/>
+    <mergeCell ref="B201:B253"/>
+    <mergeCell ref="B254:B269"/>
+    <mergeCell ref="B270:B287"/>
+    <mergeCell ref="B288:B301"/>
+    <mergeCell ref="B302:B333"/>
+    <mergeCell ref="B334:B337"/>
+    <mergeCell ref="B338:B341"/>
+    <mergeCell ref="B342:B346"/>
+    <mergeCell ref="B347:B351"/>
+    <mergeCell ref="B352:B355"/>
+    <mergeCell ref="B356:B359"/>
+    <mergeCell ref="B360:B363"/>
+    <mergeCell ref="B364:B367"/>
+    <mergeCell ref="B368:B371"/>
+    <mergeCell ref="B372:B378"/>
+    <mergeCell ref="B379:B385"/>
+    <mergeCell ref="B386:B392"/>
+    <mergeCell ref="B393:B399"/>
+    <mergeCell ref="B400:B404"/>
+    <mergeCell ref="B405:B407"/>
+    <mergeCell ref="B408:B410"/>
+    <mergeCell ref="B411:B415"/>
+    <mergeCell ref="B416:B418"/>
+    <mergeCell ref="B419:B421"/>
+    <mergeCell ref="B422:B424"/>
+    <mergeCell ref="B425:B430"/>
+    <mergeCell ref="B431:B436"/>
+    <mergeCell ref="B437:B442"/>
+    <mergeCell ref="B443:B450"/>
+    <mergeCell ref="B451:B456"/>
+    <mergeCell ref="B457:B462"/>
+    <mergeCell ref="B463:B468"/>
+    <mergeCell ref="B469:B474"/>
+    <mergeCell ref="B475:B480"/>
+    <mergeCell ref="B481:B486"/>
+    <mergeCell ref="B487:B492"/>
+    <mergeCell ref="B493:B498"/>
+    <mergeCell ref="B499:B504"/>
+    <mergeCell ref="B505:B510"/>
+    <mergeCell ref="B511:B516"/>
+    <mergeCell ref="B517:B522"/>
+    <mergeCell ref="B523:B528"/>
+    <mergeCell ref="B529:B534"/>
+    <mergeCell ref="B535:B540"/>
+    <mergeCell ref="B541:B546"/>
+    <mergeCell ref="B547:B552"/>
+    <mergeCell ref="B553:B558"/>
+    <mergeCell ref="B559:B564"/>
+    <mergeCell ref="B565:B568"/>
+    <mergeCell ref="B569:B571"/>
+    <mergeCell ref="B572:B575"/>
+    <mergeCell ref="B576:B579"/>
+    <mergeCell ref="B580:B582"/>
+    <mergeCell ref="B583:B585"/>
+    <mergeCell ref="B586:B588"/>
+    <mergeCell ref="B589:B591"/>
+    <mergeCell ref="B592:B605"/>
+    <mergeCell ref="B606:B637"/>
+    <mergeCell ref="B638:B641"/>
+    <mergeCell ref="B642:B646"/>
+    <mergeCell ref="B647:B651"/>
+    <mergeCell ref="B652:B658"/>
+    <mergeCell ref="B659:B665"/>
+    <mergeCell ref="B666:B670"/>
+    <mergeCell ref="B671:B675"/>
+    <mergeCell ref="B676:B680"/>
+    <mergeCell ref="B681:B685"/>
+    <mergeCell ref="B686:B691"/>
+    <mergeCell ref="B692:B698"/>
+    <mergeCell ref="B699:B712"/>
+    <mergeCell ref="B713:B744"/>
+    <mergeCell ref="B745:B746"/>
+    <mergeCell ref="B747:B750"/>
+    <mergeCell ref="B751:B755"/>
+    <mergeCell ref="B756:B761"/>
+    <mergeCell ref="B762:B767"/>
+    <mergeCell ref="B768:B776"/>
+    <mergeCell ref="B777:B779"/>
+    <mergeCell ref="B780:B782"/>
+    <mergeCell ref="B783:B785"/>
+    <mergeCell ref="B786:B788"/>
+    <mergeCell ref="B789:B791"/>
+    <mergeCell ref="B792:B794"/>
+    <mergeCell ref="B795:B797"/>
+    <mergeCell ref="B798:B800"/>
+    <mergeCell ref="B801:B803"/>
+    <mergeCell ref="B804:B806"/>
+    <mergeCell ref="B807:B809"/>
+    <mergeCell ref="B810:B812"/>
+    <mergeCell ref="B813:B815"/>
+    <mergeCell ref="B816:B820"/>
+    <mergeCell ref="B821:B825"/>
+    <mergeCell ref="B826:B830"/>
+    <mergeCell ref="B831:B835"/>
+    <mergeCell ref="B836:B843"/>
+    <mergeCell ref="B844:B846"/>
+    <mergeCell ref="B847:B852"/>
+    <mergeCell ref="B853:B855"/>
+    <mergeCell ref="B856:B860"/>
+    <mergeCell ref="B861:B864"/>
+    <mergeCell ref="B865:B870"/>
+    <mergeCell ref="B871:B874"/>
+    <mergeCell ref="B875:B879"/>
+    <mergeCell ref="B880:B882"/>
+    <mergeCell ref="B883:B885"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="B888:B892"/>
+    <mergeCell ref="B893:B895"/>
+    <mergeCell ref="B896:B901"/>
+    <mergeCell ref="B902:B905"/>
+    <mergeCell ref="B906:B909"/>
+    <mergeCell ref="B910:B916"/>
+    <mergeCell ref="B917:B925"/>
+    <mergeCell ref="B926:B929"/>
+    <mergeCell ref="B930:B935"/>
+    <mergeCell ref="B936:B942"/>
+    <mergeCell ref="B943:B955"/>
+    <mergeCell ref="B956:B963"/>
+    <mergeCell ref="B964:B971"/>
+    <mergeCell ref="B972:B979"/>
+    <mergeCell ref="B980:B984"/>
+    <mergeCell ref="B985:B990"/>
+    <mergeCell ref="B991:B1041"/>
+    <mergeCell ref="B1042:B1076"/>
+    <mergeCell ref="B1077:B1078"/>
+    <mergeCell ref="B1079:B1080"/>
+    <mergeCell ref="B1081:B1082"/>
+    <mergeCell ref="B1083:B1084"/>
+    <mergeCell ref="B1085:B1086"/>
+    <mergeCell ref="B1087:B1088"/>
+    <mergeCell ref="B1089:B1090"/>
+    <mergeCell ref="B1091:B1092"/>
+    <mergeCell ref="B1093:B1094"/>
+    <mergeCell ref="B1095:B1096"/>
+    <mergeCell ref="B1097:B1098"/>
+    <mergeCell ref="B1099:B1100"/>
+    <mergeCell ref="B1101:B1102"/>
+    <mergeCell ref="B1103:B1104"/>
+    <mergeCell ref="B1105:B1106"/>
+    <mergeCell ref="B1107:B1108"/>
+    <mergeCell ref="B1109:B1110"/>
+    <mergeCell ref="B1111:B1112"/>
+    <mergeCell ref="B1113:B1114"/>
+    <mergeCell ref="B1115:B1116"/>
+    <mergeCell ref="B1117:B1118"/>
+    <mergeCell ref="B1119:B1120"/>
+    <mergeCell ref="B1121:B1122"/>
+    <mergeCell ref="B1123:B1124"/>
+    <mergeCell ref="B1125:B1126"/>
+    <mergeCell ref="B1127:B1128"/>
+    <mergeCell ref="B1129:B1130"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="B1133:B1134"/>
+    <mergeCell ref="B1135:B1136"/>
+    <mergeCell ref="B1137:B1138"/>
+    <mergeCell ref="B1139:B1140"/>
+    <mergeCell ref="B1141:B1142"/>
+    <mergeCell ref="B1143:B1144"/>
+    <mergeCell ref="B1145:B1146"/>
+    <mergeCell ref="B1147:B1148"/>
+    <mergeCell ref="B1149:B1150"/>
+    <mergeCell ref="B1151:B1152"/>
+    <mergeCell ref="B1153:B1154"/>
+    <mergeCell ref="B1155:B1156"/>
+    <mergeCell ref="B1157:B1158"/>
+    <mergeCell ref="B1159:B1160"/>
+    <mergeCell ref="B1161:B1162"/>
+    <mergeCell ref="B1163:B1164"/>
+    <mergeCell ref="B1165:B1166"/>
+    <mergeCell ref="B1167:B1168"/>
+    <mergeCell ref="B1169:B1170"/>
+    <mergeCell ref="B1171:B1172"/>
+    <mergeCell ref="B1173:B1174"/>
+    <mergeCell ref="B1175:B1176"/>
+    <mergeCell ref="B1177:B1178"/>
+    <mergeCell ref="B1179:B1180"/>
+    <mergeCell ref="B1181:B1182"/>
+    <mergeCell ref="B1183:B1184"/>
+    <mergeCell ref="B1185:B1186"/>
+    <mergeCell ref="B1187:B1188"/>
+    <mergeCell ref="B1189:B1190"/>
+    <mergeCell ref="B1191:B1192"/>
+    <mergeCell ref="B1193:B1194"/>
+    <mergeCell ref="B1195:B1196"/>
+    <mergeCell ref="B1197:B1198"/>
+    <mergeCell ref="B1199:B1200"/>
+    <mergeCell ref="B1201:B1202"/>
+    <mergeCell ref="B1203:B1204"/>
+    <mergeCell ref="B1205:B1206"/>
+    <mergeCell ref="B1207:B1208"/>
+    <mergeCell ref="B1209:B1210"/>
+    <mergeCell ref="B1211:B1212"/>
+    <mergeCell ref="B1213:B1214"/>
+    <mergeCell ref="B1215:B1216"/>
+    <mergeCell ref="B1217:B1218"/>
+    <mergeCell ref="B1219:B1220"/>
+    <mergeCell ref="B1221:B1222"/>
+    <mergeCell ref="B1223:B1224"/>
+    <mergeCell ref="B1225:B1226"/>
+    <mergeCell ref="B1227:B1228"/>
+    <mergeCell ref="B1229:B1230"/>
+    <mergeCell ref="B1231:B1232"/>
+    <mergeCell ref="B1233:B1234"/>
+    <mergeCell ref="B1235:B1236"/>
+    <mergeCell ref="B1237:B1238"/>
+    <mergeCell ref="B1239:B1240"/>
+    <mergeCell ref="B1241:B1242"/>
+    <mergeCell ref="B1243:B1244"/>
+    <mergeCell ref="B1245:B1246"/>
+    <mergeCell ref="B1247:B1248"/>
+    <mergeCell ref="B1249:B1250"/>
+    <mergeCell ref="B1251:B1252"/>
+    <mergeCell ref="B1253:B1254"/>
+    <mergeCell ref="B1255:B1256"/>
+    <mergeCell ref="B1257:B1258"/>
+    <mergeCell ref="B1259:B1260"/>
+    <mergeCell ref="B1261:B1262"/>
+    <mergeCell ref="B1263:B1264"/>
+    <mergeCell ref="B1265:B1266"/>
+    <mergeCell ref="B1267:B1268"/>
+    <mergeCell ref="B1269:B1270"/>
+    <mergeCell ref="B1271:B1272"/>
+    <mergeCell ref="B1273:B1274"/>
+    <mergeCell ref="B1275:B1276"/>
+    <mergeCell ref="B1277:B1278"/>
+    <mergeCell ref="B1279:B1280"/>
+    <mergeCell ref="B1281:B1282"/>
+    <mergeCell ref="B1283:B1284"/>
+    <mergeCell ref="B1285:B1286"/>
+    <mergeCell ref="B1287:B1288"/>
+    <mergeCell ref="B1289:B1290"/>
+    <mergeCell ref="B1291:B1292"/>
+    <mergeCell ref="B1293:B1294"/>
+    <mergeCell ref="B1295:B1296"/>
+    <mergeCell ref="B1297:B1298"/>
+    <mergeCell ref="B1299:B1300"/>
+    <mergeCell ref="B1301:B1302"/>
+    <mergeCell ref="B1303:B1304"/>
+    <mergeCell ref="B1305:B1306"/>
+    <mergeCell ref="B1307:B1308"/>
+    <mergeCell ref="B1309:B1310"/>
+    <mergeCell ref="B1311:B1312"/>
+    <mergeCell ref="B1313:B1314"/>
+    <mergeCell ref="B1315:B1316"/>
+    <mergeCell ref="B1317:B1318"/>
+    <mergeCell ref="B1319:B1320"/>
+    <mergeCell ref="B1321:B1322"/>
+    <mergeCell ref="B1323:B1324"/>
+    <mergeCell ref="B1325:B1326"/>
+    <mergeCell ref="B1327:B1328"/>
+    <mergeCell ref="B1329:B1330"/>
+    <mergeCell ref="B1331:B1332"/>
+    <mergeCell ref="B1333:B1334"/>
+    <mergeCell ref="B1335:B1336"/>
+    <mergeCell ref="B1337:B1338"/>
+    <mergeCell ref="B1339:B1340"/>
+    <mergeCell ref="B1341:B1342"/>
+    <mergeCell ref="B1343:B1344"/>
+    <mergeCell ref="B1345:B1346"/>
+    <mergeCell ref="B1347:B1348"/>
+    <mergeCell ref="B1349:B1350"/>
+    <mergeCell ref="B1351:B1352"/>
+    <mergeCell ref="B1353:B1354"/>
+    <mergeCell ref="B1355:B1356"/>
+    <mergeCell ref="B1357:B1358"/>
+    <mergeCell ref="B1359:B1360"/>
+    <mergeCell ref="B1361:B1362"/>
+    <mergeCell ref="B1363:B1364"/>
+    <mergeCell ref="B1365:B1366"/>
+    <mergeCell ref="B1367:B1368"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1371:B1372"/>
+    <mergeCell ref="B1373:B1374"/>
+    <mergeCell ref="B1375:B1376"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B1379:B1380"/>
+    <mergeCell ref="B1381:B1382"/>
+    <mergeCell ref="B1383:B1384"/>
+    <mergeCell ref="B1385:B1386"/>
+    <mergeCell ref="B1387:B1388"/>
+    <mergeCell ref="B1389:B1390"/>
+    <mergeCell ref="B1391:B1392"/>
+    <mergeCell ref="B1393:B1394"/>
+    <mergeCell ref="B1395:B1396"/>
+    <mergeCell ref="B1397:B1398"/>
+    <mergeCell ref="B1399:B1400"/>
+    <mergeCell ref="B1401:B1402"/>
+    <mergeCell ref="B1403:B1404"/>
+    <mergeCell ref="B1405:B1406"/>
+    <mergeCell ref="B1407:B1408"/>
+    <mergeCell ref="B1409:B1410"/>
+    <mergeCell ref="B1411:B1412"/>
+    <mergeCell ref="B1413:B1414"/>
+    <mergeCell ref="B1415:B1416"/>
+    <mergeCell ref="B1417:B1418"/>
+    <mergeCell ref="B1419:B1420"/>
+    <mergeCell ref="B1421:B1422"/>
+    <mergeCell ref="B1423:B1424"/>
+    <mergeCell ref="B1425:B1426"/>
+    <mergeCell ref="B1427:B1428"/>
+    <mergeCell ref="B1429:B1430"/>
+    <mergeCell ref="B1431:B1432"/>
+    <mergeCell ref="B1433:B1434"/>
+    <mergeCell ref="B1435:B1436"/>
+    <mergeCell ref="B1437:B1438"/>
+    <mergeCell ref="B1439:B1440"/>
+    <mergeCell ref="B1441:B1442"/>
+    <mergeCell ref="B1443:B1444"/>
+    <mergeCell ref="B1445:B1446"/>
+    <mergeCell ref="B1447:B1448"/>
+    <mergeCell ref="B1449:B1450"/>
+    <mergeCell ref="B1451:B1452"/>
+    <mergeCell ref="B1453:B1454"/>
+    <mergeCell ref="B1455:B1456"/>
+    <mergeCell ref="B1457:B1458"/>
+    <mergeCell ref="B1459:B1460"/>
+    <mergeCell ref="B1461:B1462"/>
+    <mergeCell ref="B1463:B1464"/>
+    <mergeCell ref="B1465:B1466"/>
+    <mergeCell ref="B1467:B1468"/>
+    <mergeCell ref="B1469:B1470"/>
+    <mergeCell ref="B1471:B1472"/>
+    <mergeCell ref="B1473:B1474"/>
+    <mergeCell ref="B1475:B1476"/>
+    <mergeCell ref="B1477:B1478"/>
+    <mergeCell ref="B1479:B1480"/>
+    <mergeCell ref="B1481:B1482"/>
+    <mergeCell ref="B1483:B1484"/>
+    <mergeCell ref="B1485:B1486"/>
+    <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="B1489:B1490"/>
+    <mergeCell ref="B1491:B1492"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1495:B1496"/>
+    <mergeCell ref="B1497:B1498"/>
+    <mergeCell ref="B1499:B1500"/>
+    <mergeCell ref="B1501:B1502"/>
+    <mergeCell ref="B1503:B1504"/>
+    <mergeCell ref="B1505:B1506"/>
+    <mergeCell ref="B1507:B1508"/>
+    <mergeCell ref="B1509:B1510"/>
+    <mergeCell ref="B1511:B1512"/>
+    <mergeCell ref="B1513:B1514"/>
+    <mergeCell ref="B1515:B1516"/>
+    <mergeCell ref="B1517:B1518"/>
+    <mergeCell ref="B1519:B1520"/>
+    <mergeCell ref="B1521:B1522"/>
+    <mergeCell ref="B1523:B1524"/>
+    <mergeCell ref="B1525:B1526"/>
+    <mergeCell ref="B1527:B1528"/>
+    <mergeCell ref="B1529:B1530"/>
+    <mergeCell ref="B1531:B1532"/>
+    <mergeCell ref="B1533:B1534"/>
+    <mergeCell ref="B1535:B1536"/>
+    <mergeCell ref="B1537:B1538"/>
+    <mergeCell ref="B1539:B1540"/>
+    <mergeCell ref="B1541:B1542"/>
+    <mergeCell ref="B1543:B1544"/>
+    <mergeCell ref="B1545:B1546"/>
+    <mergeCell ref="B1547:B1548"/>
+    <mergeCell ref="B1549:B1550"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B1553:B1554"/>
+    <mergeCell ref="B1555:B1556"/>
+    <mergeCell ref="B1557:B1558"/>
+    <mergeCell ref="B1559:B1560"/>
+    <mergeCell ref="B1561:B1562"/>
+    <mergeCell ref="B1563:B1564"/>
+    <mergeCell ref="B1565:B1566"/>
+    <mergeCell ref="B1567:B1568"/>
+    <mergeCell ref="B1569:B1570"/>
+    <mergeCell ref="B1571:B1572"/>
+    <mergeCell ref="B1573:B1574"/>
+    <mergeCell ref="B1575:B1576"/>
+    <mergeCell ref="B1577:B1578"/>
+    <mergeCell ref="B1579:B1580"/>
+    <mergeCell ref="B1581:B1582"/>
+    <mergeCell ref="B1583:B1584"/>
+    <mergeCell ref="B1585:B1586"/>
+    <mergeCell ref="B1587:B1588"/>
+    <mergeCell ref="B1589:B1590"/>
+    <mergeCell ref="B1591:B1592"/>
+    <mergeCell ref="B1593:B1594"/>
+    <mergeCell ref="B1595:B1596"/>
+    <mergeCell ref="B1597:B1598"/>
+    <mergeCell ref="B1599:B1600"/>
+    <mergeCell ref="B1601:B1602"/>
+    <mergeCell ref="B1603:B1604"/>
+    <mergeCell ref="B1605:B1606"/>
+    <mergeCell ref="B1607:B1608"/>
+    <mergeCell ref="B1609:B1610"/>
+    <mergeCell ref="B1611:B1612"/>
+    <mergeCell ref="B1613:B1614"/>
+    <mergeCell ref="B1615:B1616"/>
+    <mergeCell ref="B1617:B1618"/>
+    <mergeCell ref="B1619:B1620"/>
+    <mergeCell ref="B1621:B1622"/>
+    <mergeCell ref="B1623:B1624"/>
+    <mergeCell ref="B1625:B1626"/>
+    <mergeCell ref="B1627:B1628"/>
+    <mergeCell ref="B1629:B1630"/>
+    <mergeCell ref="B1631:B1632"/>
+    <mergeCell ref="B1633:B1634"/>
+    <mergeCell ref="B1635:B1636"/>
+    <mergeCell ref="B1637:B1638"/>
+    <mergeCell ref="B1639:B1640"/>
+    <mergeCell ref="B1641:B1642"/>
+    <mergeCell ref="B1643:B1644"/>
+    <mergeCell ref="B1645:B1646"/>
+    <mergeCell ref="B1647:B1648"/>
+    <mergeCell ref="B1649:B1650"/>
+    <mergeCell ref="B1651:B1652"/>
+    <mergeCell ref="B1653:B1654"/>
+    <mergeCell ref="B1655:B1656"/>
+    <mergeCell ref="B1657:B1658"/>
+    <mergeCell ref="B1659:B1660"/>
+    <mergeCell ref="B1661:B1662"/>
+    <mergeCell ref="B1663:B1664"/>
+    <mergeCell ref="B1665:B1666"/>
+    <mergeCell ref="B1667:B1668"/>
+    <mergeCell ref="B1669:B1670"/>
+    <mergeCell ref="B1671:B1672"/>
+    <mergeCell ref="B1673:B1674"/>
+    <mergeCell ref="B1675:B1676"/>
+    <mergeCell ref="B1677:B1678"/>
+    <mergeCell ref="B1679:B1680"/>
+    <mergeCell ref="B1681:B1682"/>
+    <mergeCell ref="B1683:B1684"/>
+    <mergeCell ref="B1685:B1686"/>
+    <mergeCell ref="B1687:B1688"/>
+    <mergeCell ref="B1689:B1690"/>
+    <mergeCell ref="B1691:B1692"/>
+    <mergeCell ref="B1693:B1694"/>
+    <mergeCell ref="B1695:B1696"/>
+    <mergeCell ref="B1697:B1698"/>
+    <mergeCell ref="B1699:B1700"/>
+    <mergeCell ref="B1701:B1702"/>
+    <mergeCell ref="B1703:B1704"/>
+    <mergeCell ref="B1705:B1706"/>
+    <mergeCell ref="B1707:B1708"/>
+    <mergeCell ref="B1709:B1710"/>
+    <mergeCell ref="B1711:B1712"/>
+    <mergeCell ref="B1713:B1714"/>
+    <mergeCell ref="B1715:B1716"/>
+    <mergeCell ref="B1717:B1718"/>
+    <mergeCell ref="B1719:B1720"/>
+    <mergeCell ref="B1721:B1722"/>
+    <mergeCell ref="B1723:B1724"/>
+    <mergeCell ref="B1725:B1726"/>
+    <mergeCell ref="B1727:B1728"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="B1731:B1732"/>
+    <mergeCell ref="B1733:B1734"/>
+    <mergeCell ref="B1735:B1736"/>
+    <mergeCell ref="B1737:B1738"/>
+    <mergeCell ref="B1739:B1740"/>
+    <mergeCell ref="B1741:B1742"/>
+    <mergeCell ref="B1743:B1744"/>
+    <mergeCell ref="B1745:B1746"/>
+    <mergeCell ref="B1747:B1748"/>
+    <mergeCell ref="B1749:B1750"/>
+    <mergeCell ref="B1751:B1752"/>
+    <mergeCell ref="B1753:B1754"/>
+    <mergeCell ref="B1755:B1756"/>
+    <mergeCell ref="B1757:B1758"/>
+    <mergeCell ref="B1759:B1760"/>
+    <mergeCell ref="B1761:B1762"/>
+    <mergeCell ref="B1763:B1764"/>
+    <mergeCell ref="B1765:B1766"/>
+    <mergeCell ref="B1767:B1768"/>
+    <mergeCell ref="B1769:B1770"/>
+    <mergeCell ref="B1771:B1772"/>
+    <mergeCell ref="B1773:B1774"/>
+    <mergeCell ref="B1775:B1776"/>
+    <mergeCell ref="B1777:B1778"/>
+    <mergeCell ref="B1779:B1780"/>
+    <mergeCell ref="B1781:B1782"/>
+    <mergeCell ref="B1783:B1784"/>
+    <mergeCell ref="B1785:B1786"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B1789:B1790"/>
+    <mergeCell ref="B1791:B1792"/>
+    <mergeCell ref="B1793:B1794"/>
+    <mergeCell ref="B1795:B1796"/>
+    <mergeCell ref="B1797:B1798"/>
+    <mergeCell ref="B1799:B1800"/>
+    <mergeCell ref="B1801:B1802"/>
+    <mergeCell ref="B1803:B1804"/>
+    <mergeCell ref="B1805:B1806"/>
+    <mergeCell ref="B1807:B1808"/>
+    <mergeCell ref="B1809:B1810"/>
+    <mergeCell ref="B1811:B1812"/>
+    <mergeCell ref="B1813:B1814"/>
+    <mergeCell ref="B1815:B1816"/>
+    <mergeCell ref="B1817:B1818"/>
+    <mergeCell ref="B1819:B1820"/>
+    <mergeCell ref="B1821:B1822"/>
+    <mergeCell ref="B1823:B1824"/>
+    <mergeCell ref="B1825:B1826"/>
+    <mergeCell ref="B1827:B1828"/>
+    <mergeCell ref="B1829:B1830"/>
+    <mergeCell ref="B1831:B1832"/>
+    <mergeCell ref="B1833:B1834"/>
+    <mergeCell ref="B1835:B1836"/>
+    <mergeCell ref="B1837:B1838"/>
+    <mergeCell ref="B1839:B1840"/>
+    <mergeCell ref="B1841:B1842"/>
+    <mergeCell ref="B1843:B1844"/>
+    <mergeCell ref="B1845:B1846"/>
+    <mergeCell ref="B1847:B1848"/>
+    <mergeCell ref="B1849:B1850"/>
+    <mergeCell ref="B1851:B1852"/>
+    <mergeCell ref="B1853:B1854"/>
+    <mergeCell ref="B1855:B1856"/>
+    <mergeCell ref="B1857:B1858"/>
+    <mergeCell ref="B1859:B1860"/>
+    <mergeCell ref="B1861:B1862"/>
+    <mergeCell ref="B1863:B1864"/>
+    <mergeCell ref="B1865:B1866"/>
+    <mergeCell ref="B1867:B1868"/>
+    <mergeCell ref="B1869:B1870"/>
+    <mergeCell ref="B1871:B1872"/>
+    <mergeCell ref="B1873:B1874"/>
+    <mergeCell ref="B1875:B1876"/>
+    <mergeCell ref="B1877:B1878"/>
+    <mergeCell ref="B1879:B1880"/>
+    <mergeCell ref="B1881:B1882"/>
+    <mergeCell ref="B1883:B1884"/>
+    <mergeCell ref="B1885:B1886"/>
+    <mergeCell ref="B1887:B1888"/>
+    <mergeCell ref="B1889:B1890"/>
+    <mergeCell ref="B1891:B1892"/>
+    <mergeCell ref="B1893:B1894"/>
+    <mergeCell ref="B1895:B1896"/>
+    <mergeCell ref="B1897:B1898"/>
+    <mergeCell ref="B1899:B1900"/>
+    <mergeCell ref="B1901:B1902"/>
+    <mergeCell ref="B1903:B1904"/>
+    <mergeCell ref="B1905:B1906"/>
+    <mergeCell ref="B1907:B1908"/>
+    <mergeCell ref="B1909:B1910"/>
+    <mergeCell ref="B1911:B1912"/>
+    <mergeCell ref="B1913:B1914"/>
+    <mergeCell ref="B1915:B1916"/>
+    <mergeCell ref="B1917:B1918"/>
+    <mergeCell ref="B1919:B1920"/>
+    <mergeCell ref="B1921:B1922"/>
+    <mergeCell ref="B1923:B1924"/>
+    <mergeCell ref="B1925:B1926"/>
+    <mergeCell ref="B1927:B1928"/>
+    <mergeCell ref="B1929:B1930"/>
+    <mergeCell ref="B1931:B1932"/>
+    <mergeCell ref="B1933:B1934"/>
+    <mergeCell ref="B1935:B1936"/>
+    <mergeCell ref="B1937:B1938"/>
+    <mergeCell ref="B1939:B1940"/>
+    <mergeCell ref="B1941:B1942"/>
+    <mergeCell ref="B1943:B1944"/>
+    <mergeCell ref="B1945:B1946"/>
+    <mergeCell ref="B1947:B1948"/>
+    <mergeCell ref="B1949:B1950"/>
+    <mergeCell ref="B1951:B1952"/>
+    <mergeCell ref="B1953:B1954"/>
+    <mergeCell ref="B1955:B1956"/>
+    <mergeCell ref="B1957:B1958"/>
+    <mergeCell ref="B1959:B1960"/>
+    <mergeCell ref="B1961:B1962"/>
+    <mergeCell ref="B1963:B1964"/>
+    <mergeCell ref="B1965:B1966"/>
+    <mergeCell ref="B1967:B1968"/>
+    <mergeCell ref="B1969:B1970"/>
+    <mergeCell ref="B1971:B1972"/>
+    <mergeCell ref="B1973:B1974"/>
+    <mergeCell ref="B1975:B1976"/>
+    <mergeCell ref="B1977:B1978"/>
+    <mergeCell ref="B1979:B1980"/>
+    <mergeCell ref="B1981:B1982"/>
+    <mergeCell ref="B1983:B1984"/>
+    <mergeCell ref="B1985:B1986"/>
+    <mergeCell ref="B1987:B1988"/>
+    <mergeCell ref="B1989:B1990"/>
+    <mergeCell ref="B1991:B1992"/>
+    <mergeCell ref="B1993:B1994"/>
+    <mergeCell ref="B1995:B1996"/>
+    <mergeCell ref="B1997:B1998"/>
+    <mergeCell ref="B1999:B2000"/>
+    <mergeCell ref="B2001:B2002"/>
+    <mergeCell ref="B2003:B2004"/>
+    <mergeCell ref="B2005:B2006"/>
+    <mergeCell ref="B2007:B2008"/>
+    <mergeCell ref="B2009:B2010"/>
+    <mergeCell ref="B2011:B2012"/>
+    <mergeCell ref="B2013:B2014"/>
+    <mergeCell ref="B2015:B2016"/>
+    <mergeCell ref="B2017:B2018"/>
+    <mergeCell ref="B2019:B2020"/>
+    <mergeCell ref="B2021:B2022"/>
+    <mergeCell ref="B2023:B2024"/>
+    <mergeCell ref="B2025:B2026"/>
+    <mergeCell ref="B2027:B2028"/>
+    <mergeCell ref="B2029:B2030"/>
+    <mergeCell ref="B2031:B2032"/>
+    <mergeCell ref="B2033:B2034"/>
+    <mergeCell ref="B2035:B2036"/>
+    <mergeCell ref="B2037:B2038"/>
+    <mergeCell ref="B2039:B2040"/>
+    <mergeCell ref="B2041:B2042"/>
+    <mergeCell ref="B2043:B2044"/>
+    <mergeCell ref="B2045:B2046"/>
+    <mergeCell ref="B2047:B2048"/>
+    <mergeCell ref="B2049:B2050"/>
     <mergeCell ref="B2069:B2070"/>
     <mergeCell ref="B2071:B2072"/>
     <mergeCell ref="B2073:B2074"/>
@@ -33737,645 +34374,6 @@
     <mergeCell ref="B2063:B2064"/>
     <mergeCell ref="B2065:B2066"/>
     <mergeCell ref="B2067:B2068"/>
-    <mergeCell ref="B2033:B2034"/>
-    <mergeCell ref="B2035:B2036"/>
-    <mergeCell ref="B2037:B2038"/>
-    <mergeCell ref="B2039:B2040"/>
-    <mergeCell ref="B2041:B2042"/>
-    <mergeCell ref="B2043:B2044"/>
-    <mergeCell ref="B2045:B2046"/>
-    <mergeCell ref="B2047:B2048"/>
-    <mergeCell ref="B2049:B2050"/>
-    <mergeCell ref="B2015:B2016"/>
-    <mergeCell ref="B2017:B2018"/>
-    <mergeCell ref="B2019:B2020"/>
-    <mergeCell ref="B2021:B2022"/>
-    <mergeCell ref="B2023:B2024"/>
-    <mergeCell ref="B2025:B2026"/>
-    <mergeCell ref="B2027:B2028"/>
-    <mergeCell ref="B2029:B2030"/>
-    <mergeCell ref="B2031:B2032"/>
-    <mergeCell ref="B1997:B1998"/>
-    <mergeCell ref="B1999:B2000"/>
-    <mergeCell ref="B2001:B2002"/>
-    <mergeCell ref="B2003:B2004"/>
-    <mergeCell ref="B2005:B2006"/>
-    <mergeCell ref="B2007:B2008"/>
-    <mergeCell ref="B2009:B2010"/>
-    <mergeCell ref="B2011:B2012"/>
-    <mergeCell ref="B2013:B2014"/>
-    <mergeCell ref="B1979:B1980"/>
-    <mergeCell ref="B1981:B1982"/>
-    <mergeCell ref="B1983:B1984"/>
-    <mergeCell ref="B1985:B1986"/>
-    <mergeCell ref="B1987:B1988"/>
-    <mergeCell ref="B1989:B1990"/>
-    <mergeCell ref="B1991:B1992"/>
-    <mergeCell ref="B1993:B1994"/>
-    <mergeCell ref="B1995:B1996"/>
-    <mergeCell ref="B1961:B1962"/>
-    <mergeCell ref="B1963:B1964"/>
-    <mergeCell ref="B1965:B1966"/>
-    <mergeCell ref="B1967:B1968"/>
-    <mergeCell ref="B1969:B1970"/>
-    <mergeCell ref="B1971:B1972"/>
-    <mergeCell ref="B1973:B1974"/>
-    <mergeCell ref="B1975:B1976"/>
-    <mergeCell ref="B1977:B1978"/>
-    <mergeCell ref="B1943:B1944"/>
-    <mergeCell ref="B1945:B1946"/>
-    <mergeCell ref="B1947:B1948"/>
-    <mergeCell ref="B1949:B1950"/>
-    <mergeCell ref="B1951:B1952"/>
-    <mergeCell ref="B1953:B1954"/>
-    <mergeCell ref="B1955:B1956"/>
-    <mergeCell ref="B1957:B1958"/>
-    <mergeCell ref="B1959:B1960"/>
-    <mergeCell ref="B1925:B1926"/>
-    <mergeCell ref="B1927:B1928"/>
-    <mergeCell ref="B1929:B1930"/>
-    <mergeCell ref="B1931:B1932"/>
-    <mergeCell ref="B1933:B1934"/>
-    <mergeCell ref="B1935:B1936"/>
-    <mergeCell ref="B1937:B1938"/>
-    <mergeCell ref="B1939:B1940"/>
-    <mergeCell ref="B1941:B1942"/>
-    <mergeCell ref="B1907:B1908"/>
-    <mergeCell ref="B1909:B1910"/>
-    <mergeCell ref="B1911:B1912"/>
-    <mergeCell ref="B1913:B1914"/>
-    <mergeCell ref="B1915:B1916"/>
-    <mergeCell ref="B1917:B1918"/>
-    <mergeCell ref="B1919:B1920"/>
-    <mergeCell ref="B1921:B1922"/>
-    <mergeCell ref="B1923:B1924"/>
-    <mergeCell ref="B1889:B1890"/>
-    <mergeCell ref="B1891:B1892"/>
-    <mergeCell ref="B1893:B1894"/>
-    <mergeCell ref="B1895:B1896"/>
-    <mergeCell ref="B1897:B1898"/>
-    <mergeCell ref="B1899:B1900"/>
-    <mergeCell ref="B1901:B1902"/>
-    <mergeCell ref="B1903:B1904"/>
-    <mergeCell ref="B1905:B1906"/>
-    <mergeCell ref="B1871:B1872"/>
-    <mergeCell ref="B1873:B1874"/>
-    <mergeCell ref="B1875:B1876"/>
-    <mergeCell ref="B1877:B1878"/>
-    <mergeCell ref="B1879:B1880"/>
-    <mergeCell ref="B1881:B1882"/>
-    <mergeCell ref="B1883:B1884"/>
-    <mergeCell ref="B1885:B1886"/>
-    <mergeCell ref="B1887:B1888"/>
-    <mergeCell ref="B1853:B1854"/>
-    <mergeCell ref="B1855:B1856"/>
-    <mergeCell ref="B1857:B1858"/>
-    <mergeCell ref="B1859:B1860"/>
-    <mergeCell ref="B1861:B1862"/>
-    <mergeCell ref="B1863:B1864"/>
-    <mergeCell ref="B1865:B1866"/>
-    <mergeCell ref="B1867:B1868"/>
-    <mergeCell ref="B1869:B1870"/>
-    <mergeCell ref="B1835:B1836"/>
-    <mergeCell ref="B1837:B1838"/>
-    <mergeCell ref="B1839:B1840"/>
-    <mergeCell ref="B1841:B1842"/>
-    <mergeCell ref="B1843:B1844"/>
-    <mergeCell ref="B1845:B1846"/>
-    <mergeCell ref="B1847:B1848"/>
-    <mergeCell ref="B1849:B1850"/>
-    <mergeCell ref="B1851:B1852"/>
-    <mergeCell ref="B1817:B1818"/>
-    <mergeCell ref="B1819:B1820"/>
-    <mergeCell ref="B1821:B1822"/>
-    <mergeCell ref="B1823:B1824"/>
-    <mergeCell ref="B1825:B1826"/>
-    <mergeCell ref="B1827:B1828"/>
-    <mergeCell ref="B1829:B1830"/>
-    <mergeCell ref="B1831:B1832"/>
-    <mergeCell ref="B1833:B1834"/>
-    <mergeCell ref="B1799:B1800"/>
-    <mergeCell ref="B1801:B1802"/>
-    <mergeCell ref="B1803:B1804"/>
-    <mergeCell ref="B1805:B1806"/>
-    <mergeCell ref="B1807:B1808"/>
-    <mergeCell ref="B1809:B1810"/>
-    <mergeCell ref="B1811:B1812"/>
-    <mergeCell ref="B1813:B1814"/>
-    <mergeCell ref="B1815:B1816"/>
-    <mergeCell ref="B1781:B1782"/>
-    <mergeCell ref="B1783:B1784"/>
-    <mergeCell ref="B1785:B1786"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B1789:B1790"/>
-    <mergeCell ref="B1791:B1792"/>
-    <mergeCell ref="B1793:B1794"/>
-    <mergeCell ref="B1795:B1796"/>
-    <mergeCell ref="B1797:B1798"/>
-    <mergeCell ref="B1763:B1764"/>
-    <mergeCell ref="B1765:B1766"/>
-    <mergeCell ref="B1767:B1768"/>
-    <mergeCell ref="B1769:B1770"/>
-    <mergeCell ref="B1771:B1772"/>
-    <mergeCell ref="B1773:B1774"/>
-    <mergeCell ref="B1775:B1776"/>
-    <mergeCell ref="B1777:B1778"/>
-    <mergeCell ref="B1779:B1780"/>
-    <mergeCell ref="B1745:B1746"/>
-    <mergeCell ref="B1747:B1748"/>
-    <mergeCell ref="B1749:B1750"/>
-    <mergeCell ref="B1751:B1752"/>
-    <mergeCell ref="B1753:B1754"/>
-    <mergeCell ref="B1755:B1756"/>
-    <mergeCell ref="B1757:B1758"/>
-    <mergeCell ref="B1759:B1760"/>
-    <mergeCell ref="B1761:B1762"/>
-    <mergeCell ref="B1727:B1728"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="B1731:B1732"/>
-    <mergeCell ref="B1733:B1734"/>
-    <mergeCell ref="B1735:B1736"/>
-    <mergeCell ref="B1737:B1738"/>
-    <mergeCell ref="B1739:B1740"/>
-    <mergeCell ref="B1741:B1742"/>
-    <mergeCell ref="B1743:B1744"/>
-    <mergeCell ref="B1709:B1710"/>
-    <mergeCell ref="B1711:B1712"/>
-    <mergeCell ref="B1713:B1714"/>
-    <mergeCell ref="B1715:B1716"/>
-    <mergeCell ref="B1717:B1718"/>
-    <mergeCell ref="B1719:B1720"/>
-    <mergeCell ref="B1721:B1722"/>
-    <mergeCell ref="B1723:B1724"/>
-    <mergeCell ref="B1725:B1726"/>
-    <mergeCell ref="B1691:B1692"/>
-    <mergeCell ref="B1693:B1694"/>
-    <mergeCell ref="B1695:B1696"/>
-    <mergeCell ref="B1697:B1698"/>
-    <mergeCell ref="B1699:B1700"/>
-    <mergeCell ref="B1701:B1702"/>
-    <mergeCell ref="B1703:B1704"/>
-    <mergeCell ref="B1705:B1706"/>
-    <mergeCell ref="B1707:B1708"/>
-    <mergeCell ref="B1673:B1674"/>
-    <mergeCell ref="B1675:B1676"/>
-    <mergeCell ref="B1677:B1678"/>
-    <mergeCell ref="B1679:B1680"/>
-    <mergeCell ref="B1681:B1682"/>
-    <mergeCell ref="B1683:B1684"/>
-    <mergeCell ref="B1685:B1686"/>
-    <mergeCell ref="B1687:B1688"/>
-    <mergeCell ref="B1689:B1690"/>
-    <mergeCell ref="B1655:B1656"/>
-    <mergeCell ref="B1657:B1658"/>
-    <mergeCell ref="B1659:B1660"/>
-    <mergeCell ref="B1661:B1662"/>
-    <mergeCell ref="B1663:B1664"/>
-    <mergeCell ref="B1665:B1666"/>
-    <mergeCell ref="B1667:B1668"/>
-    <mergeCell ref="B1669:B1670"/>
-    <mergeCell ref="B1671:B1672"/>
-    <mergeCell ref="B1637:B1638"/>
-    <mergeCell ref="B1639:B1640"/>
-    <mergeCell ref="B1641:B1642"/>
-    <mergeCell ref="B1643:B1644"/>
-    <mergeCell ref="B1645:B1646"/>
-    <mergeCell ref="B1647:B1648"/>
-    <mergeCell ref="B1649:B1650"/>
-    <mergeCell ref="B1651:B1652"/>
-    <mergeCell ref="B1653:B1654"/>
-    <mergeCell ref="B1619:B1620"/>
-    <mergeCell ref="B1621:B1622"/>
-    <mergeCell ref="B1623:B1624"/>
-    <mergeCell ref="B1625:B1626"/>
-    <mergeCell ref="B1627:B1628"/>
-    <mergeCell ref="B1629:B1630"/>
-    <mergeCell ref="B1631:B1632"/>
-    <mergeCell ref="B1633:B1634"/>
-    <mergeCell ref="B1635:B1636"/>
-    <mergeCell ref="B1601:B1602"/>
-    <mergeCell ref="B1603:B1604"/>
-    <mergeCell ref="B1605:B1606"/>
-    <mergeCell ref="B1607:B1608"/>
-    <mergeCell ref="B1609:B1610"/>
-    <mergeCell ref="B1611:B1612"/>
-    <mergeCell ref="B1613:B1614"/>
-    <mergeCell ref="B1615:B1616"/>
-    <mergeCell ref="B1617:B1618"/>
-    <mergeCell ref="B1583:B1584"/>
-    <mergeCell ref="B1585:B1586"/>
-    <mergeCell ref="B1587:B1588"/>
-    <mergeCell ref="B1589:B1590"/>
-    <mergeCell ref="B1591:B1592"/>
-    <mergeCell ref="B1593:B1594"/>
-    <mergeCell ref="B1595:B1596"/>
-    <mergeCell ref="B1597:B1598"/>
-    <mergeCell ref="B1599:B1600"/>
-    <mergeCell ref="B1565:B1566"/>
-    <mergeCell ref="B1567:B1568"/>
-    <mergeCell ref="B1569:B1570"/>
-    <mergeCell ref="B1571:B1572"/>
-    <mergeCell ref="B1573:B1574"/>
-    <mergeCell ref="B1575:B1576"/>
-    <mergeCell ref="B1577:B1578"/>
-    <mergeCell ref="B1579:B1580"/>
-    <mergeCell ref="B1581:B1582"/>
-    <mergeCell ref="B1547:B1548"/>
-    <mergeCell ref="B1549:B1550"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B1553:B1554"/>
-    <mergeCell ref="B1555:B1556"/>
-    <mergeCell ref="B1557:B1558"/>
-    <mergeCell ref="B1559:B1560"/>
-    <mergeCell ref="B1561:B1562"/>
-    <mergeCell ref="B1563:B1564"/>
-    <mergeCell ref="B1529:B1530"/>
-    <mergeCell ref="B1531:B1532"/>
-    <mergeCell ref="B1533:B1534"/>
-    <mergeCell ref="B1535:B1536"/>
-    <mergeCell ref="B1537:B1538"/>
-    <mergeCell ref="B1539:B1540"/>
-    <mergeCell ref="B1541:B1542"/>
-    <mergeCell ref="B1543:B1544"/>
-    <mergeCell ref="B1545:B1546"/>
-    <mergeCell ref="B1511:B1512"/>
-    <mergeCell ref="B1513:B1514"/>
-    <mergeCell ref="B1515:B1516"/>
-    <mergeCell ref="B1517:B1518"/>
-    <mergeCell ref="B1519:B1520"/>
-    <mergeCell ref="B1521:B1522"/>
-    <mergeCell ref="B1523:B1524"/>
-    <mergeCell ref="B1525:B1526"/>
-    <mergeCell ref="B1527:B1528"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1495:B1496"/>
-    <mergeCell ref="B1497:B1498"/>
-    <mergeCell ref="B1499:B1500"/>
-    <mergeCell ref="B1501:B1502"/>
-    <mergeCell ref="B1503:B1504"/>
-    <mergeCell ref="B1505:B1506"/>
-    <mergeCell ref="B1507:B1508"/>
-    <mergeCell ref="B1509:B1510"/>
-    <mergeCell ref="B1475:B1476"/>
-    <mergeCell ref="B1477:B1478"/>
-    <mergeCell ref="B1479:B1480"/>
-    <mergeCell ref="B1481:B1482"/>
-    <mergeCell ref="B1483:B1484"/>
-    <mergeCell ref="B1485:B1486"/>
-    <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="B1489:B1490"/>
-    <mergeCell ref="B1491:B1492"/>
-    <mergeCell ref="B1457:B1458"/>
-    <mergeCell ref="B1459:B1460"/>
-    <mergeCell ref="B1461:B1462"/>
-    <mergeCell ref="B1463:B1464"/>
-    <mergeCell ref="B1465:B1466"/>
-    <mergeCell ref="B1467:B1468"/>
-    <mergeCell ref="B1469:B1470"/>
-    <mergeCell ref="B1471:B1472"/>
-    <mergeCell ref="B1473:B1474"/>
-    <mergeCell ref="B1439:B1440"/>
-    <mergeCell ref="B1441:B1442"/>
-    <mergeCell ref="B1443:B1444"/>
-    <mergeCell ref="B1445:B1446"/>
-    <mergeCell ref="B1447:B1448"/>
-    <mergeCell ref="B1449:B1450"/>
-    <mergeCell ref="B1451:B1452"/>
-    <mergeCell ref="B1453:B1454"/>
-    <mergeCell ref="B1455:B1456"/>
-    <mergeCell ref="B1421:B1422"/>
-    <mergeCell ref="B1423:B1424"/>
-    <mergeCell ref="B1425:B1426"/>
-    <mergeCell ref="B1427:B1428"/>
-    <mergeCell ref="B1429:B1430"/>
-    <mergeCell ref="B1431:B1432"/>
-    <mergeCell ref="B1433:B1434"/>
-    <mergeCell ref="B1435:B1436"/>
-    <mergeCell ref="B1437:B1438"/>
-    <mergeCell ref="B1403:B1404"/>
-    <mergeCell ref="B1405:B1406"/>
-    <mergeCell ref="B1407:B1408"/>
-    <mergeCell ref="B1409:B1410"/>
-    <mergeCell ref="B1411:B1412"/>
-    <mergeCell ref="B1413:B1414"/>
-    <mergeCell ref="B1415:B1416"/>
-    <mergeCell ref="B1417:B1418"/>
-    <mergeCell ref="B1419:B1420"/>
-    <mergeCell ref="B1385:B1386"/>
-    <mergeCell ref="B1387:B1388"/>
-    <mergeCell ref="B1389:B1390"/>
-    <mergeCell ref="B1391:B1392"/>
-    <mergeCell ref="B1393:B1394"/>
-    <mergeCell ref="B1395:B1396"/>
-    <mergeCell ref="B1397:B1398"/>
-    <mergeCell ref="B1399:B1400"/>
-    <mergeCell ref="B1401:B1402"/>
-    <mergeCell ref="B1367:B1368"/>
-    <mergeCell ref="B1369:B1370"/>
-    <mergeCell ref="B1371:B1372"/>
-    <mergeCell ref="B1373:B1374"/>
-    <mergeCell ref="B1375:B1376"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B1379:B1380"/>
-    <mergeCell ref="B1381:B1382"/>
-    <mergeCell ref="B1383:B1384"/>
-    <mergeCell ref="B1349:B1350"/>
-    <mergeCell ref="B1351:B1352"/>
-    <mergeCell ref="B1353:B1354"/>
-    <mergeCell ref="B1355:B1356"/>
-    <mergeCell ref="B1357:B1358"/>
-    <mergeCell ref="B1359:B1360"/>
-    <mergeCell ref="B1361:B1362"/>
-    <mergeCell ref="B1363:B1364"/>
-    <mergeCell ref="B1365:B1366"/>
-    <mergeCell ref="B1331:B1332"/>
-    <mergeCell ref="B1333:B1334"/>
-    <mergeCell ref="B1335:B1336"/>
-    <mergeCell ref="B1337:B1338"/>
-    <mergeCell ref="B1339:B1340"/>
-    <mergeCell ref="B1341:B1342"/>
-    <mergeCell ref="B1343:B1344"/>
-    <mergeCell ref="B1345:B1346"/>
-    <mergeCell ref="B1347:B1348"/>
-    <mergeCell ref="B1313:B1314"/>
-    <mergeCell ref="B1315:B1316"/>
-    <mergeCell ref="B1317:B1318"/>
-    <mergeCell ref="B1319:B1320"/>
-    <mergeCell ref="B1321:B1322"/>
-    <mergeCell ref="B1323:B1324"/>
-    <mergeCell ref="B1325:B1326"/>
-    <mergeCell ref="B1327:B1328"/>
-    <mergeCell ref="B1329:B1330"/>
-    <mergeCell ref="B1295:B1296"/>
-    <mergeCell ref="B1297:B1298"/>
-    <mergeCell ref="B1299:B1300"/>
-    <mergeCell ref="B1301:B1302"/>
-    <mergeCell ref="B1303:B1304"/>
-    <mergeCell ref="B1305:B1306"/>
-    <mergeCell ref="B1307:B1308"/>
-    <mergeCell ref="B1309:B1310"/>
-    <mergeCell ref="B1311:B1312"/>
-    <mergeCell ref="B1277:B1278"/>
-    <mergeCell ref="B1279:B1280"/>
-    <mergeCell ref="B1281:B1282"/>
-    <mergeCell ref="B1283:B1284"/>
-    <mergeCell ref="B1285:B1286"/>
-    <mergeCell ref="B1287:B1288"/>
-    <mergeCell ref="B1289:B1290"/>
-    <mergeCell ref="B1291:B1292"/>
-    <mergeCell ref="B1293:B1294"/>
-    <mergeCell ref="B1259:B1260"/>
-    <mergeCell ref="B1261:B1262"/>
-    <mergeCell ref="B1263:B1264"/>
-    <mergeCell ref="B1265:B1266"/>
-    <mergeCell ref="B1267:B1268"/>
-    <mergeCell ref="B1269:B1270"/>
-    <mergeCell ref="B1271:B1272"/>
-    <mergeCell ref="B1273:B1274"/>
-    <mergeCell ref="B1275:B1276"/>
-    <mergeCell ref="B1241:B1242"/>
-    <mergeCell ref="B1243:B1244"/>
-    <mergeCell ref="B1245:B1246"/>
-    <mergeCell ref="B1247:B1248"/>
-    <mergeCell ref="B1249:B1250"/>
-    <mergeCell ref="B1251:B1252"/>
-    <mergeCell ref="B1253:B1254"/>
-    <mergeCell ref="B1255:B1256"/>
-    <mergeCell ref="B1257:B1258"/>
-    <mergeCell ref="B1223:B1224"/>
-    <mergeCell ref="B1225:B1226"/>
-    <mergeCell ref="B1227:B1228"/>
-    <mergeCell ref="B1229:B1230"/>
-    <mergeCell ref="B1231:B1232"/>
-    <mergeCell ref="B1233:B1234"/>
-    <mergeCell ref="B1235:B1236"/>
-    <mergeCell ref="B1237:B1238"/>
-    <mergeCell ref="B1239:B1240"/>
-    <mergeCell ref="B1205:B1206"/>
-    <mergeCell ref="B1207:B1208"/>
-    <mergeCell ref="B1209:B1210"/>
-    <mergeCell ref="B1211:B1212"/>
-    <mergeCell ref="B1213:B1214"/>
-    <mergeCell ref="B1215:B1216"/>
-    <mergeCell ref="B1217:B1218"/>
-    <mergeCell ref="B1219:B1220"/>
-    <mergeCell ref="B1221:B1222"/>
-    <mergeCell ref="B1187:B1188"/>
-    <mergeCell ref="B1189:B1190"/>
-    <mergeCell ref="B1191:B1192"/>
-    <mergeCell ref="B1193:B1194"/>
-    <mergeCell ref="B1195:B1196"/>
-    <mergeCell ref="B1197:B1198"/>
-    <mergeCell ref="B1199:B1200"/>
-    <mergeCell ref="B1201:B1202"/>
-    <mergeCell ref="B1203:B1204"/>
-    <mergeCell ref="B1169:B1170"/>
-    <mergeCell ref="B1171:B1172"/>
-    <mergeCell ref="B1173:B1174"/>
-    <mergeCell ref="B1175:B1176"/>
-    <mergeCell ref="B1177:B1178"/>
-    <mergeCell ref="B1179:B1180"/>
-    <mergeCell ref="B1181:B1182"/>
-    <mergeCell ref="B1183:B1184"/>
-    <mergeCell ref="B1185:B1186"/>
-    <mergeCell ref="B1151:B1152"/>
-    <mergeCell ref="B1153:B1154"/>
-    <mergeCell ref="B1155:B1156"/>
-    <mergeCell ref="B1157:B1158"/>
-    <mergeCell ref="B1159:B1160"/>
-    <mergeCell ref="B1161:B1162"/>
-    <mergeCell ref="B1163:B1164"/>
-    <mergeCell ref="B1165:B1166"/>
-    <mergeCell ref="B1167:B1168"/>
-    <mergeCell ref="B1133:B1134"/>
-    <mergeCell ref="B1135:B1136"/>
-    <mergeCell ref="B1137:B1138"/>
-    <mergeCell ref="B1139:B1140"/>
-    <mergeCell ref="B1141:B1142"/>
-    <mergeCell ref="B1143:B1144"/>
-    <mergeCell ref="B1145:B1146"/>
-    <mergeCell ref="B1147:B1148"/>
-    <mergeCell ref="B1149:B1150"/>
-    <mergeCell ref="B1115:B1116"/>
-    <mergeCell ref="B1117:B1118"/>
-    <mergeCell ref="B1119:B1120"/>
-    <mergeCell ref="B1121:B1122"/>
-    <mergeCell ref="B1123:B1124"/>
-    <mergeCell ref="B1125:B1126"/>
-    <mergeCell ref="B1127:B1128"/>
-    <mergeCell ref="B1129:B1130"/>
-    <mergeCell ref="B1131:B1132"/>
-    <mergeCell ref="B1097:B1098"/>
-    <mergeCell ref="B1099:B1100"/>
-    <mergeCell ref="B1101:B1102"/>
-    <mergeCell ref="B1103:B1104"/>
-    <mergeCell ref="B1105:B1106"/>
-    <mergeCell ref="B1107:B1108"/>
-    <mergeCell ref="B1109:B1110"/>
-    <mergeCell ref="B1111:B1112"/>
-    <mergeCell ref="B1113:B1114"/>
-    <mergeCell ref="B1079:B1080"/>
-    <mergeCell ref="B1081:B1082"/>
-    <mergeCell ref="B1083:B1084"/>
-    <mergeCell ref="B1085:B1086"/>
-    <mergeCell ref="B1087:B1088"/>
-    <mergeCell ref="B1089:B1090"/>
-    <mergeCell ref="B1091:B1092"/>
-    <mergeCell ref="B1093:B1094"/>
-    <mergeCell ref="B1095:B1096"/>
-    <mergeCell ref="B943:B955"/>
-    <mergeCell ref="B956:B963"/>
-    <mergeCell ref="B964:B971"/>
-    <mergeCell ref="B972:B979"/>
-    <mergeCell ref="B980:B984"/>
-    <mergeCell ref="B985:B990"/>
-    <mergeCell ref="B991:B1041"/>
-    <mergeCell ref="B1042:B1076"/>
-    <mergeCell ref="B1077:B1078"/>
-    <mergeCell ref="B893:B895"/>
-    <mergeCell ref="B896:B901"/>
-    <mergeCell ref="B902:B905"/>
-    <mergeCell ref="B906:B909"/>
-    <mergeCell ref="B910:B916"/>
-    <mergeCell ref="B917:B925"/>
-    <mergeCell ref="B926:B929"/>
-    <mergeCell ref="B930:B935"/>
-    <mergeCell ref="B936:B942"/>
-    <mergeCell ref="B856:B860"/>
-    <mergeCell ref="B861:B864"/>
-    <mergeCell ref="B865:B870"/>
-    <mergeCell ref="B871:B874"/>
-    <mergeCell ref="B875:B879"/>
-    <mergeCell ref="B880:B882"/>
-    <mergeCell ref="B883:B885"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="B888:B892"/>
-    <mergeCell ref="B813:B815"/>
-    <mergeCell ref="B816:B820"/>
-    <mergeCell ref="B821:B825"/>
-    <mergeCell ref="B826:B830"/>
-    <mergeCell ref="B831:B835"/>
-    <mergeCell ref="B836:B843"/>
-    <mergeCell ref="B844:B846"/>
-    <mergeCell ref="B847:B852"/>
-    <mergeCell ref="B853:B855"/>
-    <mergeCell ref="B786:B788"/>
-    <mergeCell ref="B789:B791"/>
-    <mergeCell ref="B792:B794"/>
-    <mergeCell ref="B795:B797"/>
-    <mergeCell ref="B798:B800"/>
-    <mergeCell ref="B801:B803"/>
-    <mergeCell ref="B804:B806"/>
-    <mergeCell ref="B807:B809"/>
-    <mergeCell ref="B810:B812"/>
-    <mergeCell ref="B745:B746"/>
-    <mergeCell ref="B747:B750"/>
-    <mergeCell ref="B751:B755"/>
-    <mergeCell ref="B756:B761"/>
-    <mergeCell ref="B762:B767"/>
-    <mergeCell ref="B768:B776"/>
-    <mergeCell ref="B777:B779"/>
-    <mergeCell ref="B780:B782"/>
-    <mergeCell ref="B783:B785"/>
-    <mergeCell ref="B659:B665"/>
-    <mergeCell ref="B666:B670"/>
-    <mergeCell ref="B671:B675"/>
-    <mergeCell ref="B676:B680"/>
-    <mergeCell ref="B681:B685"/>
-    <mergeCell ref="B686:B691"/>
-    <mergeCell ref="B692:B698"/>
-    <mergeCell ref="B699:B712"/>
-    <mergeCell ref="B713:B744"/>
-    <mergeCell ref="B583:B585"/>
-    <mergeCell ref="B586:B588"/>
-    <mergeCell ref="B589:B591"/>
-    <mergeCell ref="B592:B605"/>
-    <mergeCell ref="B606:B637"/>
-    <mergeCell ref="B638:B641"/>
-    <mergeCell ref="B642:B646"/>
-    <mergeCell ref="B647:B651"/>
-    <mergeCell ref="B652:B658"/>
-    <mergeCell ref="B541:B546"/>
-    <mergeCell ref="B547:B552"/>
-    <mergeCell ref="B553:B558"/>
-    <mergeCell ref="B559:B564"/>
-    <mergeCell ref="B565:B568"/>
-    <mergeCell ref="B569:B571"/>
-    <mergeCell ref="B572:B575"/>
-    <mergeCell ref="B576:B579"/>
-    <mergeCell ref="B580:B582"/>
-    <mergeCell ref="B487:B492"/>
-    <mergeCell ref="B493:B498"/>
-    <mergeCell ref="B499:B504"/>
-    <mergeCell ref="B505:B510"/>
-    <mergeCell ref="B511:B516"/>
-    <mergeCell ref="B517:B522"/>
-    <mergeCell ref="B523:B528"/>
-    <mergeCell ref="B529:B534"/>
-    <mergeCell ref="B535:B540"/>
-    <mergeCell ref="B431:B436"/>
-    <mergeCell ref="B437:B442"/>
-    <mergeCell ref="B443:B450"/>
-    <mergeCell ref="B451:B456"/>
-    <mergeCell ref="B457:B462"/>
-    <mergeCell ref="B463:B468"/>
-    <mergeCell ref="B469:B474"/>
-    <mergeCell ref="B475:B480"/>
-    <mergeCell ref="B481:B486"/>
-    <mergeCell ref="B393:B399"/>
-    <mergeCell ref="B400:B404"/>
-    <mergeCell ref="B405:B407"/>
-    <mergeCell ref="B408:B410"/>
-    <mergeCell ref="B411:B415"/>
-    <mergeCell ref="B416:B418"/>
-    <mergeCell ref="B419:B421"/>
-    <mergeCell ref="B422:B424"/>
-    <mergeCell ref="B425:B430"/>
-    <mergeCell ref="B347:B351"/>
-    <mergeCell ref="B352:B355"/>
-    <mergeCell ref="B356:B359"/>
-    <mergeCell ref="B360:B363"/>
-    <mergeCell ref="B364:B367"/>
-    <mergeCell ref="B368:B371"/>
-    <mergeCell ref="B372:B378"/>
-    <mergeCell ref="B379:B385"/>
-    <mergeCell ref="B386:B392"/>
-    <mergeCell ref="B115:B200"/>
-    <mergeCell ref="B201:B253"/>
-    <mergeCell ref="B254:B269"/>
-    <mergeCell ref="B270:B287"/>
-    <mergeCell ref="B288:B301"/>
-    <mergeCell ref="B302:B333"/>
-    <mergeCell ref="B334:B337"/>
-    <mergeCell ref="B338:B341"/>
-    <mergeCell ref="B342:B346"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B109:B114"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/2023-24 RLS Codebook.xlsx
+++ b/2023-24 RLS Codebook.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FFAB5FB7-467A-4FFE-BD62-267D7CBFA7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE3AF3E-00F4-4857-93CA-3E59A131CE16}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="11400" yWindow="2318" windowWidth="7500" windowHeight="9434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Codebook" sheetId="1" r:id="rId1"/>
@@ -7127,16 +7127,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7766,7 +7766,7 @@
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="3">
@@ -7780,7 +7780,7 @@
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="10"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="2">
         <v>2</v>
       </c>
@@ -7792,7 +7792,7 @@
       <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="10"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="2">
         <v>3</v>
       </c>
@@ -7804,7 +7804,7 @@
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="10"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="2">
         <v>99</v>
       </c>
@@ -7816,7 +7816,7 @@
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="3">
@@ -7830,7 +7830,7 @@
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="2">
         <v>2</v>
       </c>
@@ -7842,7 +7842,7 @@
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="2">
         <v>3</v>
       </c>
@@ -7854,7 +7854,7 @@
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="10"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="2">
         <v>99</v>
       </c>
@@ -7866,7 +7866,7 @@
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="3">
@@ -7880,7 +7880,7 @@
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="10"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="2">
         <v>2</v>
       </c>
@@ -7892,7 +7892,7 @@
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="2">
         <v>3</v>
       </c>
@@ -7904,7 +7904,7 @@
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="10"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="2">
         <v>99</v>
       </c>
@@ -7916,7 +7916,7 @@
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="3">
@@ -7930,7 +7930,7 @@
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="10"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="2">
         <v>2</v>
       </c>
@@ -7942,7 +7942,7 @@
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="10"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="2">
         <v>3</v>
       </c>
@@ -7954,7 +7954,7 @@
       <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="10"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="2">
         <v>99</v>
       </c>
@@ -7966,7 +7966,7 @@
       <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C42" s="3">
@@ -7980,7 +7980,7 @@
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="10"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="2">
         <v>2</v>
       </c>
@@ -7992,7 +7992,7 @@
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="10"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="2">
         <v>3</v>
       </c>
@@ -8004,7 +8004,7 @@
       <c r="A45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="10"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="2">
         <v>99</v>
       </c>
@@ -8016,7 +8016,7 @@
       <c r="A46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C46" s="3">
@@ -8030,7 +8030,7 @@
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="10"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="2">
         <v>2</v>
       </c>
@@ -8042,7 +8042,7 @@
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="10"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="2">
         <v>99</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="3">
@@ -8068,7 +8068,7 @@
       <c r="A50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="10"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="2">
         <v>2</v>
       </c>
@@ -8080,7 +8080,7 @@
       <c r="A51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="10"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="2">
         <v>99</v>
       </c>
@@ -8092,7 +8092,7 @@
       <c r="A52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="3">
@@ -8106,7 +8106,7 @@
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="10"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="2">
         <v>2</v>
       </c>
@@ -8118,7 +8118,7 @@
       <c r="A54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="10"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="2">
         <v>99</v>
       </c>
@@ -8130,7 +8130,7 @@
       <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="3">
@@ -8144,7 +8144,7 @@
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="10"/>
+      <c r="B56" s="8"/>
       <c r="C56" s="2">
         <v>2</v>
       </c>
@@ -8156,7 +8156,7 @@
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="10"/>
+      <c r="B57" s="8"/>
       <c r="C57" s="2">
         <v>99</v>
       </c>
@@ -8168,7 +8168,7 @@
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="3">
@@ -8182,7 +8182,7 @@
       <c r="A59" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="10"/>
+      <c r="B59" s="8"/>
       <c r="C59" s="2">
         <v>2</v>
       </c>
@@ -8194,7 +8194,7 @@
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="10"/>
+      <c r="B60" s="8"/>
       <c r="C60" s="2">
         <v>3</v>
       </c>
@@ -8206,7 +8206,7 @@
       <c r="A61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="10"/>
+      <c r="B61" s="8"/>
       <c r="C61" s="2">
         <v>99</v>
       </c>
@@ -8218,7 +8218,7 @@
       <c r="A62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="3">
@@ -8232,7 +8232,7 @@
       <c r="A63" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="10"/>
+      <c r="B63" s="8"/>
       <c r="C63" s="2">
         <v>2</v>
       </c>
@@ -8244,7 +8244,7 @@
       <c r="A64" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="10"/>
+      <c r="B64" s="8"/>
       <c r="C64" s="2">
         <v>99</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="A65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C65" s="3">
@@ -8270,7 +8270,7 @@
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="10"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="2">
         <v>2</v>
       </c>
@@ -8282,7 +8282,7 @@
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="10"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="2">
         <v>3</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="10"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="2">
         <v>4</v>
       </c>
@@ -8306,7 +8306,7 @@
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="10"/>
+      <c r="B69" s="8"/>
       <c r="C69" s="2">
         <v>99</v>
       </c>
@@ -8318,7 +8318,7 @@
       <c r="A70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C70" s="3">
@@ -8332,7 +8332,7 @@
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="10"/>
+      <c r="B71" s="8"/>
       <c r="C71" s="2">
         <v>2</v>
       </c>
@@ -8344,7 +8344,7 @@
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="10"/>
+      <c r="B72" s="8"/>
       <c r="C72" s="2">
         <v>3</v>
       </c>
@@ -8356,7 +8356,7 @@
       <c r="A73" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="10"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="2">
         <v>4</v>
       </c>
@@ -8368,7 +8368,7 @@
       <c r="A74" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="10"/>
+      <c r="B74" s="8"/>
       <c r="C74" s="2">
         <v>99</v>
       </c>
@@ -8380,7 +8380,7 @@
       <c r="A75" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C75" s="3">
@@ -8394,7 +8394,7 @@
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="10"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="2">
         <v>2</v>
       </c>
@@ -8406,7 +8406,7 @@
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="2">
         <v>99</v>
       </c>
@@ -8580,7 +8580,7 @@
       <c r="A91" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C91" s="3">
@@ -8594,7 +8594,7 @@
       <c r="A92" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B92" s="10"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="2">
         <v>2</v>
       </c>
@@ -8606,7 +8606,7 @@
       <c r="A93" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B93" s="10"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="2">
         <v>3</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="A94" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="10"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="2">
         <v>4</v>
       </c>
@@ -8630,7 +8630,7 @@
       <c r="A95" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B95" s="10"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="2">
         <v>5</v>
       </c>
@@ -8642,7 +8642,7 @@
       <c r="A96" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="10"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="2">
         <v>99</v>
       </c>
@@ -8654,7 +8654,7 @@
       <c r="A97" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>113</v>
       </c>
       <c r="C97" s="3">
@@ -8668,7 +8668,7 @@
       <c r="A98" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B98" s="10"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="2">
         <v>2</v>
       </c>
@@ -8680,7 +8680,7 @@
       <c r="A99" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B99" s="10"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="2">
         <v>3</v>
       </c>
@@ -8692,7 +8692,7 @@
       <c r="A100" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B100" s="10"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="2">
         <v>4</v>
       </c>
@@ -8704,7 +8704,7 @@
       <c r="A101" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="10"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="2">
         <v>5</v>
       </c>
@@ -8716,7 +8716,7 @@
       <c r="A102" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B102" s="10"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="2">
         <v>99</v>
       </c>
@@ -8728,7 +8728,7 @@
       <c r="A103" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C103" s="3">
@@ -8742,7 +8742,7 @@
       <c r="A104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="10"/>
+      <c r="B104" s="8"/>
       <c r="C104" s="2">
         <v>2</v>
       </c>
@@ -8754,7 +8754,7 @@
       <c r="A105" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B105" s="10"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="2">
         <v>3</v>
       </c>
@@ -8766,7 +8766,7 @@
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="10"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="2">
         <v>4</v>
       </c>
@@ -8778,7 +8778,7 @@
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="10"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="2">
         <v>5</v>
       </c>
@@ -8790,7 +8790,7 @@
       <c r="A108" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="10"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="2">
         <v>99</v>
       </c>
@@ -8802,7 +8802,7 @@
       <c r="A109" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="7" t="s">
         <v>117</v>
       </c>
       <c r="C109" s="3">
@@ -8816,7 +8816,7 @@
       <c r="A110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="10"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="2">
         <v>2</v>
       </c>
@@ -8828,7 +8828,7 @@
       <c r="A111" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="10"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="2">
         <v>3</v>
       </c>
@@ -8840,7 +8840,7 @@
       <c r="A112" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="10"/>
+      <c r="B112" s="8"/>
       <c r="C112" s="2">
         <v>4</v>
       </c>
@@ -8852,7 +8852,7 @@
       <c r="A113" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B113" s="10"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="2">
         <v>5</v>
       </c>
@@ -8864,7 +8864,7 @@
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="10"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="2">
         <v>99</v>
       </c>
@@ -10548,7 +10548,7 @@
       <c r="A254" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="7" t="s">
         <v>258</v>
       </c>
       <c r="C254" s="3">
@@ -10562,7 +10562,7 @@
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B255" s="10"/>
+      <c r="B255" s="8"/>
       <c r="C255" s="2">
         <v>1200</v>
       </c>
@@ -10574,7 +10574,7 @@
       <c r="A256" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B256" s="10"/>
+      <c r="B256" s="8"/>
       <c r="C256" s="2">
         <v>1300</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="A257" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="10"/>
+      <c r="B257" s="8"/>
       <c r="C257" s="2">
         <v>10000</v>
       </c>
@@ -10598,7 +10598,7 @@
       <c r="A258" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="10"/>
+      <c r="B258" s="8"/>
       <c r="C258" s="2">
         <v>20000</v>
       </c>
@@ -10610,7 +10610,7 @@
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259" s="10"/>
+      <c r="B259" s="8"/>
       <c r="C259" s="2">
         <v>30000</v>
       </c>
@@ -10622,7 +10622,7 @@
       <c r="A260" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B260" s="10"/>
+      <c r="B260" s="8"/>
       <c r="C260" s="2">
         <v>40001</v>
       </c>
@@ -10634,7 +10634,7 @@
       <c r="A261" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B261" s="10"/>
+      <c r="B261" s="8"/>
       <c r="C261" s="2">
         <v>40002</v>
       </c>
@@ -10646,7 +10646,7 @@
       <c r="A262" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B262" s="10"/>
+      <c r="B262" s="8"/>
       <c r="C262" s="2">
         <v>50000</v>
       </c>
@@ -10658,7 +10658,7 @@
       <c r="A263" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B263" s="10"/>
+      <c r="B263" s="8"/>
       <c r="C263" s="2">
         <v>60000</v>
       </c>
@@ -10670,7 +10670,7 @@
       <c r="A264" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B264" s="10"/>
+      <c r="B264" s="8"/>
       <c r="C264" s="2">
         <v>70000</v>
       </c>
@@ -10682,7 +10682,7 @@
       <c r="A265" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B265" s="10"/>
+      <c r="B265" s="8"/>
       <c r="C265" s="2">
         <v>80000</v>
       </c>
@@ -10694,7 +10694,7 @@
       <c r="A266" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B266" s="10"/>
+      <c r="B266" s="8"/>
       <c r="C266" s="2">
         <v>90001</v>
       </c>
@@ -10706,7 +10706,7 @@
       <c r="A267" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B267" s="10"/>
+      <c r="B267" s="8"/>
       <c r="C267" s="2">
         <v>90002</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="A268" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B268" s="10"/>
+      <c r="B268" s="8"/>
       <c r="C268" s="2">
         <v>100000</v>
       </c>
@@ -10730,7 +10730,7 @@
       <c r="A269" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B269" s="10"/>
+      <c r="B269" s="8"/>
       <c r="C269" s="2">
         <v>900000</v>
       </c>
@@ -10960,7 +10960,7 @@
       <c r="A288" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="7" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="3">
@@ -10974,7 +10974,7 @@
       <c r="A289" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B289" s="10"/>
+      <c r="B289" s="8"/>
       <c r="C289" s="2">
         <v>10000</v>
       </c>
@@ -10986,7 +10986,7 @@
       <c r="A290" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B290" s="10"/>
+      <c r="B290" s="8"/>
       <c r="C290" s="2">
         <v>20000</v>
       </c>
@@ -10998,7 +10998,7 @@
       <c r="A291" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B291" s="10"/>
+      <c r="B291" s="8"/>
       <c r="C291" s="2">
         <v>30000</v>
       </c>
@@ -11010,7 +11010,7 @@
       <c r="A292" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B292" s="10"/>
+      <c r="B292" s="8"/>
       <c r="C292" s="2">
         <v>40001</v>
       </c>
@@ -11022,7 +11022,7 @@
       <c r="A293" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B293" s="10"/>
+      <c r="B293" s="8"/>
       <c r="C293" s="2">
         <v>40002</v>
       </c>
@@ -11034,7 +11034,7 @@
       <c r="A294" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B294" s="10"/>
+      <c r="B294" s="8"/>
       <c r="C294" s="2">
         <v>50000</v>
       </c>
@@ -11046,7 +11046,7 @@
       <c r="A295" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B295" s="10"/>
+      <c r="B295" s="8"/>
       <c r="C295" s="2">
         <v>60000</v>
       </c>
@@ -11058,7 +11058,7 @@
       <c r="A296" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B296" s="10"/>
+      <c r="B296" s="8"/>
       <c r="C296" s="2">
         <v>70000</v>
       </c>
@@ -11070,7 +11070,7 @@
       <c r="A297" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B297" s="10"/>
+      <c r="B297" s="8"/>
       <c r="C297" s="2">
         <v>80000</v>
       </c>
@@ -11082,7 +11082,7 @@
       <c r="A298" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B298" s="10"/>
+      <c r="B298" s="8"/>
       <c r="C298" s="2">
         <v>90001</v>
       </c>
@@ -11094,7 +11094,7 @@
       <c r="A299" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B299" s="10"/>
+      <c r="B299" s="8"/>
       <c r="C299" s="2">
         <v>90002</v>
       </c>
@@ -11106,7 +11106,7 @@
       <c r="A300" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B300" s="10"/>
+      <c r="B300" s="8"/>
       <c r="C300" s="2">
         <v>100000</v>
       </c>
@@ -11118,7 +11118,7 @@
       <c r="A301" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B301" s="10"/>
+      <c r="B301" s="8"/>
       <c r="C301" s="2">
         <v>900000</v>
       </c>
@@ -11616,7 +11616,7 @@
       <c r="A342" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B342" s="9" t="s">
+      <c r="B342" s="7" t="s">
         <v>304</v>
       </c>
       <c r="C342" s="3">
@@ -11630,7 +11630,7 @@
       <c r="A343" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B343" s="10"/>
+      <c r="B343" s="8"/>
       <c r="C343" s="2">
         <v>2</v>
       </c>
@@ -11642,7 +11642,7 @@
       <c r="A344" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B344" s="10"/>
+      <c r="B344" s="8"/>
       <c r="C344" s="2">
         <v>3</v>
       </c>
@@ -11654,7 +11654,7 @@
       <c r="A345" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B345" s="10"/>
+      <c r="B345" s="8"/>
       <c r="C345" s="2">
         <v>4</v>
       </c>
@@ -11666,7 +11666,7 @@
       <c r="A346" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B346" s="10"/>
+      <c r="B346" s="8"/>
       <c r="C346" s="2">
         <v>99</v>
       </c>
@@ -11678,7 +11678,7 @@
       <c r="A347" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B347" s="9" t="s">
+      <c r="B347" s="7" t="s">
         <v>310</v>
       </c>
       <c r="C347" s="3">
@@ -11692,7 +11692,7 @@
       <c r="A348" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B348" s="10"/>
+      <c r="B348" s="8"/>
       <c r="C348" s="2">
         <v>2</v>
       </c>
@@ -11704,7 +11704,7 @@
       <c r="A349" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B349" s="10"/>
+      <c r="B349" s="8"/>
       <c r="C349" s="2">
         <v>3</v>
       </c>
@@ -11716,7 +11716,7 @@
       <c r="A350" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B350" s="10"/>
+      <c r="B350" s="8"/>
       <c r="C350" s="2">
         <v>4</v>
       </c>
@@ -11728,7 +11728,7 @@
       <c r="A351" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B351" s="10"/>
+      <c r="B351" s="8"/>
       <c r="C351" s="2">
         <v>99</v>
       </c>
@@ -11990,7 +11990,7 @@
       <c r="A372" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B372" s="9" t="s">
+      <c r="B372" s="7" t="s">
         <v>333</v>
       </c>
       <c r="C372" s="3">
@@ -12004,7 +12004,7 @@
       <c r="A373" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B373" s="10"/>
+      <c r="B373" s="8"/>
       <c r="C373" s="2">
         <v>2</v>
       </c>
@@ -12016,7 +12016,7 @@
       <c r="A374" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B374" s="10"/>
+      <c r="B374" s="8"/>
       <c r="C374" s="2">
         <v>3</v>
       </c>
@@ -12028,7 +12028,7 @@
       <c r="A375" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B375" s="10"/>
+      <c r="B375" s="8"/>
       <c r="C375" s="2">
         <v>4</v>
       </c>
@@ -12040,7 +12040,7 @@
       <c r="A376" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B376" s="10"/>
+      <c r="B376" s="8"/>
       <c r="C376" s="2">
         <v>5</v>
       </c>
@@ -12052,7 +12052,7 @@
       <c r="A377" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B377" s="10"/>
+      <c r="B377" s="8"/>
       <c r="C377" s="2">
         <v>6</v>
       </c>
@@ -12064,7 +12064,7 @@
       <c r="A378" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B378" s="10"/>
+      <c r="B378" s="8"/>
       <c r="C378" s="2">
         <v>99</v>
       </c>
@@ -12076,7 +12076,7 @@
       <c r="A379" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="7" t="s">
         <v>341</v>
       </c>
       <c r="C379" s="3">
@@ -12090,7 +12090,7 @@
       <c r="A380" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B380" s="10"/>
+      <c r="B380" s="8"/>
       <c r="C380" s="2">
         <v>2</v>
       </c>
@@ -12102,7 +12102,7 @@
       <c r="A381" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B381" s="10"/>
+      <c r="B381" s="8"/>
       <c r="C381" s="2">
         <v>3</v>
       </c>
@@ -12114,7 +12114,7 @@
       <c r="A382" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B382" s="10"/>
+      <c r="B382" s="8"/>
       <c r="C382" s="2">
         <v>4</v>
       </c>
@@ -12126,7 +12126,7 @@
       <c r="A383" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B383" s="10"/>
+      <c r="B383" s="8"/>
       <c r="C383" s="2">
         <v>5</v>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="A384" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B384" s="10"/>
+      <c r="B384" s="8"/>
       <c r="C384" s="2">
         <v>6</v>
       </c>
@@ -12150,7 +12150,7 @@
       <c r="A385" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B385" s="10"/>
+      <c r="B385" s="8"/>
       <c r="C385" s="2">
         <v>99</v>
       </c>
@@ -12334,7 +12334,7 @@
       <c r="A400" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="7" t="s">
         <v>353</v>
       </c>
       <c r="C400" s="3">
@@ -12348,7 +12348,7 @@
       <c r="A401" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B401" s="10"/>
+      <c r="B401" s="8"/>
       <c r="C401" s="2">
         <v>2</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="A402" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B402" s="10"/>
+      <c r="B402" s="8"/>
       <c r="C402" s="2">
         <v>3</v>
       </c>
@@ -12372,7 +12372,7 @@
       <c r="A403" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B403" s="10"/>
+      <c r="B403" s="8"/>
       <c r="C403" s="2">
         <v>4</v>
       </c>
@@ -12384,7 +12384,7 @@
       <c r="A404" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B404" s="10"/>
+      <c r="B404" s="8"/>
       <c r="C404" s="2">
         <v>99</v>
       </c>
@@ -12396,7 +12396,7 @@
       <c r="A405" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B405" s="9" t="s">
+      <c r="B405" s="7" t="s">
         <v>355</v>
       </c>
       <c r="C405" s="3">
@@ -12410,7 +12410,7 @@
       <c r="A406" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B406" s="10"/>
+      <c r="B406" s="8"/>
       <c r="C406" s="2">
         <v>2</v>
       </c>
@@ -12422,7 +12422,7 @@
       <c r="A407" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B407" s="10"/>
+      <c r="B407" s="8"/>
       <c r="C407" s="2">
         <v>99</v>
       </c>
@@ -12434,7 +12434,7 @@
       <c r="A408" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B408" s="9" t="s">
+      <c r="B408" s="7" t="s">
         <v>357</v>
       </c>
       <c r="C408" s="3">
@@ -12448,7 +12448,7 @@
       <c r="A409" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B409" s="10"/>
+      <c r="B409" s="8"/>
       <c r="C409" s="2">
         <v>2</v>
       </c>
@@ -12460,7 +12460,7 @@
       <c r="A410" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B410" s="10"/>
+      <c r="B410" s="8"/>
       <c r="C410" s="2">
         <v>99</v>
       </c>
@@ -12534,7 +12534,7 @@
       <c r="A416" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B416" s="9" t="s">
+      <c r="B416" s="7" t="s">
         <v>365</v>
       </c>
       <c r="C416" s="3">
@@ -12548,7 +12548,7 @@
       <c r="A417" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B417" s="10"/>
+      <c r="B417" s="8"/>
       <c r="C417" s="2">
         <v>2</v>
       </c>
@@ -12560,7 +12560,7 @@
       <c r="A418" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B418" s="10"/>
+      <c r="B418" s="8"/>
       <c r="C418" s="2">
         <v>99</v>
       </c>
@@ -12572,7 +12572,7 @@
       <c r="A419" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B419" s="9" t="s">
+      <c r="B419" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C419" s="3">
@@ -12586,7 +12586,7 @@
       <c r="A420" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B420" s="10"/>
+      <c r="B420" s="8"/>
       <c r="C420" s="2">
         <v>2</v>
       </c>
@@ -12598,7 +12598,7 @@
       <c r="A421" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B421" s="10"/>
+      <c r="B421" s="8"/>
       <c r="C421" s="2">
         <v>99</v>
       </c>
@@ -12610,7 +12610,7 @@
       <c r="A422" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B422" s="9" t="s">
+      <c r="B422" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C422" s="3">
@@ -12624,7 +12624,7 @@
       <c r="A423" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B423" s="10"/>
+      <c r="B423" s="8"/>
       <c r="C423" s="2">
         <v>2</v>
       </c>
@@ -12636,7 +12636,7 @@
       <c r="A424" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B424" s="10"/>
+      <c r="B424" s="8"/>
       <c r="C424" s="2">
         <v>99</v>
       </c>
@@ -12648,7 +12648,7 @@
       <c r="A425" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B425" s="9" t="s">
+      <c r="B425" s="7" t="s">
         <v>371</v>
       </c>
       <c r="C425" s="3">
@@ -12662,7 +12662,7 @@
       <c r="A426" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B426" s="10"/>
+      <c r="B426" s="8"/>
       <c r="C426" s="2">
         <v>2</v>
       </c>
@@ -12674,7 +12674,7 @@
       <c r="A427" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B427" s="10"/>
+      <c r="B427" s="8"/>
       <c r="C427" s="2">
         <v>3</v>
       </c>
@@ -12686,7 +12686,7 @@
       <c r="A428" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B428" s="10"/>
+      <c r="B428" s="8"/>
       <c r="C428" s="2">
         <v>4</v>
       </c>
@@ -12698,7 +12698,7 @@
       <c r="A429" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B429" s="10"/>
+      <c r="B429" s="8"/>
       <c r="C429" s="2">
         <v>5</v>
       </c>
@@ -12710,7 +12710,7 @@
       <c r="A430" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B430" s="10"/>
+      <c r="B430" s="8"/>
       <c r="C430" s="2">
         <v>99</v>
       </c>
@@ -12722,7 +12722,7 @@
       <c r="A431" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B431" s="9" t="s">
+      <c r="B431" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C431" s="3">
@@ -12736,7 +12736,7 @@
       <c r="A432" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B432" s="10"/>
+      <c r="B432" s="8"/>
       <c r="C432" s="2">
         <v>2</v>
       </c>
@@ -12748,7 +12748,7 @@
       <c r="A433" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B433" s="10"/>
+      <c r="B433" s="8"/>
       <c r="C433" s="2">
         <v>3</v>
       </c>
@@ -12760,7 +12760,7 @@
       <c r="A434" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B434" s="10"/>
+      <c r="B434" s="8"/>
       <c r="C434" s="2">
         <v>4</v>
       </c>
@@ -12772,7 +12772,7 @@
       <c r="A435" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B435" s="10"/>
+      <c r="B435" s="8"/>
       <c r="C435" s="2">
         <v>5</v>
       </c>
@@ -12784,7 +12784,7 @@
       <c r="A436" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B436" s="10"/>
+      <c r="B436" s="8"/>
       <c r="C436" s="2">
         <v>99</v>
       </c>
@@ -12796,7 +12796,7 @@
       <c r="A437" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B437" s="9" t="s">
+      <c r="B437" s="7" t="s">
         <v>380</v>
       </c>
       <c r="C437" s="3">
@@ -12810,7 +12810,7 @@
       <c r="A438" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B438" s="10"/>
+      <c r="B438" s="8"/>
       <c r="C438" s="2">
         <v>2</v>
       </c>
@@ -12822,7 +12822,7 @@
       <c r="A439" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B439" s="10"/>
+      <c r="B439" s="8"/>
       <c r="C439" s="2">
         <v>3</v>
       </c>
@@ -12834,7 +12834,7 @@
       <c r="A440" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B440" s="10"/>
+      <c r="B440" s="8"/>
       <c r="C440" s="2">
         <v>4</v>
       </c>
@@ -12846,7 +12846,7 @@
       <c r="A441" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B441" s="10"/>
+      <c r="B441" s="8"/>
       <c r="C441" s="2">
         <v>5</v>
       </c>
@@ -12858,7 +12858,7 @@
       <c r="A442" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B442" s="10"/>
+      <c r="B442" s="8"/>
       <c r="C442" s="2">
         <v>99</v>
       </c>
@@ -12870,7 +12870,7 @@
       <c r="A443" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B443" s="9" t="s">
+      <c r="B443" s="7" t="s">
         <v>382</v>
       </c>
       <c r="C443" s="3">
@@ -12884,7 +12884,7 @@
       <c r="A444" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B444" s="10"/>
+      <c r="B444" s="8"/>
       <c r="C444" s="2">
         <v>2</v>
       </c>
@@ -12896,7 +12896,7 @@
       <c r="A445" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B445" s="10"/>
+      <c r="B445" s="8"/>
       <c r="C445" s="2">
         <v>3</v>
       </c>
@@ -12908,7 +12908,7 @@
       <c r="A446" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B446" s="10"/>
+      <c r="B446" s="8"/>
       <c r="C446" s="2">
         <v>4</v>
       </c>
@@ -12920,7 +12920,7 @@
       <c r="A447" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B447" s="10"/>
+      <c r="B447" s="8"/>
       <c r="C447" s="2">
         <v>5</v>
       </c>
@@ -12932,7 +12932,7 @@
       <c r="A448" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B448" s="10"/>
+      <c r="B448" s="8"/>
       <c r="C448" s="2">
         <v>6</v>
       </c>
@@ -12944,7 +12944,7 @@
       <c r="A449" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B449" s="10"/>
+      <c r="B449" s="8"/>
       <c r="C449" s="2">
         <v>7</v>
       </c>
@@ -12956,7 +12956,7 @@
       <c r="A450" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B450" s="10"/>
+      <c r="B450" s="8"/>
       <c r="C450" s="2">
         <v>99</v>
       </c>
@@ -12968,7 +12968,7 @@
       <c r="A451" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B451" s="9" t="s">
+      <c r="B451" s="7" t="s">
         <v>388</v>
       </c>
       <c r="C451" s="3">
@@ -12982,7 +12982,7 @@
       <c r="A452" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B452" s="10"/>
+      <c r="B452" s="8"/>
       <c r="C452" s="2">
         <v>2</v>
       </c>
@@ -12994,7 +12994,7 @@
       <c r="A453" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B453" s="10"/>
+      <c r="B453" s="8"/>
       <c r="C453" s="2">
         <v>3</v>
       </c>
@@ -13006,7 +13006,7 @@
       <c r="A454" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B454" s="10"/>
+      <c r="B454" s="8"/>
       <c r="C454" s="2">
         <v>4</v>
       </c>
@@ -13018,7 +13018,7 @@
       <c r="A455" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B455" s="10"/>
+      <c r="B455" s="8"/>
       <c r="C455" s="2">
         <v>5</v>
       </c>
@@ -13030,7 +13030,7 @@
       <c r="A456" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B456" s="10"/>
+      <c r="B456" s="8"/>
       <c r="C456" s="2">
         <v>99</v>
       </c>
@@ -13042,7 +13042,7 @@
       <c r="A457" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B457" s="9" t="s">
+      <c r="B457" s="7" t="s">
         <v>393</v>
       </c>
       <c r="C457" s="3">
@@ -13056,7 +13056,7 @@
       <c r="A458" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B458" s="10"/>
+      <c r="B458" s="8"/>
       <c r="C458" s="2">
         <v>2</v>
       </c>
@@ -13068,7 +13068,7 @@
       <c r="A459" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B459" s="10"/>
+      <c r="B459" s="8"/>
       <c r="C459" s="2">
         <v>3</v>
       </c>
@@ -13080,7 +13080,7 @@
       <c r="A460" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B460" s="10"/>
+      <c r="B460" s="8"/>
       <c r="C460" s="2">
         <v>4</v>
       </c>
@@ -13092,7 +13092,7 @@
       <c r="A461" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B461" s="10"/>
+      <c r="B461" s="8"/>
       <c r="C461" s="2">
         <v>5</v>
       </c>
@@ -13104,7 +13104,7 @@
       <c r="A462" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B462" s="10"/>
+      <c r="B462" s="8"/>
       <c r="C462" s="2">
         <v>99</v>
       </c>
@@ -13116,7 +13116,7 @@
       <c r="A463" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B463" s="9" t="s">
+      <c r="B463" s="7" t="s">
         <v>397</v>
       </c>
       <c r="C463" s="3">
@@ -13130,7 +13130,7 @@
       <c r="A464" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B464" s="10"/>
+      <c r="B464" s="8"/>
       <c r="C464" s="2">
         <v>2</v>
       </c>
@@ -13142,7 +13142,7 @@
       <c r="A465" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B465" s="10"/>
+      <c r="B465" s="8"/>
       <c r="C465" s="2">
         <v>3</v>
       </c>
@@ -13154,7 +13154,7 @@
       <c r="A466" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B466" s="10"/>
+      <c r="B466" s="8"/>
       <c r="C466" s="2">
         <v>4</v>
       </c>
@@ -13166,7 +13166,7 @@
       <c r="A467" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B467" s="10"/>
+      <c r="B467" s="8"/>
       <c r="C467" s="2">
         <v>5</v>
       </c>
@@ -13178,7 +13178,7 @@
       <c r="A468" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B468" s="10"/>
+      <c r="B468" s="8"/>
       <c r="C468" s="2">
         <v>99</v>
       </c>
@@ -13190,7 +13190,7 @@
       <c r="A469" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B469" s="9" t="s">
+      <c r="B469" s="7" t="s">
         <v>399</v>
       </c>
       <c r="C469" s="3">
@@ -13204,7 +13204,7 @@
       <c r="A470" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B470" s="10"/>
+      <c r="B470" s="8"/>
       <c r="C470" s="2">
         <v>2</v>
       </c>
@@ -13216,7 +13216,7 @@
       <c r="A471" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B471" s="10"/>
+      <c r="B471" s="8"/>
       <c r="C471" s="2">
         <v>3</v>
       </c>
@@ -13228,7 +13228,7 @@
       <c r="A472" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B472" s="10"/>
+      <c r="B472" s="8"/>
       <c r="C472" s="2">
         <v>4</v>
       </c>
@@ -13240,7 +13240,7 @@
       <c r="A473" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B473" s="10"/>
+      <c r="B473" s="8"/>
       <c r="C473" s="2">
         <v>5</v>
       </c>
@@ -13252,7 +13252,7 @@
       <c r="A474" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B474" s="10"/>
+      <c r="B474" s="8"/>
       <c r="C474" s="2">
         <v>99</v>
       </c>
@@ -13264,7 +13264,7 @@
       <c r="A475" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B475" s="9" t="s">
+      <c r="B475" s="7" t="s">
         <v>401</v>
       </c>
       <c r="C475" s="3">
@@ -13278,7 +13278,7 @@
       <c r="A476" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B476" s="10"/>
+      <c r="B476" s="8"/>
       <c r="C476" s="2">
         <v>2</v>
       </c>
@@ -13290,7 +13290,7 @@
       <c r="A477" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B477" s="10"/>
+      <c r="B477" s="8"/>
       <c r="C477" s="2">
         <v>3</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="A478" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B478" s="10"/>
+      <c r="B478" s="8"/>
       <c r="C478" s="2">
         <v>4</v>
       </c>
@@ -13314,7 +13314,7 @@
       <c r="A479" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B479" s="10"/>
+      <c r="B479" s="8"/>
       <c r="C479" s="2">
         <v>5</v>
       </c>
@@ -13326,7 +13326,7 @@
       <c r="A480" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B480" s="10"/>
+      <c r="B480" s="8"/>
       <c r="C480" s="2">
         <v>99</v>
       </c>
@@ -13338,7 +13338,7 @@
       <c r="A481" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B481" s="9" t="s">
+      <c r="B481" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C481" s="3">
@@ -13352,7 +13352,7 @@
       <c r="A482" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B482" s="10"/>
+      <c r="B482" s="8"/>
       <c r="C482" s="2">
         <v>2</v>
       </c>
@@ -13364,7 +13364,7 @@
       <c r="A483" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B483" s="10"/>
+      <c r="B483" s="8"/>
       <c r="C483" s="2">
         <v>3</v>
       </c>
@@ -13376,7 +13376,7 @@
       <c r="A484" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B484" s="10"/>
+      <c r="B484" s="8"/>
       <c r="C484" s="2">
         <v>4</v>
       </c>
@@ -13388,7 +13388,7 @@
       <c r="A485" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B485" s="10"/>
+      <c r="B485" s="8"/>
       <c r="C485" s="2">
         <v>5</v>
       </c>
@@ -13400,7 +13400,7 @@
       <c r="A486" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B486" s="10"/>
+      <c r="B486" s="8"/>
       <c r="C486" s="2">
         <v>99</v>
       </c>
@@ -13412,7 +13412,7 @@
       <c r="A487" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B487" s="9" t="s">
+      <c r="B487" s="7" t="s">
         <v>405</v>
       </c>
       <c r="C487" s="3">
@@ -13426,7 +13426,7 @@
       <c r="A488" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B488" s="10"/>
+      <c r="B488" s="8"/>
       <c r="C488" s="2">
         <v>2</v>
       </c>
@@ -13438,7 +13438,7 @@
       <c r="A489" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B489" s="10"/>
+      <c r="B489" s="8"/>
       <c r="C489" s="2">
         <v>3</v>
       </c>
@@ -13450,7 +13450,7 @@
       <c r="A490" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B490" s="10"/>
+      <c r="B490" s="8"/>
       <c r="C490" s="2">
         <v>4</v>
       </c>
@@ -13462,7 +13462,7 @@
       <c r="A491" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B491" s="10"/>
+      <c r="B491" s="8"/>
       <c r="C491" s="2">
         <v>5</v>
       </c>
@@ -13474,7 +13474,7 @@
       <c r="A492" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B492" s="10"/>
+      <c r="B492" s="8"/>
       <c r="C492" s="2">
         <v>99</v>
       </c>
@@ -13486,7 +13486,7 @@
       <c r="A493" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B493" s="9" t="s">
+      <c r="B493" s="7" t="s">
         <v>407</v>
       </c>
       <c r="C493" s="3">
@@ -13500,7 +13500,7 @@
       <c r="A494" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B494" s="10"/>
+      <c r="B494" s="8"/>
       <c r="C494" s="2">
         <v>2</v>
       </c>
@@ -13512,7 +13512,7 @@
       <c r="A495" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B495" s="10"/>
+      <c r="B495" s="8"/>
       <c r="C495" s="2">
         <v>3</v>
       </c>
@@ -13524,7 +13524,7 @@
       <c r="A496" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B496" s="10"/>
+      <c r="B496" s="8"/>
       <c r="C496" s="2">
         <v>4</v>
       </c>
@@ -13536,7 +13536,7 @@
       <c r="A497" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B497" s="10"/>
+      <c r="B497" s="8"/>
       <c r="C497" s="2">
         <v>5</v>
       </c>
@@ -13548,7 +13548,7 @@
       <c r="A498" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B498" s="10"/>
+      <c r="B498" s="8"/>
       <c r="C498" s="2">
         <v>99</v>
       </c>
@@ -13560,7 +13560,7 @@
       <c r="A499" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B499" s="9" t="s">
+      <c r="B499" s="7" t="s">
         <v>409</v>
       </c>
       <c r="C499" s="3">
@@ -13574,7 +13574,7 @@
       <c r="A500" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B500" s="10"/>
+      <c r="B500" s="8"/>
       <c r="C500" s="2">
         <v>2</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="A501" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B501" s="10"/>
+      <c r="B501" s="8"/>
       <c r="C501" s="2">
         <v>3</v>
       </c>
@@ -13598,7 +13598,7 @@
       <c r="A502" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B502" s="10"/>
+      <c r="B502" s="8"/>
       <c r="C502" s="2">
         <v>4</v>
       </c>
@@ -13610,7 +13610,7 @@
       <c r="A503" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B503" s="10"/>
+      <c r="B503" s="8"/>
       <c r="C503" s="2">
         <v>5</v>
       </c>
@@ -13622,7 +13622,7 @@
       <c r="A504" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B504" s="10"/>
+      <c r="B504" s="8"/>
       <c r="C504" s="2">
         <v>99</v>
       </c>
@@ -13634,7 +13634,7 @@
       <c r="A505" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B505" s="9" t="s">
+      <c r="B505" s="7" t="s">
         <v>411</v>
       </c>
       <c r="C505" s="3">
@@ -13648,7 +13648,7 @@
       <c r="A506" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B506" s="10"/>
+      <c r="B506" s="8"/>
       <c r="C506" s="2">
         <v>2</v>
       </c>
@@ -13660,7 +13660,7 @@
       <c r="A507" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B507" s="10"/>
+      <c r="B507" s="8"/>
       <c r="C507" s="2">
         <v>3</v>
       </c>
@@ -13672,7 +13672,7 @@
       <c r="A508" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B508" s="10"/>
+      <c r="B508" s="8"/>
       <c r="C508" s="2">
         <v>4</v>
       </c>
@@ -13684,7 +13684,7 @@
       <c r="A509" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B509" s="10"/>
+      <c r="B509" s="8"/>
       <c r="C509" s="2">
         <v>5</v>
       </c>
@@ -13696,7 +13696,7 @@
       <c r="A510" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B510" s="10"/>
+      <c r="B510" s="8"/>
       <c r="C510" s="2">
         <v>99</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="A511" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B511" s="9" t="s">
+      <c r="B511" s="7" t="s">
         <v>413</v>
       </c>
       <c r="C511" s="3">
@@ -13722,7 +13722,7 @@
       <c r="A512" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B512" s="10"/>
+      <c r="B512" s="8"/>
       <c r="C512" s="2">
         <v>2</v>
       </c>
@@ -13734,7 +13734,7 @@
       <c r="A513" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B513" s="10"/>
+      <c r="B513" s="8"/>
       <c r="C513" s="2">
         <v>3</v>
       </c>
@@ -13746,7 +13746,7 @@
       <c r="A514" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B514" s="10"/>
+      <c r="B514" s="8"/>
       <c r="C514" s="2">
         <v>4</v>
       </c>
@@ -13758,7 +13758,7 @@
       <c r="A515" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B515" s="10"/>
+      <c r="B515" s="8"/>
       <c r="C515" s="2">
         <v>5</v>
       </c>
@@ -13770,7 +13770,7 @@
       <c r="A516" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B516" s="10"/>
+      <c r="B516" s="8"/>
       <c r="C516" s="2">
         <v>99</v>
       </c>
@@ -13782,7 +13782,7 @@
       <c r="A517" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B517" s="9" t="s">
+      <c r="B517" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C517" s="3">
@@ -13796,7 +13796,7 @@
       <c r="A518" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B518" s="10"/>
+      <c r="B518" s="8"/>
       <c r="C518" s="2">
         <v>2</v>
       </c>
@@ -13808,7 +13808,7 @@
       <c r="A519" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B519" s="10"/>
+      <c r="B519" s="8"/>
       <c r="C519" s="2">
         <v>3</v>
       </c>
@@ -13820,7 +13820,7 @@
       <c r="A520" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B520" s="10"/>
+      <c r="B520" s="8"/>
       <c r="C520" s="2">
         <v>4</v>
       </c>
@@ -13832,7 +13832,7 @@
       <c r="A521" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B521" s="10"/>
+      <c r="B521" s="8"/>
       <c r="C521" s="2">
         <v>5</v>
       </c>
@@ -13844,7 +13844,7 @@
       <c r="A522" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B522" s="10"/>
+      <c r="B522" s="8"/>
       <c r="C522" s="2">
         <v>99</v>
       </c>
@@ -13856,7 +13856,7 @@
       <c r="A523" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B523" s="9" t="s">
+      <c r="B523" s="7" t="s">
         <v>417</v>
       </c>
       <c r="C523" s="3">
@@ -13870,7 +13870,7 @@
       <c r="A524" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B524" s="10"/>
+      <c r="B524" s="8"/>
       <c r="C524" s="2">
         <v>2</v>
       </c>
@@ -13882,7 +13882,7 @@
       <c r="A525" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B525" s="10"/>
+      <c r="B525" s="8"/>
       <c r="C525" s="2">
         <v>3</v>
       </c>
@@ -13894,7 +13894,7 @@
       <c r="A526" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B526" s="10"/>
+      <c r="B526" s="8"/>
       <c r="C526" s="2">
         <v>4</v>
       </c>
@@ -13906,7 +13906,7 @@
       <c r="A527" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B527" s="10"/>
+      <c r="B527" s="8"/>
       <c r="C527" s="2">
         <v>5</v>
       </c>
@@ -13918,7 +13918,7 @@
       <c r="A528" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B528" s="10"/>
+      <c r="B528" s="8"/>
       <c r="C528" s="2">
         <v>99</v>
       </c>
@@ -13930,7 +13930,7 @@
       <c r="A529" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B529" s="9" t="s">
+      <c r="B529" s="7" t="s">
         <v>424</v>
       </c>
       <c r="C529" s="3">
@@ -13944,7 +13944,7 @@
       <c r="A530" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B530" s="10"/>
+      <c r="B530" s="8"/>
       <c r="C530" s="2">
         <v>2</v>
       </c>
@@ -13956,7 +13956,7 @@
       <c r="A531" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B531" s="10"/>
+      <c r="B531" s="8"/>
       <c r="C531" s="2">
         <v>3</v>
       </c>
@@ -13968,7 +13968,7 @@
       <c r="A532" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B532" s="10"/>
+      <c r="B532" s="8"/>
       <c r="C532" s="2">
         <v>4</v>
       </c>
@@ -13980,7 +13980,7 @@
       <c r="A533" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B533" s="10"/>
+      <c r="B533" s="8"/>
       <c r="C533" s="2">
         <v>5</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="A534" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B534" s="10"/>
+      <c r="B534" s="8"/>
       <c r="C534" s="2">
         <v>99</v>
       </c>
@@ -14004,7 +14004,7 @@
       <c r="A535" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B535" s="9" t="s">
+      <c r="B535" s="7" t="s">
         <v>426</v>
       </c>
       <c r="C535" s="3">
@@ -14018,7 +14018,7 @@
       <c r="A536" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B536" s="10"/>
+      <c r="B536" s="8"/>
       <c r="C536" s="2">
         <v>2</v>
       </c>
@@ -14030,7 +14030,7 @@
       <c r="A537" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B537" s="10"/>
+      <c r="B537" s="8"/>
       <c r="C537" s="2">
         <v>3</v>
       </c>
@@ -14042,7 +14042,7 @@
       <c r="A538" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B538" s="10"/>
+      <c r="B538" s="8"/>
       <c r="C538" s="2">
         <v>4</v>
       </c>
@@ -14054,7 +14054,7 @@
       <c r="A539" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B539" s="10"/>
+      <c r="B539" s="8"/>
       <c r="C539" s="2">
         <v>5</v>
       </c>
@@ -14066,7 +14066,7 @@
       <c r="A540" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B540" s="10"/>
+      <c r="B540" s="8"/>
       <c r="C540" s="2">
         <v>99</v>
       </c>
@@ -14078,7 +14078,7 @@
       <c r="A541" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B541" s="9" t="s">
+      <c r="B541" s="7" t="s">
         <v>428</v>
       </c>
       <c r="C541" s="3">
@@ -14092,7 +14092,7 @@
       <c r="A542" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B542" s="10"/>
+      <c r="B542" s="8"/>
       <c r="C542" s="2">
         <v>2</v>
       </c>
@@ -14104,7 +14104,7 @@
       <c r="A543" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B543" s="10"/>
+      <c r="B543" s="8"/>
       <c r="C543" s="2">
         <v>3</v>
       </c>
@@ -14116,7 +14116,7 @@
       <c r="A544" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B544" s="10"/>
+      <c r="B544" s="8"/>
       <c r="C544" s="2">
         <v>4</v>
       </c>
@@ -14128,7 +14128,7 @@
       <c r="A545" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B545" s="10"/>
+      <c r="B545" s="8"/>
       <c r="C545" s="2">
         <v>5</v>
       </c>
@@ -14140,7 +14140,7 @@
       <c r="A546" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B546" s="10"/>
+      <c r="B546" s="8"/>
       <c r="C546" s="2">
         <v>99</v>
       </c>
@@ -14152,7 +14152,7 @@
       <c r="A547" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B547" s="9" t="s">
+      <c r="B547" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C547" s="3">
@@ -14166,7 +14166,7 @@
       <c r="A548" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B548" s="10"/>
+      <c r="B548" s="8"/>
       <c r="C548" s="2">
         <v>2</v>
       </c>
@@ -14178,7 +14178,7 @@
       <c r="A549" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B549" s="10"/>
+      <c r="B549" s="8"/>
       <c r="C549" s="2">
         <v>3</v>
       </c>
@@ -14190,7 +14190,7 @@
       <c r="A550" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B550" s="10"/>
+      <c r="B550" s="8"/>
       <c r="C550" s="2">
         <v>4</v>
       </c>
@@ -14202,7 +14202,7 @@
       <c r="A551" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B551" s="10"/>
+      <c r="B551" s="8"/>
       <c r="C551" s="2">
         <v>5</v>
       </c>
@@ -14214,7 +14214,7 @@
       <c r="A552" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B552" s="10"/>
+      <c r="B552" s="8"/>
       <c r="C552" s="2">
         <v>99</v>
       </c>
@@ -14226,7 +14226,7 @@
       <c r="A553" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B553" s="9" t="s">
+      <c r="B553" s="7" t="s">
         <v>432</v>
       </c>
       <c r="C553" s="3">
@@ -14240,7 +14240,7 @@
       <c r="A554" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B554" s="10"/>
+      <c r="B554" s="8"/>
       <c r="C554" s="2">
         <v>2</v>
       </c>
@@ -14252,7 +14252,7 @@
       <c r="A555" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B555" s="10"/>
+      <c r="B555" s="8"/>
       <c r="C555" s="2">
         <v>3</v>
       </c>
@@ -14264,7 +14264,7 @@
       <c r="A556" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B556" s="10"/>
+      <c r="B556" s="8"/>
       <c r="C556" s="2">
         <v>4</v>
       </c>
@@ -14276,7 +14276,7 @@
       <c r="A557" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B557" s="10"/>
+      <c r="B557" s="8"/>
       <c r="C557" s="2">
         <v>5</v>
       </c>
@@ -14288,7 +14288,7 @@
       <c r="A558" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B558" s="10"/>
+      <c r="B558" s="8"/>
       <c r="C558" s="2">
         <v>99</v>
       </c>
@@ -14562,7 +14562,7 @@
       <c r="A580" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B580" s="9" t="s">
+      <c r="B580" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C580" s="3">
@@ -14576,7 +14576,7 @@
       <c r="A581" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B581" s="10"/>
+      <c r="B581" s="8"/>
       <c r="C581" s="2">
         <v>2</v>
       </c>
@@ -14588,7 +14588,7 @@
       <c r="A582" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B582" s="10"/>
+      <c r="B582" s="8"/>
       <c r="C582" s="2">
         <v>99</v>
       </c>
@@ -14600,7 +14600,7 @@
       <c r="A583" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B583" s="9" t="s">
+      <c r="B583" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C583" s="3">
@@ -14614,7 +14614,7 @@
       <c r="A584" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B584" s="10"/>
+      <c r="B584" s="8"/>
       <c r="C584" s="2">
         <v>2</v>
       </c>
@@ -14626,7 +14626,7 @@
       <c r="A585" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B585" s="10"/>
+      <c r="B585" s="8"/>
       <c r="C585" s="2">
         <v>99</v>
       </c>
@@ -14638,7 +14638,7 @@
       <c r="A586" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B586" s="9" t="s">
+      <c r="B586" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C586" s="3">
@@ -14652,7 +14652,7 @@
       <c r="A587" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B587" s="10"/>
+      <c r="B587" s="8"/>
       <c r="C587" s="2">
         <v>2</v>
       </c>
@@ -14664,7 +14664,7 @@
       <c r="A588" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B588" s="10"/>
+      <c r="B588" s="8"/>
       <c r="C588" s="2">
         <v>99</v>
       </c>
@@ -14676,7 +14676,7 @@
       <c r="A589" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B589" s="9" t="s">
+      <c r="B589" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C589" s="3">
@@ -14690,7 +14690,7 @@
       <c r="A590" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B590" s="10"/>
+      <c r="B590" s="8"/>
       <c r="C590" s="2">
         <v>2</v>
       </c>
@@ -14702,7 +14702,7 @@
       <c r="A591" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B591" s="10"/>
+      <c r="B591" s="8"/>
       <c r="C591" s="2">
         <v>99</v>
       </c>
@@ -14714,7 +14714,7 @@
       <c r="A592" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B592" s="9" t="s">
+      <c r="B592" s="7" t="s">
         <v>466</v>
       </c>
       <c r="C592" s="3">
@@ -14728,7 +14728,7 @@
       <c r="A593" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B593" s="10"/>
+      <c r="B593" s="8"/>
       <c r="C593" s="2">
         <v>10000</v>
       </c>
@@ -14740,7 +14740,7 @@
       <c r="A594" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B594" s="10"/>
+      <c r="B594" s="8"/>
       <c r="C594" s="2">
         <v>20000</v>
       </c>
@@ -14752,7 +14752,7 @@
       <c r="A595" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B595" s="10"/>
+      <c r="B595" s="8"/>
       <c r="C595" s="2">
         <v>30000</v>
       </c>
@@ -14764,7 +14764,7 @@
       <c r="A596" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B596" s="10"/>
+      <c r="B596" s="8"/>
       <c r="C596" s="2">
         <v>40001</v>
       </c>
@@ -14776,7 +14776,7 @@
       <c r="A597" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B597" s="10"/>
+      <c r="B597" s="8"/>
       <c r="C597" s="2">
         <v>40002</v>
       </c>
@@ -14788,7 +14788,7 @@
       <c r="A598" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B598" s="10"/>
+      <c r="B598" s="8"/>
       <c r="C598" s="2">
         <v>50000</v>
       </c>
@@ -14800,7 +14800,7 @@
       <c r="A599" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B599" s="10"/>
+      <c r="B599" s="8"/>
       <c r="C599" s="2">
         <v>60000</v>
       </c>
@@ -14812,7 +14812,7 @@
       <c r="A600" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B600" s="10"/>
+      <c r="B600" s="8"/>
       <c r="C600" s="2">
         <v>70000</v>
       </c>
@@ -14824,7 +14824,7 @@
       <c r="A601" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B601" s="10"/>
+      <c r="B601" s="8"/>
       <c r="C601" s="2">
         <v>80000</v>
       </c>
@@ -14836,7 +14836,7 @@
       <c r="A602" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B602" s="10"/>
+      <c r="B602" s="8"/>
       <c r="C602" s="2">
         <v>90001</v>
       </c>
@@ -14848,7 +14848,7 @@
       <c r="A603" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B603" s="10"/>
+      <c r="B603" s="8"/>
       <c r="C603" s="2">
         <v>90002</v>
       </c>
@@ -14860,7 +14860,7 @@
       <c r="A604" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B604" s="10"/>
+      <c r="B604" s="8"/>
       <c r="C604" s="2">
         <v>100000</v>
       </c>
@@ -14872,7 +14872,7 @@
       <c r="A605" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B605" s="10"/>
+      <c r="B605" s="8"/>
       <c r="C605" s="2">
         <v>900000</v>
       </c>
@@ -15320,7 +15320,7 @@
       <c r="A642" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B642" s="9" t="s">
+      <c r="B642" s="7" t="s">
         <v>474</v>
       </c>
       <c r="C642" s="3">
@@ -15334,7 +15334,7 @@
       <c r="A643" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B643" s="10"/>
+      <c r="B643" s="8"/>
       <c r="C643" s="2">
         <v>2</v>
       </c>
@@ -15346,7 +15346,7 @@
       <c r="A644" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B644" s="10"/>
+      <c r="B644" s="8"/>
       <c r="C644" s="2">
         <v>3</v>
       </c>
@@ -15358,7 +15358,7 @@
       <c r="A645" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B645" s="10"/>
+      <c r="B645" s="8"/>
       <c r="C645" s="2">
         <v>4</v>
       </c>
@@ -15370,7 +15370,7 @@
       <c r="A646" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B646" s="10"/>
+      <c r="B646" s="8"/>
       <c r="C646" s="2">
         <v>99</v>
       </c>
@@ -15382,7 +15382,7 @@
       <c r="A647" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B647" s="9" t="s">
+      <c r="B647" s="7" t="s">
         <v>476</v>
       </c>
       <c r="C647" s="3">
@@ -15396,7 +15396,7 @@
       <c r="A648" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B648" s="10"/>
+      <c r="B648" s="8"/>
       <c r="C648" s="2">
         <v>2</v>
       </c>
@@ -15408,7 +15408,7 @@
       <c r="A649" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B649" s="10"/>
+      <c r="B649" s="8"/>
       <c r="C649" s="2">
         <v>3</v>
       </c>
@@ -15420,7 +15420,7 @@
       <c r="A650" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B650" s="10"/>
+      <c r="B650" s="8"/>
       <c r="C650" s="2">
         <v>4</v>
       </c>
@@ -15432,7 +15432,7 @@
       <c r="A651" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B651" s="10"/>
+      <c r="B651" s="8"/>
       <c r="C651" s="2">
         <v>99</v>
       </c>
@@ -15444,7 +15444,7 @@
       <c r="A652" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B652" s="9" t="s">
+      <c r="B652" s="7" t="s">
         <v>478</v>
       </c>
       <c r="C652" s="3">
@@ -15458,7 +15458,7 @@
       <c r="A653" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B653" s="10"/>
+      <c r="B653" s="8"/>
       <c r="C653" s="2">
         <v>2</v>
       </c>
@@ -15470,7 +15470,7 @@
       <c r="A654" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B654" s="10"/>
+      <c r="B654" s="8"/>
       <c r="C654" s="2">
         <v>3</v>
       </c>
@@ -15482,7 +15482,7 @@
       <c r="A655" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B655" s="10"/>
+      <c r="B655" s="8"/>
       <c r="C655" s="2">
         <v>4</v>
       </c>
@@ -15494,7 +15494,7 @@
       <c r="A656" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B656" s="10"/>
+      <c r="B656" s="8"/>
       <c r="C656" s="2">
         <v>5</v>
       </c>
@@ -15506,7 +15506,7 @@
       <c r="A657" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B657" s="10"/>
+      <c r="B657" s="8"/>
       <c r="C657" s="2">
         <v>6</v>
       </c>
@@ -15518,7 +15518,7 @@
       <c r="A658" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B658" s="10"/>
+      <c r="B658" s="8"/>
       <c r="C658" s="2">
         <v>99</v>
       </c>
@@ -15740,7 +15740,7 @@
       <c r="A676" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B676" s="9" t="s">
+      <c r="B676" s="7" t="s">
         <v>497</v>
       </c>
       <c r="C676" s="3">
@@ -15754,7 +15754,7 @@
       <c r="A677" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B677" s="10"/>
+      <c r="B677" s="8"/>
       <c r="C677" s="2">
         <v>2</v>
       </c>
@@ -15766,7 +15766,7 @@
       <c r="A678" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B678" s="10"/>
+      <c r="B678" s="8"/>
       <c r="C678" s="2">
         <v>3</v>
       </c>
@@ -15778,7 +15778,7 @@
       <c r="A679" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B679" s="10"/>
+      <c r="B679" s="8"/>
       <c r="C679" s="2">
         <v>4</v>
       </c>
@@ -15790,7 +15790,7 @@
       <c r="A680" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B680" s="10"/>
+      <c r="B680" s="8"/>
       <c r="C680" s="2">
         <v>99</v>
       </c>
@@ -15802,7 +15802,7 @@
       <c r="A681" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B681" s="9" t="s">
+      <c r="B681" s="7" t="s">
         <v>503</v>
       </c>
       <c r="C681" s="3">
@@ -15816,7 +15816,7 @@
       <c r="A682" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B682" s="10"/>
+      <c r="B682" s="8"/>
       <c r="C682" s="2">
         <v>2</v>
       </c>
@@ -15828,7 +15828,7 @@
       <c r="A683" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B683" s="10"/>
+      <c r="B683" s="8"/>
       <c r="C683" s="2">
         <v>3</v>
       </c>
@@ -15840,7 +15840,7 @@
       <c r="A684" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B684" s="10"/>
+      <c r="B684" s="8"/>
       <c r="C684" s="2">
         <v>4</v>
       </c>
@@ -15852,7 +15852,7 @@
       <c r="A685" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B685" s="10"/>
+      <c r="B685" s="8"/>
       <c r="C685" s="2">
         <v>99</v>
       </c>
@@ -15864,7 +15864,7 @@
       <c r="A686" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B686" s="9" t="s">
+      <c r="B686" s="7" t="s">
         <v>509</v>
       </c>
       <c r="C686" s="3">
@@ -15878,7 +15878,7 @@
       <c r="A687" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B687" s="10"/>
+      <c r="B687" s="8"/>
       <c r="C687" s="2">
         <v>2</v>
       </c>
@@ -15890,7 +15890,7 @@
       <c r="A688" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B688" s="10"/>
+      <c r="B688" s="8"/>
       <c r="C688" s="2">
         <v>3</v>
       </c>
@@ -15902,7 +15902,7 @@
       <c r="A689" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B689" s="10"/>
+      <c r="B689" s="8"/>
       <c r="C689" s="2">
         <v>4</v>
       </c>
@@ -15914,7 +15914,7 @@
       <c r="A690" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B690" s="10"/>
+      <c r="B690" s="8"/>
       <c r="C690" s="2">
         <v>5</v>
       </c>
@@ -15926,7 +15926,7 @@
       <c r="A691" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B691" s="10"/>
+      <c r="B691" s="8"/>
       <c r="C691" s="2">
         <v>99</v>
       </c>
@@ -15938,7 +15938,7 @@
       <c r="A692" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B692" s="9" t="s">
+      <c r="B692" s="7" t="s">
         <v>515</v>
       </c>
       <c r="C692" s="3">
@@ -15952,7 +15952,7 @@
       <c r="A693" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B693" s="10"/>
+      <c r="B693" s="8"/>
       <c r="C693" s="2">
         <v>2</v>
       </c>
@@ -15964,7 +15964,7 @@
       <c r="A694" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B694" s="10"/>
+      <c r="B694" s="8"/>
       <c r="C694" s="2">
         <v>3</v>
       </c>
@@ -15976,7 +15976,7 @@
       <c r="A695" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B695" s="10"/>
+      <c r="B695" s="8"/>
       <c r="C695" s="2">
         <v>4</v>
       </c>
@@ -15988,7 +15988,7 @@
       <c r="A696" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B696" s="10"/>
+      <c r="B696" s="8"/>
       <c r="C696" s="2">
         <v>5</v>
       </c>
@@ -16000,7 +16000,7 @@
       <c r="A697" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B697" s="10"/>
+      <c r="B697" s="8"/>
       <c r="C697" s="2">
         <v>6</v>
       </c>
@@ -16012,7 +16012,7 @@
       <c r="A698" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B698" s="10"/>
+      <c r="B698" s="8"/>
       <c r="C698" s="2">
         <v>99</v>
       </c>
@@ -17242,7 +17242,7 @@
       <c r="A798" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B798" s="9" t="s">
+      <c r="B798" s="7" t="s">
         <v>572</v>
       </c>
       <c r="C798" s="3">
@@ -17256,7 +17256,7 @@
       <c r="A799" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B799" s="10"/>
+      <c r="B799" s="8"/>
       <c r="C799" s="2">
         <v>2</v>
       </c>
@@ -17268,7 +17268,7 @@
       <c r="A800" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B800" s="10"/>
+      <c r="B800" s="8"/>
       <c r="C800" s="2">
         <v>99</v>
       </c>
@@ -17280,7 +17280,7 @@
       <c r="A801" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B801" s="9" t="s">
+      <c r="B801" s="7" t="s">
         <v>576</v>
       </c>
       <c r="C801" s="3">
@@ -17294,7 +17294,7 @@
       <c r="A802" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B802" s="10"/>
+      <c r="B802" s="8"/>
       <c r="C802" s="2">
         <v>2</v>
       </c>
@@ -17306,7 +17306,7 @@
       <c r="A803" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B803" s="10"/>
+      <c r="B803" s="8"/>
       <c r="C803" s="2">
         <v>99</v>
       </c>
@@ -17318,7 +17318,7 @@
       <c r="A804" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B804" s="9" t="s">
+      <c r="B804" s="7" t="s">
         <v>578</v>
       </c>
       <c r="C804" s="3">
@@ -17332,7 +17332,7 @@
       <c r="A805" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B805" s="10"/>
+      <c r="B805" s="8"/>
       <c r="C805" s="2">
         <v>2</v>
       </c>
@@ -17344,7 +17344,7 @@
       <c r="A806" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B806" s="10"/>
+      <c r="B806" s="8"/>
       <c r="C806" s="2">
         <v>99</v>
       </c>
@@ -17356,7 +17356,7 @@
       <c r="A807" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B807" s="9" t="s">
+      <c r="B807" s="7" t="s">
         <v>580</v>
       </c>
       <c r="C807" s="3">
@@ -17370,7 +17370,7 @@
       <c r="A808" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B808" s="10"/>
+      <c r="B808" s="8"/>
       <c r="C808" s="2">
         <v>2</v>
       </c>
@@ -17382,7 +17382,7 @@
       <c r="A809" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B809" s="10"/>
+      <c r="B809" s="8"/>
       <c r="C809" s="2">
         <v>99</v>
       </c>
@@ -17394,7 +17394,7 @@
       <c r="A810" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B810" s="9" t="s">
+      <c r="B810" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C810" s="3">
@@ -17408,7 +17408,7 @@
       <c r="A811" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B811" s="10"/>
+      <c r="B811" s="8"/>
       <c r="C811" s="2">
         <v>2</v>
       </c>
@@ -17420,7 +17420,7 @@
       <c r="A812" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B812" s="10"/>
+      <c r="B812" s="8"/>
       <c r="C812" s="2">
         <v>99</v>
       </c>
@@ -17432,7 +17432,7 @@
       <c r="A813" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B813" s="9" t="s">
+      <c r="B813" s="7" t="s">
         <v>584</v>
       </c>
       <c r="C813" s="3">
@@ -17446,7 +17446,7 @@
       <c r="A814" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B814" s="10"/>
+      <c r="B814" s="8"/>
       <c r="C814" s="2">
         <v>2</v>
       </c>
@@ -17458,7 +17458,7 @@
       <c r="A815" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B815" s="10"/>
+      <c r="B815" s="8"/>
       <c r="C815" s="2">
         <v>99</v>
       </c>
@@ -17470,7 +17470,7 @@
       <c r="A816" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B816" s="9" t="s">
+      <c r="B816" s="7" t="s">
         <v>586</v>
       </c>
       <c r="C816" s="3">
@@ -17484,7 +17484,7 @@
       <c r="A817" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B817" s="10"/>
+      <c r="B817" s="8"/>
       <c r="C817" s="2">
         <v>2</v>
       </c>
@@ -17496,7 +17496,7 @@
       <c r="A818" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B818" s="10"/>
+      <c r="B818" s="8"/>
       <c r="C818" s="2">
         <v>3</v>
       </c>
@@ -17508,7 +17508,7 @@
       <c r="A819" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B819" s="10"/>
+      <c r="B819" s="8"/>
       <c r="C819" s="2">
         <v>4</v>
       </c>
@@ -17520,7 +17520,7 @@
       <c r="A820" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B820" s="10"/>
+      <c r="B820" s="8"/>
       <c r="C820" s="2">
         <v>99</v>
       </c>
@@ -17532,7 +17532,7 @@
       <c r="A821" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B821" s="9" t="s">
+      <c r="B821" s="7" t="s">
         <v>588</v>
       </c>
       <c r="C821" s="3">
@@ -17546,7 +17546,7 @@
       <c r="A822" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B822" s="10"/>
+      <c r="B822" s="8"/>
       <c r="C822" s="2">
         <v>2</v>
       </c>
@@ -17558,7 +17558,7 @@
       <c r="A823" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B823" s="10"/>
+      <c r="B823" s="8"/>
       <c r="C823" s="2">
         <v>3</v>
       </c>
@@ -17570,7 +17570,7 @@
       <c r="A824" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B824" s="10"/>
+      <c r="B824" s="8"/>
       <c r="C824" s="2">
         <v>4</v>
       </c>
@@ -17582,7 +17582,7 @@
       <c r="A825" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B825" s="10"/>
+      <c r="B825" s="8"/>
       <c r="C825" s="2">
         <v>99</v>
       </c>
@@ -17594,7 +17594,7 @@
       <c r="A826" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B826" s="9" t="s">
+      <c r="B826" s="7" t="s">
         <v>590</v>
       </c>
       <c r="C826" s="3">
@@ -17608,7 +17608,7 @@
       <c r="A827" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B827" s="10"/>
+      <c r="B827" s="8"/>
       <c r="C827" s="2">
         <v>2</v>
       </c>
@@ -17620,7 +17620,7 @@
       <c r="A828" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B828" s="10"/>
+      <c r="B828" s="8"/>
       <c r="C828" s="2">
         <v>3</v>
       </c>
@@ -17632,7 +17632,7 @@
       <c r="A829" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B829" s="10"/>
+      <c r="B829" s="8"/>
       <c r="C829" s="2">
         <v>4</v>
       </c>
@@ -17644,7 +17644,7 @@
       <c r="A830" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B830" s="10"/>
+      <c r="B830" s="8"/>
       <c r="C830" s="2">
         <v>99</v>
       </c>
@@ -17656,7 +17656,7 @@
       <c r="A831" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B831" s="9" t="s">
+      <c r="B831" s="7" t="s">
         <v>592</v>
       </c>
       <c r="C831" s="3">
@@ -17670,7 +17670,7 @@
       <c r="A832" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B832" s="10"/>
+      <c r="B832" s="8"/>
       <c r="C832" s="2">
         <v>2</v>
       </c>
@@ -17682,7 +17682,7 @@
       <c r="A833" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B833" s="10"/>
+      <c r="B833" s="8"/>
       <c r="C833" s="2">
         <v>3</v>
       </c>
@@ -17694,7 +17694,7 @@
       <c r="A834" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B834" s="10"/>
+      <c r="B834" s="8"/>
       <c r="C834" s="2">
         <v>4</v>
       </c>
@@ -17706,7 +17706,7 @@
       <c r="A835" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B835" s="10"/>
+      <c r="B835" s="8"/>
       <c r="C835" s="2">
         <v>99</v>
       </c>
@@ -17718,7 +17718,7 @@
       <c r="A836" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B836" s="9" t="s">
+      <c r="B836" s="7" t="s">
         <v>594</v>
       </c>
       <c r="C836" s="3">
@@ -17732,7 +17732,7 @@
       <c r="A837" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B837" s="10"/>
+      <c r="B837" s="8"/>
       <c r="C837" s="2">
         <v>2</v>
       </c>
@@ -17744,7 +17744,7 @@
       <c r="A838" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B838" s="10"/>
+      <c r="B838" s="8"/>
       <c r="C838" s="2">
         <v>3</v>
       </c>
@@ -17756,7 +17756,7 @@
       <c r="A839" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B839" s="10"/>
+      <c r="B839" s="8"/>
       <c r="C839" s="2">
         <v>4</v>
       </c>
@@ -17768,7 +17768,7 @@
       <c r="A840" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B840" s="10"/>
+      <c r="B840" s="8"/>
       <c r="C840" s="2">
         <v>5</v>
       </c>
@@ -17780,7 +17780,7 @@
       <c r="A841" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B841" s="10"/>
+      <c r="B841" s="8"/>
       <c r="C841" s="2">
         <v>6</v>
       </c>
@@ -17792,7 +17792,7 @@
       <c r="A842" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B842" s="10"/>
+      <c r="B842" s="8"/>
       <c r="C842" s="2">
         <v>7</v>
       </c>
@@ -17804,7 +17804,7 @@
       <c r="A843" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B843" s="10"/>
+      <c r="B843" s="8"/>
       <c r="C843" s="2">
         <v>99</v>
       </c>
@@ -17816,7 +17816,7 @@
       <c r="A844" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B844" s="9" t="s">
+      <c r="B844" s="7" t="s">
         <v>598</v>
       </c>
       <c r="C844" s="3">
@@ -17830,7 +17830,7 @@
       <c r="A845" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B845" s="10"/>
+      <c r="B845" s="8"/>
       <c r="C845" s="2">
         <v>2</v>
       </c>
@@ -17842,7 +17842,7 @@
       <c r="A846" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B846" s="10"/>
+      <c r="B846" s="8"/>
       <c r="C846" s="2">
         <v>99</v>
       </c>
@@ -17854,7 +17854,7 @@
       <c r="A847" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B847" s="9" t="s">
+      <c r="B847" s="7" t="s">
         <v>600</v>
       </c>
       <c r="C847" s="3">
@@ -17868,7 +17868,7 @@
       <c r="A848" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B848" s="10"/>
+      <c r="B848" s="8"/>
       <c r="C848" s="2">
         <v>2</v>
       </c>
@@ -17880,7 +17880,7 @@
       <c r="A849" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B849" s="10"/>
+      <c r="B849" s="8"/>
       <c r="C849" s="2">
         <v>3</v>
       </c>
@@ -17892,7 +17892,7 @@
       <c r="A850" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B850" s="10"/>
+      <c r="B850" s="8"/>
       <c r="C850" s="2">
         <v>4</v>
       </c>
@@ -17904,7 +17904,7 @@
       <c r="A851" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B851" s="10"/>
+      <c r="B851" s="8"/>
       <c r="C851" s="2">
         <v>5</v>
       </c>
@@ -17916,7 +17916,7 @@
       <c r="A852" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B852" s="10"/>
+      <c r="B852" s="8"/>
       <c r="C852" s="2">
         <v>9</v>
       </c>
@@ -17928,7 +17928,7 @@
       <c r="A853" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B853" s="9" t="s">
+      <c r="B853" s="7" t="s">
         <v>607</v>
       </c>
       <c r="C853" s="3">
@@ -17942,7 +17942,7 @@
       <c r="A854" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B854" s="10"/>
+      <c r="B854" s="8"/>
       <c r="C854" s="2">
         <v>2</v>
       </c>
@@ -17954,7 +17954,7 @@
       <c r="A855" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B855" s="10"/>
+      <c r="B855" s="8"/>
       <c r="C855" s="2">
         <v>99</v>
       </c>
@@ -17966,7 +17966,7 @@
       <c r="A856" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B856" s="9" t="s">
+      <c r="B856" s="7" t="s">
         <v>609</v>
       </c>
       <c r="C856" s="3">
@@ -17980,7 +17980,7 @@
       <c r="A857" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B857" s="10"/>
+      <c r="B857" s="8"/>
       <c r="C857" s="2">
         <v>2</v>
       </c>
@@ -17992,7 +17992,7 @@
       <c r="A858" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B858" s="10"/>
+      <c r="B858" s="8"/>
       <c r="C858" s="2">
         <v>3</v>
       </c>
@@ -18004,7 +18004,7 @@
       <c r="A859" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B859" s="10"/>
+      <c r="B859" s="8"/>
       <c r="C859" s="2">
         <v>4</v>
       </c>
@@ -18016,7 +18016,7 @@
       <c r="A860" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B860" s="10"/>
+      <c r="B860" s="8"/>
       <c r="C860" s="2">
         <v>99</v>
       </c>
@@ -18028,7 +18028,7 @@
       <c r="A861" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B861" s="9" t="s">
+      <c r="B861" s="7" t="s">
         <v>615</v>
       </c>
       <c r="C861" s="3">
@@ -18042,7 +18042,7 @@
       <c r="A862" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B862" s="10"/>
+      <c r="B862" s="8"/>
       <c r="C862" s="2">
         <v>2</v>
       </c>
@@ -18054,7 +18054,7 @@
       <c r="A863" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B863" s="10"/>
+      <c r="B863" s="8"/>
       <c r="C863" s="2">
         <v>3</v>
       </c>
@@ -18066,7 +18066,7 @@
       <c r="A864" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B864" s="10"/>
+      <c r="B864" s="8"/>
       <c r="C864" s="2">
         <v>99</v>
       </c>
@@ -18078,7 +18078,7 @@
       <c r="A865" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B865" s="9" t="s">
+      <c r="B865" s="7" t="s">
         <v>619</v>
       </c>
       <c r="C865" s="3">
@@ -18092,7 +18092,7 @@
       <c r="A866" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B866" s="10"/>
+      <c r="B866" s="8"/>
       <c r="C866" s="2">
         <v>2</v>
       </c>
@@ -18104,7 +18104,7 @@
       <c r="A867" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B867" s="10"/>
+      <c r="B867" s="8"/>
       <c r="C867" s="2">
         <v>3</v>
       </c>
@@ -18116,7 +18116,7 @@
       <c r="A868" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B868" s="10"/>
+      <c r="B868" s="8"/>
       <c r="C868" s="2">
         <v>4</v>
       </c>
@@ -18128,7 +18128,7 @@
       <c r="A869" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B869" s="10"/>
+      <c r="B869" s="8"/>
       <c r="C869" s="2">
         <v>5</v>
       </c>
@@ -18140,7 +18140,7 @@
       <c r="A870" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B870" s="10"/>
+      <c r="B870" s="8"/>
       <c r="C870" s="2">
         <v>99</v>
       </c>
@@ -18152,7 +18152,7 @@
       <c r="A871" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B871" s="9" t="s">
+      <c r="B871" s="7" t="s">
         <v>626</v>
       </c>
       <c r="C871" s="3">
@@ -18166,7 +18166,7 @@
       <c r="A872" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B872" s="10"/>
+      <c r="B872" s="8"/>
       <c r="C872" s="2">
         <v>2</v>
       </c>
@@ -18178,7 +18178,7 @@
       <c r="A873" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B873" s="10"/>
+      <c r="B873" s="8"/>
       <c r="C873" s="2">
         <v>3</v>
       </c>
@@ -18190,7 +18190,7 @@
       <c r="A874" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B874" s="10"/>
+      <c r="B874" s="8"/>
       <c r="C874" s="2">
         <v>99</v>
       </c>
@@ -18202,7 +18202,7 @@
       <c r="A875" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B875" s="9" t="s">
+      <c r="B875" s="7" t="s">
         <v>632</v>
       </c>
       <c r="C875" s="3">
@@ -18216,7 +18216,7 @@
       <c r="A876" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B876" s="10"/>
+      <c r="B876" s="8"/>
       <c r="C876" s="2">
         <v>2</v>
       </c>
@@ -18228,7 +18228,7 @@
       <c r="A877" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B877" s="10"/>
+      <c r="B877" s="8"/>
       <c r="C877" s="2">
         <v>3</v>
       </c>
@@ -18240,7 +18240,7 @@
       <c r="A878" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B878" s="10"/>
+      <c r="B878" s="8"/>
       <c r="C878" s="2">
         <v>4</v>
       </c>
@@ -18252,7 +18252,7 @@
       <c r="A879" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B879" s="10"/>
+      <c r="B879" s="8"/>
       <c r="C879" s="2">
         <v>99</v>
       </c>
@@ -18264,7 +18264,7 @@
       <c r="A880" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B880" s="9" t="s">
+      <c r="B880" s="7" t="s">
         <v>638</v>
       </c>
       <c r="C880" s="3">
@@ -18278,7 +18278,7 @@
       <c r="A881" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B881" s="10"/>
+      <c r="B881" s="8"/>
       <c r="C881" s="2">
         <v>2</v>
       </c>
@@ -18290,7 +18290,7 @@
       <c r="A882" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B882" s="10"/>
+      <c r="B882" s="8"/>
       <c r="C882" s="2">
         <v>99</v>
       </c>
@@ -18340,7 +18340,7 @@
       <c r="A886" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B886" s="9" t="s">
+      <c r="B886" s="7" t="s">
         <v>644</v>
       </c>
       <c r="C886" s="3">
@@ -18354,7 +18354,7 @@
       <c r="A887" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B887" s="10"/>
+      <c r="B887" s="8"/>
       <c r="C887" s="2">
         <v>2</v>
       </c>
@@ -18366,7 +18366,7 @@
       <c r="A888" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B888" s="9" t="s">
+      <c r="B888" s="7" t="s">
         <v>647</v>
       </c>
       <c r="C888" s="3">
@@ -18380,7 +18380,7 @@
       <c r="A889" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B889" s="10"/>
+      <c r="B889" s="8"/>
       <c r="C889" s="2">
         <v>2</v>
       </c>
@@ -18392,7 +18392,7 @@
       <c r="A890" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B890" s="10"/>
+      <c r="B890" s="8"/>
       <c r="C890" s="2">
         <v>3</v>
       </c>
@@ -18404,7 +18404,7 @@
       <c r="A891" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B891" s="10"/>
+      <c r="B891" s="8"/>
       <c r="C891" s="2">
         <v>4</v>
       </c>
@@ -18416,7 +18416,7 @@
       <c r="A892" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B892" s="10"/>
+      <c r="B892" s="8"/>
       <c r="C892" s="2">
         <v>99</v>
       </c>
@@ -18466,7 +18466,7 @@
       <c r="A896" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B896" s="9" t="s">
+      <c r="B896" s="7" t="s">
         <v>657</v>
       </c>
       <c r="C896" s="3">
@@ -18480,7 +18480,7 @@
       <c r="A897" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B897" s="10"/>
+      <c r="B897" s="8"/>
       <c r="C897" s="2">
         <v>2</v>
       </c>
@@ -18492,7 +18492,7 @@
       <c r="A898" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B898" s="10"/>
+      <c r="B898" s="8"/>
       <c r="C898" s="2">
         <v>3</v>
       </c>
@@ -18504,7 +18504,7 @@
       <c r="A899" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B899" s="10"/>
+      <c r="B899" s="8"/>
       <c r="C899" s="2">
         <v>4</v>
       </c>
@@ -18516,7 +18516,7 @@
       <c r="A900" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B900" s="10"/>
+      <c r="B900" s="8"/>
       <c r="C900" s="2">
         <v>5</v>
       </c>
@@ -18528,7 +18528,7 @@
       <c r="A901" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B901" s="10"/>
+      <c r="B901" s="8"/>
       <c r="C901" s="2">
         <v>99</v>
       </c>
@@ -18726,7 +18726,7 @@
       <c r="A917" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B917" s="9" t="s">
+      <c r="B917" s="7" t="s">
         <v>676</v>
       </c>
       <c r="C917" s="3">
@@ -18740,7 +18740,7 @@
       <c r="A918" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B918" s="10"/>
+      <c r="B918" s="8"/>
       <c r="C918" s="2">
         <v>2</v>
       </c>
@@ -18752,7 +18752,7 @@
       <c r="A919" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B919" s="10"/>
+      <c r="B919" s="8"/>
       <c r="C919" s="2">
         <v>3</v>
       </c>
@@ -18764,7 +18764,7 @@
       <c r="A920" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B920" s="10"/>
+      <c r="B920" s="8"/>
       <c r="C920" s="2">
         <v>4</v>
       </c>
@@ -18776,7 +18776,7 @@
       <c r="A921" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B921" s="10"/>
+      <c r="B921" s="8"/>
       <c r="C921" s="2">
         <v>5</v>
       </c>
@@ -18788,7 +18788,7 @@
       <c r="A922" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B922" s="10"/>
+      <c r="B922" s="8"/>
       <c r="C922" s="2">
         <v>6</v>
       </c>
@@ -18800,7 +18800,7 @@
       <c r="A923" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B923" s="10"/>
+      <c r="B923" s="8"/>
       <c r="C923" s="2">
         <v>7</v>
       </c>
@@ -18812,7 +18812,7 @@
       <c r="A924" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B924" s="10"/>
+      <c r="B924" s="8"/>
       <c r="C924" s="2">
         <v>8</v>
       </c>
@@ -18824,7 +18824,7 @@
       <c r="A925" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B925" s="10"/>
+      <c r="B925" s="8"/>
       <c r="C925" s="2">
         <v>99</v>
       </c>
@@ -18836,7 +18836,7 @@
       <c r="A926" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B926" s="9" t="s">
+      <c r="B926" s="7" t="s">
         <v>686</v>
       </c>
       <c r="C926" s="3">
@@ -18850,7 +18850,7 @@
       <c r="A927" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B927" s="10"/>
+      <c r="B927" s="8"/>
       <c r="C927" s="2">
         <v>2</v>
       </c>
@@ -18862,7 +18862,7 @@
       <c r="A928" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B928" s="10"/>
+      <c r="B928" s="8"/>
       <c r="C928" s="2">
         <v>3</v>
       </c>
@@ -18874,7 +18874,7 @@
       <c r="A929" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B929" s="10"/>
+      <c r="B929" s="8"/>
       <c r="C929" s="2">
         <v>99</v>
       </c>
@@ -18886,7 +18886,7 @@
       <c r="A930" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B930" s="9" t="s">
+      <c r="B930" s="7" t="s">
         <v>691</v>
       </c>
       <c r="C930" s="3">
@@ -18900,7 +18900,7 @@
       <c r="A931" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B931" s="10"/>
+      <c r="B931" s="8"/>
       <c r="C931" s="2">
         <v>1</v>
       </c>
@@ -18912,7 +18912,7 @@
       <c r="A932" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B932" s="10"/>
+      <c r="B932" s="8"/>
       <c r="C932" s="2">
         <v>2</v>
       </c>
@@ -18924,7 +18924,7 @@
       <c r="A933" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B933" s="10"/>
+      <c r="B933" s="8"/>
       <c r="C933" s="2">
         <v>3</v>
       </c>
@@ -18936,7 +18936,7 @@
       <c r="A934" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B934" s="10"/>
+      <c r="B934" s="8"/>
       <c r="C934" s="2">
         <v>4</v>
       </c>
@@ -18948,7 +18948,7 @@
       <c r="A935" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B935" s="10"/>
+      <c r="B935" s="8"/>
       <c r="C935" s="2">
         <v>99</v>
       </c>
@@ -19046,7 +19046,7 @@
       <c r="A943" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B943" s="7" t="s">
+      <c r="B943" s="9" t="s">
         <v>702</v>
       </c>
       <c r="C943" s="3">
@@ -19060,7 +19060,7 @@
       <c r="A944" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B944" s="8"/>
+      <c r="B944" s="10"/>
       <c r="C944" s="2">
         <v>2</v>
       </c>
@@ -19072,7 +19072,7 @@
       <c r="A945" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B945" s="8"/>
+      <c r="B945" s="10"/>
       <c r="C945" s="2">
         <v>3</v>
       </c>
@@ -19084,7 +19084,7 @@
       <c r="A946" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B946" s="8"/>
+      <c r="B946" s="10"/>
       <c r="C946" s="2">
         <v>4</v>
       </c>
@@ -19096,7 +19096,7 @@
       <c r="A947" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B947" s="8"/>
+      <c r="B947" s="10"/>
       <c r="C947" s="2">
         <v>5</v>
       </c>
@@ -19108,7 +19108,7 @@
       <c r="A948" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B948" s="8"/>
+      <c r="B948" s="10"/>
       <c r="C948" s="2">
         <v>6</v>
       </c>
@@ -19120,7 +19120,7 @@
       <c r="A949" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B949" s="8"/>
+      <c r="B949" s="10"/>
       <c r="C949" s="2">
         <v>7</v>
       </c>
@@ -19132,7 +19132,7 @@
       <c r="A950" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B950" s="8"/>
+      <c r="B950" s="10"/>
       <c r="C950" s="2">
         <v>8</v>
       </c>
@@ -19144,7 +19144,7 @@
       <c r="A951" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B951" s="8"/>
+      <c r="B951" s="10"/>
       <c r="C951" s="2">
         <v>9</v>
       </c>
@@ -19156,7 +19156,7 @@
       <c r="A952" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B952" s="8"/>
+      <c r="B952" s="10"/>
       <c r="C952" s="2">
         <v>10</v>
       </c>
@@ -19168,7 +19168,7 @@
       <c r="A953" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B953" s="8"/>
+      <c r="B953" s="10"/>
       <c r="C953" s="2">
         <v>11</v>
       </c>
@@ -19180,7 +19180,7 @@
       <c r="A954" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B954" s="8"/>
+      <c r="B954" s="10"/>
       <c r="C954" s="2">
         <v>12</v>
       </c>
@@ -19192,7 +19192,7 @@
       <c r="A955" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B955" s="8"/>
+      <c r="B955" s="10"/>
       <c r="C955" s="2">
         <v>99</v>
       </c>
@@ -19634,7 +19634,7 @@
       <c r="A991" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B991" s="7" t="s">
+      <c r="B991" s="9" t="s">
         <v>740</v>
       </c>
       <c r="C991" s="3">
@@ -19648,7 +19648,7 @@
       <c r="A992" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B992" s="8"/>
+      <c r="B992" s="10"/>
       <c r="C992" s="2">
         <v>2</v>
       </c>
@@ -19660,7 +19660,7 @@
       <c r="A993" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B993" s="8"/>
+      <c r="B993" s="10"/>
       <c r="C993" s="2">
         <v>4</v>
       </c>
@@ -19672,7 +19672,7 @@
       <c r="A994" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B994" s="8"/>
+      <c r="B994" s="10"/>
       <c r="C994" s="2">
         <v>5</v>
       </c>
@@ -19684,7 +19684,7 @@
       <c r="A995" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B995" s="8"/>
+      <c r="B995" s="10"/>
       <c r="C995" s="2">
         <v>6</v>
       </c>
@@ -19696,7 +19696,7 @@
       <c r="A996" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B996" s="8"/>
+      <c r="B996" s="10"/>
       <c r="C996" s="2">
         <v>8</v>
       </c>
@@ -19708,7 +19708,7 @@
       <c r="A997" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B997" s="8"/>
+      <c r="B997" s="10"/>
       <c r="C997" s="2">
         <v>9</v>
       </c>
@@ -19720,7 +19720,7 @@
       <c r="A998" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B998" s="8"/>
+      <c r="B998" s="10"/>
       <c r="C998" s="2">
         <v>10</v>
       </c>
@@ -19732,7 +19732,7 @@
       <c r="A999" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B999" s="8"/>
+      <c r="B999" s="10"/>
       <c r="C999" s="2">
         <v>11</v>
       </c>
@@ -19744,7 +19744,7 @@
       <c r="A1000" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1000" s="8"/>
+      <c r="B1000" s="10"/>
       <c r="C1000" s="2">
         <v>12</v>
       </c>
@@ -19756,7 +19756,7 @@
       <c r="A1001" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1001" s="8"/>
+      <c r="B1001" s="10"/>
       <c r="C1001" s="2">
         <v>13</v>
       </c>
@@ -19768,7 +19768,7 @@
       <c r="A1002" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1002" s="8"/>
+      <c r="B1002" s="10"/>
       <c r="C1002" s="2">
         <v>15</v>
       </c>
@@ -19780,7 +19780,7 @@
       <c r="A1003" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1003" s="8"/>
+      <c r="B1003" s="10"/>
       <c r="C1003" s="2">
         <v>16</v>
       </c>
@@ -19792,7 +19792,7 @@
       <c r="A1004" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1004" s="8"/>
+      <c r="B1004" s="10"/>
       <c r="C1004" s="2">
         <v>17</v>
       </c>
@@ -19804,7 +19804,7 @@
       <c r="A1005" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1005" s="8"/>
+      <c r="B1005" s="10"/>
       <c r="C1005" s="2">
         <v>18</v>
       </c>
@@ -19816,7 +19816,7 @@
       <c r="A1006" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1006" s="8"/>
+      <c r="B1006" s="10"/>
       <c r="C1006" s="2">
         <v>19</v>
       </c>
@@ -19828,7 +19828,7 @@
       <c r="A1007" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1007" s="8"/>
+      <c r="B1007" s="10"/>
       <c r="C1007" s="2">
         <v>20</v>
       </c>
@@ -19840,7 +19840,7 @@
       <c r="A1008" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1008" s="8"/>
+      <c r="B1008" s="10"/>
       <c r="C1008" s="2">
         <v>21</v>
       </c>
@@ -19852,7 +19852,7 @@
       <c r="A1009" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1009" s="8"/>
+      <c r="B1009" s="10"/>
       <c r="C1009" s="2">
         <v>22</v>
       </c>
@@ -19864,7 +19864,7 @@
       <c r="A1010" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1010" s="8"/>
+      <c r="B1010" s="10"/>
       <c r="C1010" s="2">
         <v>23</v>
       </c>
@@ -19876,7 +19876,7 @@
       <c r="A1011" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1011" s="8"/>
+      <c r="B1011" s="10"/>
       <c r="C1011" s="2">
         <v>24</v>
       </c>
@@ -19888,7 +19888,7 @@
       <c r="A1012" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1012" s="8"/>
+      <c r="B1012" s="10"/>
       <c r="C1012" s="2">
         <v>25</v>
       </c>
@@ -19900,7 +19900,7 @@
       <c r="A1013" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1013" s="8"/>
+      <c r="B1013" s="10"/>
       <c r="C1013" s="2">
         <v>26</v>
       </c>
@@ -19912,7 +19912,7 @@
       <c r="A1014" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1014" s="8"/>
+      <c r="B1014" s="10"/>
       <c r="C1014" s="2">
         <v>27</v>
       </c>
@@ -19924,7 +19924,7 @@
       <c r="A1015" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1015" s="8"/>
+      <c r="B1015" s="10"/>
       <c r="C1015" s="2">
         <v>28</v>
       </c>
@@ -19936,7 +19936,7 @@
       <c r="A1016" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1016" s="8"/>
+      <c r="B1016" s="10"/>
       <c r="C1016" s="2">
         <v>29</v>
       </c>
@@ -19948,7 +19948,7 @@
       <c r="A1017" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1017" s="8"/>
+      <c r="B1017" s="10"/>
       <c r="C1017" s="2">
         <v>30</v>
       </c>
@@ -19960,7 +19960,7 @@
       <c r="A1018" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1018" s="8"/>
+      <c r="B1018" s="10"/>
       <c r="C1018" s="2">
         <v>31</v>
       </c>
@@ -19972,7 +19972,7 @@
       <c r="A1019" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1019" s="8"/>
+      <c r="B1019" s="10"/>
       <c r="C1019" s="2">
         <v>32</v>
       </c>
@@ -19984,7 +19984,7 @@
       <c r="A1020" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1020" s="8"/>
+      <c r="B1020" s="10"/>
       <c r="C1020" s="2">
         <v>33</v>
       </c>
@@ -19996,7 +19996,7 @@
       <c r="A1021" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1021" s="8"/>
+      <c r="B1021" s="10"/>
       <c r="C1021" s="2">
         <v>34</v>
       </c>
@@ -20008,7 +20008,7 @@
       <c r="A1022" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1022" s="8"/>
+      <c r="B1022" s="10"/>
       <c r="C1022" s="2">
         <v>35</v>
       </c>
@@ -20020,7 +20020,7 @@
       <c r="A1023" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1023" s="8"/>
+      <c r="B1023" s="10"/>
       <c r="C1023" s="2">
         <v>36</v>
       </c>
@@ -20032,7 +20032,7 @@
       <c r="A1024" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1024" s="8"/>
+      <c r="B1024" s="10"/>
       <c r="C1024" s="2">
         <v>37</v>
       </c>
@@ -20044,7 +20044,7 @@
       <c r="A1025" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1025" s="8"/>
+      <c r="B1025" s="10"/>
       <c r="C1025" s="2">
         <v>38</v>
       </c>
@@ -20056,7 +20056,7 @@
       <c r="A1026" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1026" s="8"/>
+      <c r="B1026" s="10"/>
       <c r="C1026" s="2">
         <v>39</v>
       </c>
@@ -20068,7 +20068,7 @@
       <c r="A1027" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1027" s="8"/>
+      <c r="B1027" s="10"/>
       <c r="C1027" s="2">
         <v>40</v>
       </c>
@@ -20080,7 +20080,7 @@
       <c r="A1028" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1028" s="8"/>
+      <c r="B1028" s="10"/>
       <c r="C1028" s="2">
         <v>41</v>
       </c>
@@ -20092,7 +20092,7 @@
       <c r="A1029" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1029" s="8"/>
+      <c r="B1029" s="10"/>
       <c r="C1029" s="2">
         <v>42</v>
       </c>
@@ -20104,7 +20104,7 @@
       <c r="A1030" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1030" s="8"/>
+      <c r="B1030" s="10"/>
       <c r="C1030" s="2">
         <v>44</v>
       </c>
@@ -20116,7 +20116,7 @@
       <c r="A1031" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1031" s="8"/>
+      <c r="B1031" s="10"/>
       <c r="C1031" s="2">
         <v>45</v>
       </c>
@@ -20128,7 +20128,7 @@
       <c r="A1032" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1032" s="8"/>
+      <c r="B1032" s="10"/>
       <c r="C1032" s="2">
         <v>46</v>
       </c>
@@ -20140,7 +20140,7 @@
       <c r="A1033" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1033" s="8"/>
+      <c r="B1033" s="10"/>
       <c r="C1033" s="2">
         <v>47</v>
       </c>
@@ -20152,7 +20152,7 @@
       <c r="A1034" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1034" s="8"/>
+      <c r="B1034" s="10"/>
       <c r="C1034" s="2">
         <v>48</v>
       </c>
@@ -20164,7 +20164,7 @@
       <c r="A1035" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1035" s="8"/>
+      <c r="B1035" s="10"/>
       <c r="C1035" s="2">
         <v>49</v>
       </c>
@@ -20176,7 +20176,7 @@
       <c r="A1036" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1036" s="8"/>
+      <c r="B1036" s="10"/>
       <c r="C1036" s="2">
         <v>50</v>
       </c>
@@ -20188,7 +20188,7 @@
       <c r="A1037" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1037" s="8"/>
+      <c r="B1037" s="10"/>
       <c r="C1037" s="2">
         <v>51</v>
       </c>
@@ -20200,7 +20200,7 @@
       <c r="A1038" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1038" s="8"/>
+      <c r="B1038" s="10"/>
       <c r="C1038" s="2">
         <v>53</v>
       </c>
@@ -20212,7 +20212,7 @@
       <c r="A1039" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1039" s="8"/>
+      <c r="B1039" s="10"/>
       <c r="C1039" s="2">
         <v>54</v>
       </c>
@@ -20224,7 +20224,7 @@
       <c r="A1040" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1040" s="8"/>
+      <c r="B1040" s="10"/>
       <c r="C1040" s="2">
         <v>55</v>
       </c>
@@ -20236,7 +20236,7 @@
       <c r="A1041" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1041" s="8"/>
+      <c r="B1041" s="10"/>
       <c r="C1041" s="2">
         <v>56</v>
       </c>
@@ -33720,645 +33720,6 @@
     </row>
   </sheetData>
   <mergeCells count="654">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B109:B114"/>
-    <mergeCell ref="B115:B200"/>
-    <mergeCell ref="B201:B253"/>
-    <mergeCell ref="B254:B269"/>
-    <mergeCell ref="B270:B287"/>
-    <mergeCell ref="B288:B301"/>
-    <mergeCell ref="B302:B333"/>
-    <mergeCell ref="B334:B337"/>
-    <mergeCell ref="B338:B341"/>
-    <mergeCell ref="B342:B346"/>
-    <mergeCell ref="B347:B351"/>
-    <mergeCell ref="B352:B355"/>
-    <mergeCell ref="B356:B359"/>
-    <mergeCell ref="B360:B363"/>
-    <mergeCell ref="B364:B367"/>
-    <mergeCell ref="B368:B371"/>
-    <mergeCell ref="B372:B378"/>
-    <mergeCell ref="B379:B385"/>
-    <mergeCell ref="B386:B392"/>
-    <mergeCell ref="B393:B399"/>
-    <mergeCell ref="B400:B404"/>
-    <mergeCell ref="B405:B407"/>
-    <mergeCell ref="B408:B410"/>
-    <mergeCell ref="B411:B415"/>
-    <mergeCell ref="B416:B418"/>
-    <mergeCell ref="B419:B421"/>
-    <mergeCell ref="B422:B424"/>
-    <mergeCell ref="B425:B430"/>
-    <mergeCell ref="B431:B436"/>
-    <mergeCell ref="B437:B442"/>
-    <mergeCell ref="B443:B450"/>
-    <mergeCell ref="B451:B456"/>
-    <mergeCell ref="B457:B462"/>
-    <mergeCell ref="B463:B468"/>
-    <mergeCell ref="B469:B474"/>
-    <mergeCell ref="B475:B480"/>
-    <mergeCell ref="B481:B486"/>
-    <mergeCell ref="B487:B492"/>
-    <mergeCell ref="B493:B498"/>
-    <mergeCell ref="B499:B504"/>
-    <mergeCell ref="B505:B510"/>
-    <mergeCell ref="B511:B516"/>
-    <mergeCell ref="B517:B522"/>
-    <mergeCell ref="B523:B528"/>
-    <mergeCell ref="B529:B534"/>
-    <mergeCell ref="B535:B540"/>
-    <mergeCell ref="B541:B546"/>
-    <mergeCell ref="B547:B552"/>
-    <mergeCell ref="B553:B558"/>
-    <mergeCell ref="B559:B564"/>
-    <mergeCell ref="B565:B568"/>
-    <mergeCell ref="B569:B571"/>
-    <mergeCell ref="B572:B575"/>
-    <mergeCell ref="B576:B579"/>
-    <mergeCell ref="B580:B582"/>
-    <mergeCell ref="B583:B585"/>
-    <mergeCell ref="B586:B588"/>
-    <mergeCell ref="B589:B591"/>
-    <mergeCell ref="B592:B605"/>
-    <mergeCell ref="B606:B637"/>
-    <mergeCell ref="B638:B641"/>
-    <mergeCell ref="B642:B646"/>
-    <mergeCell ref="B647:B651"/>
-    <mergeCell ref="B652:B658"/>
-    <mergeCell ref="B659:B665"/>
-    <mergeCell ref="B666:B670"/>
-    <mergeCell ref="B671:B675"/>
-    <mergeCell ref="B676:B680"/>
-    <mergeCell ref="B681:B685"/>
-    <mergeCell ref="B686:B691"/>
-    <mergeCell ref="B692:B698"/>
-    <mergeCell ref="B699:B712"/>
-    <mergeCell ref="B713:B744"/>
-    <mergeCell ref="B745:B746"/>
-    <mergeCell ref="B747:B750"/>
-    <mergeCell ref="B751:B755"/>
-    <mergeCell ref="B756:B761"/>
-    <mergeCell ref="B762:B767"/>
-    <mergeCell ref="B768:B776"/>
-    <mergeCell ref="B777:B779"/>
-    <mergeCell ref="B780:B782"/>
-    <mergeCell ref="B783:B785"/>
-    <mergeCell ref="B786:B788"/>
-    <mergeCell ref="B789:B791"/>
-    <mergeCell ref="B792:B794"/>
-    <mergeCell ref="B795:B797"/>
-    <mergeCell ref="B798:B800"/>
-    <mergeCell ref="B801:B803"/>
-    <mergeCell ref="B804:B806"/>
-    <mergeCell ref="B807:B809"/>
-    <mergeCell ref="B810:B812"/>
-    <mergeCell ref="B813:B815"/>
-    <mergeCell ref="B816:B820"/>
-    <mergeCell ref="B821:B825"/>
-    <mergeCell ref="B826:B830"/>
-    <mergeCell ref="B831:B835"/>
-    <mergeCell ref="B836:B843"/>
-    <mergeCell ref="B844:B846"/>
-    <mergeCell ref="B847:B852"/>
-    <mergeCell ref="B853:B855"/>
-    <mergeCell ref="B856:B860"/>
-    <mergeCell ref="B861:B864"/>
-    <mergeCell ref="B865:B870"/>
-    <mergeCell ref="B871:B874"/>
-    <mergeCell ref="B875:B879"/>
-    <mergeCell ref="B880:B882"/>
-    <mergeCell ref="B883:B885"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="B888:B892"/>
-    <mergeCell ref="B893:B895"/>
-    <mergeCell ref="B896:B901"/>
-    <mergeCell ref="B902:B905"/>
-    <mergeCell ref="B906:B909"/>
-    <mergeCell ref="B910:B916"/>
-    <mergeCell ref="B917:B925"/>
-    <mergeCell ref="B926:B929"/>
-    <mergeCell ref="B930:B935"/>
-    <mergeCell ref="B936:B942"/>
-    <mergeCell ref="B943:B955"/>
-    <mergeCell ref="B956:B963"/>
-    <mergeCell ref="B964:B971"/>
-    <mergeCell ref="B972:B979"/>
-    <mergeCell ref="B980:B984"/>
-    <mergeCell ref="B985:B990"/>
-    <mergeCell ref="B991:B1041"/>
-    <mergeCell ref="B1042:B1076"/>
-    <mergeCell ref="B1077:B1078"/>
-    <mergeCell ref="B1079:B1080"/>
-    <mergeCell ref="B1081:B1082"/>
-    <mergeCell ref="B1083:B1084"/>
-    <mergeCell ref="B1085:B1086"/>
-    <mergeCell ref="B1087:B1088"/>
-    <mergeCell ref="B1089:B1090"/>
-    <mergeCell ref="B1091:B1092"/>
-    <mergeCell ref="B1093:B1094"/>
-    <mergeCell ref="B1095:B1096"/>
-    <mergeCell ref="B1097:B1098"/>
-    <mergeCell ref="B1099:B1100"/>
-    <mergeCell ref="B1101:B1102"/>
-    <mergeCell ref="B1103:B1104"/>
-    <mergeCell ref="B1105:B1106"/>
-    <mergeCell ref="B1107:B1108"/>
-    <mergeCell ref="B1109:B1110"/>
-    <mergeCell ref="B1111:B1112"/>
-    <mergeCell ref="B1113:B1114"/>
-    <mergeCell ref="B1115:B1116"/>
-    <mergeCell ref="B1117:B1118"/>
-    <mergeCell ref="B1119:B1120"/>
-    <mergeCell ref="B1121:B1122"/>
-    <mergeCell ref="B1123:B1124"/>
-    <mergeCell ref="B1125:B1126"/>
-    <mergeCell ref="B1127:B1128"/>
-    <mergeCell ref="B1129:B1130"/>
-    <mergeCell ref="B1131:B1132"/>
-    <mergeCell ref="B1133:B1134"/>
-    <mergeCell ref="B1135:B1136"/>
-    <mergeCell ref="B1137:B1138"/>
-    <mergeCell ref="B1139:B1140"/>
-    <mergeCell ref="B1141:B1142"/>
-    <mergeCell ref="B1143:B1144"/>
-    <mergeCell ref="B1145:B1146"/>
-    <mergeCell ref="B1147:B1148"/>
-    <mergeCell ref="B1149:B1150"/>
-    <mergeCell ref="B1151:B1152"/>
-    <mergeCell ref="B1153:B1154"/>
-    <mergeCell ref="B1155:B1156"/>
-    <mergeCell ref="B1157:B1158"/>
-    <mergeCell ref="B1159:B1160"/>
-    <mergeCell ref="B1161:B1162"/>
-    <mergeCell ref="B1163:B1164"/>
-    <mergeCell ref="B1165:B1166"/>
-    <mergeCell ref="B1167:B1168"/>
-    <mergeCell ref="B1169:B1170"/>
-    <mergeCell ref="B1171:B1172"/>
-    <mergeCell ref="B1173:B1174"/>
-    <mergeCell ref="B1175:B1176"/>
-    <mergeCell ref="B1177:B1178"/>
-    <mergeCell ref="B1179:B1180"/>
-    <mergeCell ref="B1181:B1182"/>
-    <mergeCell ref="B1183:B1184"/>
-    <mergeCell ref="B1185:B1186"/>
-    <mergeCell ref="B1187:B1188"/>
-    <mergeCell ref="B1189:B1190"/>
-    <mergeCell ref="B1191:B1192"/>
-    <mergeCell ref="B1193:B1194"/>
-    <mergeCell ref="B1195:B1196"/>
-    <mergeCell ref="B1197:B1198"/>
-    <mergeCell ref="B1199:B1200"/>
-    <mergeCell ref="B1201:B1202"/>
-    <mergeCell ref="B1203:B1204"/>
-    <mergeCell ref="B1205:B1206"/>
-    <mergeCell ref="B1207:B1208"/>
-    <mergeCell ref="B1209:B1210"/>
-    <mergeCell ref="B1211:B1212"/>
-    <mergeCell ref="B1213:B1214"/>
-    <mergeCell ref="B1215:B1216"/>
-    <mergeCell ref="B1217:B1218"/>
-    <mergeCell ref="B1219:B1220"/>
-    <mergeCell ref="B1221:B1222"/>
-    <mergeCell ref="B1223:B1224"/>
-    <mergeCell ref="B1225:B1226"/>
-    <mergeCell ref="B1227:B1228"/>
-    <mergeCell ref="B1229:B1230"/>
-    <mergeCell ref="B1231:B1232"/>
-    <mergeCell ref="B1233:B1234"/>
-    <mergeCell ref="B1235:B1236"/>
-    <mergeCell ref="B1237:B1238"/>
-    <mergeCell ref="B1239:B1240"/>
-    <mergeCell ref="B1241:B1242"/>
-    <mergeCell ref="B1243:B1244"/>
-    <mergeCell ref="B1245:B1246"/>
-    <mergeCell ref="B1247:B1248"/>
-    <mergeCell ref="B1249:B1250"/>
-    <mergeCell ref="B1251:B1252"/>
-    <mergeCell ref="B1253:B1254"/>
-    <mergeCell ref="B1255:B1256"/>
-    <mergeCell ref="B1257:B1258"/>
-    <mergeCell ref="B1259:B1260"/>
-    <mergeCell ref="B1261:B1262"/>
-    <mergeCell ref="B1263:B1264"/>
-    <mergeCell ref="B1265:B1266"/>
-    <mergeCell ref="B1267:B1268"/>
-    <mergeCell ref="B1269:B1270"/>
-    <mergeCell ref="B1271:B1272"/>
-    <mergeCell ref="B1273:B1274"/>
-    <mergeCell ref="B1275:B1276"/>
-    <mergeCell ref="B1277:B1278"/>
-    <mergeCell ref="B1279:B1280"/>
-    <mergeCell ref="B1281:B1282"/>
-    <mergeCell ref="B1283:B1284"/>
-    <mergeCell ref="B1285:B1286"/>
-    <mergeCell ref="B1287:B1288"/>
-    <mergeCell ref="B1289:B1290"/>
-    <mergeCell ref="B1291:B1292"/>
-    <mergeCell ref="B1293:B1294"/>
-    <mergeCell ref="B1295:B1296"/>
-    <mergeCell ref="B1297:B1298"/>
-    <mergeCell ref="B1299:B1300"/>
-    <mergeCell ref="B1301:B1302"/>
-    <mergeCell ref="B1303:B1304"/>
-    <mergeCell ref="B1305:B1306"/>
-    <mergeCell ref="B1307:B1308"/>
-    <mergeCell ref="B1309:B1310"/>
-    <mergeCell ref="B1311:B1312"/>
-    <mergeCell ref="B1313:B1314"/>
-    <mergeCell ref="B1315:B1316"/>
-    <mergeCell ref="B1317:B1318"/>
-    <mergeCell ref="B1319:B1320"/>
-    <mergeCell ref="B1321:B1322"/>
-    <mergeCell ref="B1323:B1324"/>
-    <mergeCell ref="B1325:B1326"/>
-    <mergeCell ref="B1327:B1328"/>
-    <mergeCell ref="B1329:B1330"/>
-    <mergeCell ref="B1331:B1332"/>
-    <mergeCell ref="B1333:B1334"/>
-    <mergeCell ref="B1335:B1336"/>
-    <mergeCell ref="B1337:B1338"/>
-    <mergeCell ref="B1339:B1340"/>
-    <mergeCell ref="B1341:B1342"/>
-    <mergeCell ref="B1343:B1344"/>
-    <mergeCell ref="B1345:B1346"/>
-    <mergeCell ref="B1347:B1348"/>
-    <mergeCell ref="B1349:B1350"/>
-    <mergeCell ref="B1351:B1352"/>
-    <mergeCell ref="B1353:B1354"/>
-    <mergeCell ref="B1355:B1356"/>
-    <mergeCell ref="B1357:B1358"/>
-    <mergeCell ref="B1359:B1360"/>
-    <mergeCell ref="B1361:B1362"/>
-    <mergeCell ref="B1363:B1364"/>
-    <mergeCell ref="B1365:B1366"/>
-    <mergeCell ref="B1367:B1368"/>
-    <mergeCell ref="B1369:B1370"/>
-    <mergeCell ref="B1371:B1372"/>
-    <mergeCell ref="B1373:B1374"/>
-    <mergeCell ref="B1375:B1376"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B1379:B1380"/>
-    <mergeCell ref="B1381:B1382"/>
-    <mergeCell ref="B1383:B1384"/>
-    <mergeCell ref="B1385:B1386"/>
-    <mergeCell ref="B1387:B1388"/>
-    <mergeCell ref="B1389:B1390"/>
-    <mergeCell ref="B1391:B1392"/>
-    <mergeCell ref="B1393:B1394"/>
-    <mergeCell ref="B1395:B1396"/>
-    <mergeCell ref="B1397:B1398"/>
-    <mergeCell ref="B1399:B1400"/>
-    <mergeCell ref="B1401:B1402"/>
-    <mergeCell ref="B1403:B1404"/>
-    <mergeCell ref="B1405:B1406"/>
-    <mergeCell ref="B1407:B1408"/>
-    <mergeCell ref="B1409:B1410"/>
-    <mergeCell ref="B1411:B1412"/>
-    <mergeCell ref="B1413:B1414"/>
-    <mergeCell ref="B1415:B1416"/>
-    <mergeCell ref="B1417:B1418"/>
-    <mergeCell ref="B1419:B1420"/>
-    <mergeCell ref="B1421:B1422"/>
-    <mergeCell ref="B1423:B1424"/>
-    <mergeCell ref="B1425:B1426"/>
-    <mergeCell ref="B1427:B1428"/>
-    <mergeCell ref="B1429:B1430"/>
-    <mergeCell ref="B1431:B1432"/>
-    <mergeCell ref="B1433:B1434"/>
-    <mergeCell ref="B1435:B1436"/>
-    <mergeCell ref="B1437:B1438"/>
-    <mergeCell ref="B1439:B1440"/>
-    <mergeCell ref="B1441:B1442"/>
-    <mergeCell ref="B1443:B1444"/>
-    <mergeCell ref="B1445:B1446"/>
-    <mergeCell ref="B1447:B1448"/>
-    <mergeCell ref="B1449:B1450"/>
-    <mergeCell ref="B1451:B1452"/>
-    <mergeCell ref="B1453:B1454"/>
-    <mergeCell ref="B1455:B1456"/>
-    <mergeCell ref="B1457:B1458"/>
-    <mergeCell ref="B1459:B1460"/>
-    <mergeCell ref="B1461:B1462"/>
-    <mergeCell ref="B1463:B1464"/>
-    <mergeCell ref="B1465:B1466"/>
-    <mergeCell ref="B1467:B1468"/>
-    <mergeCell ref="B1469:B1470"/>
-    <mergeCell ref="B1471:B1472"/>
-    <mergeCell ref="B1473:B1474"/>
-    <mergeCell ref="B1475:B1476"/>
-    <mergeCell ref="B1477:B1478"/>
-    <mergeCell ref="B1479:B1480"/>
-    <mergeCell ref="B1481:B1482"/>
-    <mergeCell ref="B1483:B1484"/>
-    <mergeCell ref="B1485:B1486"/>
-    <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="B1489:B1490"/>
-    <mergeCell ref="B1491:B1492"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1495:B1496"/>
-    <mergeCell ref="B1497:B1498"/>
-    <mergeCell ref="B1499:B1500"/>
-    <mergeCell ref="B1501:B1502"/>
-    <mergeCell ref="B1503:B1504"/>
-    <mergeCell ref="B1505:B1506"/>
-    <mergeCell ref="B1507:B1508"/>
-    <mergeCell ref="B1509:B1510"/>
-    <mergeCell ref="B1511:B1512"/>
-    <mergeCell ref="B1513:B1514"/>
-    <mergeCell ref="B1515:B1516"/>
-    <mergeCell ref="B1517:B1518"/>
-    <mergeCell ref="B1519:B1520"/>
-    <mergeCell ref="B1521:B1522"/>
-    <mergeCell ref="B1523:B1524"/>
-    <mergeCell ref="B1525:B1526"/>
-    <mergeCell ref="B1527:B1528"/>
-    <mergeCell ref="B1529:B1530"/>
-    <mergeCell ref="B1531:B1532"/>
-    <mergeCell ref="B1533:B1534"/>
-    <mergeCell ref="B1535:B1536"/>
-    <mergeCell ref="B1537:B1538"/>
-    <mergeCell ref="B1539:B1540"/>
-    <mergeCell ref="B1541:B1542"/>
-    <mergeCell ref="B1543:B1544"/>
-    <mergeCell ref="B1545:B1546"/>
-    <mergeCell ref="B1547:B1548"/>
-    <mergeCell ref="B1549:B1550"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B1553:B1554"/>
-    <mergeCell ref="B1555:B1556"/>
-    <mergeCell ref="B1557:B1558"/>
-    <mergeCell ref="B1559:B1560"/>
-    <mergeCell ref="B1561:B1562"/>
-    <mergeCell ref="B1563:B1564"/>
-    <mergeCell ref="B1565:B1566"/>
-    <mergeCell ref="B1567:B1568"/>
-    <mergeCell ref="B1569:B1570"/>
-    <mergeCell ref="B1571:B1572"/>
-    <mergeCell ref="B1573:B1574"/>
-    <mergeCell ref="B1575:B1576"/>
-    <mergeCell ref="B1577:B1578"/>
-    <mergeCell ref="B1579:B1580"/>
-    <mergeCell ref="B1581:B1582"/>
-    <mergeCell ref="B1583:B1584"/>
-    <mergeCell ref="B1585:B1586"/>
-    <mergeCell ref="B1587:B1588"/>
-    <mergeCell ref="B1589:B1590"/>
-    <mergeCell ref="B1591:B1592"/>
-    <mergeCell ref="B1593:B1594"/>
-    <mergeCell ref="B1595:B1596"/>
-    <mergeCell ref="B1597:B1598"/>
-    <mergeCell ref="B1599:B1600"/>
-    <mergeCell ref="B1601:B1602"/>
-    <mergeCell ref="B1603:B1604"/>
-    <mergeCell ref="B1605:B1606"/>
-    <mergeCell ref="B1607:B1608"/>
-    <mergeCell ref="B1609:B1610"/>
-    <mergeCell ref="B1611:B1612"/>
-    <mergeCell ref="B1613:B1614"/>
-    <mergeCell ref="B1615:B1616"/>
-    <mergeCell ref="B1617:B1618"/>
-    <mergeCell ref="B1619:B1620"/>
-    <mergeCell ref="B1621:B1622"/>
-    <mergeCell ref="B1623:B1624"/>
-    <mergeCell ref="B1625:B1626"/>
-    <mergeCell ref="B1627:B1628"/>
-    <mergeCell ref="B1629:B1630"/>
-    <mergeCell ref="B1631:B1632"/>
-    <mergeCell ref="B1633:B1634"/>
-    <mergeCell ref="B1635:B1636"/>
-    <mergeCell ref="B1637:B1638"/>
-    <mergeCell ref="B1639:B1640"/>
-    <mergeCell ref="B1641:B1642"/>
-    <mergeCell ref="B1643:B1644"/>
-    <mergeCell ref="B1645:B1646"/>
-    <mergeCell ref="B1647:B1648"/>
-    <mergeCell ref="B1649:B1650"/>
-    <mergeCell ref="B1651:B1652"/>
-    <mergeCell ref="B1653:B1654"/>
-    <mergeCell ref="B1655:B1656"/>
-    <mergeCell ref="B1657:B1658"/>
-    <mergeCell ref="B1659:B1660"/>
-    <mergeCell ref="B1661:B1662"/>
-    <mergeCell ref="B1663:B1664"/>
-    <mergeCell ref="B1665:B1666"/>
-    <mergeCell ref="B1667:B1668"/>
-    <mergeCell ref="B1669:B1670"/>
-    <mergeCell ref="B1671:B1672"/>
-    <mergeCell ref="B1673:B1674"/>
-    <mergeCell ref="B1675:B1676"/>
-    <mergeCell ref="B1677:B1678"/>
-    <mergeCell ref="B1679:B1680"/>
-    <mergeCell ref="B1681:B1682"/>
-    <mergeCell ref="B1683:B1684"/>
-    <mergeCell ref="B1685:B1686"/>
-    <mergeCell ref="B1687:B1688"/>
-    <mergeCell ref="B1689:B1690"/>
-    <mergeCell ref="B1691:B1692"/>
-    <mergeCell ref="B1693:B1694"/>
-    <mergeCell ref="B1695:B1696"/>
-    <mergeCell ref="B1697:B1698"/>
-    <mergeCell ref="B1699:B1700"/>
-    <mergeCell ref="B1701:B1702"/>
-    <mergeCell ref="B1703:B1704"/>
-    <mergeCell ref="B1705:B1706"/>
-    <mergeCell ref="B1707:B1708"/>
-    <mergeCell ref="B1709:B1710"/>
-    <mergeCell ref="B1711:B1712"/>
-    <mergeCell ref="B1713:B1714"/>
-    <mergeCell ref="B1715:B1716"/>
-    <mergeCell ref="B1717:B1718"/>
-    <mergeCell ref="B1719:B1720"/>
-    <mergeCell ref="B1721:B1722"/>
-    <mergeCell ref="B1723:B1724"/>
-    <mergeCell ref="B1725:B1726"/>
-    <mergeCell ref="B1727:B1728"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="B1731:B1732"/>
-    <mergeCell ref="B1733:B1734"/>
-    <mergeCell ref="B1735:B1736"/>
-    <mergeCell ref="B1737:B1738"/>
-    <mergeCell ref="B1739:B1740"/>
-    <mergeCell ref="B1741:B1742"/>
-    <mergeCell ref="B1743:B1744"/>
-    <mergeCell ref="B1745:B1746"/>
-    <mergeCell ref="B1747:B1748"/>
-    <mergeCell ref="B1749:B1750"/>
-    <mergeCell ref="B1751:B1752"/>
-    <mergeCell ref="B1753:B1754"/>
-    <mergeCell ref="B1755:B1756"/>
-    <mergeCell ref="B1757:B1758"/>
-    <mergeCell ref="B1759:B1760"/>
-    <mergeCell ref="B1761:B1762"/>
-    <mergeCell ref="B1763:B1764"/>
-    <mergeCell ref="B1765:B1766"/>
-    <mergeCell ref="B1767:B1768"/>
-    <mergeCell ref="B1769:B1770"/>
-    <mergeCell ref="B1771:B1772"/>
-    <mergeCell ref="B1773:B1774"/>
-    <mergeCell ref="B1775:B1776"/>
-    <mergeCell ref="B1777:B1778"/>
-    <mergeCell ref="B1779:B1780"/>
-    <mergeCell ref="B1781:B1782"/>
-    <mergeCell ref="B1783:B1784"/>
-    <mergeCell ref="B1785:B1786"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B1789:B1790"/>
-    <mergeCell ref="B1791:B1792"/>
-    <mergeCell ref="B1793:B1794"/>
-    <mergeCell ref="B1795:B1796"/>
-    <mergeCell ref="B1797:B1798"/>
-    <mergeCell ref="B1799:B1800"/>
-    <mergeCell ref="B1801:B1802"/>
-    <mergeCell ref="B1803:B1804"/>
-    <mergeCell ref="B1805:B1806"/>
-    <mergeCell ref="B1807:B1808"/>
-    <mergeCell ref="B1809:B1810"/>
-    <mergeCell ref="B1811:B1812"/>
-    <mergeCell ref="B1813:B1814"/>
-    <mergeCell ref="B1815:B1816"/>
-    <mergeCell ref="B1817:B1818"/>
-    <mergeCell ref="B1819:B1820"/>
-    <mergeCell ref="B1821:B1822"/>
-    <mergeCell ref="B1823:B1824"/>
-    <mergeCell ref="B1825:B1826"/>
-    <mergeCell ref="B1827:B1828"/>
-    <mergeCell ref="B1829:B1830"/>
-    <mergeCell ref="B1831:B1832"/>
-    <mergeCell ref="B1833:B1834"/>
-    <mergeCell ref="B1835:B1836"/>
-    <mergeCell ref="B1837:B1838"/>
-    <mergeCell ref="B1839:B1840"/>
-    <mergeCell ref="B1841:B1842"/>
-    <mergeCell ref="B1843:B1844"/>
-    <mergeCell ref="B1845:B1846"/>
-    <mergeCell ref="B1847:B1848"/>
-    <mergeCell ref="B1849:B1850"/>
-    <mergeCell ref="B1851:B1852"/>
-    <mergeCell ref="B1853:B1854"/>
-    <mergeCell ref="B1855:B1856"/>
-    <mergeCell ref="B1857:B1858"/>
-    <mergeCell ref="B1859:B1860"/>
-    <mergeCell ref="B1861:B1862"/>
-    <mergeCell ref="B1863:B1864"/>
-    <mergeCell ref="B1865:B1866"/>
-    <mergeCell ref="B1867:B1868"/>
-    <mergeCell ref="B1869:B1870"/>
-    <mergeCell ref="B1871:B1872"/>
-    <mergeCell ref="B1873:B1874"/>
-    <mergeCell ref="B1875:B1876"/>
-    <mergeCell ref="B1877:B1878"/>
-    <mergeCell ref="B1879:B1880"/>
-    <mergeCell ref="B1881:B1882"/>
-    <mergeCell ref="B1883:B1884"/>
-    <mergeCell ref="B1885:B1886"/>
-    <mergeCell ref="B1887:B1888"/>
-    <mergeCell ref="B1889:B1890"/>
-    <mergeCell ref="B1891:B1892"/>
-    <mergeCell ref="B1893:B1894"/>
-    <mergeCell ref="B1895:B1896"/>
-    <mergeCell ref="B1897:B1898"/>
-    <mergeCell ref="B1899:B1900"/>
-    <mergeCell ref="B1901:B1902"/>
-    <mergeCell ref="B1903:B1904"/>
-    <mergeCell ref="B1905:B1906"/>
-    <mergeCell ref="B1907:B1908"/>
-    <mergeCell ref="B1909:B1910"/>
-    <mergeCell ref="B1911:B1912"/>
-    <mergeCell ref="B1913:B1914"/>
-    <mergeCell ref="B1915:B1916"/>
-    <mergeCell ref="B1917:B1918"/>
-    <mergeCell ref="B1919:B1920"/>
-    <mergeCell ref="B1921:B1922"/>
-    <mergeCell ref="B1923:B1924"/>
-    <mergeCell ref="B1925:B1926"/>
-    <mergeCell ref="B1927:B1928"/>
-    <mergeCell ref="B1929:B1930"/>
-    <mergeCell ref="B1931:B1932"/>
-    <mergeCell ref="B1933:B1934"/>
-    <mergeCell ref="B1935:B1936"/>
-    <mergeCell ref="B1937:B1938"/>
-    <mergeCell ref="B1939:B1940"/>
-    <mergeCell ref="B1941:B1942"/>
-    <mergeCell ref="B1943:B1944"/>
-    <mergeCell ref="B1945:B1946"/>
-    <mergeCell ref="B1947:B1948"/>
-    <mergeCell ref="B1949:B1950"/>
-    <mergeCell ref="B1951:B1952"/>
-    <mergeCell ref="B1953:B1954"/>
-    <mergeCell ref="B1955:B1956"/>
-    <mergeCell ref="B1957:B1958"/>
-    <mergeCell ref="B1959:B1960"/>
-    <mergeCell ref="B1961:B1962"/>
-    <mergeCell ref="B1963:B1964"/>
-    <mergeCell ref="B1965:B1966"/>
-    <mergeCell ref="B1967:B1968"/>
-    <mergeCell ref="B1969:B1970"/>
-    <mergeCell ref="B1971:B1972"/>
-    <mergeCell ref="B1973:B1974"/>
-    <mergeCell ref="B1975:B1976"/>
-    <mergeCell ref="B1977:B1978"/>
-    <mergeCell ref="B1979:B1980"/>
-    <mergeCell ref="B1981:B1982"/>
-    <mergeCell ref="B1983:B1984"/>
-    <mergeCell ref="B1985:B1986"/>
-    <mergeCell ref="B1987:B1988"/>
-    <mergeCell ref="B1989:B1990"/>
-    <mergeCell ref="B1991:B1992"/>
-    <mergeCell ref="B1993:B1994"/>
-    <mergeCell ref="B1995:B1996"/>
-    <mergeCell ref="B1997:B1998"/>
-    <mergeCell ref="B1999:B2000"/>
-    <mergeCell ref="B2001:B2002"/>
-    <mergeCell ref="B2003:B2004"/>
-    <mergeCell ref="B2005:B2006"/>
-    <mergeCell ref="B2007:B2008"/>
-    <mergeCell ref="B2009:B2010"/>
-    <mergeCell ref="B2011:B2012"/>
-    <mergeCell ref="B2013:B2014"/>
-    <mergeCell ref="B2015:B2016"/>
-    <mergeCell ref="B2017:B2018"/>
-    <mergeCell ref="B2019:B2020"/>
-    <mergeCell ref="B2021:B2022"/>
-    <mergeCell ref="B2023:B2024"/>
-    <mergeCell ref="B2025:B2026"/>
-    <mergeCell ref="B2027:B2028"/>
-    <mergeCell ref="B2029:B2030"/>
-    <mergeCell ref="B2031:B2032"/>
-    <mergeCell ref="B2033:B2034"/>
-    <mergeCell ref="B2035:B2036"/>
-    <mergeCell ref="B2037:B2038"/>
-    <mergeCell ref="B2039:B2040"/>
-    <mergeCell ref="B2041:B2042"/>
-    <mergeCell ref="B2043:B2044"/>
-    <mergeCell ref="B2045:B2046"/>
-    <mergeCell ref="B2047:B2048"/>
-    <mergeCell ref="B2049:B2050"/>
     <mergeCell ref="B2069:B2070"/>
     <mergeCell ref="B2071:B2072"/>
     <mergeCell ref="B2073:B2074"/>
@@ -34374,6 +33735,645 @@
     <mergeCell ref="B2063:B2064"/>
     <mergeCell ref="B2065:B2066"/>
     <mergeCell ref="B2067:B2068"/>
+    <mergeCell ref="B2033:B2034"/>
+    <mergeCell ref="B2035:B2036"/>
+    <mergeCell ref="B2037:B2038"/>
+    <mergeCell ref="B2039:B2040"/>
+    <mergeCell ref="B2041:B2042"/>
+    <mergeCell ref="B2043:B2044"/>
+    <mergeCell ref="B2045:B2046"/>
+    <mergeCell ref="B2047:B2048"/>
+    <mergeCell ref="B2049:B2050"/>
+    <mergeCell ref="B2015:B2016"/>
+    <mergeCell ref="B2017:B2018"/>
+    <mergeCell ref="B2019:B2020"/>
+    <mergeCell ref="B2021:B2022"/>
+    <mergeCell ref="B2023:B2024"/>
+    <mergeCell ref="B2025:B2026"/>
+    <mergeCell ref="B2027:B2028"/>
+    <mergeCell ref="B2029:B2030"/>
+    <mergeCell ref="B2031:B2032"/>
+    <mergeCell ref="B1997:B1998"/>
+    <mergeCell ref="B1999:B2000"/>
+    <mergeCell ref="B2001:B2002"/>
+    <mergeCell ref="B2003:B2004"/>
+    <mergeCell ref="B2005:B2006"/>
+    <mergeCell ref="B2007:B2008"/>
+    <mergeCell ref="B2009:B2010"/>
+    <mergeCell ref="B2011:B2012"/>
+    <mergeCell ref="B2013:B2014"/>
+    <mergeCell ref="B1979:B1980"/>
+    <mergeCell ref="B1981:B1982"/>
+    <mergeCell ref="B1983:B1984"/>
+    <mergeCell ref="B1985:B1986"/>
+    <mergeCell ref="B1987:B1988"/>
+    <mergeCell ref="B1989:B1990"/>
+    <mergeCell ref="B1991:B1992"/>
+    <mergeCell ref="B1993:B1994"/>
+    <mergeCell ref="B1995:B1996"/>
+    <mergeCell ref="B1961:B1962"/>
+    <mergeCell ref="B1963:B1964"/>
+    <mergeCell ref="B1965:B1966"/>
+    <mergeCell ref="B1967:B1968"/>
+    <mergeCell ref="B1969:B1970"/>
+    <mergeCell ref="B1971:B1972"/>
+    <mergeCell ref="B1973:B1974"/>
+    <mergeCell ref="B1975:B1976"/>
+    <mergeCell ref="B1977:B1978"/>
+    <mergeCell ref="B1943:B1944"/>
+    <mergeCell ref="B1945:B1946"/>
+    <mergeCell ref="B1947:B1948"/>
+    <mergeCell ref="B1949:B1950"/>
+    <mergeCell ref="B1951:B1952"/>
+    <mergeCell ref="B1953:B1954"/>
+    <mergeCell ref="B1955:B1956"/>
+    <mergeCell ref="B1957:B1958"/>
+    <mergeCell ref="B1959:B1960"/>
+    <mergeCell ref="B1925:B1926"/>
+    <mergeCell ref="B1927:B1928"/>
+    <mergeCell ref="B1929:B1930"/>
+    <mergeCell ref="B1931:B1932"/>
+    <mergeCell ref="B1933:B1934"/>
+    <mergeCell ref="B1935:B1936"/>
+    <mergeCell ref="B1937:B1938"/>
+    <mergeCell ref="B1939:B1940"/>
+    <mergeCell ref="B1941:B1942"/>
+    <mergeCell ref="B1907:B1908"/>
+    <mergeCell ref="B1909:B1910"/>
+    <mergeCell ref="B1911:B1912"/>
+    <mergeCell ref="B1913:B1914"/>
+    <mergeCell ref="B1915:B1916"/>
+    <mergeCell ref="B1917:B1918"/>
+    <mergeCell ref="B1919:B1920"/>
+    <mergeCell ref="B1921:B1922"/>
+    <mergeCell ref="B1923:B1924"/>
+    <mergeCell ref="B1889:B1890"/>
+    <mergeCell ref="B1891:B1892"/>
+    <mergeCell ref="B1893:B1894"/>
+    <mergeCell ref="B1895:B1896"/>
+    <mergeCell ref="B1897:B1898"/>
+    <mergeCell ref="B1899:B1900"/>
+    <mergeCell ref="B1901:B1902"/>
+    <mergeCell ref="B1903:B1904"/>
+    <mergeCell ref="B1905:B1906"/>
+    <mergeCell ref="B1871:B1872"/>
+    <mergeCell ref="B1873:B1874"/>
+    <mergeCell ref="B1875:B1876"/>
+    <mergeCell ref="B1877:B1878"/>
+    <mergeCell ref="B1879:B1880"/>
+    <mergeCell ref="B1881:B1882"/>
+    <mergeCell ref="B1883:B1884"/>
+    <mergeCell ref="B1885:B1886"/>
+    <mergeCell ref="B1887:B1888"/>
+    <mergeCell ref="B1853:B1854"/>
+    <mergeCell ref="B1855:B1856"/>
+    <mergeCell ref="B1857:B1858"/>
+    <mergeCell ref="B1859:B1860"/>
+    <mergeCell ref="B1861:B1862"/>
+    <mergeCell ref="B1863:B1864"/>
+    <mergeCell ref="B1865:B1866"/>
+    <mergeCell ref="B1867:B1868"/>
+    <mergeCell ref="B1869:B1870"/>
+    <mergeCell ref="B1835:B1836"/>
+    <mergeCell ref="B1837:B1838"/>
+    <mergeCell ref="B1839:B1840"/>
+    <mergeCell ref="B1841:B1842"/>
+    <mergeCell ref="B1843:B1844"/>
+    <mergeCell ref="B1845:B1846"/>
+    <mergeCell ref="B1847:B1848"/>
+    <mergeCell ref="B1849:B1850"/>
+    <mergeCell ref="B1851:B1852"/>
+    <mergeCell ref="B1817:B1818"/>
+    <mergeCell ref="B1819:B1820"/>
+    <mergeCell ref="B1821:B1822"/>
+    <mergeCell ref="B1823:B1824"/>
+    <mergeCell ref="B1825:B1826"/>
+    <mergeCell ref="B1827:B1828"/>
+    <mergeCell ref="B1829:B1830"/>
+    <mergeCell ref="B1831:B1832"/>
+    <mergeCell ref="B1833:B1834"/>
+    <mergeCell ref="B1799:B1800"/>
+    <mergeCell ref="B1801:B1802"/>
+    <mergeCell ref="B1803:B1804"/>
+    <mergeCell ref="B1805:B1806"/>
+    <mergeCell ref="B1807:B1808"/>
+    <mergeCell ref="B1809:B1810"/>
+    <mergeCell ref="B1811:B1812"/>
+    <mergeCell ref="B1813:B1814"/>
+    <mergeCell ref="B1815:B1816"/>
+    <mergeCell ref="B1781:B1782"/>
+    <mergeCell ref="B1783:B1784"/>
+    <mergeCell ref="B1785:B1786"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B1789:B1790"/>
+    <mergeCell ref="B1791:B1792"/>
+    <mergeCell ref="B1793:B1794"/>
+    <mergeCell ref="B1795:B1796"/>
+    <mergeCell ref="B1797:B1798"/>
+    <mergeCell ref="B1763:B1764"/>
+    <mergeCell ref="B1765:B1766"/>
+    <mergeCell ref="B1767:B1768"/>
+    <mergeCell ref="B1769:B1770"/>
+    <mergeCell ref="B1771:B1772"/>
+    <mergeCell ref="B1773:B1774"/>
+    <mergeCell ref="B1775:B1776"/>
+    <mergeCell ref="B1777:B1778"/>
+    <mergeCell ref="B1779:B1780"/>
+    <mergeCell ref="B1745:B1746"/>
+    <mergeCell ref="B1747:B1748"/>
+    <mergeCell ref="B1749:B1750"/>
+    <mergeCell ref="B1751:B1752"/>
+    <mergeCell ref="B1753:B1754"/>
+    <mergeCell ref="B1755:B1756"/>
+    <mergeCell ref="B1757:B1758"/>
+    <mergeCell ref="B1759:B1760"/>
+    <mergeCell ref="B1761:B1762"/>
+    <mergeCell ref="B1727:B1728"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="B1731:B1732"/>
+    <mergeCell ref="B1733:B1734"/>
+    <mergeCell ref="B1735:B1736"/>
+    <mergeCell ref="B1737:B1738"/>
+    <mergeCell ref="B1739:B1740"/>
+    <mergeCell ref="B1741:B1742"/>
+    <mergeCell ref="B1743:B1744"/>
+    <mergeCell ref="B1709:B1710"/>
+    <mergeCell ref="B1711:B1712"/>
+    <mergeCell ref="B1713:B1714"/>
+    <mergeCell ref="B1715:B1716"/>
+    <mergeCell ref="B1717:B1718"/>
+    <mergeCell ref="B1719:B1720"/>
+    <mergeCell ref="B1721:B1722"/>
+    <mergeCell ref="B1723:B1724"/>
+    <mergeCell ref="B1725:B1726"/>
+    <mergeCell ref="B1691:B1692"/>
+    <mergeCell ref="B1693:B1694"/>
+    <mergeCell ref="B1695:B1696"/>
+    <mergeCell ref="B1697:B1698"/>
+    <mergeCell ref="B1699:B1700"/>
+    <mergeCell ref="B1701:B1702"/>
+    <mergeCell ref="B1703:B1704"/>
+    <mergeCell ref="B1705:B1706"/>
+    <mergeCell ref="B1707:B1708"/>
+    <mergeCell ref="B1673:B1674"/>
+    <mergeCell ref="B1675:B1676"/>
+    <mergeCell ref="B1677:B1678"/>
+    <mergeCell ref="B1679:B1680"/>
+    <mergeCell ref="B1681:B1682"/>
+    <mergeCell ref="B1683:B1684"/>
+    <mergeCell ref="B1685:B1686"/>
+    <mergeCell ref="B1687:B1688"/>
+    <mergeCell ref="B1689:B1690"/>
+    <mergeCell ref="B1655:B1656"/>
+    <mergeCell ref="B1657:B1658"/>
+    <mergeCell ref="B1659:B1660"/>
+    <mergeCell ref="B1661:B1662"/>
+    <mergeCell ref="B1663:B1664"/>
+    <mergeCell ref="B1665:B1666"/>
+    <mergeCell ref="B1667:B1668"/>
+    <mergeCell ref="B1669:B1670"/>
+    <mergeCell ref="B1671:B1672"/>
+    <mergeCell ref="B1637:B1638"/>
+    <mergeCell ref="B1639:B1640"/>
+    <mergeCell ref="B1641:B1642"/>
+    <mergeCell ref="B1643:B1644"/>
+    <mergeCell ref="B1645:B1646"/>
+    <mergeCell ref="B1647:B1648"/>
+    <mergeCell ref="B1649:B1650"/>
+    <mergeCell ref="B1651:B1652"/>
+    <mergeCell ref="B1653:B1654"/>
+    <mergeCell ref="B1619:B1620"/>
+    <mergeCell ref="B1621:B1622"/>
+    <mergeCell ref="B1623:B1624"/>
+    <mergeCell ref="B1625:B1626"/>
+    <mergeCell ref="B1627:B1628"/>
+    <mergeCell ref="B1629:B1630"/>
+    <mergeCell ref="B1631:B1632"/>
+    <mergeCell ref="B1633:B1634"/>
+    <mergeCell ref="B1635:B1636"/>
+    <mergeCell ref="B1601:B1602"/>
+    <mergeCell ref="B1603:B1604"/>
+    <mergeCell ref="B1605:B1606"/>
+    <mergeCell ref="B1607:B1608"/>
+    <mergeCell ref="B1609:B1610"/>
+    <mergeCell ref="B1611:B1612"/>
+    <mergeCell ref="B1613:B1614"/>
+    <mergeCell ref="B1615:B1616"/>
+    <mergeCell ref="B1617:B1618"/>
+    <mergeCell ref="B1583:B1584"/>
+    <mergeCell ref="B1585:B1586"/>
+    <mergeCell ref="B1587:B1588"/>
+    <mergeCell ref="B1589:B1590"/>
+    <mergeCell ref="B1591:B1592"/>
+    <mergeCell ref="B1593:B1594"/>
+    <mergeCell ref="B1595:B1596"/>
+    <mergeCell ref="B1597:B1598"/>
+    <mergeCell ref="B1599:B1600"/>
+    <mergeCell ref="B1565:B1566"/>
+    <mergeCell ref="B1567:B1568"/>
+    <mergeCell ref="B1569:B1570"/>
+    <mergeCell ref="B1571:B1572"/>
+    <mergeCell ref="B1573:B1574"/>
+    <mergeCell ref="B1575:B1576"/>
+    <mergeCell ref="B1577:B1578"/>
+    <mergeCell ref="B1579:B1580"/>
+    <mergeCell ref="B1581:B1582"/>
+    <mergeCell ref="B1547:B1548"/>
+    <mergeCell ref="B1549:B1550"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B1553:B1554"/>
+    <mergeCell ref="B1555:B1556"/>
+    <mergeCell ref="B1557:B1558"/>
+    <mergeCell ref="B1559:B1560"/>
+    <mergeCell ref="B1561:B1562"/>
+    <mergeCell ref="B1563:B1564"/>
+    <mergeCell ref="B1529:B1530"/>
+    <mergeCell ref="B1531:B1532"/>
+    <mergeCell ref="B1533:B1534"/>
+    <mergeCell ref="B1535:B1536"/>
+    <mergeCell ref="B1537:B1538"/>
+    <mergeCell ref="B1539:B1540"/>
+    <mergeCell ref="B1541:B1542"/>
+    <mergeCell ref="B1543:B1544"/>
+    <mergeCell ref="B1545:B1546"/>
+    <mergeCell ref="B1511:B1512"/>
+    <mergeCell ref="B1513:B1514"/>
+    <mergeCell ref="B1515:B1516"/>
+    <mergeCell ref="B1517:B1518"/>
+    <mergeCell ref="B1519:B1520"/>
+    <mergeCell ref="B1521:B1522"/>
+    <mergeCell ref="B1523:B1524"/>
+    <mergeCell ref="B1525:B1526"/>
+    <mergeCell ref="B1527:B1528"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1495:B1496"/>
+    <mergeCell ref="B1497:B1498"/>
+    <mergeCell ref="B1499:B1500"/>
+    <mergeCell ref="B1501:B1502"/>
+    <mergeCell ref="B1503:B1504"/>
+    <mergeCell ref="B1505:B1506"/>
+    <mergeCell ref="B1507:B1508"/>
+    <mergeCell ref="B1509:B1510"/>
+    <mergeCell ref="B1475:B1476"/>
+    <mergeCell ref="B1477:B1478"/>
+    <mergeCell ref="B1479:B1480"/>
+    <mergeCell ref="B1481:B1482"/>
+    <mergeCell ref="B1483:B1484"/>
+    <mergeCell ref="B1485:B1486"/>
+    <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="B1489:B1490"/>
+    <mergeCell ref="B1491:B1492"/>
+    <mergeCell ref="B1457:B1458"/>
+    <mergeCell ref="B1459:B1460"/>
+    <mergeCell ref="B1461:B1462"/>
+    <mergeCell ref="B1463:B1464"/>
+    <mergeCell ref="B1465:B1466"/>
+    <mergeCell ref="B1467:B1468"/>
+    <mergeCell ref="B1469:B1470"/>
+    <mergeCell ref="B1471:B1472"/>
+    <mergeCell ref="B1473:B1474"/>
+    <mergeCell ref="B1439:B1440"/>
+    <mergeCell ref="B1441:B1442"/>
+    <mergeCell ref="B1443:B1444"/>
+    <mergeCell ref="B1445:B1446"/>
+    <mergeCell ref="B1447:B1448"/>
+    <mergeCell ref="B1449:B1450"/>
+    <mergeCell ref="B1451:B1452"/>
+    <mergeCell ref="B1453:B1454"/>
+    <mergeCell ref="B1455:B1456"/>
+    <mergeCell ref="B1421:B1422"/>
+    <mergeCell ref="B1423:B1424"/>
+    <mergeCell ref="B1425:B1426"/>
+    <mergeCell ref="B1427:B1428"/>
+    <mergeCell ref="B1429:B1430"/>
+    <mergeCell ref="B1431:B1432"/>
+    <mergeCell ref="B1433:B1434"/>
+    <mergeCell ref="B1435:B1436"/>
+    <mergeCell ref="B1437:B1438"/>
+    <mergeCell ref="B1403:B1404"/>
+    <mergeCell ref="B1405:B1406"/>
+    <mergeCell ref="B1407:B1408"/>
+    <mergeCell ref="B1409:B1410"/>
+    <mergeCell ref="B1411:B1412"/>
+    <mergeCell ref="B1413:B1414"/>
+    <mergeCell ref="B1415:B1416"/>
+    <mergeCell ref="B1417:B1418"/>
+    <mergeCell ref="B1419:B1420"/>
+    <mergeCell ref="B1385:B1386"/>
+    <mergeCell ref="B1387:B1388"/>
+    <mergeCell ref="B1389:B1390"/>
+    <mergeCell ref="B1391:B1392"/>
+    <mergeCell ref="B1393:B1394"/>
+    <mergeCell ref="B1395:B1396"/>
+    <mergeCell ref="B1397:B1398"/>
+    <mergeCell ref="B1399:B1400"/>
+    <mergeCell ref="B1401:B1402"/>
+    <mergeCell ref="B1367:B1368"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1371:B1372"/>
+    <mergeCell ref="B1373:B1374"/>
+    <mergeCell ref="B1375:B1376"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B1379:B1380"/>
+    <mergeCell ref="B1381:B1382"/>
+    <mergeCell ref="B1383:B1384"/>
+    <mergeCell ref="B1349:B1350"/>
+    <mergeCell ref="B1351:B1352"/>
+    <mergeCell ref="B1353:B1354"/>
+    <mergeCell ref="B1355:B1356"/>
+    <mergeCell ref="B1357:B1358"/>
+    <mergeCell ref="B1359:B1360"/>
+    <mergeCell ref="B1361:B1362"/>
+    <mergeCell ref="B1363:B1364"/>
+    <mergeCell ref="B1365:B1366"/>
+    <mergeCell ref="B1331:B1332"/>
+    <mergeCell ref="B1333:B1334"/>
+    <mergeCell ref="B1335:B1336"/>
+    <mergeCell ref="B1337:B1338"/>
+    <mergeCell ref="B1339:B1340"/>
+    <mergeCell ref="B1341:B1342"/>
+    <mergeCell ref="B1343:B1344"/>
+    <mergeCell ref="B1345:B1346"/>
+    <mergeCell ref="B1347:B1348"/>
+    <mergeCell ref="B1313:B1314"/>
+    <mergeCell ref="B1315:B1316"/>
+    <mergeCell ref="B1317:B1318"/>
+    <mergeCell ref="B1319:B1320"/>
+    <mergeCell ref="B1321:B1322"/>
+    <mergeCell ref="B1323:B1324"/>
+    <mergeCell ref="B1325:B1326"/>
+    <mergeCell ref="B1327:B1328"/>
+    <mergeCell ref="B1329:B1330"/>
+    <mergeCell ref="B1295:B1296"/>
+    <mergeCell ref="B1297:B1298"/>
+    <mergeCell ref="B1299:B1300"/>
+    <mergeCell ref="B1301:B1302"/>
+    <mergeCell ref="B1303:B1304"/>
+    <mergeCell ref="B1305:B1306"/>
+    <mergeCell ref="B1307:B1308"/>
+    <mergeCell ref="B1309:B1310"/>
+    <mergeCell ref="B1311:B1312"/>
+    <mergeCell ref="B1277:B1278"/>
+    <mergeCell ref="B1279:B1280"/>
+    <mergeCell ref="B1281:B1282"/>
+    <mergeCell ref="B1283:B1284"/>
+    <mergeCell ref="B1285:B1286"/>
+    <mergeCell ref="B1287:B1288"/>
+    <mergeCell ref="B1289:B1290"/>
+    <mergeCell ref="B1291:B1292"/>
+    <mergeCell ref="B1293:B1294"/>
+    <mergeCell ref="B1259:B1260"/>
+    <mergeCell ref="B1261:B1262"/>
+    <mergeCell ref="B1263:B1264"/>
+    <mergeCell ref="B1265:B1266"/>
+    <mergeCell ref="B1267:B1268"/>
+    <mergeCell ref="B1269:B1270"/>
+    <mergeCell ref="B1271:B1272"/>
+    <mergeCell ref="B1273:B1274"/>
+    <mergeCell ref="B1275:B1276"/>
+    <mergeCell ref="B1241:B1242"/>
+    <mergeCell ref="B1243:B1244"/>
+    <mergeCell ref="B1245:B1246"/>
+    <mergeCell ref="B1247:B1248"/>
+    <mergeCell ref="B1249:B1250"/>
+    <mergeCell ref="B1251:B1252"/>
+    <mergeCell ref="B1253:B1254"/>
+    <mergeCell ref="B1255:B1256"/>
+    <mergeCell ref="B1257:B1258"/>
+    <mergeCell ref="B1223:B1224"/>
+    <mergeCell ref="B1225:B1226"/>
+    <mergeCell ref="B1227:B1228"/>
+    <mergeCell ref="B1229:B1230"/>
+    <mergeCell ref="B1231:B1232"/>
+    <mergeCell ref="B1233:B1234"/>
+    <mergeCell ref="B1235:B1236"/>
+    <mergeCell ref="B1237:B1238"/>
+    <mergeCell ref="B1239:B1240"/>
+    <mergeCell ref="B1205:B1206"/>
+    <mergeCell ref="B1207:B1208"/>
+    <mergeCell ref="B1209:B1210"/>
+    <mergeCell ref="B1211:B1212"/>
+    <mergeCell ref="B1213:B1214"/>
+    <mergeCell ref="B1215:B1216"/>
+    <mergeCell ref="B1217:B1218"/>
+    <mergeCell ref="B1219:B1220"/>
+    <mergeCell ref="B1221:B1222"/>
+    <mergeCell ref="B1187:B1188"/>
+    <mergeCell ref="B1189:B1190"/>
+    <mergeCell ref="B1191:B1192"/>
+    <mergeCell ref="B1193:B1194"/>
+    <mergeCell ref="B1195:B1196"/>
+    <mergeCell ref="B1197:B1198"/>
+    <mergeCell ref="B1199:B1200"/>
+    <mergeCell ref="B1201:B1202"/>
+    <mergeCell ref="B1203:B1204"/>
+    <mergeCell ref="B1169:B1170"/>
+    <mergeCell ref="B1171:B1172"/>
+    <mergeCell ref="B1173:B1174"/>
+    <mergeCell ref="B1175:B1176"/>
+    <mergeCell ref="B1177:B1178"/>
+    <mergeCell ref="B1179:B1180"/>
+    <mergeCell ref="B1181:B1182"/>
+    <mergeCell ref="B1183:B1184"/>
+    <mergeCell ref="B1185:B1186"/>
+    <mergeCell ref="B1151:B1152"/>
+    <mergeCell ref="B1153:B1154"/>
+    <mergeCell ref="B1155:B1156"/>
+    <mergeCell ref="B1157:B1158"/>
+    <mergeCell ref="B1159:B1160"/>
+    <mergeCell ref="B1161:B1162"/>
+    <mergeCell ref="B1163:B1164"/>
+    <mergeCell ref="B1165:B1166"/>
+    <mergeCell ref="B1167:B1168"/>
+    <mergeCell ref="B1133:B1134"/>
+    <mergeCell ref="B1135:B1136"/>
+    <mergeCell ref="B1137:B1138"/>
+    <mergeCell ref="B1139:B1140"/>
+    <mergeCell ref="B1141:B1142"/>
+    <mergeCell ref="B1143:B1144"/>
+    <mergeCell ref="B1145:B1146"/>
+    <mergeCell ref="B1147:B1148"/>
+    <mergeCell ref="B1149:B1150"/>
+    <mergeCell ref="B1115:B1116"/>
+    <mergeCell ref="B1117:B1118"/>
+    <mergeCell ref="B1119:B1120"/>
+    <mergeCell ref="B1121:B1122"/>
+    <mergeCell ref="B1123:B1124"/>
+    <mergeCell ref="B1125:B1126"/>
+    <mergeCell ref="B1127:B1128"/>
+    <mergeCell ref="B1129:B1130"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="B1097:B1098"/>
+    <mergeCell ref="B1099:B1100"/>
+    <mergeCell ref="B1101:B1102"/>
+    <mergeCell ref="B1103:B1104"/>
+    <mergeCell ref="B1105:B1106"/>
+    <mergeCell ref="B1107:B1108"/>
+    <mergeCell ref="B1109:B1110"/>
+    <mergeCell ref="B1111:B1112"/>
+    <mergeCell ref="B1113:B1114"/>
+    <mergeCell ref="B1079:B1080"/>
+    <mergeCell ref="B1081:B1082"/>
+    <mergeCell ref="B1083:B1084"/>
+    <mergeCell ref="B1085:B1086"/>
+    <mergeCell ref="B1087:B1088"/>
+    <mergeCell ref="B1089:B1090"/>
+    <mergeCell ref="B1091:B1092"/>
+    <mergeCell ref="B1093:B1094"/>
+    <mergeCell ref="B1095:B1096"/>
+    <mergeCell ref="B943:B955"/>
+    <mergeCell ref="B956:B963"/>
+    <mergeCell ref="B964:B971"/>
+    <mergeCell ref="B972:B979"/>
+    <mergeCell ref="B980:B984"/>
+    <mergeCell ref="B985:B990"/>
+    <mergeCell ref="B991:B1041"/>
+    <mergeCell ref="B1042:B1076"/>
+    <mergeCell ref="B1077:B1078"/>
+    <mergeCell ref="B893:B895"/>
+    <mergeCell ref="B896:B901"/>
+    <mergeCell ref="B902:B905"/>
+    <mergeCell ref="B906:B909"/>
+    <mergeCell ref="B910:B916"/>
+    <mergeCell ref="B917:B925"/>
+    <mergeCell ref="B926:B929"/>
+    <mergeCell ref="B930:B935"/>
+    <mergeCell ref="B936:B942"/>
+    <mergeCell ref="B856:B860"/>
+    <mergeCell ref="B861:B864"/>
+    <mergeCell ref="B865:B870"/>
+    <mergeCell ref="B871:B874"/>
+    <mergeCell ref="B875:B879"/>
+    <mergeCell ref="B880:B882"/>
+    <mergeCell ref="B883:B885"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="B888:B892"/>
+    <mergeCell ref="B813:B815"/>
+    <mergeCell ref="B816:B820"/>
+    <mergeCell ref="B821:B825"/>
+    <mergeCell ref="B826:B830"/>
+    <mergeCell ref="B831:B835"/>
+    <mergeCell ref="B836:B843"/>
+    <mergeCell ref="B844:B846"/>
+    <mergeCell ref="B847:B852"/>
+    <mergeCell ref="B853:B855"/>
+    <mergeCell ref="B786:B788"/>
+    <mergeCell ref="B789:B791"/>
+    <mergeCell ref="B792:B794"/>
+    <mergeCell ref="B795:B797"/>
+    <mergeCell ref="B798:B800"/>
+    <mergeCell ref="B801:B803"/>
+    <mergeCell ref="B804:B806"/>
+    <mergeCell ref="B807:B809"/>
+    <mergeCell ref="B810:B812"/>
+    <mergeCell ref="B745:B746"/>
+    <mergeCell ref="B747:B750"/>
+    <mergeCell ref="B751:B755"/>
+    <mergeCell ref="B756:B761"/>
+    <mergeCell ref="B762:B767"/>
+    <mergeCell ref="B768:B776"/>
+    <mergeCell ref="B777:B779"/>
+    <mergeCell ref="B780:B782"/>
+    <mergeCell ref="B783:B785"/>
+    <mergeCell ref="B659:B665"/>
+    <mergeCell ref="B666:B670"/>
+    <mergeCell ref="B671:B675"/>
+    <mergeCell ref="B676:B680"/>
+    <mergeCell ref="B681:B685"/>
+    <mergeCell ref="B686:B691"/>
+    <mergeCell ref="B692:B698"/>
+    <mergeCell ref="B699:B712"/>
+    <mergeCell ref="B713:B744"/>
+    <mergeCell ref="B583:B585"/>
+    <mergeCell ref="B586:B588"/>
+    <mergeCell ref="B589:B591"/>
+    <mergeCell ref="B592:B605"/>
+    <mergeCell ref="B606:B637"/>
+    <mergeCell ref="B638:B641"/>
+    <mergeCell ref="B642:B646"/>
+    <mergeCell ref="B647:B651"/>
+    <mergeCell ref="B652:B658"/>
+    <mergeCell ref="B541:B546"/>
+    <mergeCell ref="B547:B552"/>
+    <mergeCell ref="B553:B558"/>
+    <mergeCell ref="B559:B564"/>
+    <mergeCell ref="B565:B568"/>
+    <mergeCell ref="B569:B571"/>
+    <mergeCell ref="B572:B575"/>
+    <mergeCell ref="B576:B579"/>
+    <mergeCell ref="B580:B582"/>
+    <mergeCell ref="B487:B492"/>
+    <mergeCell ref="B493:B498"/>
+    <mergeCell ref="B499:B504"/>
+    <mergeCell ref="B505:B510"/>
+    <mergeCell ref="B511:B516"/>
+    <mergeCell ref="B517:B522"/>
+    <mergeCell ref="B523:B528"/>
+    <mergeCell ref="B529:B534"/>
+    <mergeCell ref="B535:B540"/>
+    <mergeCell ref="B431:B436"/>
+    <mergeCell ref="B437:B442"/>
+    <mergeCell ref="B443:B450"/>
+    <mergeCell ref="B451:B456"/>
+    <mergeCell ref="B457:B462"/>
+    <mergeCell ref="B463:B468"/>
+    <mergeCell ref="B469:B474"/>
+    <mergeCell ref="B475:B480"/>
+    <mergeCell ref="B481:B486"/>
+    <mergeCell ref="B393:B399"/>
+    <mergeCell ref="B400:B404"/>
+    <mergeCell ref="B405:B407"/>
+    <mergeCell ref="B408:B410"/>
+    <mergeCell ref="B411:B415"/>
+    <mergeCell ref="B416:B418"/>
+    <mergeCell ref="B419:B421"/>
+    <mergeCell ref="B422:B424"/>
+    <mergeCell ref="B425:B430"/>
+    <mergeCell ref="B347:B351"/>
+    <mergeCell ref="B352:B355"/>
+    <mergeCell ref="B356:B359"/>
+    <mergeCell ref="B360:B363"/>
+    <mergeCell ref="B364:B367"/>
+    <mergeCell ref="B368:B371"/>
+    <mergeCell ref="B372:B378"/>
+    <mergeCell ref="B379:B385"/>
+    <mergeCell ref="B386:B392"/>
+    <mergeCell ref="B115:B200"/>
+    <mergeCell ref="B201:B253"/>
+    <mergeCell ref="B254:B269"/>
+    <mergeCell ref="B270:B287"/>
+    <mergeCell ref="B288:B301"/>
+    <mergeCell ref="B302:B333"/>
+    <mergeCell ref="B334:B337"/>
+    <mergeCell ref="B338:B341"/>
+    <mergeCell ref="B342:B346"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B109:B114"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/2023-24 RLS Codebook.xlsx
+++ b/2023-24 RLS Codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhil2\OneDrive\Documents\GitHub\Religion_data_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C202AD16-7DA5-4B59-A391-DF87DA53F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D79865C-5462-4D96-B31D-154CCA373A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7127,16 +7127,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7762,7 +7762,7 @@
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="3">
@@ -7776,7 +7776,7 @@
       <c r="A27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="10"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="2">
         <v>2</v>
       </c>
@@ -7788,7 +7788,7 @@
       <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="10"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="2">
         <v>3</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="A29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="10"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="2">
         <v>99</v>
       </c>
@@ -7812,7 +7812,7 @@
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C30" s="3">
@@ -7826,7 +7826,7 @@
       <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="2">
         <v>2</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="A32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="10"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="2">
         <v>3</v>
       </c>
@@ -7850,7 +7850,7 @@
       <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="10"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="2">
         <v>99</v>
       </c>
@@ -7862,7 +7862,7 @@
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="3">
@@ -7876,7 +7876,7 @@
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="10"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="2">
         <v>2</v>
       </c>
@@ -7888,7 +7888,7 @@
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="2">
         <v>3</v>
       </c>
@@ -7900,7 +7900,7 @@
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="10"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="2">
         <v>99</v>
       </c>
@@ -7912,7 +7912,7 @@
       <c r="A38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="3">
@@ -7926,7 +7926,7 @@
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="10"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="2">
         <v>2</v>
       </c>
@@ -7938,7 +7938,7 @@
       <c r="A40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="10"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="2">
         <v>3</v>
       </c>
@@ -7950,7 +7950,7 @@
       <c r="A41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="10"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="2">
         <v>99</v>
       </c>
@@ -7962,7 +7962,7 @@
       <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C42" s="3">
@@ -7976,7 +7976,7 @@
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="10"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="2">
         <v>2</v>
       </c>
@@ -7988,7 +7988,7 @@
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="10"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="2">
         <v>3</v>
       </c>
@@ -8000,7 +8000,7 @@
       <c r="A45" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="10"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="2">
         <v>99</v>
       </c>
@@ -8012,7 +8012,7 @@
       <c r="A46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C46" s="3">
@@ -8026,7 +8026,7 @@
       <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="10"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="2">
         <v>2</v>
       </c>
@@ -8038,7 +8038,7 @@
       <c r="A48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="10"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="2">
         <v>99</v>
       </c>
@@ -8050,7 +8050,7 @@
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="3">
@@ -8064,7 +8064,7 @@
       <c r="A50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="10"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="2">
         <v>2</v>
       </c>
@@ -8076,7 +8076,7 @@
       <c r="A51" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="10"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="2">
         <v>99</v>
       </c>
@@ -8088,7 +8088,7 @@
       <c r="A52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="3">
@@ -8102,7 +8102,7 @@
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="10"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="2">
         <v>2</v>
       </c>
@@ -8114,7 +8114,7 @@
       <c r="A54" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="10"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="2">
         <v>99</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="A55" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C55" s="3">
@@ -8140,7 +8140,7 @@
       <c r="A56" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="10"/>
+      <c r="B56" s="8"/>
       <c r="C56" s="2">
         <v>2</v>
       </c>
@@ -8152,7 +8152,7 @@
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="10"/>
+      <c r="B57" s="8"/>
       <c r="C57" s="2">
         <v>99</v>
       </c>
@@ -8164,7 +8164,7 @@
       <c r="A58" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="3">
@@ -8178,7 +8178,7 @@
       <c r="A59" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="10"/>
+      <c r="B59" s="8"/>
       <c r="C59" s="2">
         <v>2</v>
       </c>
@@ -8190,7 +8190,7 @@
       <c r="A60" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="10"/>
+      <c r="B60" s="8"/>
       <c r="C60" s="2">
         <v>3</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="A61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="10"/>
+      <c r="B61" s="8"/>
       <c r="C61" s="2">
         <v>99</v>
       </c>
@@ -8214,7 +8214,7 @@
       <c r="A62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="3">
@@ -8228,7 +8228,7 @@
       <c r="A63" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="10"/>
+      <c r="B63" s="8"/>
       <c r="C63" s="2">
         <v>2</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="A64" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="10"/>
+      <c r="B64" s="8"/>
       <c r="C64" s="2">
         <v>99</v>
       </c>
@@ -8252,7 +8252,7 @@
       <c r="A65" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C65" s="3">
@@ -8266,7 +8266,7 @@
       <c r="A66" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="10"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="2">
         <v>2</v>
       </c>
@@ -8278,7 +8278,7 @@
       <c r="A67" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B67" s="10"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="2">
         <v>3</v>
       </c>
@@ -8290,7 +8290,7 @@
       <c r="A68" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="10"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="2">
         <v>4</v>
       </c>
@@ -8302,7 +8302,7 @@
       <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="10"/>
+      <c r="B69" s="8"/>
       <c r="C69" s="2">
         <v>99</v>
       </c>
@@ -8314,7 +8314,7 @@
       <c r="A70" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C70" s="3">
@@ -8328,7 +8328,7 @@
       <c r="A71" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="10"/>
+      <c r="B71" s="8"/>
       <c r="C71" s="2">
         <v>2</v>
       </c>
@@ -8340,7 +8340,7 @@
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="10"/>
+      <c r="B72" s="8"/>
       <c r="C72" s="2">
         <v>3</v>
       </c>
@@ -8352,7 +8352,7 @@
       <c r="A73" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="10"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="2">
         <v>4</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="A74" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="10"/>
+      <c r="B74" s="8"/>
       <c r="C74" s="2">
         <v>99</v>
       </c>
@@ -8376,7 +8376,7 @@
       <c r="A75" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C75" s="3">
@@ -8390,7 +8390,7 @@
       <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B76" s="10"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="2">
         <v>2</v>
       </c>
@@ -8402,7 +8402,7 @@
       <c r="A77" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="2">
         <v>99</v>
       </c>
@@ -8576,7 +8576,7 @@
       <c r="A91" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C91" s="3">
@@ -8590,7 +8590,7 @@
       <c r="A92" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B92" s="10"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="2">
         <v>2</v>
       </c>
@@ -8602,7 +8602,7 @@
       <c r="A93" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B93" s="10"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="2">
         <v>3</v>
       </c>
@@ -8614,7 +8614,7 @@
       <c r="A94" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="10"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="2">
         <v>4</v>
       </c>
@@ -8626,7 +8626,7 @@
       <c r="A95" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B95" s="10"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="2">
         <v>5</v>
       </c>
@@ -8638,7 +8638,7 @@
       <c r="A96" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B96" s="10"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="2">
         <v>99</v>
       </c>
@@ -8650,7 +8650,7 @@
       <c r="A97" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>113</v>
       </c>
       <c r="C97" s="3">
@@ -8664,7 +8664,7 @@
       <c r="A98" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B98" s="10"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="2">
         <v>2</v>
       </c>
@@ -8676,7 +8676,7 @@
       <c r="A99" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B99" s="10"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="2">
         <v>3</v>
       </c>
@@ -8688,7 +8688,7 @@
       <c r="A100" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B100" s="10"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="2">
         <v>4</v>
       </c>
@@ -8700,7 +8700,7 @@
       <c r="A101" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B101" s="10"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="2">
         <v>5</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="A102" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B102" s="10"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="2">
         <v>99</v>
       </c>
@@ -8724,7 +8724,7 @@
       <c r="A103" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>115</v>
       </c>
       <c r="C103" s="3">
@@ -8738,7 +8738,7 @@
       <c r="A104" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B104" s="10"/>
+      <c r="B104" s="8"/>
       <c r="C104" s="2">
         <v>2</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="A105" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B105" s="10"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="2">
         <v>3</v>
       </c>
@@ -8762,7 +8762,7 @@
       <c r="A106" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="10"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="2">
         <v>4</v>
       </c>
@@ -8774,7 +8774,7 @@
       <c r="A107" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B107" s="10"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="2">
         <v>5</v>
       </c>
@@ -8786,7 +8786,7 @@
       <c r="A108" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="10"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="2">
         <v>99</v>
       </c>
@@ -8798,7 +8798,7 @@
       <c r="A109" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="7" t="s">
         <v>117</v>
       </c>
       <c r="C109" s="3">
@@ -8812,7 +8812,7 @@
       <c r="A110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="10"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="2">
         <v>2</v>
       </c>
@@ -8824,7 +8824,7 @@
       <c r="A111" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="10"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="2">
         <v>3</v>
       </c>
@@ -8836,7 +8836,7 @@
       <c r="A112" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="10"/>
+      <c r="B112" s="8"/>
       <c r="C112" s="2">
         <v>4</v>
       </c>
@@ -8848,7 +8848,7 @@
       <c r="A113" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B113" s="10"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="2">
         <v>5</v>
       </c>
@@ -8860,7 +8860,7 @@
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="10"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="2">
         <v>99</v>
       </c>
@@ -10544,7 +10544,7 @@
       <c r="A254" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="7" t="s">
         <v>258</v>
       </c>
       <c r="C254" s="3">
@@ -10558,7 +10558,7 @@
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B255" s="10"/>
+      <c r="B255" s="8"/>
       <c r="C255" s="2">
         <v>1200</v>
       </c>
@@ -10570,7 +10570,7 @@
       <c r="A256" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B256" s="10"/>
+      <c r="B256" s="8"/>
       <c r="C256" s="2">
         <v>1300</v>
       </c>
@@ -10582,7 +10582,7 @@
       <c r="A257" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B257" s="10"/>
+      <c r="B257" s="8"/>
       <c r="C257" s="2">
         <v>10000</v>
       </c>
@@ -10594,7 +10594,7 @@
       <c r="A258" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B258" s="10"/>
+      <c r="B258" s="8"/>
       <c r="C258" s="2">
         <v>20000</v>
       </c>
@@ -10606,7 +10606,7 @@
       <c r="A259" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B259" s="10"/>
+      <c r="B259" s="8"/>
       <c r="C259" s="2">
         <v>30000</v>
       </c>
@@ -10618,7 +10618,7 @@
       <c r="A260" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B260" s="10"/>
+      <c r="B260" s="8"/>
       <c r="C260" s="2">
         <v>40001</v>
       </c>
@@ -10630,7 +10630,7 @@
       <c r="A261" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B261" s="10"/>
+      <c r="B261" s="8"/>
       <c r="C261" s="2">
         <v>40002</v>
       </c>
@@ -10642,7 +10642,7 @@
       <c r="A262" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B262" s="10"/>
+      <c r="B262" s="8"/>
       <c r="C262" s="2">
         <v>50000</v>
       </c>
@@ -10654,7 +10654,7 @@
       <c r="A263" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B263" s="10"/>
+      <c r="B263" s="8"/>
       <c r="C263" s="2">
         <v>60000</v>
       </c>
@@ -10666,7 +10666,7 @@
       <c r="A264" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B264" s="10"/>
+      <c r="B264" s="8"/>
       <c r="C264" s="2">
         <v>70000</v>
       </c>
@@ -10678,7 +10678,7 @@
       <c r="A265" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B265" s="10"/>
+      <c r="B265" s="8"/>
       <c r="C265" s="2">
         <v>80000</v>
       </c>
@@ -10690,7 +10690,7 @@
       <c r="A266" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B266" s="10"/>
+      <c r="B266" s="8"/>
       <c r="C266" s="2">
         <v>90001</v>
       </c>
@@ -10702,7 +10702,7 @@
       <c r="A267" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B267" s="10"/>
+      <c r="B267" s="8"/>
       <c r="C267" s="2">
         <v>90002</v>
       </c>
@@ -10714,7 +10714,7 @@
       <c r="A268" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B268" s="10"/>
+      <c r="B268" s="8"/>
       <c r="C268" s="2">
         <v>100000</v>
       </c>
@@ -10726,7 +10726,7 @@
       <c r="A269" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B269" s="10"/>
+      <c r="B269" s="8"/>
       <c r="C269" s="2">
         <v>900000</v>
       </c>
@@ -10956,7 +10956,7 @@
       <c r="A288" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="7" t="s">
         <v>287</v>
       </c>
       <c r="C288" s="3">
@@ -10970,7 +10970,7 @@
       <c r="A289" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B289" s="10"/>
+      <c r="B289" s="8"/>
       <c r="C289" s="2">
         <v>10000</v>
       </c>
@@ -10982,7 +10982,7 @@
       <c r="A290" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B290" s="10"/>
+      <c r="B290" s="8"/>
       <c r="C290" s="2">
         <v>20000</v>
       </c>
@@ -10994,7 +10994,7 @@
       <c r="A291" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B291" s="10"/>
+      <c r="B291" s="8"/>
       <c r="C291" s="2">
         <v>30000</v>
       </c>
@@ -11006,7 +11006,7 @@
       <c r="A292" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B292" s="10"/>
+      <c r="B292" s="8"/>
       <c r="C292" s="2">
         <v>40001</v>
       </c>
@@ -11018,7 +11018,7 @@
       <c r="A293" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B293" s="10"/>
+      <c r="B293" s="8"/>
       <c r="C293" s="2">
         <v>40002</v>
       </c>
@@ -11030,7 +11030,7 @@
       <c r="A294" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B294" s="10"/>
+      <c r="B294" s="8"/>
       <c r="C294" s="2">
         <v>50000</v>
       </c>
@@ -11042,7 +11042,7 @@
       <c r="A295" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B295" s="10"/>
+      <c r="B295" s="8"/>
       <c r="C295" s="2">
         <v>60000</v>
       </c>
@@ -11054,7 +11054,7 @@
       <c r="A296" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B296" s="10"/>
+      <c r="B296" s="8"/>
       <c r="C296" s="2">
         <v>70000</v>
       </c>
@@ -11066,7 +11066,7 @@
       <c r="A297" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B297" s="10"/>
+      <c r="B297" s="8"/>
       <c r="C297" s="2">
         <v>80000</v>
       </c>
@@ -11078,7 +11078,7 @@
       <c r="A298" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B298" s="10"/>
+      <c r="B298" s="8"/>
       <c r="C298" s="2">
         <v>90001</v>
       </c>
@@ -11090,7 +11090,7 @@
       <c r="A299" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B299" s="10"/>
+      <c r="B299" s="8"/>
       <c r="C299" s="2">
         <v>90002</v>
       </c>
@@ -11102,7 +11102,7 @@
       <c r="A300" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B300" s="10"/>
+      <c r="B300" s="8"/>
       <c r="C300" s="2">
         <v>100000</v>
       </c>
@@ -11114,7 +11114,7 @@
       <c r="A301" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B301" s="10"/>
+      <c r="B301" s="8"/>
       <c r="C301" s="2">
         <v>900000</v>
       </c>
@@ -11612,7 +11612,7 @@
       <c r="A342" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B342" s="9" t="s">
+      <c r="B342" s="7" t="s">
         <v>304</v>
       </c>
       <c r="C342" s="3">
@@ -11626,7 +11626,7 @@
       <c r="A343" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B343" s="10"/>
+      <c r="B343" s="8"/>
       <c r="C343" s="2">
         <v>2</v>
       </c>
@@ -11638,7 +11638,7 @@
       <c r="A344" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B344" s="10"/>
+      <c r="B344" s="8"/>
       <c r="C344" s="2">
         <v>3</v>
       </c>
@@ -11650,7 +11650,7 @@
       <c r="A345" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B345" s="10"/>
+      <c r="B345" s="8"/>
       <c r="C345" s="2">
         <v>4</v>
       </c>
@@ -11662,7 +11662,7 @@
       <c r="A346" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B346" s="10"/>
+      <c r="B346" s="8"/>
       <c r="C346" s="2">
         <v>99</v>
       </c>
@@ -11674,7 +11674,7 @@
       <c r="A347" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B347" s="9" t="s">
+      <c r="B347" s="7" t="s">
         <v>310</v>
       </c>
       <c r="C347" s="3">
@@ -11688,7 +11688,7 @@
       <c r="A348" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B348" s="10"/>
+      <c r="B348" s="8"/>
       <c r="C348" s="2">
         <v>2</v>
       </c>
@@ -11700,7 +11700,7 @@
       <c r="A349" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B349" s="10"/>
+      <c r="B349" s="8"/>
       <c r="C349" s="2">
         <v>3</v>
       </c>
@@ -11712,7 +11712,7 @@
       <c r="A350" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B350" s="10"/>
+      <c r="B350" s="8"/>
       <c r="C350" s="2">
         <v>4</v>
       </c>
@@ -11724,7 +11724,7 @@
       <c r="A351" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B351" s="10"/>
+      <c r="B351" s="8"/>
       <c r="C351" s="2">
         <v>99</v>
       </c>
@@ -11986,7 +11986,7 @@
       <c r="A372" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B372" s="9" t="s">
+      <c r="B372" s="7" t="s">
         <v>333</v>
       </c>
       <c r="C372" s="3">
@@ -12000,7 +12000,7 @@
       <c r="A373" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B373" s="10"/>
+      <c r="B373" s="8"/>
       <c r="C373" s="2">
         <v>2</v>
       </c>
@@ -12012,7 +12012,7 @@
       <c r="A374" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B374" s="10"/>
+      <c r="B374" s="8"/>
       <c r="C374" s="2">
         <v>3</v>
       </c>
@@ -12024,7 +12024,7 @@
       <c r="A375" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B375" s="10"/>
+      <c r="B375" s="8"/>
       <c r="C375" s="2">
         <v>4</v>
       </c>
@@ -12036,7 +12036,7 @@
       <c r="A376" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B376" s="10"/>
+      <c r="B376" s="8"/>
       <c r="C376" s="2">
         <v>5</v>
       </c>
@@ -12048,7 +12048,7 @@
       <c r="A377" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B377" s="10"/>
+      <c r="B377" s="8"/>
       <c r="C377" s="2">
         <v>6</v>
       </c>
@@ -12060,7 +12060,7 @@
       <c r="A378" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B378" s="10"/>
+      <c r="B378" s="8"/>
       <c r="C378" s="2">
         <v>99</v>
       </c>
@@ -12072,7 +12072,7 @@
       <c r="A379" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="7" t="s">
         <v>341</v>
       </c>
       <c r="C379" s="3">
@@ -12086,7 +12086,7 @@
       <c r="A380" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B380" s="10"/>
+      <c r="B380" s="8"/>
       <c r="C380" s="2">
         <v>2</v>
       </c>
@@ -12098,7 +12098,7 @@
       <c r="A381" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B381" s="10"/>
+      <c r="B381" s="8"/>
       <c r="C381" s="2">
         <v>3</v>
       </c>
@@ -12110,7 +12110,7 @@
       <c r="A382" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B382" s="10"/>
+      <c r="B382" s="8"/>
       <c r="C382" s="2">
         <v>4</v>
       </c>
@@ -12122,7 +12122,7 @@
       <c r="A383" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B383" s="10"/>
+      <c r="B383" s="8"/>
       <c r="C383" s="2">
         <v>5</v>
       </c>
@@ -12134,7 +12134,7 @@
       <c r="A384" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B384" s="10"/>
+      <c r="B384" s="8"/>
       <c r="C384" s="2">
         <v>6</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="A385" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B385" s="10"/>
+      <c r="B385" s="8"/>
       <c r="C385" s="2">
         <v>99</v>
       </c>
@@ -12330,7 +12330,7 @@
       <c r="A400" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="7" t="s">
         <v>353</v>
       </c>
       <c r="C400" s="3">
@@ -12344,7 +12344,7 @@
       <c r="A401" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B401" s="10"/>
+      <c r="B401" s="8"/>
       <c r="C401" s="2">
         <v>2</v>
       </c>
@@ -12356,7 +12356,7 @@
       <c r="A402" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B402" s="10"/>
+      <c r="B402" s="8"/>
       <c r="C402" s="2">
         <v>3</v>
       </c>
@@ -12368,7 +12368,7 @@
       <c r="A403" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B403" s="10"/>
+      <c r="B403" s="8"/>
       <c r="C403" s="2">
         <v>4</v>
       </c>
@@ -12380,7 +12380,7 @@
       <c r="A404" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B404" s="10"/>
+      <c r="B404" s="8"/>
       <c r="C404" s="2">
         <v>99</v>
       </c>
@@ -12392,7 +12392,7 @@
       <c r="A405" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B405" s="9" t="s">
+      <c r="B405" s="7" t="s">
         <v>355</v>
       </c>
       <c r="C405" s="3">
@@ -12406,7 +12406,7 @@
       <c r="A406" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B406" s="10"/>
+      <c r="B406" s="8"/>
       <c r="C406" s="2">
         <v>2</v>
       </c>
@@ -12418,7 +12418,7 @@
       <c r="A407" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B407" s="10"/>
+      <c r="B407" s="8"/>
       <c r="C407" s="2">
         <v>99</v>
       </c>
@@ -12430,7 +12430,7 @@
       <c r="A408" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B408" s="9" t="s">
+      <c r="B408" s="7" t="s">
         <v>357</v>
       </c>
       <c r="C408" s="3">
@@ -12444,7 +12444,7 @@
       <c r="A409" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B409" s="10"/>
+      <c r="B409" s="8"/>
       <c r="C409" s="2">
         <v>2</v>
       </c>
@@ -12456,7 +12456,7 @@
       <c r="A410" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B410" s="10"/>
+      <c r="B410" s="8"/>
       <c r="C410" s="2">
         <v>99</v>
       </c>
@@ -12530,7 +12530,7 @@
       <c r="A416" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B416" s="9" t="s">
+      <c r="B416" s="7" t="s">
         <v>365</v>
       </c>
       <c r="C416" s="3">
@@ -12544,7 +12544,7 @@
       <c r="A417" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B417" s="10"/>
+      <c r="B417" s="8"/>
       <c r="C417" s="2">
         <v>2</v>
       </c>
@@ -12556,7 +12556,7 @@
       <c r="A418" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B418" s="10"/>
+      <c r="B418" s="8"/>
       <c r="C418" s="2">
         <v>99</v>
       </c>
@@ -12568,7 +12568,7 @@
       <c r="A419" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B419" s="9" t="s">
+      <c r="B419" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C419" s="3">
@@ -12582,7 +12582,7 @@
       <c r="A420" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B420" s="10"/>
+      <c r="B420" s="8"/>
       <c r="C420" s="2">
         <v>2</v>
       </c>
@@ -12594,7 +12594,7 @@
       <c r="A421" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B421" s="10"/>
+      <c r="B421" s="8"/>
       <c r="C421" s="2">
         <v>99</v>
       </c>
@@ -12606,7 +12606,7 @@
       <c r="A422" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B422" s="9" t="s">
+      <c r="B422" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C422" s="3">
@@ -12620,7 +12620,7 @@
       <c r="A423" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B423" s="10"/>
+      <c r="B423" s="8"/>
       <c r="C423" s="2">
         <v>2</v>
       </c>
@@ -12632,7 +12632,7 @@
       <c r="A424" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B424" s="10"/>
+      <c r="B424" s="8"/>
       <c r="C424" s="2">
         <v>99</v>
       </c>
@@ -12644,7 +12644,7 @@
       <c r="A425" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B425" s="9" t="s">
+      <c r="B425" s="7" t="s">
         <v>371</v>
       </c>
       <c r="C425" s="3">
@@ -12658,7 +12658,7 @@
       <c r="A426" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B426" s="10"/>
+      <c r="B426" s="8"/>
       <c r="C426" s="2">
         <v>2</v>
       </c>
@@ -12670,7 +12670,7 @@
       <c r="A427" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B427" s="10"/>
+      <c r="B427" s="8"/>
       <c r="C427" s="2">
         <v>3</v>
       </c>
@@ -12682,7 +12682,7 @@
       <c r="A428" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B428" s="10"/>
+      <c r="B428" s="8"/>
       <c r="C428" s="2">
         <v>4</v>
       </c>
@@ -12694,7 +12694,7 @@
       <c r="A429" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B429" s="10"/>
+      <c r="B429" s="8"/>
       <c r="C429" s="2">
         <v>5</v>
       </c>
@@ -12706,7 +12706,7 @@
       <c r="A430" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B430" s="10"/>
+      <c r="B430" s="8"/>
       <c r="C430" s="2">
         <v>99</v>
       </c>
@@ -12718,7 +12718,7 @@
       <c r="A431" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B431" s="9" t="s">
+      <c r="B431" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C431" s="3">
@@ -12732,7 +12732,7 @@
       <c r="A432" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B432" s="10"/>
+      <c r="B432" s="8"/>
       <c r="C432" s="2">
         <v>2</v>
       </c>
@@ -12744,7 +12744,7 @@
       <c r="A433" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B433" s="10"/>
+      <c r="B433" s="8"/>
       <c r="C433" s="2">
         <v>3</v>
       </c>
@@ -12756,7 +12756,7 @@
       <c r="A434" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B434" s="10"/>
+      <c r="B434" s="8"/>
       <c r="C434" s="2">
         <v>4</v>
       </c>
@@ -12768,7 +12768,7 @@
       <c r="A435" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B435" s="10"/>
+      <c r="B435" s="8"/>
       <c r="C435" s="2">
         <v>5</v>
       </c>
@@ -12780,7 +12780,7 @@
       <c r="A436" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B436" s="10"/>
+      <c r="B436" s="8"/>
       <c r="C436" s="2">
         <v>99</v>
       </c>
@@ -12792,7 +12792,7 @@
       <c r="A437" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B437" s="9" t="s">
+      <c r="B437" s="7" t="s">
         <v>380</v>
       </c>
       <c r="C437" s="3">
@@ -12806,7 +12806,7 @@
       <c r="A438" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B438" s="10"/>
+      <c r="B438" s="8"/>
       <c r="C438" s="2">
         <v>2</v>
       </c>
@@ -12818,7 +12818,7 @@
       <c r="A439" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B439" s="10"/>
+      <c r="B439" s="8"/>
       <c r="C439" s="2">
         <v>3</v>
       </c>
@@ -12830,7 +12830,7 @@
       <c r="A440" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B440" s="10"/>
+      <c r="B440" s="8"/>
       <c r="C440" s="2">
         <v>4</v>
       </c>
@@ -12842,7 +12842,7 @@
       <c r="A441" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B441" s="10"/>
+      <c r="B441" s="8"/>
       <c r="C441" s="2">
         <v>5</v>
       </c>
@@ -12854,7 +12854,7 @@
       <c r="A442" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B442" s="10"/>
+      <c r="B442" s="8"/>
       <c r="C442" s="2">
         <v>99</v>
       </c>
@@ -12866,7 +12866,7 @@
       <c r="A443" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B443" s="9" t="s">
+      <c r="B443" s="7" t="s">
         <v>382</v>
       </c>
       <c r="C443" s="3">
@@ -12880,7 +12880,7 @@
       <c r="A444" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B444" s="10"/>
+      <c r="B444" s="8"/>
       <c r="C444" s="2">
         <v>2</v>
       </c>
@@ -12892,7 +12892,7 @@
       <c r="A445" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B445" s="10"/>
+      <c r="B445" s="8"/>
       <c r="C445" s="2">
         <v>3</v>
       </c>
@@ -12904,7 +12904,7 @@
       <c r="A446" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B446" s="10"/>
+      <c r="B446" s="8"/>
       <c r="C446" s="2">
         <v>4</v>
       </c>
@@ -12916,7 +12916,7 @@
       <c r="A447" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B447" s="10"/>
+      <c r="B447" s="8"/>
       <c r="C447" s="2">
         <v>5</v>
       </c>
@@ -12928,7 +12928,7 @@
       <c r="A448" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B448" s="10"/>
+      <c r="B448" s="8"/>
       <c r="C448" s="2">
         <v>6</v>
       </c>
@@ -12940,7 +12940,7 @@
       <c r="A449" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B449" s="10"/>
+      <c r="B449" s="8"/>
       <c r="C449" s="2">
         <v>7</v>
       </c>
@@ -12952,7 +12952,7 @@
       <c r="A450" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B450" s="10"/>
+      <c r="B450" s="8"/>
       <c r="C450" s="2">
         <v>99</v>
       </c>
@@ -12964,7 +12964,7 @@
       <c r="A451" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B451" s="9" t="s">
+      <c r="B451" s="7" t="s">
         <v>388</v>
       </c>
       <c r="C451" s="3">
@@ -12978,7 +12978,7 @@
       <c r="A452" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B452" s="10"/>
+      <c r="B452" s="8"/>
       <c r="C452" s="2">
         <v>2</v>
       </c>
@@ -12990,7 +12990,7 @@
       <c r="A453" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B453" s="10"/>
+      <c r="B453" s="8"/>
       <c r="C453" s="2">
         <v>3</v>
       </c>
@@ -13002,7 +13002,7 @@
       <c r="A454" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B454" s="10"/>
+      <c r="B454" s="8"/>
       <c r="C454" s="2">
         <v>4</v>
       </c>
@@ -13014,7 +13014,7 @@
       <c r="A455" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B455" s="10"/>
+      <c r="B455" s="8"/>
       <c r="C455" s="2">
         <v>5</v>
       </c>
@@ -13026,7 +13026,7 @@
       <c r="A456" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B456" s="10"/>
+      <c r="B456" s="8"/>
       <c r="C456" s="2">
         <v>99</v>
       </c>
@@ -13038,7 +13038,7 @@
       <c r="A457" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B457" s="9" t="s">
+      <c r="B457" s="7" t="s">
         <v>393</v>
       </c>
       <c r="C457" s="3">
@@ -13052,7 +13052,7 @@
       <c r="A458" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B458" s="10"/>
+      <c r="B458" s="8"/>
       <c r="C458" s="2">
         <v>2</v>
       </c>
@@ -13064,7 +13064,7 @@
       <c r="A459" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B459" s="10"/>
+      <c r="B459" s="8"/>
       <c r="C459" s="2">
         <v>3</v>
       </c>
@@ -13076,7 +13076,7 @@
       <c r="A460" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B460" s="10"/>
+      <c r="B460" s="8"/>
       <c r="C460" s="2">
         <v>4</v>
       </c>
@@ -13088,7 +13088,7 @@
       <c r="A461" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B461" s="10"/>
+      <c r="B461" s="8"/>
       <c r="C461" s="2">
         <v>5</v>
       </c>
@@ -13100,7 +13100,7 @@
       <c r="A462" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B462" s="10"/>
+      <c r="B462" s="8"/>
       <c r="C462" s="2">
         <v>99</v>
       </c>
@@ -13112,7 +13112,7 @@
       <c r="A463" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B463" s="9" t="s">
+      <c r="B463" s="7" t="s">
         <v>397</v>
       </c>
       <c r="C463" s="3">
@@ -13126,7 +13126,7 @@
       <c r="A464" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B464" s="10"/>
+      <c r="B464" s="8"/>
       <c r="C464" s="2">
         <v>2</v>
       </c>
@@ -13138,7 +13138,7 @@
       <c r="A465" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B465" s="10"/>
+      <c r="B465" s="8"/>
       <c r="C465" s="2">
         <v>3</v>
       </c>
@@ -13150,7 +13150,7 @@
       <c r="A466" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B466" s="10"/>
+      <c r="B466" s="8"/>
       <c r="C466" s="2">
         <v>4</v>
       </c>
@@ -13162,7 +13162,7 @@
       <c r="A467" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B467" s="10"/>
+      <c r="B467" s="8"/>
       <c r="C467" s="2">
         <v>5</v>
       </c>
@@ -13174,7 +13174,7 @@
       <c r="A468" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B468" s="10"/>
+      <c r="B468" s="8"/>
       <c r="C468" s="2">
         <v>99</v>
       </c>
@@ -13186,7 +13186,7 @@
       <c r="A469" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B469" s="9" t="s">
+      <c r="B469" s="7" t="s">
         <v>399</v>
       </c>
       <c r="C469" s="3">
@@ -13200,7 +13200,7 @@
       <c r="A470" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B470" s="10"/>
+      <c r="B470" s="8"/>
       <c r="C470" s="2">
         <v>2</v>
       </c>
@@ -13212,7 +13212,7 @@
       <c r="A471" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B471" s="10"/>
+      <c r="B471" s="8"/>
       <c r="C471" s="2">
         <v>3</v>
       </c>
@@ -13224,7 +13224,7 @@
       <c r="A472" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B472" s="10"/>
+      <c r="B472" s="8"/>
       <c r="C472" s="2">
         <v>4</v>
       </c>
@@ -13236,7 +13236,7 @@
       <c r="A473" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B473" s="10"/>
+      <c r="B473" s="8"/>
       <c r="C473" s="2">
         <v>5</v>
       </c>
@@ -13248,7 +13248,7 @@
       <c r="A474" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B474" s="10"/>
+      <c r="B474" s="8"/>
       <c r="C474" s="2">
         <v>99</v>
       </c>
@@ -13260,7 +13260,7 @@
       <c r="A475" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B475" s="9" t="s">
+      <c r="B475" s="7" t="s">
         <v>401</v>
       </c>
       <c r="C475" s="3">
@@ -13274,7 +13274,7 @@
       <c r="A476" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B476" s="10"/>
+      <c r="B476" s="8"/>
       <c r="C476" s="2">
         <v>2</v>
       </c>
@@ -13286,7 +13286,7 @@
       <c r="A477" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B477" s="10"/>
+      <c r="B477" s="8"/>
       <c r="C477" s="2">
         <v>3</v>
       </c>
@@ -13298,7 +13298,7 @@
       <c r="A478" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B478" s="10"/>
+      <c r="B478" s="8"/>
       <c r="C478" s="2">
         <v>4</v>
       </c>
@@ -13310,7 +13310,7 @@
       <c r="A479" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B479" s="10"/>
+      <c r="B479" s="8"/>
       <c r="C479" s="2">
         <v>5</v>
       </c>
@@ -13322,7 +13322,7 @@
       <c r="A480" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B480" s="10"/>
+      <c r="B480" s="8"/>
       <c r="C480" s="2">
         <v>99</v>
       </c>
@@ -13334,7 +13334,7 @@
       <c r="A481" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B481" s="9" t="s">
+      <c r="B481" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C481" s="3">
@@ -13348,7 +13348,7 @@
       <c r="A482" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B482" s="10"/>
+      <c r="B482" s="8"/>
       <c r="C482" s="2">
         <v>2</v>
       </c>
@@ -13360,7 +13360,7 @@
       <c r="A483" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B483" s="10"/>
+      <c r="B483" s="8"/>
       <c r="C483" s="2">
         <v>3</v>
       </c>
@@ -13372,7 +13372,7 @@
       <c r="A484" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B484" s="10"/>
+      <c r="B484" s="8"/>
       <c r="C484" s="2">
         <v>4</v>
       </c>
@@ -13384,7 +13384,7 @@
       <c r="A485" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B485" s="10"/>
+      <c r="B485" s="8"/>
       <c r="C485" s="2">
         <v>5</v>
       </c>
@@ -13396,7 +13396,7 @@
       <c r="A486" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B486" s="10"/>
+      <c r="B486" s="8"/>
       <c r="C486" s="2">
         <v>99</v>
       </c>
@@ -13408,7 +13408,7 @@
       <c r="A487" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B487" s="9" t="s">
+      <c r="B487" s="7" t="s">
         <v>405</v>
       </c>
       <c r="C487" s="3">
@@ -13422,7 +13422,7 @@
       <c r="A488" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B488" s="10"/>
+      <c r="B488" s="8"/>
       <c r="C488" s="2">
         <v>2</v>
       </c>
@@ -13434,7 +13434,7 @@
       <c r="A489" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B489" s="10"/>
+      <c r="B489" s="8"/>
       <c r="C489" s="2">
         <v>3</v>
       </c>
@@ -13446,7 +13446,7 @@
       <c r="A490" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B490" s="10"/>
+      <c r="B490" s="8"/>
       <c r="C490" s="2">
         <v>4</v>
       </c>
@@ -13458,7 +13458,7 @@
       <c r="A491" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B491" s="10"/>
+      <c r="B491" s="8"/>
       <c r="C491" s="2">
         <v>5</v>
       </c>
@@ -13470,7 +13470,7 @@
       <c r="A492" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B492" s="10"/>
+      <c r="B492" s="8"/>
       <c r="C492" s="2">
         <v>99</v>
       </c>
@@ -13482,7 +13482,7 @@
       <c r="A493" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B493" s="9" t="s">
+      <c r="B493" s="7" t="s">
         <v>407</v>
       </c>
       <c r="C493" s="3">
@@ -13496,7 +13496,7 @@
       <c r="A494" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B494" s="10"/>
+      <c r="B494" s="8"/>
       <c r="C494" s="2">
         <v>2</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="A495" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B495" s="10"/>
+      <c r="B495" s="8"/>
       <c r="C495" s="2">
         <v>3</v>
       </c>
@@ -13520,7 +13520,7 @@
       <c r="A496" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B496" s="10"/>
+      <c r="B496" s="8"/>
       <c r="C496" s="2">
         <v>4</v>
       </c>
@@ -13532,7 +13532,7 @@
       <c r="A497" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B497" s="10"/>
+      <c r="B497" s="8"/>
       <c r="C497" s="2">
         <v>5</v>
       </c>
@@ -13544,7 +13544,7 @@
       <c r="A498" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B498" s="10"/>
+      <c r="B498" s="8"/>
       <c r="C498" s="2">
         <v>99</v>
       </c>
@@ -13556,7 +13556,7 @@
       <c r="A499" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B499" s="9" t="s">
+      <c r="B499" s="7" t="s">
         <v>409</v>
       </c>
       <c r="C499" s="3">
@@ -13570,7 +13570,7 @@
       <c r="A500" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B500" s="10"/>
+      <c r="B500" s="8"/>
       <c r="C500" s="2">
         <v>2</v>
       </c>
@@ -13582,7 +13582,7 @@
       <c r="A501" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B501" s="10"/>
+      <c r="B501" s="8"/>
       <c r="C501" s="2">
         <v>3</v>
       </c>
@@ -13594,7 +13594,7 @@
       <c r="A502" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B502" s="10"/>
+      <c r="B502" s="8"/>
       <c r="C502" s="2">
         <v>4</v>
       </c>
@@ -13606,7 +13606,7 @@
       <c r="A503" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B503" s="10"/>
+      <c r="B503" s="8"/>
       <c r="C503" s="2">
         <v>5</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="A504" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B504" s="10"/>
+      <c r="B504" s="8"/>
       <c r="C504" s="2">
         <v>99</v>
       </c>
@@ -13630,7 +13630,7 @@
       <c r="A505" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B505" s="9" t="s">
+      <c r="B505" s="7" t="s">
         <v>411</v>
       </c>
       <c r="C505" s="3">
@@ -13644,7 +13644,7 @@
       <c r="A506" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B506" s="10"/>
+      <c r="B506" s="8"/>
       <c r="C506" s="2">
         <v>2</v>
       </c>
@@ -13656,7 +13656,7 @@
       <c r="A507" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B507" s="10"/>
+      <c r="B507" s="8"/>
       <c r="C507" s="2">
         <v>3</v>
       </c>
@@ -13668,7 +13668,7 @@
       <c r="A508" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B508" s="10"/>
+      <c r="B508" s="8"/>
       <c r="C508" s="2">
         <v>4</v>
       </c>
@@ -13680,7 +13680,7 @@
       <c r="A509" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B509" s="10"/>
+      <c r="B509" s="8"/>
       <c r="C509" s="2">
         <v>5</v>
       </c>
@@ -13692,7 +13692,7 @@
       <c r="A510" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B510" s="10"/>
+      <c r="B510" s="8"/>
       <c r="C510" s="2">
         <v>99</v>
       </c>
@@ -13704,7 +13704,7 @@
       <c r="A511" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B511" s="9" t="s">
+      <c r="B511" s="7" t="s">
         <v>413</v>
       </c>
       <c r="C511" s="3">
@@ -13718,7 +13718,7 @@
       <c r="A512" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B512" s="10"/>
+      <c r="B512" s="8"/>
       <c r="C512" s="2">
         <v>2</v>
       </c>
@@ -13730,7 +13730,7 @@
       <c r="A513" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B513" s="10"/>
+      <c r="B513" s="8"/>
       <c r="C513" s="2">
         <v>3</v>
       </c>
@@ -13742,7 +13742,7 @@
       <c r="A514" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B514" s="10"/>
+      <c r="B514" s="8"/>
       <c r="C514" s="2">
         <v>4</v>
       </c>
@@ -13754,7 +13754,7 @@
       <c r="A515" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B515" s="10"/>
+      <c r="B515" s="8"/>
       <c r="C515" s="2">
         <v>5</v>
       </c>
@@ -13766,7 +13766,7 @@
       <c r="A516" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B516" s="10"/>
+      <c r="B516" s="8"/>
       <c r="C516" s="2">
         <v>99</v>
       </c>
@@ -13778,7 +13778,7 @@
       <c r="A517" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B517" s="9" t="s">
+      <c r="B517" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C517" s="3">
@@ -13792,7 +13792,7 @@
       <c r="A518" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B518" s="10"/>
+      <c r="B518" s="8"/>
       <c r="C518" s="2">
         <v>2</v>
       </c>
@@ -13804,7 +13804,7 @@
       <c r="A519" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B519" s="10"/>
+      <c r="B519" s="8"/>
       <c r="C519" s="2">
         <v>3</v>
       </c>
@@ -13816,7 +13816,7 @@
       <c r="A520" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B520" s="10"/>
+      <c r="B520" s="8"/>
       <c r="C520" s="2">
         <v>4</v>
       </c>
@@ -13828,7 +13828,7 @@
       <c r="A521" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B521" s="10"/>
+      <c r="B521" s="8"/>
       <c r="C521" s="2">
         <v>5</v>
       </c>
@@ -13840,7 +13840,7 @@
       <c r="A522" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B522" s="10"/>
+      <c r="B522" s="8"/>
       <c r="C522" s="2">
         <v>99</v>
       </c>
@@ -13852,7 +13852,7 @@
       <c r="A523" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B523" s="9" t="s">
+      <c r="B523" s="7" t="s">
         <v>417</v>
       </c>
       <c r="C523" s="3">
@@ -13866,7 +13866,7 @@
       <c r="A524" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B524" s="10"/>
+      <c r="B524" s="8"/>
       <c r="C524" s="2">
         <v>2</v>
       </c>
@@ -13878,7 +13878,7 @@
       <c r="A525" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B525" s="10"/>
+      <c r="B525" s="8"/>
       <c r="C525" s="2">
         <v>3</v>
       </c>
@@ -13890,7 +13890,7 @@
       <c r="A526" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B526" s="10"/>
+      <c r="B526" s="8"/>
       <c r="C526" s="2">
         <v>4</v>
       </c>
@@ -13902,7 +13902,7 @@
       <c r="A527" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B527" s="10"/>
+      <c r="B527" s="8"/>
       <c r="C527" s="2">
         <v>5</v>
       </c>
@@ -13914,7 +13914,7 @@
       <c r="A528" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B528" s="10"/>
+      <c r="B528" s="8"/>
       <c r="C528" s="2">
         <v>99</v>
       </c>
@@ -13926,7 +13926,7 @@
       <c r="A529" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B529" s="9" t="s">
+      <c r="B529" s="7" t="s">
         <v>424</v>
       </c>
       <c r="C529" s="3">
@@ -13940,7 +13940,7 @@
       <c r="A530" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B530" s="10"/>
+      <c r="B530" s="8"/>
       <c r="C530" s="2">
         <v>2</v>
       </c>
@@ -13952,7 +13952,7 @@
       <c r="A531" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B531" s="10"/>
+      <c r="B531" s="8"/>
       <c r="C531" s="2">
         <v>3</v>
       </c>
@@ -13964,7 +13964,7 @@
       <c r="A532" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B532" s="10"/>
+      <c r="B532" s="8"/>
       <c r="C532" s="2">
         <v>4</v>
       </c>
@@ -13976,7 +13976,7 @@
       <c r="A533" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B533" s="10"/>
+      <c r="B533" s="8"/>
       <c r="C533" s="2">
         <v>5</v>
       </c>
@@ -13988,7 +13988,7 @@
       <c r="A534" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B534" s="10"/>
+      <c r="B534" s="8"/>
       <c r="C534" s="2">
         <v>99</v>
       </c>
@@ -14000,7 +14000,7 @@
       <c r="A535" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B535" s="9" t="s">
+      <c r="B535" s="7" t="s">
         <v>426</v>
       </c>
       <c r="C535" s="3">
@@ -14014,7 +14014,7 @@
       <c r="A536" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B536" s="10"/>
+      <c r="B536" s="8"/>
       <c r="C536" s="2">
         <v>2</v>
       </c>
@@ -14026,7 +14026,7 @@
       <c r="A537" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B537" s="10"/>
+      <c r="B537" s="8"/>
       <c r="C537" s="2">
         <v>3</v>
       </c>
@@ -14038,7 +14038,7 @@
       <c r="A538" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B538" s="10"/>
+      <c r="B538" s="8"/>
       <c r="C538" s="2">
         <v>4</v>
       </c>
@@ -14050,7 +14050,7 @@
       <c r="A539" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B539" s="10"/>
+      <c r="B539" s="8"/>
       <c r="C539" s="2">
         <v>5</v>
       </c>
@@ -14062,7 +14062,7 @@
       <c r="A540" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B540" s="10"/>
+      <c r="B540" s="8"/>
       <c r="C540" s="2">
         <v>99</v>
       </c>
@@ -14074,7 +14074,7 @@
       <c r="A541" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B541" s="9" t="s">
+      <c r="B541" s="7" t="s">
         <v>428</v>
       </c>
       <c r="C541" s="3">
@@ -14088,7 +14088,7 @@
       <c r="A542" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B542" s="10"/>
+      <c r="B542" s="8"/>
       <c r="C542" s="2">
         <v>2</v>
       </c>
@@ -14100,7 +14100,7 @@
       <c r="A543" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B543" s="10"/>
+      <c r="B543" s="8"/>
       <c r="C543" s="2">
         <v>3</v>
       </c>
@@ -14112,7 +14112,7 @@
       <c r="A544" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B544" s="10"/>
+      <c r="B544" s="8"/>
       <c r="C544" s="2">
         <v>4</v>
       </c>
@@ -14124,7 +14124,7 @@
       <c r="A545" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B545" s="10"/>
+      <c r="B545" s="8"/>
       <c r="C545" s="2">
         <v>5</v>
       </c>
@@ -14136,7 +14136,7 @@
       <c r="A546" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B546" s="10"/>
+      <c r="B546" s="8"/>
       <c r="C546" s="2">
         <v>99</v>
       </c>
@@ -14148,7 +14148,7 @@
       <c r="A547" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B547" s="9" t="s">
+      <c r="B547" s="7" t="s">
         <v>430</v>
       </c>
       <c r="C547" s="3">
@@ -14162,7 +14162,7 @@
       <c r="A548" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B548" s="10"/>
+      <c r="B548" s="8"/>
       <c r="C548" s="2">
         <v>2</v>
       </c>
@@ -14174,7 +14174,7 @@
       <c r="A549" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B549" s="10"/>
+      <c r="B549" s="8"/>
       <c r="C549" s="2">
         <v>3</v>
       </c>
@@ -14186,7 +14186,7 @@
       <c r="A550" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B550" s="10"/>
+      <c r="B550" s="8"/>
       <c r="C550" s="2">
         <v>4</v>
       </c>
@@ -14198,7 +14198,7 @@
       <c r="A551" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B551" s="10"/>
+      <c r="B551" s="8"/>
       <c r="C551" s="2">
         <v>5</v>
       </c>
@@ -14210,7 +14210,7 @@
       <c r="A552" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B552" s="10"/>
+      <c r="B552" s="8"/>
       <c r="C552" s="2">
         <v>99</v>
       </c>
@@ -14222,7 +14222,7 @@
       <c r="A553" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B553" s="9" t="s">
+      <c r="B553" s="7" t="s">
         <v>432</v>
       </c>
       <c r="C553" s="3">
@@ -14236,7 +14236,7 @@
       <c r="A554" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B554" s="10"/>
+      <c r="B554" s="8"/>
       <c r="C554" s="2">
         <v>2</v>
       </c>
@@ -14248,7 +14248,7 @@
       <c r="A555" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B555" s="10"/>
+      <c r="B555" s="8"/>
       <c r="C555" s="2">
         <v>3</v>
       </c>
@@ -14260,7 +14260,7 @@
       <c r="A556" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B556" s="10"/>
+      <c r="B556" s="8"/>
       <c r="C556" s="2">
         <v>4</v>
       </c>
@@ -14272,7 +14272,7 @@
       <c r="A557" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B557" s="10"/>
+      <c r="B557" s="8"/>
       <c r="C557" s="2">
         <v>5</v>
       </c>
@@ -14284,7 +14284,7 @@
       <c r="A558" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B558" s="10"/>
+      <c r="B558" s="8"/>
       <c r="C558" s="2">
         <v>99</v>
       </c>
@@ -14558,7 +14558,7 @@
       <c r="A580" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B580" s="9" t="s">
+      <c r="B580" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C580" s="3">
@@ -14572,7 +14572,7 @@
       <c r="A581" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B581" s="10"/>
+      <c r="B581" s="8"/>
       <c r="C581" s="2">
         <v>2</v>
       </c>
@@ -14584,7 +14584,7 @@
       <c r="A582" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B582" s="10"/>
+      <c r="B582" s="8"/>
       <c r="C582" s="2">
         <v>99</v>
       </c>
@@ -14596,7 +14596,7 @@
       <c r="A583" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B583" s="9" t="s">
+      <c r="B583" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C583" s="3">
@@ -14610,7 +14610,7 @@
       <c r="A584" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B584" s="10"/>
+      <c r="B584" s="8"/>
       <c r="C584" s="2">
         <v>2</v>
       </c>
@@ -14622,7 +14622,7 @@
       <c r="A585" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B585" s="10"/>
+      <c r="B585" s="8"/>
       <c r="C585" s="2">
         <v>99</v>
       </c>
@@ -14634,7 +14634,7 @@
       <c r="A586" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B586" s="9" t="s">
+      <c r="B586" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C586" s="3">
@@ -14648,7 +14648,7 @@
       <c r="A587" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B587" s="10"/>
+      <c r="B587" s="8"/>
       <c r="C587" s="2">
         <v>2</v>
       </c>
@@ -14660,7 +14660,7 @@
       <c r="A588" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B588" s="10"/>
+      <c r="B588" s="8"/>
       <c r="C588" s="2">
         <v>99</v>
       </c>
@@ -14672,7 +14672,7 @@
       <c r="A589" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B589" s="9" t="s">
+      <c r="B589" s="7" t="s">
         <v>52</v>
       </c>
       <c r="C589" s="3">
@@ -14686,7 +14686,7 @@
       <c r="A590" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B590" s="10"/>
+      <c r="B590" s="8"/>
       <c r="C590" s="2">
         <v>2</v>
       </c>
@@ -14698,7 +14698,7 @@
       <c r="A591" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B591" s="10"/>
+      <c r="B591" s="8"/>
       <c r="C591" s="2">
         <v>99</v>
       </c>
@@ -14710,7 +14710,7 @@
       <c r="A592" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B592" s="9" t="s">
+      <c r="B592" s="7" t="s">
         <v>466</v>
       </c>
       <c r="C592" s="3">
@@ -14724,7 +14724,7 @@
       <c r="A593" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B593" s="10"/>
+      <c r="B593" s="8"/>
       <c r="C593" s="2">
         <v>10000</v>
       </c>
@@ -14736,7 +14736,7 @@
       <c r="A594" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B594" s="10"/>
+      <c r="B594" s="8"/>
       <c r="C594" s="2">
         <v>20000</v>
       </c>
@@ -14748,7 +14748,7 @@
       <c r="A595" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B595" s="10"/>
+      <c r="B595" s="8"/>
       <c r="C595" s="2">
         <v>30000</v>
       </c>
@@ -14760,7 +14760,7 @@
       <c r="A596" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B596" s="10"/>
+      <c r="B596" s="8"/>
       <c r="C596" s="2">
         <v>40001</v>
       </c>
@@ -14772,7 +14772,7 @@
       <c r="A597" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B597" s="10"/>
+      <c r="B597" s="8"/>
       <c r="C597" s="2">
         <v>40002</v>
       </c>
@@ -14784,7 +14784,7 @@
       <c r="A598" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B598" s="10"/>
+      <c r="B598" s="8"/>
       <c r="C598" s="2">
         <v>50000</v>
       </c>
@@ -14796,7 +14796,7 @@
       <c r="A599" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B599" s="10"/>
+      <c r="B599" s="8"/>
       <c r="C599" s="2">
         <v>60000</v>
       </c>
@@ -14808,7 +14808,7 @@
       <c r="A600" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B600" s="10"/>
+      <c r="B600" s="8"/>
       <c r="C600" s="2">
         <v>70000</v>
       </c>
@@ -14820,7 +14820,7 @@
       <c r="A601" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B601" s="10"/>
+      <c r="B601" s="8"/>
       <c r="C601" s="2">
         <v>80000</v>
       </c>
@@ -14832,7 +14832,7 @@
       <c r="A602" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B602" s="10"/>
+      <c r="B602" s="8"/>
       <c r="C602" s="2">
         <v>90001</v>
       </c>
@@ -14844,7 +14844,7 @@
       <c r="A603" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B603" s="10"/>
+      <c r="B603" s="8"/>
       <c r="C603" s="2">
         <v>90002</v>
       </c>
@@ -14856,7 +14856,7 @@
       <c r="A604" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B604" s="10"/>
+      <c r="B604" s="8"/>
       <c r="C604" s="2">
         <v>100000</v>
       </c>
@@ -14868,7 +14868,7 @@
       <c r="A605" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B605" s="10"/>
+      <c r="B605" s="8"/>
       <c r="C605" s="2">
         <v>900000</v>
       </c>
@@ -15316,7 +15316,7 @@
       <c r="A642" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B642" s="9" t="s">
+      <c r="B642" s="7" t="s">
         <v>474</v>
       </c>
       <c r="C642" s="3">
@@ -15330,7 +15330,7 @@
       <c r="A643" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B643" s="10"/>
+      <c r="B643" s="8"/>
       <c r="C643" s="2">
         <v>2</v>
       </c>
@@ -15342,7 +15342,7 @@
       <c r="A644" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B644" s="10"/>
+      <c r="B644" s="8"/>
       <c r="C644" s="2">
         <v>3</v>
       </c>
@@ -15354,7 +15354,7 @@
       <c r="A645" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B645" s="10"/>
+      <c r="B645" s="8"/>
       <c r="C645" s="2">
         <v>4</v>
       </c>
@@ -15366,7 +15366,7 @@
       <c r="A646" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B646" s="10"/>
+      <c r="B646" s="8"/>
       <c r="C646" s="2">
         <v>99</v>
       </c>
@@ -15378,7 +15378,7 @@
       <c r="A647" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B647" s="9" t="s">
+      <c r="B647" s="7" t="s">
         <v>476</v>
       </c>
       <c r="C647" s="3">
@@ -15392,7 +15392,7 @@
       <c r="A648" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B648" s="10"/>
+      <c r="B648" s="8"/>
       <c r="C648" s="2">
         <v>2</v>
       </c>
@@ -15404,7 +15404,7 @@
       <c r="A649" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B649" s="10"/>
+      <c r="B649" s="8"/>
       <c r="C649" s="2">
         <v>3</v>
       </c>
@@ -15416,7 +15416,7 @@
       <c r="A650" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B650" s="10"/>
+      <c r="B650" s="8"/>
       <c r="C650" s="2">
         <v>4</v>
       </c>
@@ -15428,7 +15428,7 @@
       <c r="A651" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B651" s="10"/>
+      <c r="B651" s="8"/>
       <c r="C651" s="2">
         <v>99</v>
       </c>
@@ -15440,7 +15440,7 @@
       <c r="A652" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B652" s="9" t="s">
+      <c r="B652" s="7" t="s">
         <v>478</v>
       </c>
       <c r="C652" s="3">
@@ -15454,7 +15454,7 @@
       <c r="A653" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B653" s="10"/>
+      <c r="B653" s="8"/>
       <c r="C653" s="2">
         <v>2</v>
       </c>
@@ -15466,7 +15466,7 @@
       <c r="A654" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B654" s="10"/>
+      <c r="B654" s="8"/>
       <c r="C654" s="2">
         <v>3</v>
       </c>
@@ -15478,7 +15478,7 @@
       <c r="A655" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B655" s="10"/>
+      <c r="B655" s="8"/>
       <c r="C655" s="2">
         <v>4</v>
       </c>
@@ -15490,7 +15490,7 @@
       <c r="A656" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B656" s="10"/>
+      <c r="B656" s="8"/>
       <c r="C656" s="2">
         <v>5</v>
       </c>
@@ -15502,7 +15502,7 @@
       <c r="A657" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B657" s="10"/>
+      <c r="B657" s="8"/>
       <c r="C657" s="2">
         <v>6</v>
       </c>
@@ -15514,7 +15514,7 @@
       <c r="A658" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B658" s="10"/>
+      <c r="B658" s="8"/>
       <c r="C658" s="2">
         <v>99</v>
       </c>
@@ -15736,7 +15736,7 @@
       <c r="A676" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B676" s="9" t="s">
+      <c r="B676" s="7" t="s">
         <v>497</v>
       </c>
       <c r="C676" s="3">
@@ -15750,7 +15750,7 @@
       <c r="A677" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B677" s="10"/>
+      <c r="B677" s="8"/>
       <c r="C677" s="2">
         <v>2</v>
       </c>
@@ -15762,7 +15762,7 @@
       <c r="A678" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B678" s="10"/>
+      <c r="B678" s="8"/>
       <c r="C678" s="2">
         <v>3</v>
       </c>
@@ -15774,7 +15774,7 @@
       <c r="A679" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B679" s="10"/>
+      <c r="B679" s="8"/>
       <c r="C679" s="2">
         <v>4</v>
       </c>
@@ -15786,7 +15786,7 @@
       <c r="A680" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="B680" s="10"/>
+      <c r="B680" s="8"/>
       <c r="C680" s="2">
         <v>99</v>
       </c>
@@ -15798,7 +15798,7 @@
       <c r="A681" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B681" s="9" t="s">
+      <c r="B681" s="7" t="s">
         <v>503</v>
       </c>
       <c r="C681" s="3">
@@ -15812,7 +15812,7 @@
       <c r="A682" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B682" s="10"/>
+      <c r="B682" s="8"/>
       <c r="C682" s="2">
         <v>2</v>
       </c>
@@ -15824,7 +15824,7 @@
       <c r="A683" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B683" s="10"/>
+      <c r="B683" s="8"/>
       <c r="C683" s="2">
         <v>3</v>
       </c>
@@ -15836,7 +15836,7 @@
       <c r="A684" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B684" s="10"/>
+      <c r="B684" s="8"/>
       <c r="C684" s="2">
         <v>4</v>
       </c>
@@ -15848,7 +15848,7 @@
       <c r="A685" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B685" s="10"/>
+      <c r="B685" s="8"/>
       <c r="C685" s="2">
         <v>99</v>
       </c>
@@ -15860,7 +15860,7 @@
       <c r="A686" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B686" s="9" t="s">
+      <c r="B686" s="7" t="s">
         <v>509</v>
       </c>
       <c r="C686" s="3">
@@ -15874,7 +15874,7 @@
       <c r="A687" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B687" s="10"/>
+      <c r="B687" s="8"/>
       <c r="C687" s="2">
         <v>2</v>
       </c>
@@ -15886,7 +15886,7 @@
       <c r="A688" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B688" s="10"/>
+      <c r="B688" s="8"/>
       <c r="C688" s="2">
         <v>3</v>
       </c>
@@ -15898,7 +15898,7 @@
       <c r="A689" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B689" s="10"/>
+      <c r="B689" s="8"/>
       <c r="C689" s="2">
         <v>4</v>
       </c>
@@ -15910,7 +15910,7 @@
       <c r="A690" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B690" s="10"/>
+      <c r="B690" s="8"/>
       <c r="C690" s="2">
         <v>5</v>
       </c>
@@ -15922,7 +15922,7 @@
       <c r="A691" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B691" s="10"/>
+      <c r="B691" s="8"/>
       <c r="C691" s="2">
         <v>99</v>
       </c>
@@ -15934,7 +15934,7 @@
       <c r="A692" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B692" s="9" t="s">
+      <c r="B692" s="7" t="s">
         <v>515</v>
       </c>
       <c r="C692" s="3">
@@ -15948,7 +15948,7 @@
       <c r="A693" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B693" s="10"/>
+      <c r="B693" s="8"/>
       <c r="C693" s="2">
         <v>2</v>
       </c>
@@ -15960,7 +15960,7 @@
       <c r="A694" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B694" s="10"/>
+      <c r="B694" s="8"/>
       <c r="C694" s="2">
         <v>3</v>
       </c>
@@ -15972,7 +15972,7 @@
       <c r="A695" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B695" s="10"/>
+      <c r="B695" s="8"/>
       <c r="C695" s="2">
         <v>4</v>
       </c>
@@ -15984,7 +15984,7 @@
       <c r="A696" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B696" s="10"/>
+      <c r="B696" s="8"/>
       <c r="C696" s="2">
         <v>5</v>
       </c>
@@ -15996,7 +15996,7 @@
       <c r="A697" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B697" s="10"/>
+      <c r="B697" s="8"/>
       <c r="C697" s="2">
         <v>6</v>
       </c>
@@ -16008,7 +16008,7 @@
       <c r="A698" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B698" s="10"/>
+      <c r="B698" s="8"/>
       <c r="C698" s="2">
         <v>99</v>
       </c>
@@ -17238,7 +17238,7 @@
       <c r="A798" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B798" s="9" t="s">
+      <c r="B798" s="7" t="s">
         <v>572</v>
       </c>
       <c r="C798" s="3">
@@ -17252,7 +17252,7 @@
       <c r="A799" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B799" s="10"/>
+      <c r="B799" s="8"/>
       <c r="C799" s="2">
         <v>2</v>
       </c>
@@ -17264,7 +17264,7 @@
       <c r="A800" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B800" s="10"/>
+      <c r="B800" s="8"/>
       <c r="C800" s="2">
         <v>99</v>
       </c>
@@ -17276,7 +17276,7 @@
       <c r="A801" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B801" s="9" t="s">
+      <c r="B801" s="7" t="s">
         <v>576</v>
       </c>
       <c r="C801" s="3">
@@ -17290,7 +17290,7 @@
       <c r="A802" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B802" s="10"/>
+      <c r="B802" s="8"/>
       <c r="C802" s="2">
         <v>2</v>
       </c>
@@ -17302,7 +17302,7 @@
       <c r="A803" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B803" s="10"/>
+      <c r="B803" s="8"/>
       <c r="C803" s="2">
         <v>99</v>
       </c>
@@ -17314,7 +17314,7 @@
       <c r="A804" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B804" s="9" t="s">
+      <c r="B804" s="7" t="s">
         <v>578</v>
       </c>
       <c r="C804" s="3">
@@ -17328,7 +17328,7 @@
       <c r="A805" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B805" s="10"/>
+      <c r="B805" s="8"/>
       <c r="C805" s="2">
         <v>2</v>
       </c>
@@ -17340,7 +17340,7 @@
       <c r="A806" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B806" s="10"/>
+      <c r="B806" s="8"/>
       <c r="C806" s="2">
         <v>99</v>
       </c>
@@ -17352,7 +17352,7 @@
       <c r="A807" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B807" s="9" t="s">
+      <c r="B807" s="7" t="s">
         <v>580</v>
       </c>
       <c r="C807" s="3">
@@ -17366,7 +17366,7 @@
       <c r="A808" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B808" s="10"/>
+      <c r="B808" s="8"/>
       <c r="C808" s="2">
         <v>2</v>
       </c>
@@ -17378,7 +17378,7 @@
       <c r="A809" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B809" s="10"/>
+      <c r="B809" s="8"/>
       <c r="C809" s="2">
         <v>99</v>
       </c>
@@ -17390,7 +17390,7 @@
       <c r="A810" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B810" s="9" t="s">
+      <c r="B810" s="7" t="s">
         <v>582</v>
       </c>
       <c r="C810" s="3">
@@ -17404,7 +17404,7 @@
       <c r="A811" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B811" s="10"/>
+      <c r="B811" s="8"/>
       <c r="C811" s="2">
         <v>2</v>
       </c>
@@ -17416,7 +17416,7 @@
       <c r="A812" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B812" s="10"/>
+      <c r="B812" s="8"/>
       <c r="C812" s="2">
         <v>99</v>
       </c>
@@ -17428,7 +17428,7 @@
       <c r="A813" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B813" s="9" t="s">
+      <c r="B813" s="7" t="s">
         <v>584</v>
       </c>
       <c r="C813" s="3">
@@ -17442,7 +17442,7 @@
       <c r="A814" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B814" s="10"/>
+      <c r="B814" s="8"/>
       <c r="C814" s="2">
         <v>2</v>
       </c>
@@ -17454,7 +17454,7 @@
       <c r="A815" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B815" s="10"/>
+      <c r="B815" s="8"/>
       <c r="C815" s="2">
         <v>99</v>
       </c>
@@ -17466,7 +17466,7 @@
       <c r="A816" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B816" s="9" t="s">
+      <c r="B816" s="7" t="s">
         <v>586</v>
       </c>
       <c r="C816" s="3">
@@ -17480,7 +17480,7 @@
       <c r="A817" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B817" s="10"/>
+      <c r="B817" s="8"/>
       <c r="C817" s="2">
         <v>2</v>
       </c>
@@ -17492,7 +17492,7 @@
       <c r="A818" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B818" s="10"/>
+      <c r="B818" s="8"/>
       <c r="C818" s="2">
         <v>3</v>
       </c>
@@ -17504,7 +17504,7 @@
       <c r="A819" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B819" s="10"/>
+      <c r="B819" s="8"/>
       <c r="C819" s="2">
         <v>4</v>
       </c>
@@ -17516,7 +17516,7 @@
       <c r="A820" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B820" s="10"/>
+      <c r="B820" s="8"/>
       <c r="C820" s="2">
         <v>99</v>
       </c>
@@ -17528,7 +17528,7 @@
       <c r="A821" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B821" s="9" t="s">
+      <c r="B821" s="7" t="s">
         <v>588</v>
       </c>
       <c r="C821" s="3">
@@ -17542,7 +17542,7 @@
       <c r="A822" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B822" s="10"/>
+      <c r="B822" s="8"/>
       <c r="C822" s="2">
         <v>2</v>
       </c>
@@ -17554,7 +17554,7 @@
       <c r="A823" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B823" s="10"/>
+      <c r="B823" s="8"/>
       <c r="C823" s="2">
         <v>3</v>
       </c>
@@ -17566,7 +17566,7 @@
       <c r="A824" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B824" s="10"/>
+      <c r="B824" s="8"/>
       <c r="C824" s="2">
         <v>4</v>
       </c>
@@ -17578,7 +17578,7 @@
       <c r="A825" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B825" s="10"/>
+      <c r="B825" s="8"/>
       <c r="C825" s="2">
         <v>99</v>
       </c>
@@ -17590,7 +17590,7 @@
       <c r="A826" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B826" s="9" t="s">
+      <c r="B826" s="7" t="s">
         <v>590</v>
       </c>
       <c r="C826" s="3">
@@ -17604,7 +17604,7 @@
       <c r="A827" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B827" s="10"/>
+      <c r="B827" s="8"/>
       <c r="C827" s="2">
         <v>2</v>
       </c>
@@ -17616,7 +17616,7 @@
       <c r="A828" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B828" s="10"/>
+      <c r="B828" s="8"/>
       <c r="C828" s="2">
         <v>3</v>
       </c>
@@ -17628,7 +17628,7 @@
       <c r="A829" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B829" s="10"/>
+      <c r="B829" s="8"/>
       <c r="C829" s="2">
         <v>4</v>
       </c>
@@ -17640,7 +17640,7 @@
       <c r="A830" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B830" s="10"/>
+      <c r="B830" s="8"/>
       <c r="C830" s="2">
         <v>99</v>
       </c>
@@ -17652,7 +17652,7 @@
       <c r="A831" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B831" s="9" t="s">
+      <c r="B831" s="7" t="s">
         <v>592</v>
       </c>
       <c r="C831" s="3">
@@ -17666,7 +17666,7 @@
       <c r="A832" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B832" s="10"/>
+      <c r="B832" s="8"/>
       <c r="C832" s="2">
         <v>2</v>
       </c>
@@ -17678,7 +17678,7 @@
       <c r="A833" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B833" s="10"/>
+      <c r="B833" s="8"/>
       <c r="C833" s="2">
         <v>3</v>
       </c>
@@ -17690,7 +17690,7 @@
       <c r="A834" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B834" s="10"/>
+      <c r="B834" s="8"/>
       <c r="C834" s="2">
         <v>4</v>
       </c>
@@ -17702,7 +17702,7 @@
       <c r="A835" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B835" s="10"/>
+      <c r="B835" s="8"/>
       <c r="C835" s="2">
         <v>99</v>
       </c>
@@ -17714,7 +17714,7 @@
       <c r="A836" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B836" s="9" t="s">
+      <c r="B836" s="7" t="s">
         <v>594</v>
       </c>
       <c r="C836" s="3">
@@ -17728,7 +17728,7 @@
       <c r="A837" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B837" s="10"/>
+      <c r="B837" s="8"/>
       <c r="C837" s="2">
         <v>2</v>
       </c>
@@ -17740,7 +17740,7 @@
       <c r="A838" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B838" s="10"/>
+      <c r="B838" s="8"/>
       <c r="C838" s="2">
         <v>3</v>
       </c>
@@ -17752,7 +17752,7 @@
       <c r="A839" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B839" s="10"/>
+      <c r="B839" s="8"/>
       <c r="C839" s="2">
         <v>4</v>
       </c>
@@ -17764,7 +17764,7 @@
       <c r="A840" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B840" s="10"/>
+      <c r="B840" s="8"/>
       <c r="C840" s="2">
         <v>5</v>
       </c>
@@ -17776,7 +17776,7 @@
       <c r="A841" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B841" s="10"/>
+      <c r="B841" s="8"/>
       <c r="C841" s="2">
         <v>6</v>
       </c>
@@ -17788,7 +17788,7 @@
       <c r="A842" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B842" s="10"/>
+      <c r="B842" s="8"/>
       <c r="C842" s="2">
         <v>7</v>
       </c>
@@ -17800,7 +17800,7 @@
       <c r="A843" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B843" s="10"/>
+      <c r="B843" s="8"/>
       <c r="C843" s="2">
         <v>99</v>
       </c>
@@ -17812,7 +17812,7 @@
       <c r="A844" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B844" s="9" t="s">
+      <c r="B844" s="7" t="s">
         <v>598</v>
       </c>
       <c r="C844" s="3">
@@ -17826,7 +17826,7 @@
       <c r="A845" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B845" s="10"/>
+      <c r="B845" s="8"/>
       <c r="C845" s="2">
         <v>2</v>
       </c>
@@ -17838,7 +17838,7 @@
       <c r="A846" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B846" s="10"/>
+      <c r="B846" s="8"/>
       <c r="C846" s="2">
         <v>99</v>
       </c>
@@ -17850,7 +17850,7 @@
       <c r="A847" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B847" s="9" t="s">
+      <c r="B847" s="7" t="s">
         <v>600</v>
       </c>
       <c r="C847" s="3">
@@ -17864,7 +17864,7 @@
       <c r="A848" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B848" s="10"/>
+      <c r="B848" s="8"/>
       <c r="C848" s="2">
         <v>2</v>
       </c>
@@ -17876,7 +17876,7 @@
       <c r="A849" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B849" s="10"/>
+      <c r="B849" s="8"/>
       <c r="C849" s="2">
         <v>3</v>
       </c>
@@ -17888,7 +17888,7 @@
       <c r="A850" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B850" s="10"/>
+      <c r="B850" s="8"/>
       <c r="C850" s="2">
         <v>4</v>
       </c>
@@ -17900,7 +17900,7 @@
       <c r="A851" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B851" s="10"/>
+      <c r="B851" s="8"/>
       <c r="C851" s="2">
         <v>5</v>
       </c>
@@ -17912,7 +17912,7 @@
       <c r="A852" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B852" s="10"/>
+      <c r="B852" s="8"/>
       <c r="C852" s="2">
         <v>9</v>
       </c>
@@ -17924,7 +17924,7 @@
       <c r="A853" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B853" s="9" t="s">
+      <c r="B853" s="7" t="s">
         <v>607</v>
       </c>
       <c r="C853" s="3">
@@ -17938,7 +17938,7 @@
       <c r="A854" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B854" s="10"/>
+      <c r="B854" s="8"/>
       <c r="C854" s="2">
         <v>2</v>
       </c>
@@ -17950,7 +17950,7 @@
       <c r="A855" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B855" s="10"/>
+      <c r="B855" s="8"/>
       <c r="C855" s="2">
         <v>99</v>
       </c>
@@ -17962,7 +17962,7 @@
       <c r="A856" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="B856" s="9" t="s">
+      <c r="B856" s="7" t="s">
         <v>609</v>
       </c>
       <c r="C856" s="3">
@@ -17976,7 +17976,7 @@
       <c r="A857" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B857" s="10"/>
+      <c r="B857" s="8"/>
       <c r="C857" s="2">
         <v>2</v>
       </c>
@@ -17988,7 +17988,7 @@
       <c r="A858" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B858" s="10"/>
+      <c r="B858" s="8"/>
       <c r="C858" s="2">
         <v>3</v>
       </c>
@@ -18000,7 +18000,7 @@
       <c r="A859" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B859" s="10"/>
+      <c r="B859" s="8"/>
       <c r="C859" s="2">
         <v>4</v>
       </c>
@@ -18012,7 +18012,7 @@
       <c r="A860" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B860" s="10"/>
+      <c r="B860" s="8"/>
       <c r="C860" s="2">
         <v>99</v>
       </c>
@@ -18024,7 +18024,7 @@
       <c r="A861" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B861" s="9" t="s">
+      <c r="B861" s="7" t="s">
         <v>615</v>
       </c>
       <c r="C861" s="3">
@@ -18038,7 +18038,7 @@
       <c r="A862" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B862" s="10"/>
+      <c r="B862" s="8"/>
       <c r="C862" s="2">
         <v>2</v>
       </c>
@@ -18050,7 +18050,7 @@
       <c r="A863" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B863" s="10"/>
+      <c r="B863" s="8"/>
       <c r="C863" s="2">
         <v>3</v>
       </c>
@@ -18062,7 +18062,7 @@
       <c r="A864" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="B864" s="10"/>
+      <c r="B864" s="8"/>
       <c r="C864" s="2">
         <v>99</v>
       </c>
@@ -18074,7 +18074,7 @@
       <c r="A865" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B865" s="9" t="s">
+      <c r="B865" s="7" t="s">
         <v>619</v>
       </c>
       <c r="C865" s="3">
@@ -18088,7 +18088,7 @@
       <c r="A866" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B866" s="10"/>
+      <c r="B866" s="8"/>
       <c r="C866" s="2">
         <v>2</v>
       </c>
@@ -18100,7 +18100,7 @@
       <c r="A867" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B867" s="10"/>
+      <c r="B867" s="8"/>
       <c r="C867" s="2">
         <v>3</v>
       </c>
@@ -18112,7 +18112,7 @@
       <c r="A868" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B868" s="10"/>
+      <c r="B868" s="8"/>
       <c r="C868" s="2">
         <v>4</v>
       </c>
@@ -18124,7 +18124,7 @@
       <c r="A869" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B869" s="10"/>
+      <c r="B869" s="8"/>
       <c r="C869" s="2">
         <v>5</v>
       </c>
@@ -18136,7 +18136,7 @@
       <c r="A870" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B870" s="10"/>
+      <c r="B870" s="8"/>
       <c r="C870" s="2">
         <v>99</v>
       </c>
@@ -18148,7 +18148,7 @@
       <c r="A871" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B871" s="9" t="s">
+      <c r="B871" s="7" t="s">
         <v>626</v>
       </c>
       <c r="C871" s="3">
@@ -18162,7 +18162,7 @@
       <c r="A872" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B872" s="10"/>
+      <c r="B872" s="8"/>
       <c r="C872" s="2">
         <v>2</v>
       </c>
@@ -18174,7 +18174,7 @@
       <c r="A873" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B873" s="10"/>
+      <c r="B873" s="8"/>
       <c r="C873" s="2">
         <v>3</v>
       </c>
@@ -18186,7 +18186,7 @@
       <c r="A874" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B874" s="10"/>
+      <c r="B874" s="8"/>
       <c r="C874" s="2">
         <v>99</v>
       </c>
@@ -18198,7 +18198,7 @@
       <c r="A875" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B875" s="9" t="s">
+      <c r="B875" s="7" t="s">
         <v>632</v>
       </c>
       <c r="C875" s="3">
@@ -18212,7 +18212,7 @@
       <c r="A876" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B876" s="10"/>
+      <c r="B876" s="8"/>
       <c r="C876" s="2">
         <v>2</v>
       </c>
@@ -18224,7 +18224,7 @@
       <c r="A877" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B877" s="10"/>
+      <c r="B877" s="8"/>
       <c r="C877" s="2">
         <v>3</v>
       </c>
@@ -18236,7 +18236,7 @@
       <c r="A878" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B878" s="10"/>
+      <c r="B878" s="8"/>
       <c r="C878" s="2">
         <v>4</v>
       </c>
@@ -18248,7 +18248,7 @@
       <c r="A879" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B879" s="10"/>
+      <c r="B879" s="8"/>
       <c r="C879" s="2">
         <v>99</v>
       </c>
@@ -18260,7 +18260,7 @@
       <c r="A880" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B880" s="9" t="s">
+      <c r="B880" s="7" t="s">
         <v>638</v>
       </c>
       <c r="C880" s="3">
@@ -18274,7 +18274,7 @@
       <c r="A881" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B881" s="10"/>
+      <c r="B881" s="8"/>
       <c r="C881" s="2">
         <v>2</v>
       </c>
@@ -18286,7 +18286,7 @@
       <c r="A882" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B882" s="10"/>
+      <c r="B882" s="8"/>
       <c r="C882" s="2">
         <v>99</v>
       </c>
@@ -18336,7 +18336,7 @@
       <c r="A886" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B886" s="9" t="s">
+      <c r="B886" s="7" t="s">
         <v>644</v>
       </c>
       <c r="C886" s="3">
@@ -18350,7 +18350,7 @@
       <c r="A887" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B887" s="10"/>
+      <c r="B887" s="8"/>
       <c r="C887" s="2">
         <v>2</v>
       </c>
@@ -18362,7 +18362,7 @@
       <c r="A888" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B888" s="9" t="s">
+      <c r="B888" s="7" t="s">
         <v>647</v>
       </c>
       <c r="C888" s="3">
@@ -18376,7 +18376,7 @@
       <c r="A889" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B889" s="10"/>
+      <c r="B889" s="8"/>
       <c r="C889" s="2">
         <v>2</v>
       </c>
@@ -18388,7 +18388,7 @@
       <c r="A890" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B890" s="10"/>
+      <c r="B890" s="8"/>
       <c r="C890" s="2">
         <v>3</v>
       </c>
@@ -18400,7 +18400,7 @@
       <c r="A891" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B891" s="10"/>
+      <c r="B891" s="8"/>
       <c r="C891" s="2">
         <v>4</v>
       </c>
@@ -18412,7 +18412,7 @@
       <c r="A892" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B892" s="10"/>
+      <c r="B892" s="8"/>
       <c r="C892" s="2">
         <v>99</v>
       </c>
@@ -18462,7 +18462,7 @@
       <c r="A896" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="B896" s="9" t="s">
+      <c r="B896" s="7" t="s">
         <v>657</v>
       </c>
       <c r="C896" s="3">
@@ -18476,7 +18476,7 @@
       <c r="A897" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B897" s="10"/>
+      <c r="B897" s="8"/>
       <c r="C897" s="2">
         <v>2</v>
       </c>
@@ -18488,7 +18488,7 @@
       <c r="A898" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B898" s="10"/>
+      <c r="B898" s="8"/>
       <c r="C898" s="2">
         <v>3</v>
       </c>
@@ -18500,7 +18500,7 @@
       <c r="A899" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B899" s="10"/>
+      <c r="B899" s="8"/>
       <c r="C899" s="2">
         <v>4</v>
       </c>
@@ -18512,7 +18512,7 @@
       <c r="A900" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B900" s="10"/>
+      <c r="B900" s="8"/>
       <c r="C900" s="2">
         <v>5</v>
       </c>
@@ -18524,7 +18524,7 @@
       <c r="A901" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B901" s="10"/>
+      <c r="B901" s="8"/>
       <c r="C901" s="2">
         <v>99</v>
       </c>
@@ -18722,7 +18722,7 @@
       <c r="A917" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B917" s="9" t="s">
+      <c r="B917" s="7" t="s">
         <v>676</v>
       </c>
       <c r="C917" s="3">
@@ -18736,7 +18736,7 @@
       <c r="A918" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B918" s="10"/>
+      <c r="B918" s="8"/>
       <c r="C918" s="2">
         <v>2</v>
       </c>
@@ -18748,7 +18748,7 @@
       <c r="A919" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B919" s="10"/>
+      <c r="B919" s="8"/>
       <c r="C919" s="2">
         <v>3</v>
       </c>
@@ -18760,7 +18760,7 @@
       <c r="A920" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B920" s="10"/>
+      <c r="B920" s="8"/>
       <c r="C920" s="2">
         <v>4</v>
       </c>
@@ -18772,7 +18772,7 @@
       <c r="A921" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B921" s="10"/>
+      <c r="B921" s="8"/>
       <c r="C921" s="2">
         <v>5</v>
       </c>
@@ -18784,7 +18784,7 @@
       <c r="A922" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B922" s="10"/>
+      <c r="B922" s="8"/>
       <c r="C922" s="2">
         <v>6</v>
       </c>
@@ -18796,7 +18796,7 @@
       <c r="A923" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B923" s="10"/>
+      <c r="B923" s="8"/>
       <c r="C923" s="2">
         <v>7</v>
       </c>
@@ -18808,7 +18808,7 @@
       <c r="A924" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B924" s="10"/>
+      <c r="B924" s="8"/>
       <c r="C924" s="2">
         <v>8</v>
       </c>
@@ -18820,7 +18820,7 @@
       <c r="A925" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B925" s="10"/>
+      <c r="B925" s="8"/>
       <c r="C925" s="2">
         <v>99</v>
       </c>
@@ -18832,7 +18832,7 @@
       <c r="A926" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B926" s="9" t="s">
+      <c r="B926" s="7" t="s">
         <v>686</v>
       </c>
       <c r="C926" s="3">
@@ -18846,7 +18846,7 @@
       <c r="A927" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B927" s="10"/>
+      <c r="B927" s="8"/>
       <c r="C927" s="2">
         <v>2</v>
       </c>
@@ -18858,7 +18858,7 @@
       <c r="A928" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B928" s="10"/>
+      <c r="B928" s="8"/>
       <c r="C928" s="2">
         <v>3</v>
       </c>
@@ -18870,7 +18870,7 @@
       <c r="A929" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B929" s="10"/>
+      <c r="B929" s="8"/>
       <c r="C929" s="2">
         <v>99</v>
       </c>
@@ -18882,7 +18882,7 @@
       <c r="A930" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B930" s="9" t="s">
+      <c r="B930" s="7" t="s">
         <v>691</v>
       </c>
       <c r="C930" s="3">
@@ -18896,7 +18896,7 @@
       <c r="A931" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B931" s="10"/>
+      <c r="B931" s="8"/>
       <c r="C931" s="2">
         <v>1</v>
       </c>
@@ -18908,7 +18908,7 @@
       <c r="A932" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B932" s="10"/>
+      <c r="B932" s="8"/>
       <c r="C932" s="2">
         <v>2</v>
       </c>
@@ -18920,7 +18920,7 @@
       <c r="A933" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B933" s="10"/>
+      <c r="B933" s="8"/>
       <c r="C933" s="2">
         <v>3</v>
       </c>
@@ -18932,7 +18932,7 @@
       <c r="A934" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B934" s="10"/>
+      <c r="B934" s="8"/>
       <c r="C934" s="2">
         <v>4</v>
       </c>
@@ -18944,7 +18944,7 @@
       <c r="A935" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="B935" s="10"/>
+      <c r="B935" s="8"/>
       <c r="C935" s="2">
         <v>99</v>
       </c>
@@ -19042,7 +19042,7 @@
       <c r="A943" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B943" s="7" t="s">
+      <c r="B943" s="9" t="s">
         <v>702</v>
       </c>
       <c r="C943" s="3">
@@ -19056,7 +19056,7 @@
       <c r="A944" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B944" s="8"/>
+      <c r="B944" s="10"/>
       <c r="C944" s="2">
         <v>2</v>
       </c>
@@ -19068,7 +19068,7 @@
       <c r="A945" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B945" s="8"/>
+      <c r="B945" s="10"/>
       <c r="C945" s="2">
         <v>3</v>
       </c>
@@ -19080,7 +19080,7 @@
       <c r="A946" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B946" s="8"/>
+      <c r="B946" s="10"/>
       <c r="C946" s="2">
         <v>4</v>
       </c>
@@ -19092,7 +19092,7 @@
       <c r="A947" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B947" s="8"/>
+      <c r="B947" s="10"/>
       <c r="C947" s="2">
         <v>5</v>
       </c>
@@ -19104,7 +19104,7 @@
       <c r="A948" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B948" s="8"/>
+      <c r="B948" s="10"/>
       <c r="C948" s="2">
         <v>6</v>
       </c>
@@ -19116,7 +19116,7 @@
       <c r="A949" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B949" s="8"/>
+      <c r="B949" s="10"/>
       <c r="C949" s="2">
         <v>7</v>
       </c>
@@ -19128,7 +19128,7 @@
       <c r="A950" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B950" s="8"/>
+      <c r="B950" s="10"/>
       <c r="C950" s="2">
         <v>8</v>
       </c>
@@ -19140,7 +19140,7 @@
       <c r="A951" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B951" s="8"/>
+      <c r="B951" s="10"/>
       <c r="C951" s="2">
         <v>9</v>
       </c>
@@ -19152,7 +19152,7 @@
       <c r="A952" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B952" s="8"/>
+      <c r="B952" s="10"/>
       <c r="C952" s="2">
         <v>10</v>
       </c>
@@ -19164,7 +19164,7 @@
       <c r="A953" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B953" s="8"/>
+      <c r="B953" s="10"/>
       <c r="C953" s="2">
         <v>11</v>
       </c>
@@ -19176,7 +19176,7 @@
       <c r="A954" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B954" s="8"/>
+      <c r="B954" s="10"/>
       <c r="C954" s="2">
         <v>12</v>
       </c>
@@ -19188,7 +19188,7 @@
       <c r="A955" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B955" s="8"/>
+      <c r="B955" s="10"/>
       <c r="C955" s="2">
         <v>99</v>
       </c>
@@ -19630,7 +19630,7 @@
       <c r="A991" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B991" s="7" t="s">
+      <c r="B991" s="9" t="s">
         <v>740</v>
       </c>
       <c r="C991" s="3">
@@ -19644,7 +19644,7 @@
       <c r="A992" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B992" s="8"/>
+      <c r="B992" s="10"/>
       <c r="C992" s="2">
         <v>2</v>
       </c>
@@ -19656,7 +19656,7 @@
       <c r="A993" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B993" s="8"/>
+      <c r="B993" s="10"/>
       <c r="C993" s="2">
         <v>4</v>
       </c>
@@ -19668,7 +19668,7 @@
       <c r="A994" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B994" s="8"/>
+      <c r="B994" s="10"/>
       <c r="C994" s="2">
         <v>5</v>
       </c>
@@ -19680,7 +19680,7 @@
       <c r="A995" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B995" s="8"/>
+      <c r="B995" s="10"/>
       <c r="C995" s="2">
         <v>6</v>
       </c>
@@ -19692,7 +19692,7 @@
       <c r="A996" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B996" s="8"/>
+      <c r="B996" s="10"/>
       <c r="C996" s="2">
         <v>8</v>
       </c>
@@ -19704,7 +19704,7 @@
       <c r="A997" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B997" s="8"/>
+      <c r="B997" s="10"/>
       <c r="C997" s="2">
         <v>9</v>
       </c>
@@ -19716,7 +19716,7 @@
       <c r="A998" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B998" s="8"/>
+      <c r="B998" s="10"/>
       <c r="C998" s="2">
         <v>10</v>
       </c>
@@ -19728,7 +19728,7 @@
       <c r="A999" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B999" s="8"/>
+      <c r="B999" s="10"/>
       <c r="C999" s="2">
         <v>11</v>
       </c>
@@ -19740,7 +19740,7 @@
       <c r="A1000" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1000" s="8"/>
+      <c r="B1000" s="10"/>
       <c r="C1000" s="2">
         <v>12</v>
       </c>
@@ -19752,7 +19752,7 @@
       <c r="A1001" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1001" s="8"/>
+      <c r="B1001" s="10"/>
       <c r="C1001" s="2">
         <v>13</v>
       </c>
@@ -19764,7 +19764,7 @@
       <c r="A1002" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1002" s="8"/>
+      <c r="B1002" s="10"/>
       <c r="C1002" s="2">
         <v>15</v>
       </c>
@@ -19776,7 +19776,7 @@
       <c r="A1003" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1003" s="8"/>
+      <c r="B1003" s="10"/>
       <c r="C1003" s="2">
         <v>16</v>
       </c>
@@ -19788,7 +19788,7 @@
       <c r="A1004" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1004" s="8"/>
+      <c r="B1004" s="10"/>
       <c r="C1004" s="2">
         <v>17</v>
       </c>
@@ -19800,7 +19800,7 @@
       <c r="A1005" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1005" s="8"/>
+      <c r="B1005" s="10"/>
       <c r="C1005" s="2">
         <v>18</v>
       </c>
@@ -19812,7 +19812,7 @@
       <c r="A1006" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1006" s="8"/>
+      <c r="B1006" s="10"/>
       <c r="C1006" s="2">
         <v>19</v>
       </c>
@@ -19824,7 +19824,7 @@
       <c r="A1007" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1007" s="8"/>
+      <c r="B1007" s="10"/>
       <c r="C1007" s="2">
         <v>20</v>
       </c>
@@ -19836,7 +19836,7 @@
       <c r="A1008" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1008" s="8"/>
+      <c r="B1008" s="10"/>
       <c r="C1008" s="2">
         <v>21</v>
       </c>
@@ -19848,7 +19848,7 @@
       <c r="A1009" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1009" s="8"/>
+      <c r="B1009" s="10"/>
       <c r="C1009" s="2">
         <v>22</v>
       </c>
@@ -19860,7 +19860,7 @@
       <c r="A1010" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1010" s="8"/>
+      <c r="B1010" s="10"/>
       <c r="C1010" s="2">
         <v>23</v>
       </c>
@@ -19872,7 +19872,7 @@
       <c r="A1011" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1011" s="8"/>
+      <c r="B1011" s="10"/>
       <c r="C1011" s="2">
         <v>24</v>
       </c>
@@ -19884,7 +19884,7 @@
       <c r="A1012" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1012" s="8"/>
+      <c r="B1012" s="10"/>
       <c r="C1012" s="2">
         <v>25</v>
       </c>
@@ -19896,7 +19896,7 @@
       <c r="A1013" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1013" s="8"/>
+      <c r="B1013" s="10"/>
       <c r="C1013" s="2">
         <v>26</v>
       </c>
@@ -19908,7 +19908,7 @@
       <c r="A1014" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1014" s="8"/>
+      <c r="B1014" s="10"/>
       <c r="C1014" s="2">
         <v>27</v>
       </c>
@@ -19920,7 +19920,7 @@
       <c r="A1015" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1015" s="8"/>
+      <c r="B1015" s="10"/>
       <c r="C1015" s="2">
         <v>28</v>
       </c>
@@ -19932,7 +19932,7 @@
       <c r="A1016" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1016" s="8"/>
+      <c r="B1016" s="10"/>
       <c r="C1016" s="2">
         <v>29</v>
       </c>
@@ -19944,7 +19944,7 @@
       <c r="A1017" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1017" s="8"/>
+      <c r="B1017" s="10"/>
       <c r="C1017" s="2">
         <v>30</v>
       </c>
@@ -19956,7 +19956,7 @@
       <c r="A1018" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1018" s="8"/>
+      <c r="B1018" s="10"/>
       <c r="C1018" s="2">
         <v>31</v>
       </c>
@@ -19968,7 +19968,7 @@
       <c r="A1019" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1019" s="8"/>
+      <c r="B1019" s="10"/>
       <c r="C1019" s="2">
         <v>32</v>
       </c>
@@ -19980,7 +19980,7 @@
       <c r="A1020" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1020" s="8"/>
+      <c r="B1020" s="10"/>
       <c r="C1020" s="2">
         <v>33</v>
       </c>
@@ -19992,7 +19992,7 @@
       <c r="A1021" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1021" s="8"/>
+      <c r="B1021" s="10"/>
       <c r="C1021" s="2">
         <v>34</v>
       </c>
@@ -20004,7 +20004,7 @@
       <c r="A1022" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1022" s="8"/>
+      <c r="B1022" s="10"/>
       <c r="C1022" s="2">
         <v>35</v>
       </c>
@@ -20016,7 +20016,7 @@
       <c r="A1023" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1023" s="8"/>
+      <c r="B1023" s="10"/>
       <c r="C1023" s="2">
         <v>36</v>
       </c>
@@ -20028,7 +20028,7 @@
       <c r="A1024" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1024" s="8"/>
+      <c r="B1024" s="10"/>
       <c r="C1024" s="2">
         <v>37</v>
       </c>
@@ -20040,7 +20040,7 @@
       <c r="A1025" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1025" s="8"/>
+      <c r="B1025" s="10"/>
       <c r="C1025" s="2">
         <v>38</v>
       </c>
@@ -20052,7 +20052,7 @@
       <c r="A1026" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1026" s="8"/>
+      <c r="B1026" s="10"/>
       <c r="C1026" s="2">
         <v>39</v>
       </c>
@@ -20064,7 +20064,7 @@
       <c r="A1027" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1027" s="8"/>
+      <c r="B1027" s="10"/>
       <c r="C1027" s="2">
         <v>40</v>
       </c>
@@ -20076,7 +20076,7 @@
       <c r="A1028" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1028" s="8"/>
+      <c r="B1028" s="10"/>
       <c r="C1028" s="2">
         <v>41</v>
       </c>
@@ -20088,7 +20088,7 @@
       <c r="A1029" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1029" s="8"/>
+      <c r="B1029" s="10"/>
       <c r="C1029" s="2">
         <v>42</v>
       </c>
@@ -20100,7 +20100,7 @@
       <c r="A1030" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1030" s="8"/>
+      <c r="B1030" s="10"/>
       <c r="C1030" s="2">
         <v>44</v>
       </c>
@@ -20112,7 +20112,7 @@
       <c r="A1031" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1031" s="8"/>
+      <c r="B1031" s="10"/>
       <c r="C1031" s="2">
         <v>45</v>
       </c>
@@ -20124,7 +20124,7 @@
       <c r="A1032" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1032" s="8"/>
+      <c r="B1032" s="10"/>
       <c r="C1032" s="2">
         <v>46</v>
       </c>
@@ -20136,7 +20136,7 @@
       <c r="A1033" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1033" s="8"/>
+      <c r="B1033" s="10"/>
       <c r="C1033" s="2">
         <v>47</v>
       </c>
@@ -20148,7 +20148,7 @@
       <c r="A1034" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1034" s="8"/>
+      <c r="B1034" s="10"/>
       <c r="C1034" s="2">
         <v>48</v>
       </c>
@@ -20160,7 +20160,7 @@
       <c r="A1035" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1035" s="8"/>
+      <c r="B1035" s="10"/>
       <c r="C1035" s="2">
         <v>49</v>
       </c>
@@ -20172,7 +20172,7 @@
       <c r="A1036" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1036" s="8"/>
+      <c r="B1036" s="10"/>
       <c r="C1036" s="2">
         <v>50</v>
       </c>
@@ -20184,7 +20184,7 @@
       <c r="A1037" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1037" s="8"/>
+      <c r="B1037" s="10"/>
       <c r="C1037" s="2">
         <v>51</v>
       </c>
@@ -20196,7 +20196,7 @@
       <c r="A1038" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1038" s="8"/>
+      <c r="B1038" s="10"/>
       <c r="C1038" s="2">
         <v>53</v>
       </c>
@@ -20208,7 +20208,7 @@
       <c r="A1039" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1039" s="8"/>
+      <c r="B1039" s="10"/>
       <c r="C1039" s="2">
         <v>54</v>
       </c>
@@ -20220,7 +20220,7 @@
       <c r="A1040" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1040" s="8"/>
+      <c r="B1040" s="10"/>
       <c r="C1040" s="2">
         <v>55</v>
       </c>
@@ -20232,7 +20232,7 @@
       <c r="A1041" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B1041" s="8"/>
+      <c r="B1041" s="10"/>
       <c r="C1041" s="2">
         <v>56</v>
       </c>
@@ -33716,645 +33716,6 @@
     </row>
   </sheetData>
   <mergeCells count="654">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B103:B108"/>
-    <mergeCell ref="B109:B114"/>
-    <mergeCell ref="B115:B200"/>
-    <mergeCell ref="B201:B253"/>
-    <mergeCell ref="B254:B269"/>
-    <mergeCell ref="B270:B287"/>
-    <mergeCell ref="B288:B301"/>
-    <mergeCell ref="B302:B333"/>
-    <mergeCell ref="B334:B337"/>
-    <mergeCell ref="B338:B341"/>
-    <mergeCell ref="B342:B346"/>
-    <mergeCell ref="B347:B351"/>
-    <mergeCell ref="B352:B355"/>
-    <mergeCell ref="B356:B359"/>
-    <mergeCell ref="B360:B363"/>
-    <mergeCell ref="B364:B367"/>
-    <mergeCell ref="B368:B371"/>
-    <mergeCell ref="B372:B378"/>
-    <mergeCell ref="B379:B385"/>
-    <mergeCell ref="B386:B392"/>
-    <mergeCell ref="B393:B399"/>
-    <mergeCell ref="B400:B404"/>
-    <mergeCell ref="B405:B407"/>
-    <mergeCell ref="B408:B410"/>
-    <mergeCell ref="B411:B415"/>
-    <mergeCell ref="B416:B418"/>
-    <mergeCell ref="B419:B421"/>
-    <mergeCell ref="B422:B424"/>
-    <mergeCell ref="B425:B430"/>
-    <mergeCell ref="B431:B436"/>
-    <mergeCell ref="B437:B442"/>
-    <mergeCell ref="B443:B450"/>
-    <mergeCell ref="B451:B456"/>
-    <mergeCell ref="B457:B462"/>
-    <mergeCell ref="B463:B468"/>
-    <mergeCell ref="B469:B474"/>
-    <mergeCell ref="B475:B480"/>
-    <mergeCell ref="B481:B486"/>
-    <mergeCell ref="B487:B492"/>
-    <mergeCell ref="B493:B498"/>
-    <mergeCell ref="B499:B504"/>
-    <mergeCell ref="B505:B510"/>
-    <mergeCell ref="B511:B516"/>
-    <mergeCell ref="B517:B522"/>
-    <mergeCell ref="B523:B528"/>
-    <mergeCell ref="B529:B534"/>
-    <mergeCell ref="B535:B540"/>
-    <mergeCell ref="B541:B546"/>
-    <mergeCell ref="B547:B552"/>
-    <mergeCell ref="B553:B558"/>
-    <mergeCell ref="B559:B564"/>
-    <mergeCell ref="B565:B568"/>
-    <mergeCell ref="B569:B571"/>
-    <mergeCell ref="B572:B575"/>
-    <mergeCell ref="B576:B579"/>
-    <mergeCell ref="B580:B582"/>
-    <mergeCell ref="B583:B585"/>
-    <mergeCell ref="B586:B588"/>
-    <mergeCell ref="B589:B591"/>
-    <mergeCell ref="B592:B605"/>
-    <mergeCell ref="B606:B637"/>
-    <mergeCell ref="B638:B641"/>
-    <mergeCell ref="B642:B646"/>
-    <mergeCell ref="B647:B651"/>
-    <mergeCell ref="B652:B658"/>
-    <mergeCell ref="B659:B665"/>
-    <mergeCell ref="B666:B670"/>
-    <mergeCell ref="B671:B675"/>
-    <mergeCell ref="B676:B680"/>
-    <mergeCell ref="B681:B685"/>
-    <mergeCell ref="B686:B691"/>
-    <mergeCell ref="B692:B698"/>
-    <mergeCell ref="B699:B712"/>
-    <mergeCell ref="B713:B744"/>
-    <mergeCell ref="B745:B746"/>
-    <mergeCell ref="B747:B750"/>
-    <mergeCell ref="B751:B755"/>
-    <mergeCell ref="B756:B761"/>
-    <mergeCell ref="B762:B767"/>
-    <mergeCell ref="B768:B776"/>
-    <mergeCell ref="B777:B779"/>
-    <mergeCell ref="B780:B782"/>
-    <mergeCell ref="B783:B785"/>
-    <mergeCell ref="B786:B788"/>
-    <mergeCell ref="B789:B791"/>
-    <mergeCell ref="B792:B794"/>
-    <mergeCell ref="B795:B797"/>
-    <mergeCell ref="B798:B800"/>
-    <mergeCell ref="B801:B803"/>
-    <mergeCell ref="B804:B806"/>
-    <mergeCell ref="B807:B809"/>
-    <mergeCell ref="B810:B812"/>
-    <mergeCell ref="B813:B815"/>
-    <mergeCell ref="B816:B820"/>
-    <mergeCell ref="B821:B825"/>
-    <mergeCell ref="B826:B830"/>
-    <mergeCell ref="B831:B835"/>
-    <mergeCell ref="B836:B843"/>
-    <mergeCell ref="B844:B846"/>
-    <mergeCell ref="B847:B852"/>
-    <mergeCell ref="B853:B855"/>
-    <mergeCell ref="B856:B860"/>
-    <mergeCell ref="B861:B864"/>
-    <mergeCell ref="B865:B870"/>
-    <mergeCell ref="B871:B874"/>
-    <mergeCell ref="B875:B879"/>
-    <mergeCell ref="B880:B882"/>
-    <mergeCell ref="B883:B885"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="B888:B892"/>
-    <mergeCell ref="B893:B895"/>
-    <mergeCell ref="B896:B901"/>
-    <mergeCell ref="B902:B905"/>
-    <mergeCell ref="B906:B909"/>
-    <mergeCell ref="B910:B916"/>
-    <mergeCell ref="B917:B925"/>
-    <mergeCell ref="B926:B929"/>
-    <mergeCell ref="B930:B935"/>
-    <mergeCell ref="B936:B942"/>
-    <mergeCell ref="B943:B955"/>
-    <mergeCell ref="B956:B963"/>
-    <mergeCell ref="B964:B971"/>
-    <mergeCell ref="B972:B979"/>
-    <mergeCell ref="B980:B984"/>
-    <mergeCell ref="B985:B990"/>
-    <mergeCell ref="B991:B1041"/>
-    <mergeCell ref="B1042:B1076"/>
-    <mergeCell ref="B1077:B1078"/>
-    <mergeCell ref="B1079:B1080"/>
-    <mergeCell ref="B1081:B1082"/>
-    <mergeCell ref="B1083:B1084"/>
-    <mergeCell ref="B1085:B1086"/>
-    <mergeCell ref="B1087:B1088"/>
-    <mergeCell ref="B1089:B1090"/>
-    <mergeCell ref="B1091:B1092"/>
-    <mergeCell ref="B1093:B1094"/>
-    <mergeCell ref="B1095:B1096"/>
-    <mergeCell ref="B1097:B1098"/>
-    <mergeCell ref="B1099:B1100"/>
-    <mergeCell ref="B1101:B1102"/>
-    <mergeCell ref="B1103:B1104"/>
-    <mergeCell ref="B1105:B1106"/>
-    <mergeCell ref="B1107:B1108"/>
-    <mergeCell ref="B1109:B1110"/>
-    <mergeCell ref="B1111:B1112"/>
-    <mergeCell ref="B1113:B1114"/>
-    <mergeCell ref="B1115:B1116"/>
-    <mergeCell ref="B1117:B1118"/>
-    <mergeCell ref="B1119:B1120"/>
-    <mergeCell ref="B1121:B1122"/>
-    <mergeCell ref="B1123:B1124"/>
-    <mergeCell ref="B1125:B1126"/>
-    <mergeCell ref="B1127:B1128"/>
-    <mergeCell ref="B1129:B1130"/>
-    <mergeCell ref="B1131:B1132"/>
-    <mergeCell ref="B1133:B1134"/>
-    <mergeCell ref="B1135:B1136"/>
-    <mergeCell ref="B1137:B1138"/>
-    <mergeCell ref="B1139:B1140"/>
-    <mergeCell ref="B1141:B1142"/>
-    <mergeCell ref="B1143:B1144"/>
-    <mergeCell ref="B1145:B1146"/>
-    <mergeCell ref="B1147:B1148"/>
-    <mergeCell ref="B1149:B1150"/>
-    <mergeCell ref="B1151:B1152"/>
-    <mergeCell ref="B1153:B1154"/>
-    <mergeCell ref="B1155:B1156"/>
-    <mergeCell ref="B1157:B1158"/>
-    <mergeCell ref="B1159:B1160"/>
-    <mergeCell ref="B1161:B1162"/>
-    <mergeCell ref="B1163:B1164"/>
-    <mergeCell ref="B1165:B1166"/>
-    <mergeCell ref="B1167:B1168"/>
-    <mergeCell ref="B1169:B1170"/>
-    <mergeCell ref="B1171:B1172"/>
-    <mergeCell ref="B1173:B1174"/>
-    <mergeCell ref="B1175:B1176"/>
-    <mergeCell ref="B1177:B1178"/>
-    <mergeCell ref="B1179:B1180"/>
-    <mergeCell ref="B1181:B1182"/>
-    <mergeCell ref="B1183:B1184"/>
-    <mergeCell ref="B1185:B1186"/>
-    <mergeCell ref="B1187:B1188"/>
-    <mergeCell ref="B1189:B1190"/>
-    <mergeCell ref="B1191:B1192"/>
-    <mergeCell ref="B1193:B1194"/>
-    <mergeCell ref="B1195:B1196"/>
-    <mergeCell ref="B1197:B1198"/>
-    <mergeCell ref="B1199:B1200"/>
-    <mergeCell ref="B1201:B1202"/>
-    <mergeCell ref="B1203:B1204"/>
-    <mergeCell ref="B1205:B1206"/>
-    <mergeCell ref="B1207:B1208"/>
-    <mergeCell ref="B1209:B1210"/>
-    <mergeCell ref="B1211:B1212"/>
-    <mergeCell ref="B1213:B1214"/>
-    <mergeCell ref="B1215:B1216"/>
-    <mergeCell ref="B1217:B1218"/>
-    <mergeCell ref="B1219:B1220"/>
-    <mergeCell ref="B1221:B1222"/>
-    <mergeCell ref="B1223:B1224"/>
-    <mergeCell ref="B1225:B1226"/>
-    <mergeCell ref="B1227:B1228"/>
-    <mergeCell ref="B1229:B1230"/>
-    <mergeCell ref="B1231:B1232"/>
-    <mergeCell ref="B1233:B1234"/>
-    <mergeCell ref="B1235:B1236"/>
-    <mergeCell ref="B1237:B1238"/>
-    <mergeCell ref="B1239:B1240"/>
-    <mergeCell ref="B1241:B1242"/>
-    <mergeCell ref="B1243:B1244"/>
-    <mergeCell ref="B1245:B1246"/>
-    <mergeCell ref="B1247:B1248"/>
-    <mergeCell ref="B1249:B1250"/>
-    <mergeCell ref="B1251:B1252"/>
-    <mergeCell ref="B1253:B1254"/>
-    <mergeCell ref="B1255:B1256"/>
-    <mergeCell ref="B1257:B1258"/>
-    <mergeCell ref="B1259:B1260"/>
-    <mergeCell ref="B1261:B1262"/>
-    <mergeCell ref="B1263:B1264"/>
-    <mergeCell ref="B1265:B1266"/>
-    <mergeCell ref="B1267:B1268"/>
-    <mergeCell ref="B1269:B1270"/>
-    <mergeCell ref="B1271:B1272"/>
-    <mergeCell ref="B1273:B1274"/>
-    <mergeCell ref="B1275:B1276"/>
-    <mergeCell ref="B1277:B1278"/>
-    <mergeCell ref="B1279:B1280"/>
-    <mergeCell ref="B1281:B1282"/>
-    <mergeCell ref="B1283:B1284"/>
-    <mergeCell ref="B1285:B1286"/>
-    <mergeCell ref="B1287:B1288"/>
-    <mergeCell ref="B1289:B1290"/>
-    <mergeCell ref="B1291:B1292"/>
-    <mergeCell ref="B1293:B1294"/>
-    <mergeCell ref="B1295:B1296"/>
-    <mergeCell ref="B1297:B1298"/>
-    <mergeCell ref="B1299:B1300"/>
-    <mergeCell ref="B1301:B1302"/>
-    <mergeCell ref="B1303:B1304"/>
-    <mergeCell ref="B1305:B1306"/>
-    <mergeCell ref="B1307:B1308"/>
-    <mergeCell ref="B1309:B1310"/>
-    <mergeCell ref="B1311:B1312"/>
-    <mergeCell ref="B1313:B1314"/>
-    <mergeCell ref="B1315:B1316"/>
-    <mergeCell ref="B1317:B1318"/>
-    <mergeCell ref="B1319:B1320"/>
-    <mergeCell ref="B1321:B1322"/>
-    <mergeCell ref="B1323:B1324"/>
-    <mergeCell ref="B1325:B1326"/>
-    <mergeCell ref="B1327:B1328"/>
-    <mergeCell ref="B1329:B1330"/>
-    <mergeCell ref="B1331:B1332"/>
-    <mergeCell ref="B1333:B1334"/>
-    <mergeCell ref="B1335:B1336"/>
-    <mergeCell ref="B1337:B1338"/>
-    <mergeCell ref="B1339:B1340"/>
-    <mergeCell ref="B1341:B1342"/>
-    <mergeCell ref="B1343:B1344"/>
-    <mergeCell ref="B1345:B1346"/>
-    <mergeCell ref="B1347:B1348"/>
-    <mergeCell ref="B1349:B1350"/>
-    <mergeCell ref="B1351:B1352"/>
-    <mergeCell ref="B1353:B1354"/>
-    <mergeCell ref="B1355:B1356"/>
-    <mergeCell ref="B1357:B1358"/>
-    <mergeCell ref="B1359:B1360"/>
-    <mergeCell ref="B1361:B1362"/>
-    <mergeCell ref="B1363:B1364"/>
-    <mergeCell ref="B1365:B1366"/>
-    <mergeCell ref="B1367:B1368"/>
-    <mergeCell ref="B1369:B1370"/>
-    <mergeCell ref="B1371:B1372"/>
-    <mergeCell ref="B1373:B1374"/>
-    <mergeCell ref="B1375:B1376"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B1379:B1380"/>
-    <mergeCell ref="B1381:B1382"/>
-    <mergeCell ref="B1383:B1384"/>
-    <mergeCell ref="B1385:B1386"/>
-    <mergeCell ref="B1387:B1388"/>
-    <mergeCell ref="B1389:B1390"/>
-    <mergeCell ref="B1391:B1392"/>
-    <mergeCell ref="B1393:B1394"/>
-    <mergeCell ref="B1395:B1396"/>
-    <mergeCell ref="B1397:B1398"/>
-    <mergeCell ref="B1399:B1400"/>
-    <mergeCell ref="B1401:B1402"/>
-    <mergeCell ref="B1403:B1404"/>
-    <mergeCell ref="B1405:B1406"/>
-    <mergeCell ref="B1407:B1408"/>
-    <mergeCell ref="B1409:B1410"/>
-    <mergeCell ref="B1411:B1412"/>
-    <mergeCell ref="B1413:B1414"/>
-    <mergeCell ref="B1415:B1416"/>
-    <mergeCell ref="B1417:B1418"/>
-    <mergeCell ref="B1419:B1420"/>
-    <mergeCell ref="B1421:B1422"/>
-    <mergeCell ref="B1423:B1424"/>
-    <mergeCell ref="B1425:B1426"/>
-    <mergeCell ref="B1427:B1428"/>
-    <mergeCell ref="B1429:B1430"/>
-    <mergeCell ref="B1431:B1432"/>
-    <mergeCell ref="B1433:B1434"/>
-    <mergeCell ref="B1435:B1436"/>
-    <mergeCell ref="B1437:B1438"/>
-    <mergeCell ref="B1439:B1440"/>
-    <mergeCell ref="B1441:B1442"/>
-    <mergeCell ref="B1443:B1444"/>
-    <mergeCell ref="B1445:B1446"/>
-    <mergeCell ref="B1447:B1448"/>
-    <mergeCell ref="B1449:B1450"/>
-    <mergeCell ref="B1451:B1452"/>
-    <mergeCell ref="B1453:B1454"/>
-    <mergeCell ref="B1455:B1456"/>
-    <mergeCell ref="B1457:B1458"/>
-    <mergeCell ref="B1459:B1460"/>
-    <mergeCell ref="B1461:B1462"/>
-    <mergeCell ref="B1463:B1464"/>
-    <mergeCell ref="B1465:B1466"/>
-    <mergeCell ref="B1467:B1468"/>
-    <mergeCell ref="B1469:B1470"/>
-    <mergeCell ref="B1471:B1472"/>
-    <mergeCell ref="B1473:B1474"/>
-    <mergeCell ref="B1475:B1476"/>
-    <mergeCell ref="B1477:B1478"/>
-    <mergeCell ref="B1479:B1480"/>
-    <mergeCell ref="B1481:B1482"/>
-    <mergeCell ref="B1483:B1484"/>
-    <mergeCell ref="B1485:B1486"/>
-    <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="B1489:B1490"/>
-    <mergeCell ref="B1491:B1492"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1495:B1496"/>
-    <mergeCell ref="B1497:B1498"/>
-    <mergeCell ref="B1499:B1500"/>
-    <mergeCell ref="B1501:B1502"/>
-    <mergeCell ref="B1503:B1504"/>
-    <mergeCell ref="B1505:B1506"/>
-    <mergeCell ref="B1507:B1508"/>
-    <mergeCell ref="B1509:B1510"/>
-    <mergeCell ref="B1511:B1512"/>
-    <mergeCell ref="B1513:B1514"/>
-    <mergeCell ref="B1515:B1516"/>
-    <mergeCell ref="B1517:B1518"/>
-    <mergeCell ref="B1519:B1520"/>
-    <mergeCell ref="B1521:B1522"/>
-    <mergeCell ref="B1523:B1524"/>
-    <mergeCell ref="B1525:B1526"/>
-    <mergeCell ref="B1527:B1528"/>
-    <mergeCell ref="B1529:B1530"/>
-    <mergeCell ref="B1531:B1532"/>
-    <mergeCell ref="B1533:B1534"/>
-    <mergeCell ref="B1535:B1536"/>
-    <mergeCell ref="B1537:B1538"/>
-    <mergeCell ref="B1539:B1540"/>
-    <mergeCell ref="B1541:B1542"/>
-    <mergeCell ref="B1543:B1544"/>
-    <mergeCell ref="B1545:B1546"/>
-    <mergeCell ref="B1547:B1548"/>
-    <mergeCell ref="B1549:B1550"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B1553:B1554"/>
-    <mergeCell ref="B1555:B1556"/>
-    <mergeCell ref="B1557:B1558"/>
-    <mergeCell ref="B1559:B1560"/>
-    <mergeCell ref="B1561:B1562"/>
-    <mergeCell ref="B1563:B1564"/>
-    <mergeCell ref="B1565:B1566"/>
-    <mergeCell ref="B1567:B1568"/>
-    <mergeCell ref="B1569:B1570"/>
-    <mergeCell ref="B1571:B1572"/>
-    <mergeCell ref="B1573:B1574"/>
-    <mergeCell ref="B1575:B1576"/>
-    <mergeCell ref="B1577:B1578"/>
-    <mergeCell ref="B1579:B1580"/>
-    <mergeCell ref="B1581:B1582"/>
-    <mergeCell ref="B1583:B1584"/>
-    <mergeCell ref="B1585:B1586"/>
-    <mergeCell ref="B1587:B1588"/>
-    <mergeCell ref="B1589:B1590"/>
-    <mergeCell ref="B1591:B1592"/>
-    <mergeCell ref="B1593:B1594"/>
-    <mergeCell ref="B1595:B1596"/>
-    <mergeCell ref="B1597:B1598"/>
-    <mergeCell ref="B1599:B1600"/>
-    <mergeCell ref="B1601:B1602"/>
-    <mergeCell ref="B1603:B1604"/>
-    <mergeCell ref="B1605:B1606"/>
-    <mergeCell ref="B1607:B1608"/>
-    <mergeCell ref="B1609:B1610"/>
-    <mergeCell ref="B1611:B1612"/>
-    <mergeCell ref="B1613:B1614"/>
-    <mergeCell ref="B1615:B1616"/>
-    <mergeCell ref="B1617:B1618"/>
-    <mergeCell ref="B1619:B1620"/>
-    <mergeCell ref="B1621:B1622"/>
-    <mergeCell ref="B1623:B1624"/>
-    <mergeCell ref="B1625:B1626"/>
-    <mergeCell ref="B1627:B1628"/>
-    <mergeCell ref="B1629:B1630"/>
-    <mergeCell ref="B1631:B1632"/>
-    <mergeCell ref="B1633:B1634"/>
-    <mergeCell ref="B1635:B1636"/>
-    <mergeCell ref="B1637:B1638"/>
-    <mergeCell ref="B1639:B1640"/>
-    <mergeCell ref="B1641:B1642"/>
-    <mergeCell ref="B1643:B1644"/>
-    <mergeCell ref="B1645:B1646"/>
-    <mergeCell ref="B1647:B1648"/>
-    <mergeCell ref="B1649:B1650"/>
-    <mergeCell ref="B1651:B1652"/>
-    <mergeCell ref="B1653:B1654"/>
-    <mergeCell ref="B1655:B1656"/>
-    <mergeCell ref="B1657:B1658"/>
-    <mergeCell ref="B1659:B1660"/>
-    <mergeCell ref="B1661:B1662"/>
-    <mergeCell ref="B1663:B1664"/>
-    <mergeCell ref="B1665:B1666"/>
-    <mergeCell ref="B1667:B1668"/>
-    <mergeCell ref="B1669:B1670"/>
-    <mergeCell ref="B1671:B1672"/>
-    <mergeCell ref="B1673:B1674"/>
-    <mergeCell ref="B1675:B1676"/>
-    <mergeCell ref="B1677:B1678"/>
-    <mergeCell ref="B1679:B1680"/>
-    <mergeCell ref="B1681:B1682"/>
-    <mergeCell ref="B1683:B1684"/>
-    <mergeCell ref="B1685:B1686"/>
-    <mergeCell ref="B1687:B1688"/>
-    <mergeCell ref="B1689:B1690"/>
-    <mergeCell ref="B1691:B1692"/>
-    <mergeCell ref="B1693:B1694"/>
-    <mergeCell ref="B1695:B1696"/>
-    <mergeCell ref="B1697:B1698"/>
-    <mergeCell ref="B1699:B1700"/>
-    <mergeCell ref="B1701:B1702"/>
-    <mergeCell ref="B1703:B1704"/>
-    <mergeCell ref="B1705:B1706"/>
-    <mergeCell ref="B1707:B1708"/>
-    <mergeCell ref="B1709:B1710"/>
-    <mergeCell ref="B1711:B1712"/>
-    <mergeCell ref="B1713:B1714"/>
-    <mergeCell ref="B1715:B1716"/>
-    <mergeCell ref="B1717:B1718"/>
-    <mergeCell ref="B1719:B1720"/>
-    <mergeCell ref="B1721:B1722"/>
-    <mergeCell ref="B1723:B1724"/>
-    <mergeCell ref="B1725:B1726"/>
-    <mergeCell ref="B1727:B1728"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="B1731:B1732"/>
-    <mergeCell ref="B1733:B1734"/>
-    <mergeCell ref="B1735:B1736"/>
-    <mergeCell ref="B1737:B1738"/>
-    <mergeCell ref="B1739:B1740"/>
-    <mergeCell ref="B1741:B1742"/>
-    <mergeCell ref="B1743:B1744"/>
-    <mergeCell ref="B1745:B1746"/>
-    <mergeCell ref="B1747:B1748"/>
-    <mergeCell ref="B1749:B1750"/>
-    <mergeCell ref="B1751:B1752"/>
-    <mergeCell ref="B1753:B1754"/>
-    <mergeCell ref="B1755:B1756"/>
-    <mergeCell ref="B1757:B1758"/>
-    <mergeCell ref="B1759:B1760"/>
-    <mergeCell ref="B1761:B1762"/>
-    <mergeCell ref="B1763:B1764"/>
-    <mergeCell ref="B1765:B1766"/>
-    <mergeCell ref="B1767:B1768"/>
-    <mergeCell ref="B1769:B1770"/>
-    <mergeCell ref="B1771:B1772"/>
-    <mergeCell ref="B1773:B1774"/>
-    <mergeCell ref="B1775:B1776"/>
-    <mergeCell ref="B1777:B1778"/>
-    <mergeCell ref="B1779:B1780"/>
-    <mergeCell ref="B1781:B1782"/>
-    <mergeCell ref="B1783:B1784"/>
-    <mergeCell ref="B1785:B1786"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B1789:B1790"/>
-    <mergeCell ref="B1791:B1792"/>
-    <mergeCell ref="B1793:B1794"/>
-    <mergeCell ref="B1795:B1796"/>
-    <mergeCell ref="B1797:B1798"/>
-    <mergeCell ref="B1799:B1800"/>
-    <mergeCell ref="B1801:B1802"/>
-    <mergeCell ref="B1803:B1804"/>
-    <mergeCell ref="B1805:B1806"/>
-    <mergeCell ref="B1807:B1808"/>
-    <mergeCell ref="B1809:B1810"/>
-    <mergeCell ref="B1811:B1812"/>
-    <mergeCell ref="B1813:B1814"/>
-    <mergeCell ref="B1815:B1816"/>
-    <mergeCell ref="B1817:B1818"/>
-    <mergeCell ref="B1819:B1820"/>
-    <mergeCell ref="B1821:B1822"/>
-    <mergeCell ref="B1823:B1824"/>
-    <mergeCell ref="B1825:B1826"/>
-    <mergeCell ref="B1827:B1828"/>
-    <mergeCell ref="B1829:B1830"/>
-    <mergeCell ref="B1831:B1832"/>
-    <mergeCell ref="B1833:B1834"/>
-    <mergeCell ref="B1835:B1836"/>
-    <mergeCell ref="B1837:B1838"/>
-    <mergeCell ref="B1839:B1840"/>
-    <mergeCell ref="B1841:B1842"/>
-    <mergeCell ref="B1843:B1844"/>
-    <mergeCell ref="B1845:B1846"/>
-    <mergeCell ref="B1847:B1848"/>
-    <mergeCell ref="B1849:B1850"/>
-    <mergeCell ref="B1851:B1852"/>
-    <mergeCell ref="B1853:B1854"/>
-    <mergeCell ref="B1855:B1856"/>
-    <mergeCell ref="B1857:B1858"/>
-    <mergeCell ref="B1859:B1860"/>
-    <mergeCell ref="B1861:B1862"/>
-    <mergeCell ref="B1863:B1864"/>
-    <mergeCell ref="B1865:B1866"/>
-    <mergeCell ref="B1867:B1868"/>
-    <mergeCell ref="B1869:B1870"/>
-    <mergeCell ref="B1871:B1872"/>
-    <mergeCell ref="B1873:B1874"/>
-    <mergeCell ref="B1875:B1876"/>
-    <mergeCell ref="B1877:B1878"/>
-    <mergeCell ref="B1879:B1880"/>
-    <mergeCell ref="B1881:B1882"/>
-    <mergeCell ref="B1883:B1884"/>
-    <mergeCell ref="B1885:B1886"/>
-    <mergeCell ref="B1887:B1888"/>
-    <mergeCell ref="B1889:B1890"/>
-    <mergeCell ref="B1891:B1892"/>
-    <mergeCell ref="B1893:B1894"/>
-    <mergeCell ref="B1895:B1896"/>
-    <mergeCell ref="B1897:B1898"/>
-    <mergeCell ref="B1899:B1900"/>
-    <mergeCell ref="B1901:B1902"/>
-    <mergeCell ref="B1903:B1904"/>
-    <mergeCell ref="B1905:B1906"/>
-    <mergeCell ref="B1907:B1908"/>
-    <mergeCell ref="B1909:B1910"/>
-    <mergeCell ref="B1911:B1912"/>
-    <mergeCell ref="B1913:B1914"/>
-    <mergeCell ref="B1915:B1916"/>
-    <mergeCell ref="B1917:B1918"/>
-    <mergeCell ref="B1919:B1920"/>
-    <mergeCell ref="B1921:B1922"/>
-    <mergeCell ref="B1923:B1924"/>
-    <mergeCell ref="B1925:B1926"/>
-    <mergeCell ref="B1927:B1928"/>
-    <mergeCell ref="B1929:B1930"/>
-    <mergeCell ref="B1931:B1932"/>
-    <mergeCell ref="B1933:B1934"/>
-    <mergeCell ref="B1935:B1936"/>
-    <mergeCell ref="B1937:B1938"/>
-    <mergeCell ref="B1939:B1940"/>
-    <mergeCell ref="B1941:B1942"/>
-    <mergeCell ref="B1943:B1944"/>
-    <mergeCell ref="B1945:B1946"/>
-    <mergeCell ref="B1947:B1948"/>
-    <mergeCell ref="B1949:B1950"/>
-    <mergeCell ref="B1951:B1952"/>
-    <mergeCell ref="B1953:B1954"/>
-    <mergeCell ref="B1955:B1956"/>
-    <mergeCell ref="B1957:B1958"/>
-    <mergeCell ref="B1959:B1960"/>
-    <mergeCell ref="B1961:B1962"/>
-    <mergeCell ref="B1963:B1964"/>
-    <mergeCell ref="B1965:B1966"/>
-    <mergeCell ref="B1967:B1968"/>
-    <mergeCell ref="B1969:B1970"/>
-    <mergeCell ref="B1971:B1972"/>
-    <mergeCell ref="B1973:B1974"/>
-    <mergeCell ref="B1975:B1976"/>
-    <mergeCell ref="B1977:B1978"/>
-    <mergeCell ref="B1979:B1980"/>
-    <mergeCell ref="B1981:B1982"/>
-    <mergeCell ref="B1983:B1984"/>
-    <mergeCell ref="B1985:B1986"/>
-    <mergeCell ref="B1987:B1988"/>
-    <mergeCell ref="B1989:B1990"/>
-    <mergeCell ref="B1991:B1992"/>
-    <mergeCell ref="B1993:B1994"/>
-    <mergeCell ref="B1995:B1996"/>
-    <mergeCell ref="B1997:B1998"/>
-    <mergeCell ref="B1999:B2000"/>
-    <mergeCell ref="B2001:B2002"/>
-    <mergeCell ref="B2003:B2004"/>
-    <mergeCell ref="B2005:B2006"/>
-    <mergeCell ref="B2007:B2008"/>
-    <mergeCell ref="B2009:B2010"/>
-    <mergeCell ref="B2011:B2012"/>
-    <mergeCell ref="B2013:B2014"/>
-    <mergeCell ref="B2015:B2016"/>
-    <mergeCell ref="B2017:B2018"/>
-    <mergeCell ref="B2019:B2020"/>
-    <mergeCell ref="B2021:B2022"/>
-    <mergeCell ref="B2023:B2024"/>
-    <mergeCell ref="B2025:B2026"/>
-    <mergeCell ref="B2027:B2028"/>
-    <mergeCell ref="B2029:B2030"/>
-    <mergeCell ref="B2031:B2032"/>
-    <mergeCell ref="B2033:B2034"/>
-    <mergeCell ref="B2035:B2036"/>
-    <mergeCell ref="B2037:B2038"/>
-    <mergeCell ref="B2039:B2040"/>
-    <mergeCell ref="B2041:B2042"/>
-    <mergeCell ref="B2043:B2044"/>
-    <mergeCell ref="B2045:B2046"/>
-    <mergeCell ref="B2047:B2048"/>
-    <mergeCell ref="B2049:B2050"/>
     <mergeCell ref="B2069:B2070"/>
     <mergeCell ref="B2071:B2072"/>
     <mergeCell ref="B2073:B2074"/>
@@ -34370,6 +33731,645 @@
     <mergeCell ref="B2063:B2064"/>
     <mergeCell ref="B2065:B2066"/>
     <mergeCell ref="B2067:B2068"/>
+    <mergeCell ref="B2033:B2034"/>
+    <mergeCell ref="B2035:B2036"/>
+    <mergeCell ref="B2037:B2038"/>
+    <mergeCell ref="B2039:B2040"/>
+    <mergeCell ref="B2041:B2042"/>
+    <mergeCell ref="B2043:B2044"/>
+    <mergeCell ref="B2045:B2046"/>
+    <mergeCell ref="B2047:B2048"/>
+    <mergeCell ref="B2049:B2050"/>
+    <mergeCell ref="B2015:B2016"/>
+    <mergeCell ref="B2017:B2018"/>
+    <mergeCell ref="B2019:B2020"/>
+    <mergeCell ref="B2021:B2022"/>
+    <mergeCell ref="B2023:B2024"/>
+    <mergeCell ref="B2025:B2026"/>
+    <mergeCell ref="B2027:B2028"/>
+    <mergeCell ref="B2029:B2030"/>
+    <mergeCell ref="B2031:B2032"/>
+    <mergeCell ref="B1997:B1998"/>
+    <mergeCell ref="B1999:B2000"/>
+    <mergeCell ref="B2001:B2002"/>
+    <mergeCell ref="B2003:B2004"/>
+    <mergeCell ref="B2005:B2006"/>
+    <mergeCell ref="B2007:B2008"/>
+    <mergeCell ref="B2009:B2010"/>
+    <mergeCell ref="B2011:B2012"/>
+    <mergeCell ref="B2013:B2014"/>
+    <mergeCell ref="B1979:B1980"/>
+    <mergeCell ref="B1981:B1982"/>
+    <mergeCell ref="B1983:B1984"/>
+    <mergeCell ref="B1985:B1986"/>
+    <mergeCell ref="B1987:B1988"/>
+    <mergeCell ref="B1989:B1990"/>
+    <mergeCell ref="B1991:B1992"/>
+    <mergeCell ref="B1993:B1994"/>
+    <mergeCell ref="B1995:B1996"/>
+    <mergeCell ref="B1961:B1962"/>
+    <mergeCell ref="B1963:B1964"/>
+    <mergeCell ref="B1965:B1966"/>
+    <mergeCell ref="B1967:B1968"/>
+    <mergeCell ref="B1969:B1970"/>
+    <mergeCell ref="B1971:B1972"/>
+    <mergeCell ref="B1973:B1974"/>
+    <mergeCell ref="B1975:B1976"/>
+    <mergeCell ref="B1977:B1978"/>
+    <mergeCell ref="B1943:B1944"/>
+    <mergeCell ref="B1945:B1946"/>
+    <mergeCell ref="B1947:B1948"/>
+    <mergeCell ref="B1949:B1950"/>
+    <mergeCell ref="B1951:B1952"/>
+    <mergeCell ref="B1953:B1954"/>
+    <mergeCell ref="B1955:B1956"/>
+    <mergeCell ref="B1957:B1958"/>
+    <mergeCell ref="B1959:B1960"/>
+    <mergeCell ref="B1925:B1926"/>
+    <mergeCell ref="B1927:B1928"/>
+    <mergeCell ref="B1929:B1930"/>
+    <mergeCell ref="B1931:B1932"/>
+    <mergeCell ref="B1933:B1934"/>
+    <mergeCell ref="B1935:B1936"/>
+    <mergeCell ref="B1937:B1938"/>
+    <mergeCell ref="B1939:B1940"/>
+    <mergeCell ref="B1941:B1942"/>
+    <mergeCell ref="B1907:B1908"/>
+    <mergeCell ref="B1909:B1910"/>
+    <mergeCell ref="B1911:B1912"/>
+    <mergeCell ref="B1913:B1914"/>
+    <mergeCell ref="B1915:B1916"/>
+    <mergeCell ref="B1917:B1918"/>
+    <mergeCell ref="B1919:B1920"/>
+    <mergeCell ref="B1921:B1922"/>
+    <mergeCell ref="B1923:B1924"/>
+    <mergeCell ref="B1889:B1890"/>
+    <mergeCell ref="B1891:B1892"/>
+    <mergeCell ref="B1893:B1894"/>
+    <mergeCell ref="B1895:B1896"/>
+    <mergeCell ref="B1897:B1898"/>
+    <mergeCell ref="B1899:B1900"/>
+    <mergeCell ref="B1901:B1902"/>
+    <mergeCell ref="B1903:B1904"/>
+    <mergeCell ref="B1905:B1906"/>
+    <mergeCell ref="B1871:B1872"/>
+    <mergeCell ref="B1873:B1874"/>
+    <mergeCell ref="B1875:B1876"/>
+    <mergeCell ref="B1877:B1878"/>
+    <mergeCell ref="B1879:B1880"/>
+    <mergeCell ref="B1881:B1882"/>
+    <mergeCell ref="B1883:B1884"/>
+    <mergeCell ref="B1885:B1886"/>
+    <mergeCell ref="B1887:B1888"/>
+    <mergeCell ref="B1853:B1854"/>
+    <mergeCell ref="B1855:B1856"/>
+    <mergeCell ref="B1857:B1858"/>
+    <mergeCell ref="B1859:B1860"/>
+    <mergeCell ref="B1861:B1862"/>
+    <mergeCell ref="B1863:B1864"/>
+    <mergeCell ref="B1865:B1866"/>
+    <mergeCell ref="B1867:B1868"/>
+    <mergeCell ref="B1869:B1870"/>
+    <mergeCell ref="B1835:B1836"/>
+    <mergeCell ref="B1837:B1838"/>
+    <mergeCell ref="B1839:B1840"/>
+    <mergeCell ref="B1841:B1842"/>
+    <mergeCell ref="B1843:B1844"/>
+    <mergeCell ref="B1845:B1846"/>
+    <mergeCell ref="B1847:B1848"/>
+    <mergeCell ref="B1849:B1850"/>
+    <mergeCell ref="B1851:B1852"/>
+    <mergeCell ref="B1817:B1818"/>
+    <mergeCell ref="B1819:B1820"/>
+    <mergeCell ref="B1821:B1822"/>
+    <mergeCell ref="B1823:B1824"/>
+    <mergeCell ref="B1825:B1826"/>
+    <mergeCell ref="B1827:B1828"/>
+    <mergeCell ref="B1829:B1830"/>
+    <mergeCell ref="B1831:B1832"/>
+    <mergeCell ref="B1833:B1834"/>
+    <mergeCell ref="B1799:B1800"/>
+    <mergeCell ref="B1801:B1802"/>
+    <mergeCell ref="B1803:B1804"/>
+    <mergeCell ref="B1805:B1806"/>
+    <mergeCell ref="B1807:B1808"/>
+    <mergeCell ref="B1809:B1810"/>
+    <mergeCell ref="B1811:B1812"/>
+    <mergeCell ref="B1813:B1814"/>
+    <mergeCell ref="B1815:B1816"/>
+    <mergeCell ref="B1781:B1782"/>
+    <mergeCell ref="B1783:B1784"/>
+    <mergeCell ref="B1785:B1786"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B1789:B1790"/>
+    <mergeCell ref="B1791:B1792"/>
+    <mergeCell ref="B1793:B1794"/>
+    <mergeCell ref="B1795:B1796"/>
+    <mergeCell ref="B1797:B1798"/>
+    <mergeCell ref="B1763:B1764"/>
+    <mergeCell ref="B1765:B1766"/>
+    <mergeCell ref="B1767:B1768"/>
+    <mergeCell ref="B1769:B1770"/>
+    <mergeCell ref="B1771:B1772"/>
+    <mergeCell ref="B1773:B1774"/>
+    <mergeCell ref="B1775:B1776"/>
+    <mergeCell ref="B1777:B1778"/>
+    <mergeCell ref="B1779:B1780"/>
+    <mergeCell ref="B1745:B1746"/>
+    <mergeCell ref="B1747:B1748"/>
+    <mergeCell ref="B1749:B1750"/>
+    <mergeCell ref="B1751:B1752"/>
+    <mergeCell ref="B1753:B1754"/>
+    <mergeCell ref="B1755:B1756"/>
+    <mergeCell ref="B1757:B1758"/>
+    <mergeCell ref="B1759:B1760"/>
+    <mergeCell ref="B1761:B1762"/>
+    <mergeCell ref="B1727:B1728"/>
+    <mergeCell ref="B1729:B1730"/>
+    <mergeCell ref="B1731:B1732"/>
+    <mergeCell ref="B1733:B1734"/>
+    <mergeCell ref="B1735:B1736"/>
+    <mergeCell ref="B1737:B1738"/>
+    <mergeCell ref="B1739:B1740"/>
+    <mergeCell ref="B1741:B1742"/>
+    <mergeCell ref="B1743:B1744"/>
+    <mergeCell ref="B1709:B1710"/>
+    <mergeCell ref="B1711:B1712"/>
+    <mergeCell ref="B1713:B1714"/>
+    <mergeCell ref="B1715:B1716"/>
+    <mergeCell ref="B1717:B1718"/>
+    <mergeCell ref="B1719:B1720"/>
+    <mergeCell ref="B1721:B1722"/>
+    <mergeCell ref="B1723:B1724"/>
+    <mergeCell ref="B1725:B1726"/>
+    <mergeCell ref="B1691:B1692"/>
+    <mergeCell ref="B1693:B1694"/>
+    <mergeCell ref="B1695:B1696"/>
+    <mergeCell ref="B1697:B1698"/>
+    <mergeCell ref="B1699:B1700"/>
+    <mergeCell ref="B1701:B1702"/>
+    <mergeCell ref="B1703:B1704"/>
+    <mergeCell ref="B1705:B1706"/>
+    <mergeCell ref="B1707:B1708"/>
+    <mergeCell ref="B1673:B1674"/>
+    <mergeCell ref="B1675:B1676"/>
+    <mergeCell ref="B1677:B1678"/>
+    <mergeCell ref="B1679:B1680"/>
+    <mergeCell ref="B1681:B1682"/>
+    <mergeCell ref="B1683:B1684"/>
+    <mergeCell ref="B1685:B1686"/>
+    <mergeCell ref="B1687:B1688"/>
+    <mergeCell ref="B1689:B1690"/>
+    <mergeCell ref="B1655:B1656"/>
+    <mergeCell ref="B1657:B1658"/>
+    <mergeCell ref="B1659:B1660"/>
+    <mergeCell ref="B1661:B1662"/>
+    <mergeCell ref="B1663:B1664"/>
+    <mergeCell ref="B1665:B1666"/>
+    <mergeCell ref="B1667:B1668"/>
+    <mergeCell ref="B1669:B1670"/>
+    <mergeCell ref="B1671:B1672"/>
+    <mergeCell ref="B1637:B1638"/>
+    <mergeCell ref="B1639:B1640"/>
+    <mergeCell ref="B1641:B1642"/>
+    <mergeCell ref="B1643:B1644"/>
+    <mergeCell ref="B1645:B1646"/>
+    <mergeCell ref="B1647:B1648"/>
+    <mergeCell ref="B1649:B1650"/>
+    <mergeCell ref="B1651:B1652"/>
+    <mergeCell ref="B1653:B1654"/>
+    <mergeCell ref="B1619:B1620"/>
+    <mergeCell ref="B1621:B1622"/>
+    <mergeCell ref="B1623:B1624"/>
+    <mergeCell ref="B1625:B1626"/>
+    <mergeCell ref="B1627:B1628"/>
+    <mergeCell ref="B1629:B1630"/>
+    <mergeCell ref="B1631:B1632"/>
+    <mergeCell ref="B1633:B1634"/>
+    <mergeCell ref="B1635:B1636"/>
+    <mergeCell ref="B1601:B1602"/>
+    <mergeCell ref="B1603:B1604"/>
+    <mergeCell ref="B1605:B1606"/>
+    <mergeCell ref="B1607:B1608"/>
+    <mergeCell ref="B1609:B1610"/>
+    <mergeCell ref="B1611:B1612"/>
+    <mergeCell ref="B1613:B1614"/>
+    <mergeCell ref="B1615:B1616"/>
+    <mergeCell ref="B1617:B1618"/>
+    <mergeCell ref="B1583:B1584"/>
+    <mergeCell ref="B1585:B1586"/>
+    <mergeCell ref="B1587:B1588"/>
+    <mergeCell ref="B1589:B1590"/>
+    <mergeCell ref="B1591:B1592"/>
+    <mergeCell ref="B1593:B1594"/>
+    <mergeCell ref="B1595:B1596"/>
+    <mergeCell ref="B1597:B1598"/>
+    <mergeCell ref="B1599:B1600"/>
+    <mergeCell ref="B1565:B1566"/>
+    <mergeCell ref="B1567:B1568"/>
+    <mergeCell ref="B1569:B1570"/>
+    <mergeCell ref="B1571:B1572"/>
+    <mergeCell ref="B1573:B1574"/>
+    <mergeCell ref="B1575:B1576"/>
+    <mergeCell ref="B1577:B1578"/>
+    <mergeCell ref="B1579:B1580"/>
+    <mergeCell ref="B1581:B1582"/>
+    <mergeCell ref="B1547:B1548"/>
+    <mergeCell ref="B1549:B1550"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B1553:B1554"/>
+    <mergeCell ref="B1555:B1556"/>
+    <mergeCell ref="B1557:B1558"/>
+    <mergeCell ref="B1559:B1560"/>
+    <mergeCell ref="B1561:B1562"/>
+    <mergeCell ref="B1563:B1564"/>
+    <mergeCell ref="B1529:B1530"/>
+    <mergeCell ref="B1531:B1532"/>
+    <mergeCell ref="B1533:B1534"/>
+    <mergeCell ref="B1535:B1536"/>
+    <mergeCell ref="B1537:B1538"/>
+    <mergeCell ref="B1539:B1540"/>
+    <mergeCell ref="B1541:B1542"/>
+    <mergeCell ref="B1543:B1544"/>
+    <mergeCell ref="B1545:B1546"/>
+    <mergeCell ref="B1511:B1512"/>
+    <mergeCell ref="B1513:B1514"/>
+    <mergeCell ref="B1515:B1516"/>
+    <mergeCell ref="B1517:B1518"/>
+    <mergeCell ref="B1519:B1520"/>
+    <mergeCell ref="B1521:B1522"/>
+    <mergeCell ref="B1523:B1524"/>
+    <mergeCell ref="B1525:B1526"/>
+    <mergeCell ref="B1527:B1528"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1495:B1496"/>
+    <mergeCell ref="B1497:B1498"/>
+    <mergeCell ref="B1499:B1500"/>
+    <mergeCell ref="B1501:B1502"/>
+    <mergeCell ref="B1503:B1504"/>
+    <mergeCell ref="B1505:B1506"/>
+    <mergeCell ref="B1507:B1508"/>
+    <mergeCell ref="B1509:B1510"/>
+    <mergeCell ref="B1475:B1476"/>
+    <mergeCell ref="B1477:B1478"/>
+    <mergeCell ref="B1479:B1480"/>
+    <mergeCell ref="B1481:B1482"/>
+    <mergeCell ref="B1483:B1484"/>
+    <mergeCell ref="B1485:B1486"/>
+    <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="B1489:B1490"/>
+    <mergeCell ref="B1491:B1492"/>
+    <mergeCell ref="B1457:B1458"/>
+    <mergeCell ref="B1459:B1460"/>
+    <mergeCell ref="B1461:B1462"/>
+    <mergeCell ref="B1463:B1464"/>
+    <mergeCell ref="B1465:B1466"/>
+    <mergeCell ref="B1467:B1468"/>
+    <mergeCell ref="B1469:B1470"/>
+    <mergeCell ref="B1471:B1472"/>
+    <mergeCell ref="B1473:B1474"/>
+    <mergeCell ref="B1439:B1440"/>
+    <mergeCell ref="B1441:B1442"/>
+    <mergeCell ref="B1443:B1444"/>
+    <mergeCell ref="B1445:B1446"/>
+    <mergeCell ref="B1447:B1448"/>
+    <mergeCell ref="B1449:B1450"/>
+    <mergeCell ref="B1451:B1452"/>
+    <mergeCell ref="B1453:B1454"/>
+    <mergeCell ref="B1455:B1456"/>
+    <mergeCell ref="B1421:B1422"/>
+    <mergeCell ref="B1423:B1424"/>
+    <mergeCell ref="B1425:B1426"/>
+    <mergeCell ref="B1427:B1428"/>
+    <mergeCell ref="B1429:B1430"/>
+    <mergeCell ref="B1431:B1432"/>
+    <mergeCell ref="B1433:B1434"/>
+    <mergeCell ref="B1435:B1436"/>
+    <mergeCell ref="B1437:B1438"/>
+    <mergeCell ref="B1403:B1404"/>
+    <mergeCell ref="B1405:B1406"/>
+    <mergeCell ref="B1407:B1408"/>
+    <mergeCell ref="B1409:B1410"/>
+    <mergeCell ref="B1411:B1412"/>
+    <mergeCell ref="B1413:B1414"/>
+    <mergeCell ref="B1415:B1416"/>
+    <mergeCell ref="B1417:B1418"/>
+    <mergeCell ref="B1419:B1420"/>
+    <mergeCell ref="B1385:B1386"/>
+    <mergeCell ref="B1387:B1388"/>
+    <mergeCell ref="B1389:B1390"/>
+    <mergeCell ref="B1391:B1392"/>
+    <mergeCell ref="B1393:B1394"/>
+    <mergeCell ref="B1395:B1396"/>
+    <mergeCell ref="B1397:B1398"/>
+    <mergeCell ref="B1399:B1400"/>
+    <mergeCell ref="B1401:B1402"/>
+    <mergeCell ref="B1367:B1368"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1371:B1372"/>
+    <mergeCell ref="B1373:B1374"/>
+    <mergeCell ref="B1375:B1376"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B1379:B1380"/>
+    <mergeCell ref="B1381:B1382"/>
+    <mergeCell ref="B1383:B1384"/>
+    <mergeCell ref="B1349:B1350"/>
+    <mergeCell ref="B1351:B1352"/>
+    <mergeCell ref="B1353:B1354"/>
+    <mergeCell ref="B1355:B1356"/>
+    <mergeCell ref="B1357:B1358"/>
+    <mergeCell ref="B1359:B1360"/>
+    <mergeCell ref="B1361:B1362"/>
+    <mergeCell ref="B1363:B1364"/>
+    <mergeCell ref="B1365:B1366"/>
+    <mergeCell ref="B1331:B1332"/>
+    <mergeCell ref="B1333:B1334"/>
+    <mergeCell ref="B1335:B1336"/>
+    <mergeCell ref="B1337:B1338"/>
+    <mergeCell ref="B1339:B1340"/>
+    <mergeCell ref="B1341:B1342"/>
+    <mergeCell ref="B1343:B1344"/>
+    <mergeCell ref="B1345:B1346"/>
+    <mergeCell ref="B1347:B1348"/>
+    <mergeCell ref="B1313:B1314"/>
+    <mergeCell ref="B1315:B1316"/>
+    <mergeCell ref="B1317:B1318"/>
+    <mergeCell ref="B1319:B1320"/>
+    <mergeCell ref="B1321:B1322"/>
+    <mergeCell ref="B1323:B1324"/>
+    <mergeCell ref="B1325:B1326"/>
+    <mergeCell ref="B1327:B1328"/>
+    <mergeCell ref="B1329:B1330"/>
+    <mergeCell ref="B1295:B1296"/>
+    <mergeCell ref="B1297:B1298"/>
+    <mergeCell ref="B1299:B1300"/>
+    <mergeCell ref="B1301:B1302"/>
+    <mergeCell ref="B1303:B1304"/>
+    <mergeCell ref="B1305:B1306"/>
+    <mergeCell ref="B1307:B1308"/>
+    <mergeCell ref="B1309:B1310"/>
+    <mergeCell ref="B1311:B1312"/>
+    <mergeCell ref="B1277:B1278"/>
+    <mergeCell ref="B1279:B1280"/>
+    <mergeCell ref="B1281:B1282"/>
+    <mergeCell ref="B1283:B1284"/>
+    <mergeCell ref="B1285:B1286"/>
+    <mergeCell ref="B1287:B1288"/>
+    <mergeCell ref="B1289:B1290"/>
+    <mergeCell ref="B1291:B1292"/>
+    <mergeCell ref="B1293:B1294"/>
+    <mergeCell ref="B1259:B1260"/>
+    <mergeCell ref="B1261:B1262"/>
+    <mergeCell ref="B1263:B1264"/>
+    <mergeCell ref="B1265:B1266"/>
+    <mergeCell ref="B1267:B1268"/>
+    <mergeCell ref="B1269:B1270"/>
+    <mergeCell ref="B1271:B1272"/>
+    <mergeCell ref="B1273:B1274"/>
+    <mergeCell ref="B1275:B1276"/>
+    <mergeCell ref="B1241:B1242"/>
+    <mergeCell ref="B1243:B1244"/>
+    <mergeCell ref="B1245:B1246"/>
+    <mergeCell ref="B1247:B1248"/>
+    <mergeCell ref="B1249:B1250"/>
+    <mergeCell ref="B1251:B1252"/>
+    <mergeCell ref="B1253:B1254"/>
+    <mergeCell ref="B1255:B1256"/>
+    <mergeCell ref="B1257:B1258"/>
+    <mergeCell ref="B1223:B1224"/>
+    <mergeCell ref="B1225:B1226"/>
+    <mergeCell ref="B1227:B1228"/>
+    <mergeCell ref="B1229:B1230"/>
+    <mergeCell ref="B1231:B1232"/>
+    <mergeCell ref="B1233:B1234"/>
+    <mergeCell ref="B1235:B1236"/>
+    <mergeCell ref="B1237:B1238"/>
+    <mergeCell ref="B1239:B1240"/>
+    <mergeCell ref="B1205:B1206"/>
+    <mergeCell ref="B1207:B1208"/>
+    <mergeCell ref="B1209:B1210"/>
+    <mergeCell ref="B1211:B1212"/>
+    <mergeCell ref="B1213:B1214"/>
+    <mergeCell ref="B1215:B1216"/>
+    <mergeCell ref="B1217:B1218"/>
+    <mergeCell ref="B1219:B1220"/>
+    <mergeCell ref="B1221:B1222"/>
+    <mergeCell ref="B1187:B1188"/>
+    <mergeCell ref="B1189:B1190"/>
+    <mergeCell ref="B1191:B1192"/>
+    <mergeCell ref="B1193:B1194"/>
+    <mergeCell ref="B1195:B1196"/>
+    <mergeCell ref="B1197:B1198"/>
+    <mergeCell ref="B1199:B1200"/>
+    <mergeCell ref="B1201:B1202"/>
+    <mergeCell ref="B1203:B1204"/>
+    <mergeCell ref="B1169:B1170"/>
+    <mergeCell ref="B1171:B1172"/>
+    <mergeCell ref="B1173:B1174"/>
+    <mergeCell ref="B1175:B1176"/>
+    <mergeCell ref="B1177:B1178"/>
+    <mergeCell ref="B1179:B1180"/>
+    <mergeCell ref="B1181:B1182"/>
+    <mergeCell ref="B1183:B1184"/>
+    <mergeCell ref="B1185:B1186"/>
+    <mergeCell ref="B1151:B1152"/>
+    <mergeCell ref="B1153:B1154"/>
+    <mergeCell ref="B1155:B1156"/>
+    <mergeCell ref="B1157:B1158"/>
+    <mergeCell ref="B1159:B1160"/>
+    <mergeCell ref="B1161:B1162"/>
+    <mergeCell ref="B1163:B1164"/>
+    <mergeCell ref="B1165:B1166"/>
+    <mergeCell ref="B1167:B1168"/>
+    <mergeCell ref="B1133:B1134"/>
+    <mergeCell ref="B1135:B1136"/>
+    <mergeCell ref="B1137:B1138"/>
+    <mergeCell ref="B1139:B1140"/>
+    <mergeCell ref="B1141:B1142"/>
+    <mergeCell ref="B1143:B1144"/>
+    <mergeCell ref="B1145:B1146"/>
+    <mergeCell ref="B1147:B1148"/>
+    <mergeCell ref="B1149:B1150"/>
+    <mergeCell ref="B1115:B1116"/>
+    <mergeCell ref="B1117:B1118"/>
+    <mergeCell ref="B1119:B1120"/>
+    <mergeCell ref="B1121:B1122"/>
+    <mergeCell ref="B1123:B1124"/>
+    <mergeCell ref="B1125:B1126"/>
+    <mergeCell ref="B1127:B1128"/>
+    <mergeCell ref="B1129:B1130"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="B1097:B1098"/>
+    <mergeCell ref="B1099:B1100"/>
+    <mergeCell ref="B1101:B1102"/>
+    <mergeCell ref="B1103:B1104"/>
+    <mergeCell ref="B1105:B1106"/>
+    <mergeCell ref="B1107:B1108"/>
+    <mergeCell ref="B1109:B1110"/>
+    <mergeCell ref="B1111:B1112"/>
+    <mergeCell ref="B1113:B1114"/>
+    <mergeCell ref="B1079:B1080"/>
+    <mergeCell ref="B1081:B1082"/>
+    <mergeCell ref="B1083:B1084"/>
+    <mergeCell ref="B1085:B1086"/>
+    <mergeCell ref="B1087:B1088"/>
+    <mergeCell ref="B1089:B1090"/>
+    <mergeCell ref="B1091:B1092"/>
+    <mergeCell ref="B1093:B1094"/>
+    <mergeCell ref="B1095:B1096"/>
+    <mergeCell ref="B943:B955"/>
+    <mergeCell ref="B956:B963"/>
+    <mergeCell ref="B964:B971"/>
+    <mergeCell ref="B972:B979"/>
+    <mergeCell ref="B980:B984"/>
+    <mergeCell ref="B985:B990"/>
+    <mergeCell ref="B991:B1041"/>
+    <mergeCell ref="B1042:B1076"/>
+    <mergeCell ref="B1077:B1078"/>
+    <mergeCell ref="B893:B895"/>
+    <mergeCell ref="B896:B901"/>
+    <mergeCell ref="B902:B905"/>
+    <mergeCell ref="B906:B909"/>
+    <mergeCell ref="B910:B916"/>
+    <mergeCell ref="B917:B925"/>
+    <mergeCell ref="B926:B929"/>
+    <mergeCell ref="B930:B935"/>
+    <mergeCell ref="B936:B942"/>
+    <mergeCell ref="B856:B860"/>
+    <mergeCell ref="B861:B864"/>
+    <mergeCell ref="B865:B870"/>
+    <mergeCell ref="B871:B874"/>
+    <mergeCell ref="B875:B879"/>
+    <mergeCell ref="B880:B882"/>
+    <mergeCell ref="B883:B885"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="B888:B892"/>
+    <mergeCell ref="B813:B815"/>
+    <mergeCell ref="B816:B820"/>
+    <mergeCell ref="B821:B825"/>
+    <mergeCell ref="B826:B830"/>
+    <mergeCell ref="B831:B835"/>
+    <mergeCell ref="B836:B843"/>
+    <mergeCell ref="B844:B846"/>
+    <mergeCell ref="B847:B852"/>
+    <mergeCell ref="B853:B855"/>
+    <mergeCell ref="B786:B788"/>
+    <mergeCell ref="B789:B791"/>
+    <mergeCell ref="B792:B794"/>
+    <mergeCell ref="B795:B797"/>
+    <mergeCell ref="B798:B800"/>
+    <mergeCell ref="B801:B803"/>
+    <mergeCell ref="B804:B806"/>
+    <mergeCell ref="B807:B809"/>
+    <mergeCell ref="B810:B812"/>
+    <mergeCell ref="B745:B746"/>
+    <mergeCell ref="B747:B750"/>
+    <mergeCell ref="B751:B755"/>
+    <mergeCell ref="B756:B761"/>
+    <mergeCell ref="B762:B767"/>
+    <mergeCell ref="B768:B776"/>
+    <mergeCell ref="B777:B779"/>
+    <mergeCell ref="B780:B782"/>
+    <mergeCell ref="B783:B785"/>
+    <mergeCell ref="B659:B665"/>
+    <mergeCell ref="B666:B670"/>
+    <mergeCell ref="B671:B675"/>
+    <mergeCell ref="B676:B680"/>
+    <mergeCell ref="B681:B685"/>
+    <mergeCell ref="B686:B691"/>
+    <mergeCell ref="B692:B698"/>
+    <mergeCell ref="B699:B712"/>
+    <mergeCell ref="B713:B744"/>
+    <mergeCell ref="B583:B585"/>
+    <mergeCell ref="B586:B588"/>
+    <mergeCell ref="B589:B591"/>
+    <mergeCell ref="B592:B605"/>
+    <mergeCell ref="B606:B637"/>
+    <mergeCell ref="B638:B641"/>
+    <mergeCell ref="B642:B646"/>
+    <mergeCell ref="B647:B651"/>
+    <mergeCell ref="B652:B658"/>
+    <mergeCell ref="B541:B546"/>
+    <mergeCell ref="B547:B552"/>
+    <mergeCell ref="B553:B558"/>
+    <mergeCell ref="B559:B564"/>
+    <mergeCell ref="B565:B568"/>
+    <mergeCell ref="B569:B571"/>
+    <mergeCell ref="B572:B575"/>
+    <mergeCell ref="B576:B579"/>
+    <mergeCell ref="B580:B582"/>
+    <mergeCell ref="B487:B492"/>
+    <mergeCell ref="B493:B498"/>
+    <mergeCell ref="B499:B504"/>
+    <mergeCell ref="B505:B510"/>
+    <mergeCell ref="B511:B516"/>
+    <mergeCell ref="B517:B522"/>
+    <mergeCell ref="B523:B528"/>
+    <mergeCell ref="B529:B534"/>
+    <mergeCell ref="B535:B540"/>
+    <mergeCell ref="B431:B436"/>
+    <mergeCell ref="B437:B442"/>
+    <mergeCell ref="B443:B450"/>
+    <mergeCell ref="B451:B456"/>
+    <mergeCell ref="B457:B462"/>
+    <mergeCell ref="B463:B468"/>
+    <mergeCell ref="B469:B474"/>
+    <mergeCell ref="B475:B480"/>
+    <mergeCell ref="B481:B486"/>
+    <mergeCell ref="B393:B399"/>
+    <mergeCell ref="B400:B404"/>
+    <mergeCell ref="B405:B407"/>
+    <mergeCell ref="B408:B410"/>
+    <mergeCell ref="B411:B415"/>
+    <mergeCell ref="B416:B418"/>
+    <mergeCell ref="B419:B421"/>
+    <mergeCell ref="B422:B424"/>
+    <mergeCell ref="B425:B430"/>
+    <mergeCell ref="B347:B351"/>
+    <mergeCell ref="B352:B355"/>
+    <mergeCell ref="B356:B359"/>
+    <mergeCell ref="B360:B363"/>
+    <mergeCell ref="B364:B367"/>
+    <mergeCell ref="B368:B371"/>
+    <mergeCell ref="B372:B378"/>
+    <mergeCell ref="B379:B385"/>
+    <mergeCell ref="B386:B392"/>
+    <mergeCell ref="B115:B200"/>
+    <mergeCell ref="B201:B253"/>
+    <mergeCell ref="B254:B269"/>
+    <mergeCell ref="B270:B287"/>
+    <mergeCell ref="B288:B301"/>
+    <mergeCell ref="B302:B333"/>
+    <mergeCell ref="B334:B337"/>
+    <mergeCell ref="B338:B341"/>
+    <mergeCell ref="B342:B346"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B103:B108"/>
+    <mergeCell ref="B109:B114"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
